--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3053" uniqueCount="1108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3054" uniqueCount="1109">
   <si>
     <t xml:space="preserve">Argus — Catálogo de Dados</t>
   </si>
@@ -147,7 +147,7 @@
     <t xml:space="preserve">Data</t>
   </si>
   <si>
-    <t xml:space="preserve">Catálogo montado em 03/10/2026. Códigos marcados Confirmar e A mapear devem passar pelo validador antes de entrar no pipeline.</t>
+    <t xml:space="preserve">Planilha gerada a partir dos CSVs em docs/catalogo/. Edite os CSVs e rode o gerador; resultado da validação em validacao.md.</t>
   </si>
   <si>
     <t xml:space="preserve">Resumo do catálogo</t>
@@ -543,7 +543,7 @@
     <t xml:space="preserve">Rendimento médio real habitual</t>
   </si>
   <si>
-    <t xml:space="preserve">t6390 (a confirmar)</t>
+    <t xml:space="preserve">t6390</t>
   </si>
   <si>
     <t xml:space="preserve">R$</t>
@@ -579,19 +579,19 @@
     <t xml:space="preserve">Formal</t>
   </si>
   <si>
-    <t xml:space="preserve">Novo CAGED — saldo de empregos formais</t>
+    <t xml:space="preserve">Estoque de empregos formais (Novo CAGED)</t>
   </si>
   <si>
     <t xml:space="preserve">BCB SGS / MTE PDET</t>
   </si>
   <si>
-    <t xml:space="preserve">28763 (a confirmar)</t>
+    <t xml:space="preserve">28763</t>
   </si>
   <si>
     <t xml:space="preserve">Postos</t>
   </si>
   <si>
-    <t xml:space="preserve">Equivalente ao payroll; por setor via microdados MTE (v2)</t>
+    <t xml:space="preserve">Saldo mensal do CAGED = variação do estoque (série derivada); por setor via microdados MTE (v2)</t>
   </si>
   <si>
     <t xml:space="preserve">BR-023</t>
@@ -858,7 +858,7 @@
     <t xml:space="preserve">IC-Br — índice de commodities BCB (total, agro, metal, energia)</t>
   </si>
   <si>
-    <t xml:space="preserve">27574–27577 (a confirmar)</t>
+    <t xml:space="preserve">27574–27577</t>
   </si>
   <si>
     <t xml:space="preserve">Equivalente a container freight/commodities como indicador antecedente</t>
@@ -933,7 +933,7 @@
     <t xml:space="preserve">% a.a.</t>
   </si>
   <si>
-    <t xml:space="preserve">Fonte dos ciclos do Copom</t>
+    <t xml:space="preserve">Fonte dos ciclos do Copom; o SGS registra a meta vigente até a próxima reunião (data futura é normal)</t>
   </si>
   <si>
     <t xml:space="preserve">BR-051</t>
@@ -1173,7 +1173,7 @@
     <t xml:space="preserve">Resultado primário do setor público consolidado — 12m % PIB</t>
   </si>
   <si>
-    <t xml:space="preserve">5793 (a confirmar)</t>
+    <t xml:space="preserve">5793</t>
   </si>
   <si>
     <t xml:space="preserve">% PIB</t>
@@ -1311,7 +1311,7 @@
     <t xml:space="preserve">Transações correntes</t>
   </si>
   <si>
-    <t xml:space="preserve">22701 (a confirmar)</t>
+    <t xml:space="preserve">22701</t>
   </si>
   <si>
     <t xml:space="preserve">BR-082</t>
@@ -1326,7 +1326,7 @@
     <t xml:space="preserve">Investimento direto no país (IDP)</t>
   </si>
   <si>
-    <t xml:space="preserve">22885 (a confirmar)</t>
+    <t xml:space="preserve">22885</t>
   </si>
   <si>
     <t xml:space="preserve">BR-084</t>
@@ -1347,7 +1347,7 @@
     <t xml:space="preserve">Câmbio</t>
   </si>
   <si>
-    <t xml:space="preserve">USD/BRL PTAX venda</t>
+    <t xml:space="preserve">Taxa de câmbio livre — dólar americano (venda)</t>
   </si>
   <si>
     <t xml:space="preserve">1</t>
@@ -1356,13 +1356,16 @@
     <t xml:space="preserve">R$/US$</t>
   </si>
   <si>
+    <t xml:space="preserve">Título oficial SGS 1: "Taxa de câmbio - Livre - Dólar americano (venda) - diário"</t>
+  </si>
+  <si>
     <t xml:space="preserve">BR-086</t>
   </si>
   <si>
     <t xml:space="preserve">Taxa de câmbio efetiva real</t>
   </si>
   <si>
-    <t xml:space="preserve">11752 (a confirmar)</t>
+    <t xml:space="preserve">11752</t>
   </si>
   <si>
     <t xml:space="preserve">BR-087</t>
@@ -1419,7 +1422,7 @@
     <t xml:space="preserve">Endividamento das famílias com o SFN (% renda 12m)</t>
   </si>
   <si>
-    <t xml:space="preserve">29037 (a confirmar)</t>
+    <t xml:space="preserve">29037</t>
   </si>
   <si>
     <t xml:space="preserve">Ex-habitacional: 29038</t>
@@ -1431,7 +1434,7 @@
     <t xml:space="preserve">Comprometimento de renda com serviço da dívida</t>
   </si>
   <si>
-    <t xml:space="preserve">29034 (a confirmar)</t>
+    <t xml:space="preserve">29034</t>
   </si>
   <si>
     <t xml:space="preserve">Equivalente a debt service % DPI</t>
@@ -1644,7 +1647,7 @@
     <t xml:space="preserve">Ipeadata</t>
   </si>
   <si>
-    <t xml:space="preserve">JPM366_EMBI366 (a confirmar)</t>
+    <t xml:space="preserve">JPM366_EMBI366</t>
   </si>
   <si>
     <t xml:space="preserve">Conferir se ainda é atualizado</t>
@@ -4388,7 +4391,7 @@
       </c>
       <c r="I7" s="16" t="n">
         <f aca="false">COUNTIF(Brasil!$L$6:$L$130,H7)</f>
-        <v>22</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4420,7 +4423,7 @@
       </c>
       <c r="I8" s="16" t="n">
         <f aca="false">COUNTIF(Brasil!$L$6:$L$130,H8)</f>
-        <v>60</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5173,7 +5176,7 @@
         <v>27</v>
       </c>
       <c r="L6" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M6" s="26" t="s">
         <v>81</v>
@@ -5214,7 +5217,7 @@
         <v>27</v>
       </c>
       <c r="L7" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M7" s="26" t="s">
         <v>88</v>
@@ -5255,7 +5258,7 @@
         <v>27</v>
       </c>
       <c r="L8" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M8" s="26"/>
     </row>
@@ -5294,7 +5297,7 @@
         <v>27</v>
       </c>
       <c r="L9" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M9" s="26" t="s">
         <v>95</v>
@@ -5335,7 +5338,7 @@
         <v>27</v>
       </c>
       <c r="L10" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M10" s="26" t="s">
         <v>104</v>
@@ -5376,7 +5379,7 @@
         <v>27</v>
       </c>
       <c r="L11" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M11" s="26" t="s">
         <v>109</v>
@@ -5417,7 +5420,7 @@
         <v>27</v>
       </c>
       <c r="L12" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M12" s="26" t="s">
         <v>113</v>
@@ -5458,7 +5461,7 @@
         <v>27</v>
       </c>
       <c r="L13" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M13" s="26" t="s">
         <v>117</v>
@@ -5499,7 +5502,7 @@
         <v>27</v>
       </c>
       <c r="L14" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M14" s="26"/>
     </row>
@@ -5702,7 +5705,7 @@
         <v>27</v>
       </c>
       <c r="L19" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M19" s="26" t="s">
         <v>149</v>
@@ -5743,7 +5746,7 @@
         <v>27</v>
       </c>
       <c r="L20" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M20" s="26" t="s">
         <v>156</v>
@@ -5903,7 +5906,7 @@
         <v>27</v>
       </c>
       <c r="L24" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M24" s="26" t="s">
         <v>172</v>
@@ -5991,7 +5994,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="25" t="s">
         <v>180</v>
       </c>
@@ -6017,16 +6020,16 @@
         <v>185</v>
       </c>
       <c r="I27" s="26" t="s">
-        <v>102</v>
+        <v>163</v>
       </c>
       <c r="J27" s="26" t="s">
-        <v>103</v>
+        <v>164</v>
       </c>
       <c r="K27" s="26" t="s">
         <v>27</v>
       </c>
       <c r="L27" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M27" s="26" t="s">
         <v>186</v>
@@ -6149,7 +6152,7 @@
         <v>27</v>
       </c>
       <c r="L30" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M30" s="26" t="s">
         <v>207</v>
@@ -6190,7 +6193,7 @@
         <v>27</v>
       </c>
       <c r="L31" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M31" s="26" t="s">
         <v>211</v>
@@ -6231,7 +6234,7 @@
         <v>27</v>
       </c>
       <c r="L32" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M32" s="26" t="s">
         <v>215</v>
@@ -6625,7 +6628,7 @@
         <v>27</v>
       </c>
       <c r="L42" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M42" s="26"/>
     </row>
@@ -6664,7 +6667,7 @@
         <v>27</v>
       </c>
       <c r="L43" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M43" s="26"/>
     </row>
@@ -6742,7 +6745,7 @@
         <v>27</v>
       </c>
       <c r="L45" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M45" s="26"/>
     </row>
@@ -6781,7 +6784,7 @@
         <v>27</v>
       </c>
       <c r="L46" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M46" s="26" t="s">
         <v>261</v>
@@ -6863,7 +6866,7 @@
         <v>27</v>
       </c>
       <c r="L48" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M48" s="26" t="s">
         <v>270</v>
@@ -6943,7 +6946,7 @@
         <v>27</v>
       </c>
       <c r="L50" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M50" s="26" t="s">
         <v>276</v>
@@ -6984,7 +6987,7 @@
         <v>27</v>
       </c>
       <c r="L51" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M51" s="26"/>
     </row>
@@ -7023,7 +7026,7 @@
         <v>27</v>
       </c>
       <c r="L52" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M52" s="26" t="s">
         <v>283</v>
@@ -7111,7 +7114,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="25" t="s">
         <v>295</v>
       </c>
@@ -7146,7 +7149,7 @@
         <v>27</v>
       </c>
       <c r="L55" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M55" s="26" t="s">
         <v>300</v>
@@ -7390,7 +7393,7 @@
         <v>27</v>
       </c>
       <c r="L61" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M61" s="26" t="s">
         <v>324</v>
@@ -7714,7 +7717,7 @@
         <v>27</v>
       </c>
       <c r="L69" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M69" s="26"/>
     </row>
@@ -7753,7 +7756,7 @@
         <v>27</v>
       </c>
       <c r="L70" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M70" s="26"/>
     </row>
@@ -7792,7 +7795,7 @@
         <v>27</v>
       </c>
       <c r="L71" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M71" s="26"/>
     </row>
@@ -7911,7 +7914,7 @@
         <v>27</v>
       </c>
       <c r="L74" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M74" s="26"/>
     </row>
@@ -8028,7 +8031,7 @@
         <v>27</v>
       </c>
       <c r="L77" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M77" s="26"/>
     </row>
@@ -8067,7 +8070,7 @@
         <v>27</v>
       </c>
       <c r="L78" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M78" s="26"/>
     </row>
@@ -8225,7 +8228,7 @@
         <v>27</v>
       </c>
       <c r="L82" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M82" s="26"/>
     </row>
@@ -8387,7 +8390,7 @@
         <v>27</v>
       </c>
       <c r="L86" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M86" s="26"/>
     </row>
@@ -8465,7 +8468,7 @@
         <v>27</v>
       </c>
       <c r="L88" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M88" s="26"/>
     </row>
@@ -8545,13 +8548,15 @@
         <v>27</v>
       </c>
       <c r="L90" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="M90" s="26"/>
+        <v>12</v>
+      </c>
+      <c r="M90" s="26" t="s">
+        <v>441</v>
+      </c>
     </row>
     <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="25" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B91" s="26" t="s">
         <v>50</v>
@@ -8560,13 +8565,13 @@
         <v>437</v>
       </c>
       <c r="D91" s="27" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="E91" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F91" s="26" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="G91" s="26" t="s">
         <v>100</v>
@@ -8584,13 +8589,13 @@
         <v>27</v>
       </c>
       <c r="L91" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M91" s="26"/>
     </row>
     <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="25" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B92" s="26" t="s">
         <v>50</v>
@@ -8599,7 +8604,7 @@
         <v>437</v>
       </c>
       <c r="D92" s="27" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="E92" s="26" t="s">
         <v>98</v>
@@ -8629,7 +8634,7 @@
     </row>
     <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="25" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B93" s="26" t="s">
         <v>50</v>
@@ -8638,13 +8643,13 @@
         <v>437</v>
       </c>
       <c r="D93" s="27" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E93" s="26" t="s">
         <v>146</v>
       </c>
       <c r="F93" s="26" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G93" s="26" t="s">
         <v>148</v>
@@ -8662,34 +8667,34 @@
         <v>27</v>
       </c>
       <c r="L93" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M93" s="26"/>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="25" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B94" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C94" s="26" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D94" s="27" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="E94" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F94" s="26" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="G94" s="26" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H94" s="26" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="I94" s="26" t="s">
         <v>79</v>
@@ -8707,19 +8712,19 @@
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="25" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B95" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C95" s="26" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D95" s="27" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="E95" s="26" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="F95" s="26" t="s">
         <v>16</v>
@@ -8746,22 +8751,22 @@
     </row>
     <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="25" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="B96" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C96" s="26" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D96" s="27" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="E96" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F96" s="26" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="G96" s="26" t="s">
         <v>100</v>
@@ -8779,30 +8784,30 @@
         <v>27</v>
       </c>
       <c r="L96" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M96" s="26" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="25" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B97" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C97" s="26" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D97" s="27" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="E97" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F97" s="26" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="G97" s="26" t="s">
         <v>100</v>
@@ -8820,15 +8825,15 @@
         <v>27</v>
       </c>
       <c r="L97" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M97" s="26" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="25" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="B98" s="26" t="s">
         <v>51</v>
@@ -8837,13 +8842,13 @@
         <v>353</v>
       </c>
       <c r="D98" s="27" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E98" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="G98" s="26" t="s">
         <v>100</v>
@@ -8867,7 +8872,7 @@
     </row>
     <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="25" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="B99" s="26" t="s">
         <v>51</v>
@@ -8876,13 +8881,13 @@
         <v>353</v>
       </c>
       <c r="D99" s="27" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="E99" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F99" s="26" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="G99" s="26" t="s">
         <v>100</v>
@@ -8906,7 +8911,7 @@
     </row>
     <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="25" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B100" s="26" t="s">
         <v>51</v>
@@ -8915,13 +8920,13 @@
         <v>353</v>
       </c>
       <c r="D100" s="27" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="E100" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F100" s="26" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="G100" s="26" t="s">
         <v>100</v>
@@ -8945,7 +8950,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="25" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="B101" s="26" t="s">
         <v>51</v>
@@ -8954,13 +8959,13 @@
         <v>353</v>
       </c>
       <c r="D101" s="27" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="E101" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="G101" s="26" t="s">
         <v>100</v>
@@ -8984,22 +8989,22 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="25" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="B102" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C102" s="26" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D102" s="27" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E102" s="26" t="s">
         <v>76</v>
       </c>
       <c r="F102" s="26" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="G102" s="26" t="s">
         <v>124</v>
@@ -9020,12 +9025,12 @@
         <v>22</v>
       </c>
       <c r="M102" s="26" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="25" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="B103" s="26" t="s">
         <v>51</v>
@@ -9034,7 +9039,7 @@
         <v>127</v>
       </c>
       <c r="D103" s="27" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="E103" s="26" t="s">
         <v>129</v>
@@ -9064,16 +9069,16 @@
     </row>
     <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="25" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B104" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C104" s="26" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="D104" s="27" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="E104" s="26" t="s">
         <v>98</v>
@@ -9103,7 +9108,7 @@
     </row>
     <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="25" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B105" s="26" t="s">
         <v>52</v>
@@ -9112,19 +9117,19 @@
         <v>353</v>
       </c>
       <c r="D105" s="27" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="E105" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F105" s="26" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="G105" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H105" s="26" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="I105" s="26" t="s">
         <v>163</v>
@@ -9142,7 +9147,7 @@
     </row>
     <row r="106" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="25" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B106" s="26" t="s">
         <v>52</v>
@@ -9151,13 +9156,13 @@
         <v>353</v>
       </c>
       <c r="D106" s="27" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="E106" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F106" s="26" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="G106" s="26" t="s">
         <v>100</v>
@@ -9181,22 +9186,22 @@
     </row>
     <row r="107" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="25" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="B107" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C107" s="26" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="D107" s="27" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="E107" s="26" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F107" s="26" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="G107" s="26" t="s">
         <v>100</v>
@@ -9220,22 +9225,22 @@
     </row>
     <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="25" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="B108" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C108" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D108" s="27" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="E108" s="26" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="F108" s="26" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="G108" s="26" t="s">
         <v>100</v>
@@ -9256,27 +9261,27 @@
         <v>18</v>
       </c>
       <c r="M108" s="26" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="25" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="B109" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C109" s="26" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="D109" s="27" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="E109" s="26" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="F109" s="26" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="G109" s="26" t="s">
         <v>78</v>
@@ -9297,21 +9302,21 @@
         <v>14</v>
       </c>
       <c r="M109" s="26" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="25" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="B110" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C110" s="26" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D110" s="27" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="E110" s="26" t="s">
         <v>76</v>
@@ -9335,36 +9340,36 @@
         <v>27</v>
       </c>
       <c r="L110" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M110" s="26" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="25" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="B111" s="26" t="s">
         <v>53</v>
       </c>
       <c r="C111" s="26" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D111" s="27" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="E111" s="26" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="F111" s="26" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="G111" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H111" s="26" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="I111" s="26" t="s">
         <v>79</v>
@@ -9379,12 +9384,12 @@
         <v>14</v>
       </c>
       <c r="M111" s="26" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="25" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="B112" s="26" t="s">
         <v>53</v>
@@ -9393,13 +9398,13 @@
         <v>296</v>
       </c>
       <c r="D112" s="27" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="E112" s="26" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="G112" s="26" t="s">
         <v>140</v>
@@ -9420,12 +9425,12 @@
         <v>14</v>
       </c>
       <c r="M112" s="26" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="25" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B113" s="26" t="s">
         <v>53</v>
@@ -9434,13 +9439,13 @@
         <v>296</v>
       </c>
       <c r="D113" s="27" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="E113" s="26" t="s">
         <v>286</v>
       </c>
       <c r="F113" s="26" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="G113" s="26" t="s">
         <v>140</v>
@@ -9464,22 +9469,22 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="25" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="B114" s="26" t="s">
         <v>53</v>
       </c>
       <c r="C114" s="26" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D114" s="27" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="E114" s="26" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="F114" s="26" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G114" s="26" t="s">
         <v>140</v>
@@ -9500,24 +9505,24 @@
         <v>14</v>
       </c>
       <c r="M114" s="26" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="25" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B115" s="26" t="s">
         <v>53</v>
       </c>
       <c r="C115" s="26" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="D115" s="27" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="E115" s="26" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="F115" s="26" t="s">
         <v>124</v>
@@ -9541,12 +9546,12 @@
         <v>20</v>
       </c>
       <c r="M115" s="26" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="25" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B116" s="26" t="s">
         <v>53</v>
@@ -9555,13 +9560,13 @@
         <v>102</v>
       </c>
       <c r="D116" s="27" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="E116" s="26" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="F116" s="26" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="G116" s="26" t="s">
         <v>140</v>
@@ -9582,27 +9587,27 @@
         <v>18</v>
       </c>
       <c r="M116" s="26" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="25" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B117" s="26" t="s">
         <v>54</v>
       </c>
       <c r="C117" s="26" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D117" s="27" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="E117" s="26" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="F117" s="26" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="G117" s="26" t="s">
         <v>140</v>
@@ -9626,22 +9631,22 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="25" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B118" s="26" t="s">
         <v>54</v>
       </c>
       <c r="C118" s="26" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="D118" s="27" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="E118" s="26" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="F118" s="26" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="G118" s="26" t="s">
         <v>140</v>
@@ -9665,28 +9670,28 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="25" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B119" s="26" t="s">
         <v>54</v>
       </c>
       <c r="C119" s="26" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="D119" s="27" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E119" s="26" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="F119" s="26" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="G119" s="26" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H119" s="26" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="I119" s="26" t="s">
         <v>331</v>
@@ -9704,19 +9709,19 @@
     </row>
     <row r="120" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="25" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B120" s="26" t="s">
         <v>54</v>
       </c>
       <c r="C120" s="26" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="D120" s="27" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="E120" s="26" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="F120" s="26" t="s">
         <v>24</v>
@@ -9740,33 +9745,33 @@
         <v>24</v>
       </c>
       <c r="M120" s="26" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="25" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B121" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C121" s="26" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="D121" s="27" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="E121" s="26" t="s">
         <v>195</v>
       </c>
       <c r="F121" s="26" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="G121" s="26" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H121" s="26" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="I121" s="26" t="s">
         <v>22</v>
@@ -9781,27 +9786,27 @@
         <v>22</v>
       </c>
       <c r="M121" s="26" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="25" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B122" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C122" s="26" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D122" s="27" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E122" s="26" t="s">
         <v>195</v>
       </c>
       <c r="F122" s="26" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="G122" s="26" t="s">
         <v>148</v>
@@ -9822,27 +9827,27 @@
         <v>22</v>
       </c>
       <c r="M122" s="26" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="25" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="B123" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C123" s="26" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D123" s="27" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="E123" s="26" t="s">
         <v>195</v>
       </c>
       <c r="F123" s="26" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="G123" s="26" t="s">
         <v>140</v>
@@ -9866,22 +9871,22 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="25" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B124" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C124" s="26" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="D124" s="27" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="E124" s="26" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="F124" s="26" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="G124" s="26" t="s">
         <v>78</v>
@@ -9905,22 +9910,22 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="25" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B125" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C125" s="26" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D125" s="27" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="E125" s="26" t="s">
         <v>195</v>
       </c>
       <c r="F125" s="26" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="G125" s="26" t="s">
         <v>100</v>
@@ -9944,22 +9949,22 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="25" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B126" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C126" s="26" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D126" s="27" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="E126" s="26" t="s">
         <v>195</v>
       </c>
       <c r="F126" s="26" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="G126" s="26" t="s">
         <v>78</v>
@@ -9980,27 +9985,27 @@
         <v>22</v>
       </c>
       <c r="M126" s="26" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="25" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B127" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C127" s="26" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="D127" s="27" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="E127" s="26" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="F127" s="26" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="G127" s="26" t="s">
         <v>78</v>
@@ -10024,7 +10029,7 @@
     </row>
     <row r="128" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="25" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B128" s="26" t="s">
         <v>55</v>
@@ -10033,10 +10038,10 @@
         <v>326</v>
       </c>
       <c r="D128" s="27" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="E128" s="26" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="F128" s="26" t="s">
         <v>24</v>
@@ -10063,7 +10068,7 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="25" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="B129" s="26" t="s">
         <v>55</v>
@@ -10072,19 +10077,19 @@
         <v>326</v>
       </c>
       <c r="D129" s="27" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="E129" s="26" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="F129" s="26" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="G129" s="26" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H129" s="26" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="I129" s="26" t="s">
         <v>22</v>
@@ -10099,27 +10104,27 @@
         <v>22</v>
       </c>
       <c r="M129" s="26" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="25" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B130" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C130" s="26" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="D130" s="27" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="E130" s="26" t="s">
         <v>195</v>
       </c>
       <c r="F130" s="26" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="G130" s="26" t="s">
         <v>124</v>
@@ -10217,12 +10222,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10283,28 +10288,28 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="G6" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I6" s="26" t="s">
         <v>163</v>
@@ -10322,22 +10327,22 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G7" s="26" t="s">
         <v>100</v>
@@ -10361,22 +10366,22 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="G8" s="26" t="s">
         <v>100</v>
@@ -10400,22 +10405,22 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="G9" s="26" t="s">
         <v>100</v>
@@ -10439,28 +10444,28 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>195</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="G10" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="I10" s="26" t="s">
         <v>22</v>
@@ -10478,28 +10483,28 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B11" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="G11" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I11" s="26" t="s">
         <v>102</v>
@@ -10517,28 +10522,28 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B12" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="G12" s="26" t="s">
         <v>148</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I12" s="26" t="s">
         <v>102</v>
@@ -10556,19 +10561,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B13" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="F13" s="26" t="s">
         <v>124</v>
@@ -10592,27 +10597,27 @@
         <v>20</v>
       </c>
       <c r="M13" s="26" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="B14" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="G14" s="26" t="s">
         <v>100</v>
@@ -10636,7 +10641,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="B15" s="26" t="s">
         <v>46</v>
@@ -10645,13 +10650,13 @@
         <v>193</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>195</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="G15" s="26" t="s">
         <v>100</v>
@@ -10675,22 +10680,22 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B16" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="G16" s="26" t="s">
         <v>78</v>
@@ -10714,28 +10719,28 @@
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B17" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="G17" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="I17" s="26" t="s">
         <v>79</v>
@@ -10753,22 +10758,22 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="B18" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="E18" s="26" t="s">
         <v>195</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>100</v>
@@ -10792,22 +10797,22 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B19" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="G19" s="26" t="s">
         <v>100</v>
@@ -10828,12 +10833,12 @@
         <v>18</v>
       </c>
       <c r="M19" s="26" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="B20" s="26" t="s">
         <v>46</v>
@@ -10842,13 +10847,13 @@
         <v>193</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="G20" s="26" t="s">
         <v>100</v>
@@ -10869,27 +10874,27 @@
         <v>12</v>
       </c>
       <c r="M20" s="26" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="B21" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="G21" s="26" t="s">
         <v>100</v>
@@ -10913,22 +10918,22 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="B22" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="G22" s="26" t="s">
         <v>100</v>
@@ -10949,27 +10954,27 @@
         <v>12</v>
       </c>
       <c r="M22" s="26" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="B23" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="G23" s="26" t="s">
         <v>100</v>
@@ -10993,22 +10998,22 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="25" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B24" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="G24" s="26" t="s">
         <v>100</v>
@@ -11032,22 +11037,22 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="25" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="B25" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="G25" s="26" t="s">
         <v>100</v>
@@ -11071,22 +11076,22 @@
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="25" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B26" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="G26" s="26" t="s">
         <v>100</v>
@@ -11110,7 +11115,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="25" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B27" s="26" t="s">
         <v>47</v>
@@ -11119,13 +11124,13 @@
         <v>144</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="G27" s="26" t="s">
         <v>140</v>
@@ -11146,12 +11151,12 @@
         <v>14</v>
       </c>
       <c r="M27" s="26" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="25" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="B28" s="26" t="s">
         <v>47</v>
@@ -11160,10 +11165,10 @@
         <v>144</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F28" s="26" t="s">
         <v>124</v>
@@ -11187,12 +11192,12 @@
         <v>20</v>
       </c>
       <c r="M28" s="26" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="25" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B29" s="26" t="s">
         <v>47</v>
@@ -11201,13 +11206,13 @@
         <v>144</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="G29" s="26" t="s">
         <v>100</v>
@@ -11228,27 +11233,27 @@
         <v>14</v>
       </c>
       <c r="M29" s="26" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="25" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="B30" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D30" s="27" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="G30" s="26" t="s">
         <v>100</v>
@@ -11272,19 +11277,19 @@
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="25" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="B31" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="F31" s="26" t="s">
         <v>124</v>
@@ -11293,7 +11298,7 @@
         <v>148</v>
       </c>
       <c r="H31" s="26" t="s">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="I31" s="26" t="s">
         <v>79</v>
@@ -11311,7 +11316,7 @@
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="25" t="s">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="B32" s="26" t="s">
         <v>45</v>
@@ -11320,19 +11325,19 @@
         <v>74</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="G32" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H32" s="26" t="s">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="I32" s="26" t="s">
         <v>79</v>
@@ -11350,7 +11355,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="25" t="s">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B33" s="26" t="s">
         <v>45</v>
@@ -11359,19 +11364,19 @@
         <v>74</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="E33" s="26" t="s">
         <v>195</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="G33" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H33" s="26" t="s">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="I33" s="26" t="s">
         <v>22</v>
@@ -11389,7 +11394,7 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="25" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B34" s="26" t="s">
         <v>45</v>
@@ -11398,19 +11403,19 @@
         <v>74</v>
       </c>
       <c r="D34" s="27" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="E34" s="26" t="s">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="G34" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H34" s="26" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="I34" s="26" t="s">
         <v>79</v>
@@ -11428,7 +11433,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="25" t="s">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="B35" s="26" t="s">
         <v>45</v>
@@ -11437,19 +11442,19 @@
         <v>74</v>
       </c>
       <c r="D35" s="27" t="s">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="G35" s="26" t="s">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="H35" s="26" t="s">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="I35" s="26" t="s">
         <v>86</v>
@@ -11464,27 +11469,27 @@
         <v>12</v>
       </c>
       <c r="M35" s="26" t="s">
-        <v>740</v>
+        <v>741</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="25" t="s">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="B36" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D36" s="27" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="E36" s="26" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="G36" s="26" t="s">
         <v>100</v>
@@ -11508,28 +11513,28 @@
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="25" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B37" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="G37" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H37" s="26" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="I37" s="26" t="s">
         <v>102</v>
@@ -11547,19 +11552,19 @@
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="25" t="s">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="B38" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D38" s="27" t="s">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="E38" s="26" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F38" s="26" t="s">
         <v>16</v>
@@ -11586,22 +11591,22 @@
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="25" t="s">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="B39" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="G39" s="26" t="s">
         <v>78</v>
@@ -11625,28 +11630,28 @@
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="25" t="s">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="B40" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="G40" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H40" s="26" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="I40" s="26" t="s">
         <v>102</v>
@@ -11664,28 +11669,28 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="25" t="s">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="B41" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="D41" s="27" t="s">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="G41" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H41" s="26" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="I41" s="26" t="s">
         <v>86</v>
@@ -11700,27 +11705,27 @@
         <v>14</v>
       </c>
       <c r="M41" s="26" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="25" t="s">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="B42" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D42" s="27" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="E42" s="26" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="G42" s="26" t="s">
         <v>100</v>
@@ -11741,24 +11746,24 @@
         <v>14</v>
       </c>
       <c r="M42" s="26" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="25" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B43" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D43" s="27" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="F43" s="26" t="s">
         <v>124</v>
@@ -11782,27 +11787,27 @@
         <v>20</v>
       </c>
       <c r="M43" s="26" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="25" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="B44" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="G44" s="26" t="s">
         <v>100</v>
@@ -11823,12 +11828,12 @@
         <v>14</v>
       </c>
       <c r="M44" s="26" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="25" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="B45" s="26" t="s">
         <v>56</v>
@@ -11837,13 +11842,13 @@
         <v>54</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="G45" s="26" t="s">
         <v>140</v>
@@ -11867,22 +11872,22 @@
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="25" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B46" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="E46" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G46" s="26" t="s">
         <v>148</v>
@@ -11906,25 +11911,25 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="25" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="B47" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="G47" s="26" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H47" s="26" t="s">
         <v>337</v>
@@ -11942,12 +11947,12 @@
         <v>14</v>
       </c>
       <c r="M47" s="26" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="25" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="B48" s="26" t="s">
         <v>56</v>
@@ -11956,13 +11961,13 @@
         <v>405</v>
       </c>
       <c r="D48" s="27" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="E48" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F48" s="26" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="G48" s="26" t="s">
         <v>78</v>
@@ -11983,27 +11988,27 @@
         <v>12</v>
       </c>
       <c r="M48" s="26" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="25" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="B49" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="E49" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F49" s="26" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="G49" s="26" t="s">
         <v>140</v>
@@ -12027,22 +12032,22 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="25" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="B50" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D50" s="27" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="E50" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F50" s="26" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="G50" s="26" t="s">
         <v>140</v>
@@ -12066,19 +12071,19 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="25" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B51" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="E51" s="26" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="F51" s="26" t="s">
         <v>124</v>
@@ -12105,19 +12110,19 @@
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="25" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B52" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="E52" s="26" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="F52" s="26" t="s">
         <v>124</v>
@@ -12141,12 +12146,12 @@
         <v>20</v>
       </c>
       <c r="M52" s="26" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="25" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="B53" s="26" t="s">
         <v>56</v>
@@ -12155,13 +12160,13 @@
         <v>353</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="F53" s="26" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="G53" s="26" t="s">
         <v>148</v>
@@ -12185,7 +12190,7 @@
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="25" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B54" s="26" t="s">
         <v>56</v>
@@ -12194,19 +12199,19 @@
         <v>340</v>
       </c>
       <c r="D54" s="27" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="E54" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F54" s="26" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G54" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H54" s="26" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="I54" s="26" t="s">
         <v>163</v>
@@ -12224,7 +12229,7 @@
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="25" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B55" s="26" t="s">
         <v>56</v>
@@ -12233,19 +12238,19 @@
         <v>340</v>
       </c>
       <c r="D55" s="27" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="F55" s="26" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="G55" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H55" s="26" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="I55" s="26" t="s">
         <v>163</v>
@@ -12260,12 +12265,12 @@
         <v>18</v>
       </c>
       <c r="M55" s="26" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="25" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="B56" s="26" t="s">
         <v>56</v>
@@ -12274,13 +12279,13 @@
         <v>373</v>
       </c>
       <c r="D56" s="27" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="E56" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F56" s="26" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="G56" s="26" t="s">
         <v>148</v>
@@ -12304,7 +12309,7 @@
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="25" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B57" s="26" t="s">
         <v>56</v>
@@ -12313,13 +12318,13 @@
         <v>373</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="E57" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F57" s="26" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="G57" s="26" t="s">
         <v>148</v>
@@ -12343,7 +12348,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="25" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="B58" s="26" t="s">
         <v>56</v>
@@ -12352,13 +12357,13 @@
         <v>353</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="E58" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F58" s="26" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="G58" s="26" t="s">
         <v>78</v>
@@ -12382,7 +12387,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="25" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="B59" s="26" t="s">
         <v>56</v>
@@ -12391,13 +12396,13 @@
         <v>387</v>
       </c>
       <c r="D59" s="27" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E59" s="26" t="s">
         <v>195</v>
       </c>
       <c r="F59" s="26" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="G59" s="26" t="s">
         <v>78</v>
@@ -12421,28 +12426,28 @@
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="25" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="B60" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C60" s="26" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F60" s="26" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="G60" s="26" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H60" s="26" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="I60" s="26" t="s">
         <v>79</v>
@@ -12457,33 +12462,33 @@
         <v>14</v>
       </c>
       <c r="M60" s="26" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="25" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B61" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D61" s="27" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E61" s="26" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F61" s="26" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="G61" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H61" s="26" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="I61" s="26" t="s">
         <v>102</v>
@@ -12501,28 +12506,28 @@
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="25" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="B62" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C62" s="26" t="s">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="D62" s="27" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="E62" s="26" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="G62" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H62" s="26" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="I62" s="26" t="s">
         <v>102</v>
@@ -12537,27 +12542,27 @@
         <v>20</v>
       </c>
       <c r="M62" s="26" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="25" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B63" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C63" s="26" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D63" s="27" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="E63" s="26" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F63" s="26" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
       <c r="G63" s="26" t="s">
         <v>78</v>
@@ -12581,22 +12586,22 @@
     </row>
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="25" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B64" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C64" s="26" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="D64" s="27" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="E64" s="26" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="F64" s="26" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="G64" s="26" t="s">
         <v>100</v>
@@ -12620,22 +12625,22 @@
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="25" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B65" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D65" s="27" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="E65" s="26" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="G65" s="26" t="s">
         <v>100</v>
@@ -12659,7 +12664,7 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="25" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="B66" s="26" t="s">
         <v>57</v>
@@ -12668,10 +12673,10 @@
         <v>353</v>
       </c>
       <c r="D66" s="27" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="E66" s="26" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="F66" s="26" t="s">
         <v>124</v>
@@ -12698,7 +12703,7 @@
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="25" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="B67" s="26" t="s">
         <v>58</v>
@@ -12707,13 +12712,13 @@
         <v>127</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="E67" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="G67" s="26" t="s">
         <v>100</v>
@@ -12734,12 +12739,12 @@
         <v>14</v>
       </c>
       <c r="M67" s="26" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="25" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B68" s="26" t="s">
         <v>58</v>
@@ -12748,13 +12753,13 @@
         <v>127</v>
       </c>
       <c r="D68" s="27" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="E68" s="26" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="G68" s="26" t="s">
         <v>100</v>
@@ -12778,28 +12783,28 @@
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="25" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="B69" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D69" s="27" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="E69" s="26" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G69" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H69" s="26" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="I69" s="26" t="s">
         <v>163</v>
@@ -12817,28 +12822,28 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="25" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="B70" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C70" s="26" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D70" s="27" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="E70" s="26" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="G70" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H70" s="26" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="I70" s="26" t="s">
         <v>86</v>
@@ -12856,22 +12861,22 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="25" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="B71" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C71" s="26" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="E71" s="26" t="s">
         <v>195</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="G71" s="26" t="s">
         <v>78</v>
@@ -12895,22 +12900,22 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="25" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B72" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C72" s="26" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="E72" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G72" s="26" t="s">
         <v>78</v>
@@ -12934,22 +12939,22 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="25" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B73" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C73" s="26" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="E73" s="26" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="F73" s="26" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="G73" s="26" t="s">
         <v>78</v>
@@ -12973,7 +12978,7 @@
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="25" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B74" s="26" t="s">
         <v>58</v>
@@ -12982,19 +12987,19 @@
         <v>353</v>
       </c>
       <c r="D74" s="27" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="E74" s="26" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="F74" s="26" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="G74" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H74" s="26" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="I74" s="26" t="s">
         <v>163</v>
@@ -13012,7 +13017,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="25" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B75" s="26" t="s">
         <v>58</v>
@@ -13021,16 +13026,16 @@
         <v>353</v>
       </c>
       <c r="D75" s="27" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="E75" s="26" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
       <c r="F75" s="26" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="G75" s="26" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="H75" s="26" t="s">
         <v>85</v>
@@ -13051,7 +13056,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="25" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B76" s="26" t="s">
         <v>58</v>
@@ -13060,13 +13065,13 @@
         <v>353</v>
       </c>
       <c r="D76" s="27" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="E76" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="G76" s="26" t="s">
         <v>78</v>
@@ -13090,28 +13095,28 @@
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="25" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B77" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C77" s="26" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D77" s="27" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="E77" s="26" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="G77" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H77" s="26" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="I77" s="26" t="s">
         <v>102</v>
@@ -13129,22 +13134,22 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="25" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
       <c r="B78" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C78" s="26" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D78" s="27" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="E78" s="26" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="G78" s="26" t="s">
         <v>78</v>
@@ -13165,33 +13170,33 @@
         <v>22</v>
       </c>
       <c r="M78" s="26" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="25" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
       <c r="B79" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C79" s="26" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="G79" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H79" s="26" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="I79" s="26" t="s">
         <v>102</v>
@@ -13209,22 +13214,22 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="25" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="B80" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C80" s="26" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D80" s="27" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="E80" s="26" t="s">
         <v>195</v>
       </c>
       <c r="F80" s="26" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="G80" s="26" t="s">
         <v>78</v>
@@ -13248,28 +13253,28 @@
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="25" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="B81" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C81" s="26" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="E81" s="26" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="F81" s="26" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="G81" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H81" s="26" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="I81" s="26" t="s">
         <v>102</v>
@@ -13287,22 +13292,22 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="25" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B82" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C82" s="26" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="D82" s="27" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="E82" s="26" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="F82" s="26" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="G82" s="26" t="s">
         <v>100</v>
@@ -13326,19 +13331,19 @@
     </row>
     <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="25" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B83" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C83" s="26" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D83" s="27" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="F83" s="26" t="s">
         <v>16</v>
@@ -13347,7 +13352,7 @@
         <v>78</v>
       </c>
       <c r="H83" s="26" t="s">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="I83" s="26" t="s">
         <v>163</v>
@@ -13365,19 +13370,19 @@
     </row>
     <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="25" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="B84" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C84" s="26" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="D84" s="27" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="F84" s="26" t="s">
         <v>124</v>
@@ -13386,7 +13391,7 @@
         <v>100</v>
       </c>
       <c r="H84" s="26" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="I84" s="26" t="s">
         <v>102</v>
@@ -13401,12 +13406,12 @@
         <v>20</v>
       </c>
       <c r="M84" s="26" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="25" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B85" s="26" t="s">
         <v>60</v>
@@ -13415,13 +13420,13 @@
         <v>387</v>
       </c>
       <c r="D85" s="27" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="E85" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F85" s="26" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="G85" s="26" t="s">
         <v>78</v>
@@ -13445,7 +13450,7 @@
     </row>
     <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="25" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B86" s="26" t="s">
         <v>60</v>
@@ -13454,16 +13459,16 @@
         <v>405</v>
       </c>
       <c r="D86" s="27" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="E86" s="26" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="F86" s="26" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="G86" s="26" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
       <c r="H86" s="26" t="s">
         <v>381</v>
@@ -13484,7 +13489,7 @@
     </row>
     <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="25" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B87" s="26" t="s">
         <v>60</v>
@@ -13493,16 +13498,16 @@
         <v>405</v>
       </c>
       <c r="D87" s="27" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="E87" s="26" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="F87" s="26" t="s">
         <v>411</v>
       </c>
       <c r="G87" s="26" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H87" s="26" t="s">
         <v>381</v>
@@ -13520,27 +13525,27 @@
         <v>18</v>
       </c>
       <c r="M87" s="26" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="25" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B88" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C88" s="26" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D88" s="27" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="E88" s="26" t="s">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="F88" s="26" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="G88" s="26" t="s">
         <v>100</v>
@@ -13564,22 +13569,22 @@
     </row>
     <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="25" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="B89" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C89" s="26" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D89" s="27" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="E89" s="26" t="s">
         <v>195</v>
       </c>
       <c r="F89" s="26" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="G89" s="26" t="s">
         <v>78</v>
@@ -13603,22 +13608,22 @@
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="25" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B90" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C90" s="26" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D90" s="27" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="E90" s="26" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="F90" s="26" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="G90" s="26" t="s">
         <v>100</v>
@@ -13642,22 +13647,22 @@
     </row>
     <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="25" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B91" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="D91" s="27" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="E91" s="26" t="s">
         <v>195</v>
       </c>
       <c r="F91" s="26" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="G91" s="26" t="s">
         <v>78</v>
@@ -13678,33 +13683,33 @@
         <v>22</v>
       </c>
       <c r="M91" s="26" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="25" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B92" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C92" s="26" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D92" s="27" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="E92" s="26" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="F92" s="26" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="G92" s="26" t="s">
         <v>148</v>
       </c>
       <c r="H92" s="26" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="I92" s="26" t="s">
         <v>163</v>
@@ -13722,7 +13727,7 @@
     </row>
     <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="25" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B93" s="26" t="s">
         <v>60</v>
@@ -13731,10 +13736,10 @@
         <v>437</v>
       </c>
       <c r="D93" s="27" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="E93" s="26" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F93" s="26" t="s">
         <v>124</v>
@@ -13758,12 +13763,12 @@
         <v>20</v>
       </c>
       <c r="M93" s="26" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="25" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B94" s="26" t="s">
         <v>60</v>
@@ -13772,13 +13777,13 @@
         <v>437</v>
       </c>
       <c r="D94" s="27" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="E94" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F94" s="26" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="G94" s="26" t="s">
         <v>140</v>
@@ -13799,27 +13804,27 @@
         <v>14</v>
       </c>
       <c r="M94" s="26" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="25" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
       <c r="B95" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C95" s="26" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D95" s="27" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="E95" s="26" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="F95" s="26" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="G95" s="26" t="s">
         <v>140</v>
@@ -13843,19 +13848,19 @@
     </row>
     <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="25" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="B96" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C96" s="26" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="D96" s="27" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="E96" s="26" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="F96" s="26" t="s">
         <v>124</v>
@@ -13882,7 +13887,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="25" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="B97" s="26" t="s">
         <v>61</v>
@@ -13891,13 +13896,13 @@
         <v>353</v>
       </c>
       <c r="D97" s="27" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="E97" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F97" s="26" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="G97" s="26" t="s">
         <v>140</v>
@@ -13918,27 +13923,27 @@
         <v>14</v>
       </c>
       <c r="M97" s="26" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="25" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B98" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C98" s="26" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="D98" s="27" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="E98" s="26" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="G98" s="26" t="s">
         <v>100</v>
@@ -13962,7 +13967,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="25" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="B99" s="26" t="s">
         <v>61</v>
@@ -13971,13 +13976,13 @@
         <v>353</v>
       </c>
       <c r="D99" s="27" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="E99" s="26" t="s">
         <v>195</v>
       </c>
       <c r="F99" s="26" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="G99" s="26" t="s">
         <v>140</v>
@@ -14001,22 +14006,22 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="25" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="B100" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C100" s="26" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="D100" s="27" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="E100" s="26" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="F100" s="26" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="G100" s="26" t="s">
         <v>100</v>
@@ -14040,28 +14045,28 @@
     </row>
     <row r="101" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="25" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="B101" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="D101" s="27" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="E101" s="26" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="G101" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H101" s="26" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="I101" s="26" t="s">
         <v>79</v>
@@ -14076,7 +14081,7 @@
         <v>14</v>
       </c>
       <c r="M101" s="26" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
     </row>
   </sheetData>
@@ -14148,12 +14153,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14169,10 +14174,10 @@
         <v>65</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="D5" s="24" t="s">
         <v>67</v>
@@ -14186,56 +14191,56 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>29</v>
@@ -14244,33 +14249,33 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="D10" s="26" t="s">
         <v>22</v>
@@ -14279,61 +14284,61 @@
         <v>27</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>31</v>
@@ -14342,36 +14347,36 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="E14" s="26" t="s">
         <v>31</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>27</v>
@@ -14380,16 +14385,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="E16" s="26" t="s">
         <v>31</v>
@@ -14398,16 +14403,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="E17" s="26" t="s">
         <v>33</v>
@@ -14451,12 +14456,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14472,19 +14477,19 @@
         <v>67</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14492,59 +14497,59 @@
         <v>98</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
+        <v>1068</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>1069</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>1064</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>1070</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>1066</v>
+      </c>
+      <c r="F7" s="26" t="s">
         <v>1067</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>1068</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>1063</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>1069</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>1065</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>1066</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14552,39 +14557,39 @@
         <v>76</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14592,19 +14597,19 @@
         <v>416</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14612,219 +14617,219 @@
         <v>286</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D14" s="26" t="s">
         <v>124</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="E15" s="29" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="B17" s="26" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>1095</v>
+      </c>
+      <c r="E17" s="29" t="s">
         <v>1079</v>
       </c>
-      <c r="C17" s="26" t="s">
-        <v>1093</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>1094</v>
-      </c>
-      <c r="E17" s="29" t="s">
-        <v>1078</v>
-      </c>
       <c r="F17" s="26" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="B18" s="26" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>1097</v>
+      </c>
+      <c r="E18" s="29" t="s">
         <v>1079</v>
       </c>
-      <c r="C18" s="26" t="s">
-        <v>1093</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>1096</v>
-      </c>
-      <c r="E18" s="29" t="s">
-        <v>1078</v>
-      </c>
       <c r="F18" s="26" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="B19" s="26" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>1100</v>
+      </c>
+      <c r="E19" s="29" t="s">
         <v>1079</v>
       </c>
-      <c r="C19" s="26" t="s">
-        <v>1098</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>1099</v>
-      </c>
-      <c r="E19" s="29" t="s">
-        <v>1078</v>
-      </c>
       <c r="F19" s="26" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B22" s="26" t="s">
+        <v>1080</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>1099</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E22" s="29" t="s">
         <v>1079</v>
       </c>
-      <c r="C22" s="26" t="s">
-        <v>1098</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>1106</v>
-      </c>
-      <c r="E22" s="29" t="s">
-        <v>1078</v>
-      </c>
       <c r="F22" s="26" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
   </sheetData>

--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3054" uniqueCount="1109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3059" uniqueCount="1120">
   <si>
     <t xml:space="preserve">Argus — Catálogo de Dados</t>
   </si>
@@ -510,7 +510,10 @@
     <t xml:space="preserve">Taxa de participação e nível de ocupação</t>
   </si>
   <si>
-    <t xml:space="preserve">PNAD Contínua mensal (tabela a mapear)</t>
+    <t xml:space="preserve">t5944 / t6379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNAD Contínua mensal: t5944 participação, t6379 nível da ocupação</t>
   </si>
   <si>
     <t xml:space="preserve">BR-017</t>
@@ -519,6 +522,9 @@
     <t xml:space="preserve">População ocupada (total, formal, informal)</t>
   </si>
   <si>
+    <t xml:space="preserve">t8501</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mil pessoas</t>
   </si>
   <si>
@@ -528,7 +534,7 @@
     <t xml:space="preserve">Nível, MoM %, YoY %, real/nominal, % PIB</t>
   </si>
   <si>
-    <t xml:space="preserve">Informalidade = derivada</t>
+    <t xml:space="preserve">PNAD Contínua mensal, por situação de informalidade</t>
   </si>
   <si>
     <t xml:space="preserve">BR-018</t>
@@ -537,6 +543,12 @@
     <t xml:space="preserve">Taxa de informalidade</t>
   </si>
   <si>
+    <t xml:space="preserve">t8513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNAD Contínua mensal</t>
+  </si>
+  <si>
     <t xml:space="preserve">BR-019</t>
   </si>
   <si>
@@ -558,7 +570,10 @@
     <t xml:space="preserve">Massa de rendimento real habitual</t>
   </si>
   <si>
-    <t xml:space="preserve">Liga Trabalho a Consumo</t>
+    <t xml:space="preserve">t6392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PNAD Contínua mensal, habitualmente recebido; liga Trabalho a Consumo</t>
   </si>
   <si>
     <t xml:space="preserve">BR-021</t>
@@ -744,7 +759,7 @@
     <t xml:space="preserve">Núcleos EX3 e P55</t>
   </si>
   <si>
-    <t xml:space="preserve">Não apareceram na busca do portal; localizar no SGS</t>
+    <t xml:space="preserve">Não encontrados no portal do BCB por "núcleo ex3" nem "p55" (busca de 2026-10-04); localizar no SGS</t>
   </si>
   <si>
     <t xml:space="preserve">BR-035</t>
@@ -1185,12 +1200,24 @@
     <t xml:space="preserve">Resultado nominal e juros nominais — 12m % PIB</t>
   </si>
   <si>
+    <t xml:space="preserve">5727 / 5760</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5727 resultado nominal, 5760 juros nominais; NFSP sem desvalorização cambial, 12m % PIB</t>
+  </si>
+  <si>
     <t xml:space="preserve">BR-071</t>
   </si>
   <si>
     <t xml:space="preserve">Primário por esfera (Gov. Central, regionais, estatais)</t>
   </si>
   <si>
+    <t xml:space="preserve">5783 / 5789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5783 Governo Federal e BC, 5789 estatais (12m % PIB); governos regionais: código a localizar</t>
+  </si>
+  <si>
     <t xml:space="preserve">BR-072</t>
   </si>
   <si>
@@ -1318,6 +1345,12 @@
   </si>
   <si>
     <t xml:space="preserve">Transações correntes — 12m % PIB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transações correntes acumulado em 12 meses em relação ao PIB</t>
   </si>
   <si>
     <t xml:space="preserve">BR-083</t>
@@ -4423,7 +4456,7 @@
       </c>
       <c r="I8" s="16" t="n">
         <f aca="false">COUNTIF(Brasil!$L$6:$L$130,H8)</f>
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4455,7 +4488,7 @@
       </c>
       <c r="I9" s="16" t="n">
         <f aca="false">COUNTIF(Brasil!$L$6:$L$130,H9)</f>
-        <v>14</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5787,13 +5820,15 @@
         <v>27</v>
       </c>
       <c r="L21" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="M21" s="26"/>
+        <v>14</v>
+      </c>
+      <c r="M21" s="26" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B22" s="26" t="s">
         <v>46</v>
@@ -5802,39 +5837,39 @@
         <v>151</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="E22" s="26" t="s">
         <v>76</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="G22" s="26" t="s">
         <v>155</v>
       </c>
       <c r="H22" s="26" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="I22" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J22" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K22" s="26" t="s">
         <v>27</v>
       </c>
       <c r="L22" s="26" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M22" s="26" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B23" s="26" t="s">
         <v>46</v>
@@ -5843,13 +5878,13 @@
         <v>151</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E23" s="26" t="s">
         <v>76</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>159</v>
+        <v>170</v>
       </c>
       <c r="G23" s="26" t="s">
         <v>155</v>
@@ -5867,13 +5902,15 @@
         <v>27</v>
       </c>
       <c r="L23" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="M23" s="26"/>
+        <v>14</v>
+      </c>
+      <c r="M23" s="26" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="25" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B24" s="26" t="s">
         <v>46</v>
@@ -5882,19 +5919,19 @@
         <v>151</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="E24" s="26" t="s">
         <v>76</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="G24" s="26" t="s">
         <v>155</v>
       </c>
       <c r="H24" s="26" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="I24" s="26" t="s">
         <v>79</v>
@@ -5909,12 +5946,12 @@
         <v>12</v>
       </c>
       <c r="M24" s="26" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="25" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B25" s="26" t="s">
         <v>46</v>
@@ -5923,13 +5960,13 @@
         <v>151</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="E25" s="26" t="s">
         <v>76</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>159</v>
+        <v>179</v>
       </c>
       <c r="G25" s="26" t="s">
         <v>155</v>
@@ -5947,15 +5984,15 @@
         <v>27</v>
       </c>
       <c r="L25" s="26" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M25" s="26" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="25" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B26" s="26" t="s">
         <v>46</v>
@@ -5964,13 +6001,13 @@
         <v>151</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="E26" s="26" t="s">
         <v>76</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="G26" s="26" t="s">
         <v>78</v>
@@ -5991,39 +6028,39 @@
         <v>16</v>
       </c>
       <c r="M26" s="26" t="s">
-        <v>179</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="25" t="s">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B27" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C27" s="26" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>182</v>
+        <v>187</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="G27" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H27" s="26" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="I27" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J27" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K27" s="26" t="s">
         <v>27</v>
@@ -6032,24 +6069,24 @@
         <v>12</v>
       </c>
       <c r="M27" s="26" t="s">
-        <v>186</v>
+        <v>191</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="25" t="s">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="B28" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C28" s="26" t="s">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F28" s="26" t="s">
         <v>124</v>
@@ -6058,7 +6095,7 @@
         <v>100</v>
       </c>
       <c r="H28" s="26" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="I28" s="26" t="s">
         <v>102</v>
@@ -6073,39 +6110,39 @@
         <v>18</v>
       </c>
       <c r="M28" s="26" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="25" t="s">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="B29" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C29" s="26" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="G29" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H29" s="26" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="I29" s="26" t="s">
         <v>22</v>
       </c>
       <c r="J29" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K29" s="26" t="s">
         <v>31</v>
@@ -6114,39 +6151,39 @@
         <v>22</v>
       </c>
       <c r="M29" s="26" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="25" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="B30" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D30" s="27" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="E30" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G30" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H30" s="26" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I30" s="26" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J30" s="26" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K30" s="26" t="s">
         <v>27</v>
@@ -6155,27 +6192,27 @@
         <v>12</v>
       </c>
       <c r="M30" s="26" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="25" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="B31" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>209</v>
+        <v>214</v>
       </c>
       <c r="E31" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F31" s="26" t="s">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="G31" s="26" t="s">
         <v>100</v>
@@ -6196,39 +6233,39 @@
         <v>12</v>
       </c>
       <c r="M31" s="26" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="25" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="B32" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C32" s="26" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="E32" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="G32" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H32" s="26" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I32" s="26" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J32" s="26" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K32" s="26" t="s">
         <v>27</v>
@@ -6237,39 +6274,39 @@
         <v>12</v>
       </c>
       <c r="M32" s="26" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="25" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="B33" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C33" s="26" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="E33" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="G33" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H33" s="26" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I33" s="26" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J33" s="26" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K33" s="26" t="s">
         <v>31</v>
@@ -6281,34 +6318,34 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="25" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="B34" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C34" s="26" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D34" s="27" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E34" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="G34" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H34" s="26" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I34" s="26" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J34" s="26" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K34" s="26" t="s">
         <v>27</v>
@@ -6320,34 +6357,34 @@
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="25" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B35" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C35" s="26" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D35" s="27" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E35" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="G35" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H35" s="26" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I35" s="26" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J35" s="26" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K35" s="26" t="s">
         <v>27</v>
@@ -6359,34 +6396,34 @@
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="25" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="B36" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D36" s="27" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E36" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="G36" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H36" s="26" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I36" s="26" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J36" s="26" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K36" s="26" t="s">
         <v>27</v>
@@ -6398,34 +6435,34 @@
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="25" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="B37" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E37" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="G37" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H37" s="26" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I37" s="26" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J37" s="26" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K37" s="26" t="s">
         <v>27</v>
@@ -6437,34 +6474,34 @@
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="25" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="B38" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D38" s="27" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E38" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="G38" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H38" s="26" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I38" s="26" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J38" s="26" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K38" s="26" t="s">
         <v>27</v>
@@ -6474,18 +6511,18 @@
       </c>
       <c r="M38" s="26"/>
     </row>
-    <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="25" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="B39" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="E39" s="26" t="s">
         <v>98</v>
@@ -6497,13 +6534,13 @@
         <v>100</v>
       </c>
       <c r="H39" s="26" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I39" s="26" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J39" s="26" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K39" s="26" t="s">
         <v>27</v>
@@ -6512,39 +6549,39 @@
         <v>16</v>
       </c>
       <c r="M39" s="26" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="25" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="B40" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E40" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="G40" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H40" s="26" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I40" s="26" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J40" s="26" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K40" s="26" t="s">
         <v>27</v>
@@ -6556,34 +6593,34 @@
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="25" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="B41" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D41" s="27" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="E41" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="G41" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H41" s="26" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I41" s="26" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J41" s="26" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K41" s="26" t="s">
         <v>27</v>
@@ -6595,34 +6632,34 @@
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="25" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="B42" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D42" s="27" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="E42" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="G42" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H42" s="26" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I42" s="26" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J42" s="26" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K42" s="26" t="s">
         <v>27</v>
@@ -6634,34 +6671,34 @@
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="25" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="B43" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D43" s="27" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="E43" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="G43" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H43" s="26" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I43" s="26" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J43" s="26" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K43" s="26" t="s">
         <v>27</v>
@@ -6673,34 +6710,34 @@
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="25" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="B44" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="E44" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="G44" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H44" s="26" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I44" s="26" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J44" s="26" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K44" s="26" t="s">
         <v>31</v>
@@ -6712,22 +6749,22 @@
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="25" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="B45" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="E45" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="G45" s="26" t="s">
         <v>100</v>
@@ -6751,34 +6788,34 @@
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="25" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="B46" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="E46" s="26" t="s">
         <v>76</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="G46" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H46" s="26" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="I46" s="26" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J46" s="26" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K46" s="26" t="s">
         <v>27</v>
@@ -6787,39 +6824,39 @@
         <v>12</v>
       </c>
       <c r="M46" s="26" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="25" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="B47" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="G47" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H47" s="26" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I47" s="26" t="s">
         <v>22</v>
       </c>
       <c r="J47" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K47" s="26" t="s">
         <v>27</v>
@@ -6828,39 +6865,39 @@
         <v>22</v>
       </c>
       <c r="M47" s="26" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="25" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="B48" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D48" s="27" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="E48" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F48" s="26" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="G48" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H48" s="26" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I48" s="26" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J48" s="26" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K48" s="26" t="s">
         <v>27</v>
@@ -6869,21 +6906,21 @@
         <v>12</v>
       </c>
       <c r="M48" s="26" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="25" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="B49" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E49" s="26" t="s">
         <v>98</v>
@@ -6895,13 +6932,13 @@
         <v>100</v>
       </c>
       <c r="H49" s="26" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="I49" s="26" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J49" s="26" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="K49" s="26" t="s">
         <v>31</v>
@@ -6913,22 +6950,22 @@
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="25" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="B50" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="D50" s="27" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="E50" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F50" s="26" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="G50" s="26" t="s">
         <v>100</v>
@@ -6949,12 +6986,12 @@
         <v>12</v>
       </c>
       <c r="M50" s="26" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="25" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="B51" s="26" t="s">
         <v>47</v>
@@ -6963,13 +7000,13 @@
         <v>144</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E51" s="26" t="s">
         <v>146</v>
       </c>
       <c r="F51" s="26" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G51" s="26" t="s">
         <v>148</v>
@@ -6993,7 +7030,7 @@
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="25" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="B52" s="26" t="s">
         <v>47</v>
@@ -7002,13 +7039,13 @@
         <v>144</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E52" s="26" t="s">
         <v>146</v>
       </c>
       <c r="F52" s="26" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="G52" s="26" t="s">
         <v>140</v>
@@ -7029,12 +7066,12 @@
         <v>12</v>
       </c>
       <c r="M52" s="26" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="25" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="B53" s="26" t="s">
         <v>47</v>
@@ -7043,13 +7080,13 @@
         <v>144</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F53" s="26" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="G53" s="26" t="s">
         <v>140</v>
@@ -7070,30 +7107,30 @@
         <v>14</v>
       </c>
       <c r="M53" s="26" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="25" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B54" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C54" s="26" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="D54" s="27" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="E54" s="26" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="F54" s="26" t="s">
         <v>24</v>
       </c>
       <c r="G54" s="26" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H54" s="26" t="s">
         <v>85</v>
@@ -7111,33 +7148,33 @@
         <v>24</v>
       </c>
       <c r="M54" s="26" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="25" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="B55" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D55" s="27" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="E55" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F55" s="26" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="G55" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H55" s="26" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="I55" s="26" t="s">
         <v>86</v>
@@ -7152,33 +7189,33 @@
         <v>12</v>
       </c>
       <c r="M55" s="26" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="25" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="B56" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D56" s="27" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E56" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F56" s="26" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="G56" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H56" s="26" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="I56" s="26" t="s">
         <v>86</v>
@@ -7193,33 +7230,33 @@
         <v>12</v>
       </c>
       <c r="M56" s="26" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="25" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="B57" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="E57" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F57" s="26" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="G57" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H57" s="26" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="I57" s="26" t="s">
         <v>86</v>
@@ -7234,33 +7271,33 @@
         <v>12</v>
       </c>
       <c r="M57" s="26" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="25" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="B58" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="E58" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F58" s="26" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="G58" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H58" s="26" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="I58" s="26" t="s">
         <v>86</v>
@@ -7275,33 +7312,33 @@
         <v>12</v>
       </c>
       <c r="M58" s="26" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="25" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B59" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D59" s="27" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="E59" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F59" s="26" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="G59" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H59" s="26" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="I59" s="26" t="s">
         <v>86</v>
@@ -7319,34 +7356,34 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="25" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="B60" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="26" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F60" s="26" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="G60" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H60" s="26" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="I60" s="26" t="s">
         <v>22</v>
       </c>
       <c r="J60" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K60" s="26" t="s">
         <v>27</v>
@@ -7355,12 +7392,12 @@
         <v>22</v>
       </c>
       <c r="M60" s="26" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="25" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="B61" s="26" t="s">
         <v>48</v>
@@ -7369,19 +7406,19 @@
         <v>144</v>
       </c>
       <c r="D61" s="27" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E61" s="26" t="s">
         <v>146</v>
       </c>
       <c r="F61" s="26" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="G61" s="26" t="s">
         <v>148</v>
       </c>
       <c r="H61" s="26" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="I61" s="26" t="s">
         <v>86</v>
@@ -7396,36 +7433,36 @@
         <v>12</v>
       </c>
       <c r="M61" s="26" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="25" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="B62" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C62" s="26" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="D62" s="27" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="E62" s="26" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="F62" s="26" t="s">
         <v>24</v>
       </c>
       <c r="G62" s="26" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="H62" s="26" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="I62" s="26" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J62" s="26" t="s">
         <v>124</v>
@@ -7437,36 +7474,36 @@
         <v>24</v>
       </c>
       <c r="M62" s="26" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="25" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="B63" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C63" s="26" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="D63" s="27" t="s">
+        <v>339</v>
+      </c>
+      <c r="E63" s="26" t="s">
+        <v>340</v>
+      </c>
+      <c r="F63" s="26" t="s">
+        <v>341</v>
+      </c>
+      <c r="G63" s="26" t="s">
         <v>334</v>
       </c>
-      <c r="E63" s="26" t="s">
-        <v>335</v>
-      </c>
-      <c r="F63" s="26" t="s">
-        <v>336</v>
-      </c>
-      <c r="G63" s="26" t="s">
-        <v>329</v>
-      </c>
       <c r="H63" s="26" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="I63" s="26" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="J63" s="26" t="s">
         <v>124</v>
@@ -7478,39 +7515,39 @@
         <v>14</v>
       </c>
       <c r="M63" s="26" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="25" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="B64" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C64" s="26" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D64" s="27" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E64" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F64" s="26" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="G64" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H64" s="26" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I64" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J64" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K64" s="26" t="s">
         <v>27</v>
@@ -7519,39 +7556,39 @@
         <v>12</v>
       </c>
       <c r="M64" s="26" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="25" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="B65" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D65" s="27" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="E65" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="G65" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H65" s="26" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I65" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J65" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K65" s="26" t="s">
         <v>27</v>
@@ -7560,39 +7597,39 @@
         <v>12</v>
       </c>
       <c r="M65" s="26" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="25" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="B66" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C66" s="26" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D66" s="27" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="E66" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F66" s="26" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="G66" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H66" s="26" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="I66" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J66" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K66" s="26" t="s">
         <v>27</v>
@@ -7604,22 +7641,22 @@
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="25" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="B67" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C67" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="E67" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="G67" s="26" t="s">
         <v>100</v>
@@ -7628,10 +7665,10 @@
         <v>101</v>
       </c>
       <c r="I67" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J67" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K67" s="26" t="s">
         <v>27</v>
@@ -7643,22 +7680,22 @@
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="25" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B68" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C68" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D68" s="27" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="E68" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="G68" s="26" t="s">
         <v>100</v>
@@ -7667,10 +7704,10 @@
         <v>101</v>
       </c>
       <c r="I68" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J68" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K68" s="26" t="s">
         <v>27</v>
@@ -7679,27 +7716,27 @@
         <v>12</v>
       </c>
       <c r="M68" s="26" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="25" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="B69" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D69" s="27" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="E69" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="G69" s="26" t="s">
         <v>100</v>
@@ -7723,28 +7760,28 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="25" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="B70" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C70" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D70" s="27" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="E70" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="G70" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H70" s="26" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="I70" s="26" t="s">
         <v>86</v>
@@ -7762,28 +7799,28 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="25" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="B71" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C71" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="E71" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="G71" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H71" s="26" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="I71" s="26" t="s">
         <v>86</v>
@@ -7801,28 +7838,28 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="25" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="B72" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C72" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="E72" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
       <c r="G72" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H72" s="26" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="I72" s="26" t="s">
         <v>86</v>
@@ -7840,22 +7877,22 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="25" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
       <c r="B73" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C73" s="26" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="E73" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F73" s="26" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="G73" s="26" t="s">
         <v>140</v>
@@ -7867,7 +7904,7 @@
         <v>22</v>
       </c>
       <c r="J73" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K73" s="26" t="s">
         <v>31</v>
@@ -7876,33 +7913,33 @@
         <v>22</v>
       </c>
       <c r="M73" s="26" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="25" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="B74" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C74" s="26" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="D74" s="27" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="E74" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F74" s="26" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="G74" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H74" s="26" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="I74" s="26" t="s">
         <v>86</v>
@@ -7920,28 +7957,28 @@
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="25" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="B75" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C75" s="26" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="D75" s="27" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="E75" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F75" s="26" t="s">
-        <v>16</v>
+        <v>389</v>
       </c>
       <c r="G75" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H75" s="26" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="I75" s="26" t="s">
         <v>86</v>
@@ -7953,73 +7990,77 @@
         <v>27</v>
       </c>
       <c r="L75" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="M75" s="26"/>
+        <v>14</v>
+      </c>
+      <c r="M75" s="26" t="s">
+        <v>390</v>
+      </c>
     </row>
     <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="25" t="s">
-        <v>384</v>
+        <v>391</v>
       </c>
       <c r="B76" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C76" s="26" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="D76" s="27" t="s">
-        <v>385</v>
+        <v>392</v>
       </c>
       <c r="E76" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>16</v>
+        <v>393</v>
       </c>
       <c r="G76" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H76" s="26" t="s">
-        <v>101</v>
+        <v>386</v>
       </c>
       <c r="I76" s="26" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="J76" s="26" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="K76" s="26" t="s">
         <v>27</v>
       </c>
       <c r="L76" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="M76" s="26"/>
+        <v>14</v>
+      </c>
+      <c r="M76" s="26" t="s">
+        <v>394</v>
+      </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="25" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="B77" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C77" s="26" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="D77" s="27" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="E77" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
       <c r="G77" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H77" s="26" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="I77" s="26" t="s">
         <v>86</v>
@@ -8037,28 +8078,28 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="25" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="B78" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C78" s="26" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="D78" s="27" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
       <c r="E78" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="G78" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H78" s="26" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="I78" s="26" t="s">
         <v>86</v>
@@ -8076,22 +8117,22 @@
     </row>
     <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="25" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
       <c r="B79" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C79" s="26" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>395</v>
+        <v>404</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>396</v>
+        <v>405</v>
       </c>
       <c r="G79" s="26" t="s">
         <v>100</v>
@@ -8112,33 +8153,33 @@
         <v>14</v>
       </c>
       <c r="M79" s="26" t="s">
-        <v>397</v>
+        <v>406</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="25" t="s">
-        <v>398</v>
+        <v>407</v>
       </c>
       <c r="B80" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C80" s="26" t="s">
-        <v>394</v>
+        <v>403</v>
       </c>
       <c r="D80" s="27" t="s">
-        <v>399</v>
+        <v>408</v>
       </c>
       <c r="E80" s="26" t="s">
-        <v>400</v>
+        <v>409</v>
       </c>
       <c r="F80" s="26" t="s">
         <v>24</v>
       </c>
       <c r="G80" s="26" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="H80" s="26" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="I80" s="26" t="s">
         <v>86</v>
@@ -8156,22 +8197,22 @@
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="25" t="s">
-        <v>401</v>
+        <v>410</v>
       </c>
       <c r="B81" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C81" s="26" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>402</v>
+        <v>411</v>
       </c>
       <c r="E81" s="26" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F81" s="26" t="s">
-        <v>403</v>
+        <v>412</v>
       </c>
       <c r="G81" s="26" t="s">
         <v>100</v>
@@ -8195,28 +8236,28 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="25" t="s">
-        <v>404</v>
+        <v>413</v>
       </c>
       <c r="B82" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C82" s="26" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="D82" s="27" t="s">
-        <v>406</v>
+        <v>415</v>
       </c>
       <c r="E82" s="26" t="s">
         <v>146</v>
       </c>
       <c r="F82" s="26" t="s">
-        <v>407</v>
+        <v>416</v>
       </c>
       <c r="G82" s="26" t="s">
         <v>148</v>
       </c>
       <c r="H82" s="26" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="I82" s="26" t="s">
         <v>86</v>
@@ -8234,28 +8275,28 @@
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="25" t="s">
-        <v>408</v>
+        <v>417</v>
       </c>
       <c r="B83" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C83" s="26" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="D83" s="27" t="s">
-        <v>409</v>
+        <v>418</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>410</v>
+        <v>419</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="G83" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H83" s="26" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="I83" s="26" t="s">
         <v>86</v>
@@ -8270,33 +8311,33 @@
         <v>18</v>
       </c>
       <c r="M83" s="26" t="s">
-        <v>412</v>
+        <v>421</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="25" t="s">
-        <v>413</v>
+        <v>422</v>
       </c>
       <c r="B84" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C84" s="26" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="D84" s="27" t="s">
-        <v>415</v>
+        <v>424</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="G84" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H84" s="26" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="I84" s="26" t="s">
         <v>102</v>
@@ -8311,33 +8352,33 @@
         <v>14</v>
       </c>
       <c r="M84" s="26" t="s">
-        <v>419</v>
+        <v>428</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="25" t="s">
-        <v>420</v>
+        <v>429</v>
       </c>
       <c r="B85" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C85" s="26" t="s">
-        <v>414</v>
+        <v>423</v>
       </c>
       <c r="D85" s="27" t="s">
-        <v>421</v>
+        <v>430</v>
       </c>
       <c r="E85" s="26" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="F85" s="26" t="s">
-        <v>417</v>
+        <v>426</v>
       </c>
       <c r="G85" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H85" s="26" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="I85" s="26" t="s">
         <v>102</v>
@@ -8352,33 +8393,33 @@
         <v>14</v>
       </c>
       <c r="M85" s="26" t="s">
-        <v>422</v>
+        <v>431</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="25" t="s">
-        <v>423</v>
+        <v>432</v>
       </c>
       <c r="B86" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C86" s="26" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="D86" s="27" t="s">
-        <v>425</v>
+        <v>434</v>
       </c>
       <c r="E86" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F86" s="26" t="s">
-        <v>426</v>
+        <v>435</v>
       </c>
       <c r="G86" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H86" s="26" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="I86" s="26" t="s">
         <v>102</v>
@@ -8394,30 +8435,30 @@
       </c>
       <c r="M86" s="26"/>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="25" t="s">
-        <v>427</v>
+        <v>436</v>
       </c>
       <c r="B87" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C87" s="26" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="D87" s="27" t="s">
-        <v>428</v>
+        <v>437</v>
       </c>
       <c r="E87" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F87" s="26" t="s">
-        <v>16</v>
+        <v>438</v>
       </c>
       <c r="G87" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H87" s="26" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="I87" s="26" t="s">
         <v>86</v>
@@ -8429,34 +8470,36 @@
         <v>27</v>
       </c>
       <c r="L87" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="M87" s="26"/>
+        <v>14</v>
+      </c>
+      <c r="M87" s="26" t="s">
+        <v>439</v>
+      </c>
     </row>
     <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="25" t="s">
-        <v>429</v>
+        <v>440</v>
       </c>
       <c r="B88" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C88" s="26" t="s">
-        <v>424</v>
+        <v>433</v>
       </c>
       <c r="D88" s="27" t="s">
-        <v>430</v>
+        <v>441</v>
       </c>
       <c r="E88" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F88" s="26" t="s">
-        <v>431</v>
+        <v>442</v>
       </c>
       <c r="G88" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H88" s="26" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="I88" s="26" t="s">
         <v>102</v>
@@ -8474,34 +8517,34 @@
     </row>
     <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="25" t="s">
-        <v>432</v>
+        <v>443</v>
       </c>
       <c r="B89" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C89" s="26" t="s">
-        <v>433</v>
+        <v>444</v>
       </c>
       <c r="D89" s="27" t="s">
-        <v>434</v>
+        <v>445</v>
       </c>
       <c r="E89" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F89" s="26" t="s">
-        <v>435</v>
+        <v>446</v>
       </c>
       <c r="G89" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H89" s="26" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="I89" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J89" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K89" s="26" t="s">
         <v>27</v>
@@ -8510,33 +8553,33 @@
         <v>12</v>
       </c>
       <c r="M89" s="26" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="25" t="s">
-        <v>436</v>
+        <v>447</v>
       </c>
       <c r="B90" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C90" s="26" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="D90" s="27" t="s">
-        <v>438</v>
+        <v>449</v>
       </c>
       <c r="E90" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F90" s="26" t="s">
-        <v>439</v>
+        <v>450</v>
       </c>
       <c r="G90" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H90" s="26" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="I90" s="26" t="s">
         <v>79</v>
@@ -8551,27 +8594,27 @@
         <v>12</v>
       </c>
       <c r="M90" s="26" t="s">
-        <v>441</v>
+        <v>452</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="25" t="s">
-        <v>442</v>
+        <v>453</v>
       </c>
       <c r="B91" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="D91" s="27" t="s">
-        <v>443</v>
+        <v>454</v>
       </c>
       <c r="E91" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F91" s="26" t="s">
-        <v>444</v>
+        <v>455</v>
       </c>
       <c r="G91" s="26" t="s">
         <v>100</v>
@@ -8595,16 +8638,16 @@
     </row>
     <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="25" t="s">
-        <v>445</v>
+        <v>456</v>
       </c>
       <c r="B92" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C92" s="26" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="D92" s="27" t="s">
-        <v>446</v>
+        <v>457</v>
       </c>
       <c r="E92" s="26" t="s">
         <v>98</v>
@@ -8616,7 +8659,7 @@
         <v>148</v>
       </c>
       <c r="H92" s="26" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="I92" s="26" t="s">
         <v>102</v>
@@ -8634,28 +8677,28 @@
     </row>
     <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="25" t="s">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="B93" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C93" s="26" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="D93" s="27" t="s">
-        <v>448</v>
+        <v>459</v>
       </c>
       <c r="E93" s="26" t="s">
         <v>146</v>
       </c>
       <c r="F93" s="26" t="s">
-        <v>449</v>
+        <v>460</v>
       </c>
       <c r="G93" s="26" t="s">
         <v>148</v>
       </c>
       <c r="H93" s="26" t="s">
-        <v>440</v>
+        <v>451</v>
       </c>
       <c r="I93" s="26" t="s">
         <v>79</v>
@@ -8673,28 +8716,28 @@
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="25" t="s">
-        <v>450</v>
+        <v>461</v>
       </c>
       <c r="B94" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C94" s="26" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="D94" s="27" t="s">
-        <v>452</v>
+        <v>463</v>
       </c>
       <c r="E94" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F94" s="26" t="s">
-        <v>454</v>
+        <v>465</v>
       </c>
       <c r="G94" s="26" t="s">
-        <v>455</v>
+        <v>466</v>
       </c>
       <c r="H94" s="26" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="I94" s="26" t="s">
         <v>79</v>
@@ -8712,19 +8755,19 @@
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="25" t="s">
-        <v>457</v>
+        <v>468</v>
       </c>
       <c r="B95" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C95" s="26" t="s">
-        <v>451</v>
+        <v>462</v>
       </c>
       <c r="D95" s="27" t="s">
-        <v>458</v>
+        <v>469</v>
       </c>
       <c r="E95" s="26" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="F95" s="26" t="s">
         <v>16</v>
@@ -8751,22 +8794,22 @@
     </row>
     <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="25" t="s">
-        <v>460</v>
+        <v>471</v>
       </c>
       <c r="B96" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C96" s="26" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="D96" s="27" t="s">
-        <v>462</v>
+        <v>473</v>
       </c>
       <c r="E96" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F96" s="26" t="s">
-        <v>463</v>
+        <v>474</v>
       </c>
       <c r="G96" s="26" t="s">
         <v>100</v>
@@ -8787,27 +8830,27 @@
         <v>12</v>
       </c>
       <c r="M96" s="26" t="s">
-        <v>464</v>
+        <v>475</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="25" t="s">
-        <v>465</v>
+        <v>476</v>
       </c>
       <c r="B97" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C97" s="26" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="D97" s="27" t="s">
-        <v>466</v>
+        <v>477</v>
       </c>
       <c r="E97" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F97" s="26" t="s">
-        <v>467</v>
+        <v>478</v>
       </c>
       <c r="G97" s="26" t="s">
         <v>100</v>
@@ -8828,27 +8871,27 @@
         <v>12</v>
       </c>
       <c r="M97" s="26" t="s">
-        <v>468</v>
+        <v>479</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="25" t="s">
-        <v>469</v>
+        <v>480</v>
       </c>
       <c r="B98" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C98" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D98" s="27" t="s">
-        <v>470</v>
+        <v>481</v>
       </c>
       <c r="E98" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>471</v>
+        <v>482</v>
       </c>
       <c r="G98" s="26" t="s">
         <v>100</v>
@@ -8857,10 +8900,10 @@
         <v>101</v>
       </c>
       <c r="I98" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J98" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K98" s="26" t="s">
         <v>27</v>
@@ -8872,22 +8915,22 @@
     </row>
     <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="25" t="s">
-        <v>472</v>
+        <v>483</v>
       </c>
       <c r="B99" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C99" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D99" s="27" t="s">
-        <v>473</v>
+        <v>484</v>
       </c>
       <c r="E99" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F99" s="26" t="s">
-        <v>474</v>
+        <v>485</v>
       </c>
       <c r="G99" s="26" t="s">
         <v>100</v>
@@ -8896,10 +8939,10 @@
         <v>101</v>
       </c>
       <c r="I99" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J99" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K99" s="26" t="s">
         <v>27</v>
@@ -8911,22 +8954,22 @@
     </row>
     <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="25" t="s">
-        <v>475</v>
+        <v>486</v>
       </c>
       <c r="B100" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C100" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D100" s="27" t="s">
-        <v>476</v>
+        <v>487</v>
       </c>
       <c r="E100" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F100" s="26" t="s">
-        <v>477</v>
+        <v>488</v>
       </c>
       <c r="G100" s="26" t="s">
         <v>100</v>
@@ -8935,10 +8978,10 @@
         <v>101</v>
       </c>
       <c r="I100" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J100" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K100" s="26" t="s">
         <v>27</v>
@@ -8950,22 +8993,22 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="25" t="s">
-        <v>478</v>
+        <v>489</v>
       </c>
       <c r="B101" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D101" s="27" t="s">
-        <v>479</v>
+        <v>490</v>
       </c>
       <c r="E101" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>480</v>
+        <v>491</v>
       </c>
       <c r="G101" s="26" t="s">
         <v>100</v>
@@ -8989,22 +9032,22 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="25" t="s">
-        <v>481</v>
+        <v>492</v>
       </c>
       <c r="B102" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C102" s="26" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="D102" s="27" t="s">
-        <v>483</v>
+        <v>494</v>
       </c>
       <c r="E102" s="26" t="s">
         <v>76</v>
       </c>
       <c r="F102" s="26" t="s">
-        <v>484</v>
+        <v>495</v>
       </c>
       <c r="G102" s="26" t="s">
         <v>124</v>
@@ -9016,7 +9059,7 @@
         <v>22</v>
       </c>
       <c r="J102" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K102" s="26" t="s">
         <v>27</v>
@@ -9025,12 +9068,12 @@
         <v>22</v>
       </c>
       <c r="M102" s="26" t="s">
-        <v>485</v>
+        <v>496</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="25" t="s">
-        <v>486</v>
+        <v>497</v>
       </c>
       <c r="B103" s="26" t="s">
         <v>51</v>
@@ -9039,7 +9082,7 @@
         <v>127</v>
       </c>
       <c r="D103" s="27" t="s">
-        <v>487</v>
+        <v>498</v>
       </c>
       <c r="E103" s="26" t="s">
         <v>129</v>
@@ -9069,16 +9112,16 @@
     </row>
     <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="25" t="s">
-        <v>488</v>
+        <v>499</v>
       </c>
       <c r="B104" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C104" s="26" t="s">
-        <v>489</v>
+        <v>500</v>
       </c>
       <c r="D104" s="27" t="s">
-        <v>490</v>
+        <v>501</v>
       </c>
       <c r="E104" s="26" t="s">
         <v>98</v>
@@ -9108,34 +9151,34 @@
     </row>
     <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="25" t="s">
-        <v>491</v>
+        <v>502</v>
       </c>
       <c r="B105" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C105" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D105" s="27" t="s">
-        <v>492</v>
+        <v>503</v>
       </c>
       <c r="E105" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F105" s="26" t="s">
-        <v>493</v>
+        <v>504</v>
       </c>
       <c r="G105" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H105" s="26" t="s">
-        <v>494</v>
+        <v>505</v>
       </c>
       <c r="I105" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J105" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K105" s="26" t="s">
         <v>31</v>
@@ -9147,22 +9190,22 @@
     </row>
     <row r="106" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="25" t="s">
-        <v>495</v>
+        <v>506</v>
       </c>
       <c r="B106" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C106" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D106" s="27" t="s">
-        <v>496</v>
+        <v>507</v>
       </c>
       <c r="E106" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F106" s="26" t="s">
-        <v>497</v>
+        <v>508</v>
       </c>
       <c r="G106" s="26" t="s">
         <v>100</v>
@@ -9171,10 +9214,10 @@
         <v>101</v>
       </c>
       <c r="I106" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J106" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K106" s="26" t="s">
         <v>31</v>
@@ -9186,22 +9229,22 @@
     </row>
     <row r="107" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="25" t="s">
-        <v>498</v>
+        <v>509</v>
       </c>
       <c r="B107" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C107" s="26" t="s">
-        <v>499</v>
+        <v>510</v>
       </c>
       <c r="D107" s="27" t="s">
-        <v>500</v>
+        <v>511</v>
       </c>
       <c r="E107" s="26" t="s">
-        <v>501</v>
+        <v>512</v>
       </c>
       <c r="F107" s="26" t="s">
-        <v>502</v>
+        <v>513</v>
       </c>
       <c r="G107" s="26" t="s">
         <v>100</v>
@@ -9225,28 +9268,28 @@
     </row>
     <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="25" t="s">
-        <v>503</v>
+        <v>514</v>
       </c>
       <c r="B108" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C108" s="26" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="D108" s="27" t="s">
-        <v>505</v>
+        <v>516</v>
       </c>
       <c r="E108" s="26" t="s">
-        <v>506</v>
+        <v>517</v>
       </c>
       <c r="F108" s="26" t="s">
-        <v>507</v>
+        <v>518</v>
       </c>
       <c r="G108" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H108" s="26" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="I108" s="26" t="s">
         <v>102</v>
@@ -9261,27 +9304,27 @@
         <v>18</v>
       </c>
       <c r="M108" s="26" t="s">
-        <v>508</v>
+        <v>519</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="25" t="s">
-        <v>509</v>
+        <v>520</v>
       </c>
       <c r="B109" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C109" s="26" t="s">
-        <v>510</v>
+        <v>521</v>
       </c>
       <c r="D109" s="27" t="s">
-        <v>511</v>
+        <v>522</v>
       </c>
       <c r="E109" s="26" t="s">
-        <v>512</v>
+        <v>523</v>
       </c>
       <c r="F109" s="26" t="s">
-        <v>513</v>
+        <v>524</v>
       </c>
       <c r="G109" s="26" t="s">
         <v>78</v>
@@ -9302,21 +9345,21 @@
         <v>14</v>
       </c>
       <c r="M109" s="26" t="s">
-        <v>514</v>
+        <v>525</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="25" t="s">
-        <v>515</v>
+        <v>526</v>
       </c>
       <c r="B110" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C110" s="26" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="D110" s="27" t="s">
-        <v>517</v>
+        <v>528</v>
       </c>
       <c r="E110" s="26" t="s">
         <v>76</v>
@@ -9343,33 +9386,33 @@
         <v>12</v>
       </c>
       <c r="M110" s="26" t="s">
-        <v>518</v>
+        <v>529</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="25" t="s">
-        <v>519</v>
+        <v>530</v>
       </c>
       <c r="B111" s="26" t="s">
         <v>53</v>
       </c>
       <c r="C111" s="26" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="D111" s="27" t="s">
-        <v>521</v>
+        <v>532</v>
       </c>
       <c r="E111" s="26" t="s">
-        <v>522</v>
+        <v>533</v>
       </c>
       <c r="F111" s="26" t="s">
-        <v>523</v>
+        <v>534</v>
       </c>
       <c r="G111" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H111" s="26" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="I111" s="26" t="s">
         <v>79</v>
@@ -9384,33 +9427,33 @@
         <v>14</v>
       </c>
       <c r="M111" s="26" t="s">
-        <v>525</v>
+        <v>536</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="25" t="s">
-        <v>526</v>
+        <v>537</v>
       </c>
       <c r="B112" s="26" t="s">
         <v>53</v>
       </c>
       <c r="C112" s="26" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D112" s="27" t="s">
-        <v>527</v>
+        <v>538</v>
       </c>
       <c r="E112" s="26" t="s">
-        <v>528</v>
+        <v>539</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>529</v>
+        <v>540</v>
       </c>
       <c r="G112" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H112" s="26" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="I112" s="26" t="s">
         <v>86</v>
@@ -9425,33 +9468,33 @@
         <v>14</v>
       </c>
       <c r="M112" s="26" t="s">
-        <v>530</v>
+        <v>541</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="25" t="s">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="B113" s="26" t="s">
         <v>53</v>
       </c>
       <c r="C113" s="26" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D113" s="27" t="s">
-        <v>532</v>
+        <v>543</v>
       </c>
       <c r="E113" s="26" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="F113" s="26" t="s">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="G113" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H113" s="26" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="I113" s="26" t="s">
         <v>86</v>
@@ -9469,28 +9512,28 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="25" t="s">
-        <v>534</v>
+        <v>545</v>
       </c>
       <c r="B114" s="26" t="s">
         <v>53</v>
       </c>
       <c r="C114" s="26" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="D114" s="27" t="s">
-        <v>536</v>
+        <v>547</v>
       </c>
       <c r="E114" s="26" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="F114" s="26" t="s">
-        <v>538</v>
+        <v>549</v>
       </c>
       <c r="G114" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H114" s="26" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="I114" s="26" t="s">
         <v>86</v>
@@ -9505,24 +9548,24 @@
         <v>14</v>
       </c>
       <c r="M114" s="26" t="s">
-        <v>539</v>
+        <v>550</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="25" t="s">
-        <v>540</v>
+        <v>551</v>
       </c>
       <c r="B115" s="26" t="s">
         <v>53</v>
       </c>
       <c r="C115" s="26" t="s">
-        <v>535</v>
+        <v>546</v>
       </c>
       <c r="D115" s="27" t="s">
-        <v>541</v>
+        <v>552</v>
       </c>
       <c r="E115" s="26" t="s">
-        <v>542</v>
+        <v>553</v>
       </c>
       <c r="F115" s="26" t="s">
         <v>124</v>
@@ -9531,7 +9574,7 @@
         <v>140</v>
       </c>
       <c r="H115" s="26" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="I115" s="26" t="s">
         <v>86</v>
@@ -9546,12 +9589,12 @@
         <v>20</v>
       </c>
       <c r="M115" s="26" t="s">
-        <v>543</v>
+        <v>554</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="25" t="s">
-        <v>544</v>
+        <v>555</v>
       </c>
       <c r="B116" s="26" t="s">
         <v>53</v>
@@ -9560,13 +9603,13 @@
         <v>102</v>
       </c>
       <c r="D116" s="27" t="s">
-        <v>545</v>
+        <v>556</v>
       </c>
       <c r="E116" s="26" t="s">
-        <v>546</v>
+        <v>557</v>
       </c>
       <c r="F116" s="26" t="s">
-        <v>547</v>
+        <v>558</v>
       </c>
       <c r="G116" s="26" t="s">
         <v>140</v>
@@ -9587,36 +9630,36 @@
         <v>18</v>
       </c>
       <c r="M116" s="26" t="s">
-        <v>548</v>
+        <v>559</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="25" t="s">
-        <v>549</v>
+        <v>560</v>
       </c>
       <c r="B117" s="26" t="s">
         <v>54</v>
       </c>
       <c r="C117" s="26" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="D117" s="27" t="s">
-        <v>551</v>
+        <v>562</v>
       </c>
       <c r="E117" s="26" t="s">
-        <v>552</v>
+        <v>563</v>
       </c>
       <c r="F117" s="26" t="s">
-        <v>553</v>
+        <v>564</v>
       </c>
       <c r="G117" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H117" s="26" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="I117" s="26" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J117" s="26" t="s">
         <v>124</v>
@@ -9631,31 +9674,31 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="25" t="s">
-        <v>554</v>
+        <v>565</v>
       </c>
       <c r="B118" s="26" t="s">
         <v>54</v>
       </c>
       <c r="C118" s="26" t="s">
-        <v>550</v>
+        <v>561</v>
       </c>
       <c r="D118" s="27" t="s">
-        <v>555</v>
+        <v>566</v>
       </c>
       <c r="E118" s="26" t="s">
-        <v>556</v>
+        <v>567</v>
       </c>
       <c r="F118" s="26" t="s">
-        <v>557</v>
+        <v>568</v>
       </c>
       <c r="G118" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H118" s="26" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="I118" s="26" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J118" s="26" t="s">
         <v>124</v>
@@ -9670,31 +9713,31 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="25" t="s">
-        <v>558</v>
+        <v>569</v>
       </c>
       <c r="B119" s="26" t="s">
         <v>54</v>
       </c>
       <c r="C119" s="26" t="s">
-        <v>559</v>
+        <v>570</v>
       </c>
       <c r="D119" s="27" t="s">
-        <v>560</v>
+        <v>571</v>
       </c>
       <c r="E119" s="26" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="F119" s="26" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="G119" s="26" t="s">
-        <v>563</v>
+        <v>574</v>
       </c>
       <c r="H119" s="26" t="s">
-        <v>564</v>
+        <v>575</v>
       </c>
       <c r="I119" s="26" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J119" s="26" t="s">
         <v>124</v>
@@ -9709,19 +9752,19 @@
     </row>
     <row r="120" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="25" t="s">
-        <v>565</v>
+        <v>576</v>
       </c>
       <c r="B120" s="26" t="s">
         <v>54</v>
       </c>
       <c r="C120" s="26" t="s">
-        <v>566</v>
+        <v>577</v>
       </c>
       <c r="D120" s="27" t="s">
-        <v>567</v>
+        <v>578</v>
       </c>
       <c r="E120" s="26" t="s">
-        <v>568</v>
+        <v>579</v>
       </c>
       <c r="F120" s="26" t="s">
         <v>24</v>
@@ -9745,39 +9788,39 @@
         <v>24</v>
       </c>
       <c r="M120" s="26" t="s">
-        <v>569</v>
+        <v>580</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="25" t="s">
-        <v>570</v>
+        <v>581</v>
       </c>
       <c r="B121" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C121" s="26" t="s">
-        <v>571</v>
+        <v>582</v>
       </c>
       <c r="D121" s="27" t="s">
-        <v>572</v>
+        <v>583</v>
       </c>
       <c r="E121" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F121" s="26" t="s">
-        <v>573</v>
+        <v>584</v>
       </c>
       <c r="G121" s="26" t="s">
-        <v>574</v>
+        <v>585</v>
       </c>
       <c r="H121" s="26" t="s">
-        <v>575</v>
+        <v>586</v>
       </c>
       <c r="I121" s="26" t="s">
         <v>22</v>
       </c>
       <c r="J121" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K121" s="26" t="s">
         <v>27</v>
@@ -9786,39 +9829,39 @@
         <v>22</v>
       </c>
       <c r="M121" s="26" t="s">
-        <v>576</v>
+        <v>587</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="25" t="s">
-        <v>577</v>
+        <v>588</v>
       </c>
       <c r="B122" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C122" s="26" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="D122" s="27" t="s">
-        <v>579</v>
+        <v>590</v>
       </c>
       <c r="E122" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F122" s="26" t="s">
-        <v>580</v>
+        <v>591</v>
       </c>
       <c r="G122" s="26" t="s">
         <v>148</v>
       </c>
       <c r="H122" s="26" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="I122" s="26" t="s">
         <v>22</v>
       </c>
       <c r="J122" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K122" s="26" t="s">
         <v>27</v>
@@ -9827,39 +9870,39 @@
         <v>22</v>
       </c>
       <c r="M122" s="26" t="s">
-        <v>581</v>
+        <v>592</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="25" t="s">
-        <v>582</v>
+        <v>593</v>
       </c>
       <c r="B123" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C123" s="26" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="D123" s="27" t="s">
-        <v>583</v>
+        <v>594</v>
       </c>
       <c r="E123" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F123" s="26" t="s">
-        <v>584</v>
+        <v>595</v>
       </c>
       <c r="G123" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H123" s="26" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="I123" s="26" t="s">
         <v>22</v>
       </c>
       <c r="J123" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K123" s="26" t="s">
         <v>27</v>
@@ -9871,22 +9914,22 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="25" t="s">
-        <v>585</v>
+        <v>596</v>
       </c>
       <c r="B124" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C124" s="26" t="s">
-        <v>578</v>
+        <v>589</v>
       </c>
       <c r="D124" s="27" t="s">
-        <v>586</v>
+        <v>597</v>
       </c>
       <c r="E124" s="26" t="s">
-        <v>587</v>
+        <v>598</v>
       </c>
       <c r="F124" s="26" t="s">
-        <v>588</v>
+        <v>599</v>
       </c>
       <c r="G124" s="26" t="s">
         <v>78</v>
@@ -9910,34 +9953,34 @@
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="25" t="s">
-        <v>589</v>
+        <v>600</v>
       </c>
       <c r="B125" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C125" s="26" t="s">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="D125" s="27" t="s">
-        <v>591</v>
+        <v>602</v>
       </c>
       <c r="E125" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F125" s="26" t="s">
-        <v>592</v>
+        <v>603</v>
       </c>
       <c r="G125" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H125" s="26" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="I125" s="26" t="s">
         <v>22</v>
       </c>
       <c r="J125" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K125" s="26" t="s">
         <v>31</v>
@@ -9949,22 +9992,22 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="25" t="s">
-        <v>593</v>
+        <v>604</v>
       </c>
       <c r="B126" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C126" s="26" t="s">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="D126" s="27" t="s">
-        <v>594</v>
+        <v>605</v>
       </c>
       <c r="E126" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F126" s="26" t="s">
-        <v>595</v>
+        <v>606</v>
       </c>
       <c r="G126" s="26" t="s">
         <v>78</v>
@@ -9976,7 +10019,7 @@
         <v>22</v>
       </c>
       <c r="J126" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K126" s="26" t="s">
         <v>31</v>
@@ -9985,27 +10028,27 @@
         <v>22</v>
       </c>
       <c r="M126" s="26" t="s">
-        <v>596</v>
+        <v>607</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="25" t="s">
-        <v>597</v>
+        <v>608</v>
       </c>
       <c r="B127" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C127" s="26" t="s">
-        <v>590</v>
+        <v>601</v>
       </c>
       <c r="D127" s="27" t="s">
-        <v>598</v>
+        <v>609</v>
       </c>
       <c r="E127" s="26" t="s">
-        <v>599</v>
+        <v>610</v>
       </c>
       <c r="F127" s="26" t="s">
-        <v>600</v>
+        <v>611</v>
       </c>
       <c r="G127" s="26" t="s">
         <v>78</v>
@@ -10017,7 +10060,7 @@
         <v>22</v>
       </c>
       <c r="J127" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K127" s="26" t="s">
         <v>31</v>
@@ -10029,31 +10072,31 @@
     </row>
     <row r="128" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="25" t="s">
-        <v>601</v>
+        <v>612</v>
       </c>
       <c r="B128" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C128" s="26" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="D128" s="27" t="s">
-        <v>602</v>
+        <v>613</v>
       </c>
       <c r="E128" s="26" t="s">
-        <v>603</v>
+        <v>614</v>
       </c>
       <c r="F128" s="26" t="s">
         <v>24</v>
       </c>
       <c r="G128" s="26" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="H128" s="26" t="s">
         <v>124</v>
       </c>
       <c r="I128" s="26" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J128" s="26" t="s">
         <v>124</v>
@@ -10068,34 +10111,34 @@
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="25" t="s">
-        <v>604</v>
+        <v>615</v>
       </c>
       <c r="B129" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C129" s="26" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="D129" s="27" t="s">
-        <v>605</v>
+        <v>616</v>
       </c>
       <c r="E129" s="26" t="s">
-        <v>606</v>
+        <v>617</v>
       </c>
       <c r="F129" s="26" t="s">
-        <v>607</v>
+        <v>618</v>
       </c>
       <c r="G129" s="26" t="s">
-        <v>608</v>
+        <v>619</v>
       </c>
       <c r="H129" s="26" t="s">
-        <v>609</v>
+        <v>620</v>
       </c>
       <c r="I129" s="26" t="s">
         <v>22</v>
       </c>
       <c r="J129" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K129" s="26" t="s">
         <v>33</v>
@@ -10104,27 +10147,27 @@
         <v>22</v>
       </c>
       <c r="M129" s="26" t="s">
-        <v>610</v>
+        <v>621</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="25" t="s">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="B130" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C130" s="26" t="s">
-        <v>612</v>
+        <v>623</v>
       </c>
       <c r="D130" s="27" t="s">
-        <v>613</v>
+        <v>624</v>
       </c>
       <c r="E130" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F130" s="26" t="s">
-        <v>614</v>
+        <v>625</v>
       </c>
       <c r="G130" s="26" t="s">
         <v>124</v>
@@ -10136,7 +10179,7 @@
         <v>22</v>
       </c>
       <c r="J130" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K130" s="26" t="s">
         <v>31</v>
@@ -10222,12 +10265,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>615</v>
+        <v>626</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>616</v>
+        <v>627</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10288,34 +10331,34 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>617</v>
+        <v>628</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>618</v>
+        <v>629</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>619</v>
+        <v>630</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>621</v>
+        <v>632</v>
       </c>
       <c r="G6" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="I6" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J6" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K6" s="26" t="s">
         <v>29</v>
@@ -10327,22 +10370,22 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>623</v>
+        <v>634</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>624</v>
+        <v>635</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>625</v>
+        <v>636</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>626</v>
+        <v>637</v>
       </c>
       <c r="G7" s="26" t="s">
         <v>100</v>
@@ -10366,22 +10409,22 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>627</v>
+        <v>638</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>624</v>
+        <v>635</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>628</v>
+        <v>639</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>629</v>
+        <v>640</v>
       </c>
       <c r="G8" s="26" t="s">
         <v>100</v>
@@ -10405,22 +10448,22 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>630</v>
+        <v>641</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C9" s="26" t="s">
+        <v>642</v>
+      </c>
+      <c r="D9" s="27" t="s">
+        <v>643</v>
+      </c>
+      <c r="E9" s="26" t="s">
         <v>631</v>
       </c>
-      <c r="D9" s="27" t="s">
-        <v>632</v>
-      </c>
-      <c r="E9" s="26" t="s">
-        <v>620</v>
-      </c>
       <c r="F9" s="26" t="s">
-        <v>633</v>
+        <v>644</v>
       </c>
       <c r="G9" s="26" t="s">
         <v>100</v>
@@ -10444,34 +10487,34 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>634</v>
+        <v>645</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>635</v>
+        <v>646</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>636</v>
+        <v>647</v>
       </c>
       <c r="E10" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>637</v>
+        <v>648</v>
       </c>
       <c r="G10" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="I10" s="26" t="s">
         <v>22</v>
       </c>
       <c r="J10" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K10" s="26" t="s">
         <v>29</v>
@@ -10483,28 +10526,28 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>639</v>
+        <v>650</v>
       </c>
       <c r="B11" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>635</v>
+        <v>646</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>640</v>
+        <v>651</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>641</v>
+        <v>652</v>
       </c>
       <c r="G11" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="I11" s="26" t="s">
         <v>102</v>
@@ -10522,28 +10565,28 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>642</v>
+        <v>653</v>
       </c>
       <c r="B12" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>643</v>
+        <v>654</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>644</v>
+        <v>655</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>645</v>
+        <v>656</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>646</v>
+        <v>657</v>
       </c>
       <c r="G12" s="26" t="s">
         <v>148</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="I12" s="26" t="s">
         <v>102</v>
@@ -10561,19 +10604,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>647</v>
+        <v>658</v>
       </c>
       <c r="B13" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>649</v>
+        <v>660</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>650</v>
+        <v>661</v>
       </c>
       <c r="F13" s="26" t="s">
         <v>124</v>
@@ -10597,27 +10640,27 @@
         <v>20</v>
       </c>
       <c r="M13" s="26" t="s">
-        <v>651</v>
+        <v>662</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>652</v>
+        <v>663</v>
       </c>
       <c r="B14" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>648</v>
+        <v>659</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>653</v>
+        <v>664</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>655</v>
+        <v>666</v>
       </c>
       <c r="G14" s="26" t="s">
         <v>100</v>
@@ -10641,22 +10684,22 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>656</v>
+        <v>667</v>
       </c>
       <c r="B15" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>657</v>
+        <v>668</v>
       </c>
       <c r="E15" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>658</v>
+        <v>669</v>
       </c>
       <c r="G15" s="26" t="s">
         <v>100</v>
@@ -10668,7 +10711,7 @@
         <v>22</v>
       </c>
       <c r="J15" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K15" s="26" t="s">
         <v>29</v>
@@ -10680,22 +10723,22 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>659</v>
+        <v>670</v>
       </c>
       <c r="B16" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>660</v>
+        <v>671</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>661</v>
+        <v>672</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>662</v>
+        <v>673</v>
       </c>
       <c r="G16" s="26" t="s">
         <v>78</v>
@@ -10719,28 +10762,28 @@
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>663</v>
+        <v>674</v>
       </c>
       <c r="B17" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>660</v>
+        <v>671</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>664</v>
+        <v>675</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>665</v>
+        <v>676</v>
       </c>
       <c r="G17" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="I17" s="26" t="s">
         <v>79</v>
@@ -10758,22 +10801,22 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>666</v>
+        <v>677</v>
       </c>
       <c r="B18" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>660</v>
+        <v>671</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>667</v>
+        <v>678</v>
       </c>
       <c r="E18" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>668</v>
+        <v>679</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>100</v>
@@ -10785,7 +10828,7 @@
         <v>22</v>
       </c>
       <c r="J18" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K18" s="26" t="s">
         <v>29</v>
@@ -10797,22 +10840,22 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>669</v>
+        <v>680</v>
       </c>
       <c r="B19" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>660</v>
+        <v>671</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>670</v>
+        <v>681</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>671</v>
+        <v>682</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>672</v>
+        <v>683</v>
       </c>
       <c r="G19" s="26" t="s">
         <v>100</v>
@@ -10833,33 +10876,33 @@
         <v>18</v>
       </c>
       <c r="M19" s="26" t="s">
-        <v>673</v>
+        <v>684</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>674</v>
+        <v>685</v>
       </c>
       <c r="B20" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>675</v>
+        <v>686</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>676</v>
+        <v>687</v>
       </c>
       <c r="G20" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H20" s="26" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="I20" s="26" t="s">
         <v>86</v>
@@ -10874,27 +10917,27 @@
         <v>12</v>
       </c>
       <c r="M20" s="26" t="s">
-        <v>677</v>
+        <v>688</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>678</v>
+        <v>689</v>
       </c>
       <c r="B21" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>679</v>
+        <v>690</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>680</v>
+        <v>691</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>681</v>
+        <v>692</v>
       </c>
       <c r="G21" s="26" t="s">
         <v>100</v>
@@ -10918,22 +10961,22 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>682</v>
+        <v>693</v>
       </c>
       <c r="B22" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>679</v>
+        <v>690</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>683</v>
+        <v>694</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>684</v>
+        <v>695</v>
       </c>
       <c r="G22" s="26" t="s">
         <v>100</v>
@@ -10954,27 +10997,27 @@
         <v>12</v>
       </c>
       <c r="M22" s="26" t="s">
-        <v>685</v>
+        <v>696</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>686</v>
+        <v>697</v>
       </c>
       <c r="B23" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>679</v>
+        <v>690</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>687</v>
+        <v>698</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>688</v>
+        <v>699</v>
       </c>
       <c r="G23" s="26" t="s">
         <v>100</v>
@@ -10998,22 +11041,22 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="25" t="s">
-        <v>689</v>
+        <v>700</v>
       </c>
       <c r="B24" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>690</v>
+        <v>701</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>691</v>
+        <v>702</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>692</v>
+        <v>703</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>693</v>
+        <v>704</v>
       </c>
       <c r="G24" s="26" t="s">
         <v>100</v>
@@ -11037,22 +11080,22 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="25" t="s">
-        <v>694</v>
+        <v>705</v>
       </c>
       <c r="B25" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>690</v>
+        <v>701</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>695</v>
+        <v>706</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>696</v>
+        <v>707</v>
       </c>
       <c r="G25" s="26" t="s">
         <v>100</v>
@@ -11076,22 +11119,22 @@
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="25" t="s">
-        <v>697</v>
+        <v>708</v>
       </c>
       <c r="B26" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>698</v>
+        <v>709</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>699</v>
+        <v>710</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>620</v>
+        <v>631</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>700</v>
+        <v>711</v>
       </c>
       <c r="G26" s="26" t="s">
         <v>100</v>
@@ -11115,7 +11158,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="25" t="s">
-        <v>701</v>
+        <v>712</v>
       </c>
       <c r="B27" s="26" t="s">
         <v>47</v>
@@ -11124,13 +11167,13 @@
         <v>144</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>702</v>
+        <v>713</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>703</v>
+        <v>714</v>
       </c>
       <c r="G27" s="26" t="s">
         <v>140</v>
@@ -11151,12 +11194,12 @@
         <v>14</v>
       </c>
       <c r="M27" s="26" t="s">
-        <v>704</v>
+        <v>715</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="25" t="s">
-        <v>705</v>
+        <v>716</v>
       </c>
       <c r="B28" s="26" t="s">
         <v>47</v>
@@ -11165,10 +11208,10 @@
         <v>144</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>706</v>
+        <v>717</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>707</v>
+        <v>718</v>
       </c>
       <c r="F28" s="26" t="s">
         <v>124</v>
@@ -11192,12 +11235,12 @@
         <v>20</v>
       </c>
       <c r="M28" s="26" t="s">
-        <v>708</v>
+        <v>719</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="25" t="s">
-        <v>709</v>
+        <v>720</v>
       </c>
       <c r="B29" s="26" t="s">
         <v>47</v>
@@ -11206,13 +11249,13 @@
         <v>144</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>710</v>
+        <v>721</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>711</v>
+        <v>722</v>
       </c>
       <c r="G29" s="26" t="s">
         <v>100</v>
@@ -11233,27 +11276,27 @@
         <v>14</v>
       </c>
       <c r="M29" s="26" t="s">
-        <v>712</v>
+        <v>723</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="25" t="s">
-        <v>713</v>
+        <v>724</v>
       </c>
       <c r="B30" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>714</v>
+        <v>725</v>
       </c>
       <c r="D30" s="27" t="s">
-        <v>715</v>
+        <v>726</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>716</v>
+        <v>727</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>717</v>
+        <v>728</v>
       </c>
       <c r="G30" s="26" t="s">
         <v>100</v>
@@ -11277,19 +11320,19 @@
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="25" t="s">
-        <v>718</v>
+        <v>729</v>
       </c>
       <c r="B31" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>714</v>
+        <v>725</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>719</v>
+        <v>730</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>720</v>
+        <v>731</v>
       </c>
       <c r="F31" s="26" t="s">
         <v>124</v>
@@ -11298,7 +11341,7 @@
         <v>148</v>
       </c>
       <c r="H31" s="26" t="s">
-        <v>721</v>
+        <v>732</v>
       </c>
       <c r="I31" s="26" t="s">
         <v>79</v>
@@ -11316,7 +11359,7 @@
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="25" t="s">
-        <v>722</v>
+        <v>733</v>
       </c>
       <c r="B32" s="26" t="s">
         <v>45</v>
@@ -11325,19 +11368,19 @@
         <v>74</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>723</v>
+        <v>734</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>692</v>
+        <v>703</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>724</v>
+        <v>735</v>
       </c>
       <c r="G32" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H32" s="26" t="s">
-        <v>725</v>
+        <v>736</v>
       </c>
       <c r="I32" s="26" t="s">
         <v>79</v>
@@ -11355,7 +11398,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="25" t="s">
-        <v>726</v>
+        <v>737</v>
       </c>
       <c r="B33" s="26" t="s">
         <v>45</v>
@@ -11364,25 +11407,25 @@
         <v>74</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>727</v>
+        <v>738</v>
       </c>
       <c r="E33" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>728</v>
+        <v>739</v>
       </c>
       <c r="G33" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H33" s="26" t="s">
-        <v>729</v>
+        <v>740</v>
       </c>
       <c r="I33" s="26" t="s">
         <v>22</v>
       </c>
       <c r="J33" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K33" s="26" t="s">
         <v>29</v>
@@ -11394,7 +11437,7 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="25" t="s">
-        <v>730</v>
+        <v>741</v>
       </c>
       <c r="B34" s="26" t="s">
         <v>45</v>
@@ -11403,19 +11446,19 @@
         <v>74</v>
       </c>
       <c r="D34" s="27" t="s">
-        <v>731</v>
+        <v>742</v>
       </c>
       <c r="E34" s="26" t="s">
-        <v>732</v>
+        <v>743</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>733</v>
+        <v>744</v>
       </c>
       <c r="G34" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H34" s="26" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="I34" s="26" t="s">
         <v>79</v>
@@ -11433,7 +11476,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="25" t="s">
-        <v>735</v>
+        <v>746</v>
       </c>
       <c r="B35" s="26" t="s">
         <v>45</v>
@@ -11442,19 +11485,19 @@
         <v>74</v>
       </c>
       <c r="D35" s="27" t="s">
-        <v>736</v>
+        <v>747</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>737</v>
+        <v>748</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>738</v>
+        <v>749</v>
       </c>
       <c r="G35" s="26" t="s">
-        <v>739</v>
+        <v>750</v>
       </c>
       <c r="H35" s="26" t="s">
-        <v>740</v>
+        <v>751</v>
       </c>
       <c r="I35" s="26" t="s">
         <v>86</v>
@@ -11469,33 +11512,33 @@
         <v>12</v>
       </c>
       <c r="M35" s="26" t="s">
-        <v>741</v>
+        <v>752</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="25" t="s">
-        <v>742</v>
+        <v>753</v>
       </c>
       <c r="B36" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>743</v>
+        <v>754</v>
       </c>
       <c r="D36" s="27" t="s">
-        <v>744</v>
+        <v>755</v>
       </c>
       <c r="E36" s="26" t="s">
-        <v>745</v>
+        <v>756</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>746</v>
+        <v>757</v>
       </c>
       <c r="G36" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H36" s="26" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="I36" s="26" t="s">
         <v>102</v>
@@ -11513,28 +11556,28 @@
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="25" t="s">
-        <v>747</v>
+        <v>758</v>
       </c>
       <c r="B37" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>743</v>
+        <v>754</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>748</v>
+        <v>759</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>692</v>
+        <v>703</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>749</v>
+        <v>760</v>
       </c>
       <c r="G37" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H37" s="26" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="I37" s="26" t="s">
         <v>102</v>
@@ -11552,19 +11595,19 @@
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="25" t="s">
-        <v>750</v>
+        <v>761</v>
       </c>
       <c r="B38" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>751</v>
+        <v>762</v>
       </c>
       <c r="D38" s="27" t="s">
-        <v>752</v>
+        <v>763</v>
       </c>
       <c r="E38" s="26" t="s">
-        <v>745</v>
+        <v>756</v>
       </c>
       <c r="F38" s="26" t="s">
         <v>16</v>
@@ -11573,7 +11616,7 @@
         <v>100</v>
       </c>
       <c r="H38" s="26" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="I38" s="26" t="s">
         <v>102</v>
@@ -11591,28 +11634,28 @@
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="25" t="s">
-        <v>753</v>
+        <v>764</v>
       </c>
       <c r="B39" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>751</v>
+        <v>762</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>754</v>
+        <v>765</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>755</v>
+        <v>766</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>756</v>
+        <v>767</v>
       </c>
       <c r="G39" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H39" s="26" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="I39" s="26" t="s">
         <v>102</v>
@@ -11630,28 +11673,28 @@
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="25" t="s">
-        <v>757</v>
+        <v>768</v>
       </c>
       <c r="B40" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>758</v>
+        <v>769</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>759</v>
+        <v>770</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>692</v>
+        <v>703</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>760</v>
+        <v>771</v>
       </c>
       <c r="G40" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H40" s="26" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="I40" s="26" t="s">
         <v>102</v>
@@ -11669,28 +11712,28 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="25" t="s">
-        <v>761</v>
+        <v>772</v>
       </c>
       <c r="B41" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>758</v>
+        <v>769</v>
       </c>
       <c r="D41" s="27" t="s">
-        <v>762</v>
+        <v>773</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>745</v>
+        <v>756</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>763</v>
+        <v>774</v>
       </c>
       <c r="G41" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H41" s="26" t="s">
-        <v>638</v>
+        <v>649</v>
       </c>
       <c r="I41" s="26" t="s">
         <v>86</v>
@@ -11705,27 +11748,27 @@
         <v>14</v>
       </c>
       <c r="M41" s="26" t="s">
-        <v>764</v>
+        <v>775</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="25" t="s">
-        <v>765</v>
+        <v>776</v>
       </c>
       <c r="B42" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>766</v>
+        <v>777</v>
       </c>
       <c r="D42" s="27" t="s">
-        <v>767</v>
+        <v>778</v>
       </c>
       <c r="E42" s="26" t="s">
-        <v>768</v>
+        <v>779</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>769</v>
+        <v>780</v>
       </c>
       <c r="G42" s="26" t="s">
         <v>100</v>
@@ -11746,24 +11789,24 @@
         <v>14</v>
       </c>
       <c r="M42" s="26" t="s">
-        <v>712</v>
+        <v>723</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="25" t="s">
-        <v>770</v>
+        <v>781</v>
       </c>
       <c r="B43" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>771</v>
+        <v>782</v>
       </c>
       <c r="D43" s="27" t="s">
-        <v>772</v>
+        <v>783</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>773</v>
+        <v>784</v>
       </c>
       <c r="F43" s="26" t="s">
         <v>124</v>
@@ -11787,27 +11830,27 @@
         <v>20</v>
       </c>
       <c r="M43" s="26" t="s">
-        <v>774</v>
+        <v>785</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="25" t="s">
-        <v>775</v>
+        <v>786</v>
       </c>
       <c r="B44" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>771</v>
+        <v>782</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>776</v>
+        <v>787</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>777</v>
+        <v>788</v>
       </c>
       <c r="G44" s="26" t="s">
         <v>100</v>
@@ -11828,12 +11871,12 @@
         <v>14</v>
       </c>
       <c r="M44" s="26" t="s">
-        <v>778</v>
+        <v>789</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="25" t="s">
-        <v>779</v>
+        <v>790</v>
       </c>
       <c r="B45" s="26" t="s">
         <v>56</v>
@@ -11842,13 +11885,13 @@
         <v>54</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>780</v>
+        <v>791</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>781</v>
+        <v>792</v>
       </c>
       <c r="G45" s="26" t="s">
         <v>140</v>
@@ -11872,34 +11915,34 @@
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="25" t="s">
-        <v>782</v>
+        <v>793</v>
       </c>
       <c r="B46" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>783</v>
+        <v>794</v>
       </c>
       <c r="E46" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>784</v>
+        <v>795</v>
       </c>
       <c r="G46" s="26" t="s">
         <v>148</v>
       </c>
       <c r="H46" s="26" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="I46" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J46" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K46" s="26" t="s">
         <v>29</v>
@@ -11911,31 +11954,31 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="25" t="s">
-        <v>785</v>
+        <v>796</v>
       </c>
       <c r="B47" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>786</v>
+        <v>797</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>787</v>
+        <v>798</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>788</v>
+        <v>799</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>789</v>
+        <v>800</v>
       </c>
       <c r="G47" s="26" t="s">
-        <v>608</v>
+        <v>619</v>
       </c>
       <c r="H47" s="26" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="I47" s="26" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="J47" s="26" t="s">
         <v>124</v>
@@ -11947,27 +11990,27 @@
         <v>14</v>
       </c>
       <c r="M47" s="26" t="s">
-        <v>790</v>
+        <v>801</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="25" t="s">
-        <v>791</v>
+        <v>802</v>
       </c>
       <c r="B48" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="D48" s="27" t="s">
-        <v>792</v>
+        <v>803</v>
       </c>
       <c r="E48" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F48" s="26" t="s">
-        <v>793</v>
+        <v>804</v>
       </c>
       <c r="G48" s="26" t="s">
         <v>78</v>
@@ -11988,27 +12031,27 @@
         <v>12</v>
       </c>
       <c r="M48" s="26" t="s">
-        <v>794</v>
+        <v>805</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="25" t="s">
-        <v>795</v>
+        <v>806</v>
       </c>
       <c r="B49" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>796</v>
+        <v>807</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>797</v>
+        <v>808</v>
       </c>
       <c r="E49" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F49" s="26" t="s">
-        <v>798</v>
+        <v>809</v>
       </c>
       <c r="G49" s="26" t="s">
         <v>140</v>
@@ -12032,22 +12075,22 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="25" t="s">
-        <v>799</v>
+        <v>810</v>
       </c>
       <c r="B50" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>796</v>
+        <v>807</v>
       </c>
       <c r="D50" s="27" t="s">
-        <v>800</v>
+        <v>811</v>
       </c>
       <c r="E50" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F50" s="26" t="s">
-        <v>801</v>
+        <v>812</v>
       </c>
       <c r="G50" s="26" t="s">
         <v>140</v>
@@ -12071,19 +12114,19 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="25" t="s">
-        <v>802</v>
+        <v>813</v>
       </c>
       <c r="B51" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>796</v>
+        <v>807</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>803</v>
+        <v>814</v>
       </c>
       <c r="E51" s="26" t="s">
-        <v>707</v>
+        <v>718</v>
       </c>
       <c r="F51" s="26" t="s">
         <v>124</v>
@@ -12110,19 +12153,19 @@
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="25" t="s">
-        <v>804</v>
+        <v>815</v>
       </c>
       <c r="B52" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>805</v>
+        <v>816</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>806</v>
+        <v>817</v>
       </c>
       <c r="E52" s="26" t="s">
-        <v>807</v>
+        <v>818</v>
       </c>
       <c r="F52" s="26" t="s">
         <v>124</v>
@@ -12146,27 +12189,27 @@
         <v>20</v>
       </c>
       <c r="M52" s="26" t="s">
-        <v>808</v>
+        <v>819</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="25" t="s">
-        <v>809</v>
+        <v>820</v>
       </c>
       <c r="B53" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>810</v>
+        <v>821</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>811</v>
+        <v>822</v>
       </c>
       <c r="F53" s="26" t="s">
-        <v>812</v>
+        <v>823</v>
       </c>
       <c r="G53" s="26" t="s">
         <v>148</v>
@@ -12190,34 +12233,34 @@
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="25" t="s">
-        <v>813</v>
+        <v>824</v>
       </c>
       <c r="B54" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C54" s="26" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D54" s="27" t="s">
-        <v>814</v>
+        <v>825</v>
       </c>
       <c r="E54" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F54" s="26" t="s">
-        <v>815</v>
+        <v>826</v>
       </c>
       <c r="G54" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H54" s="26" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="I54" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J54" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K54" s="26" t="s">
         <v>29</v>
@@ -12229,34 +12272,34 @@
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="25" t="s">
-        <v>816</v>
+        <v>827</v>
       </c>
       <c r="B55" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="D55" s="27" t="s">
-        <v>817</v>
+        <v>828</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>818</v>
+        <v>829</v>
       </c>
       <c r="F55" s="26" t="s">
-        <v>819</v>
+        <v>830</v>
       </c>
       <c r="G55" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H55" s="26" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="I55" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J55" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K55" s="26" t="s">
         <v>31</v>
@@ -12265,27 +12308,27 @@
         <v>18</v>
       </c>
       <c r="M55" s="26" t="s">
-        <v>820</v>
+        <v>831</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="25" t="s">
-        <v>821</v>
+        <v>832</v>
       </c>
       <c r="B56" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D56" s="27" t="s">
-        <v>822</v>
+        <v>833</v>
       </c>
       <c r="E56" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F56" s="26" t="s">
-        <v>823</v>
+        <v>834</v>
       </c>
       <c r="G56" s="26" t="s">
         <v>148</v>
@@ -12309,22 +12352,22 @@
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="25" t="s">
-        <v>824</v>
+        <v>835</v>
       </c>
       <c r="B57" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>825</v>
+        <v>836</v>
       </c>
       <c r="E57" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F57" s="26" t="s">
-        <v>826</v>
+        <v>837</v>
       </c>
       <c r="G57" s="26" t="s">
         <v>148</v>
@@ -12348,22 +12391,22 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="25" t="s">
-        <v>827</v>
+        <v>838</v>
       </c>
       <c r="B58" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>828</v>
+        <v>839</v>
       </c>
       <c r="E58" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F58" s="26" t="s">
-        <v>829</v>
+        <v>840</v>
       </c>
       <c r="G58" s="26" t="s">
         <v>78</v>
@@ -12387,22 +12430,22 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="25" t="s">
-        <v>830</v>
+        <v>841</v>
       </c>
       <c r="B59" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="D59" s="27" t="s">
-        <v>831</v>
+        <v>842</v>
       </c>
       <c r="E59" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F59" s="26" t="s">
-        <v>832</v>
+        <v>843</v>
       </c>
       <c r="G59" s="26" t="s">
         <v>78</v>
@@ -12414,7 +12457,7 @@
         <v>22</v>
       </c>
       <c r="J59" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K59" s="26" t="s">
         <v>29</v>
@@ -12426,28 +12469,28 @@
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="25" t="s">
-        <v>833</v>
+        <v>844</v>
       </c>
       <c r="B60" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C60" s="26" t="s">
-        <v>834</v>
+        <v>845</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>835</v>
+        <v>846</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F60" s="26" t="s">
-        <v>836</v>
+        <v>847</v>
       </c>
       <c r="G60" s="26" t="s">
-        <v>837</v>
+        <v>848</v>
       </c>
       <c r="H60" s="26" t="s">
-        <v>838</v>
+        <v>849</v>
       </c>
       <c r="I60" s="26" t="s">
         <v>79</v>
@@ -12462,33 +12505,33 @@
         <v>14</v>
       </c>
       <c r="M60" s="26" t="s">
-        <v>839</v>
+        <v>850</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="25" t="s">
-        <v>840</v>
+        <v>851</v>
       </c>
       <c r="B61" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>841</v>
+        <v>852</v>
       </c>
       <c r="D61" s="27" t="s">
-        <v>842</v>
+        <v>853</v>
       </c>
       <c r="E61" s="26" t="s">
-        <v>745</v>
+        <v>756</v>
       </c>
       <c r="F61" s="26" t="s">
-        <v>843</v>
+        <v>854</v>
       </c>
       <c r="G61" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H61" s="26" t="s">
-        <v>844</v>
+        <v>855</v>
       </c>
       <c r="I61" s="26" t="s">
         <v>102</v>
@@ -12506,28 +12549,28 @@
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="25" t="s">
-        <v>845</v>
+        <v>856</v>
       </c>
       <c r="B62" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C62" s="26" t="s">
-        <v>751</v>
+        <v>762</v>
       </c>
       <c r="D62" s="27" t="s">
-        <v>846</v>
+        <v>857</v>
       </c>
       <c r="E62" s="26" t="s">
-        <v>847</v>
+        <v>858</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>848</v>
+        <v>859</v>
       </c>
       <c r="G62" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H62" s="26" t="s">
-        <v>622</v>
+        <v>633</v>
       </c>
       <c r="I62" s="26" t="s">
         <v>102</v>
@@ -12542,27 +12585,27 @@
         <v>20</v>
       </c>
       <c r="M62" s="26" t="s">
-        <v>849</v>
+        <v>860</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="25" t="s">
-        <v>850</v>
+        <v>861</v>
       </c>
       <c r="B63" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C63" s="26" t="s">
-        <v>851</v>
+        <v>862</v>
       </c>
       <c r="D63" s="27" t="s">
-        <v>852</v>
+        <v>863</v>
       </c>
       <c r="E63" s="26" t="s">
-        <v>745</v>
+        <v>756</v>
       </c>
       <c r="F63" s="26" t="s">
-        <v>853</v>
+        <v>864</v>
       </c>
       <c r="G63" s="26" t="s">
         <v>78</v>
@@ -12586,22 +12629,22 @@
     </row>
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="25" t="s">
-        <v>854</v>
+        <v>865</v>
       </c>
       <c r="B64" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C64" s="26" t="s">
-        <v>855</v>
+        <v>866</v>
       </c>
       <c r="D64" s="27" t="s">
-        <v>856</v>
+        <v>867</v>
       </c>
       <c r="E64" s="26" t="s">
-        <v>857</v>
+        <v>868</v>
       </c>
       <c r="F64" s="26" t="s">
-        <v>717</v>
+        <v>728</v>
       </c>
       <c r="G64" s="26" t="s">
         <v>100</v>
@@ -12625,22 +12668,22 @@
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="25" t="s">
-        <v>858</v>
+        <v>869</v>
       </c>
       <c r="B65" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>859</v>
+        <v>870</v>
       </c>
       <c r="D65" s="27" t="s">
-        <v>860</v>
+        <v>871</v>
       </c>
       <c r="E65" s="26" t="s">
-        <v>861</v>
+        <v>872</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>862</v>
+        <v>873</v>
       </c>
       <c r="G65" s="26" t="s">
         <v>100</v>
@@ -12664,19 +12707,19 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="25" t="s">
-        <v>863</v>
+        <v>874</v>
       </c>
       <c r="B66" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C66" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D66" s="27" t="s">
-        <v>864</v>
+        <v>875</v>
       </c>
       <c r="E66" s="26" t="s">
-        <v>865</v>
+        <v>876</v>
       </c>
       <c r="F66" s="26" t="s">
         <v>124</v>
@@ -12703,7 +12746,7 @@
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="25" t="s">
-        <v>866</v>
+        <v>877</v>
       </c>
       <c r="B67" s="26" t="s">
         <v>58</v>
@@ -12712,13 +12755,13 @@
         <v>127</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>867</v>
+        <v>878</v>
       </c>
       <c r="E67" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>868</v>
+        <v>879</v>
       </c>
       <c r="G67" s="26" t="s">
         <v>100</v>
@@ -12739,12 +12782,12 @@
         <v>14</v>
       </c>
       <c r="M67" s="26" t="s">
-        <v>869</v>
+        <v>880</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="25" t="s">
-        <v>870</v>
+        <v>881</v>
       </c>
       <c r="B68" s="26" t="s">
         <v>58</v>
@@ -12753,13 +12796,13 @@
         <v>127</v>
       </c>
       <c r="D68" s="27" t="s">
-        <v>871</v>
+        <v>882</v>
       </c>
       <c r="E68" s="26" t="s">
-        <v>654</v>
+        <v>665</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>872</v>
+        <v>883</v>
       </c>
       <c r="G68" s="26" t="s">
         <v>100</v>
@@ -12783,34 +12826,34 @@
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="25" t="s">
-        <v>873</v>
+        <v>884</v>
       </c>
       <c r="B69" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="D69" s="27" t="s">
-        <v>874</v>
+        <v>885</v>
       </c>
       <c r="E69" s="26" t="s">
-        <v>875</v>
+        <v>886</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>876</v>
+        <v>887</v>
       </c>
       <c r="G69" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H69" s="26" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="I69" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J69" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K69" s="26" t="s">
         <v>29</v>
@@ -12822,28 +12865,28 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="25" t="s">
-        <v>877</v>
+        <v>888</v>
       </c>
       <c r="B70" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C70" s="26" t="s">
-        <v>482</v>
+        <v>493</v>
       </c>
       <c r="D70" s="27" t="s">
-        <v>878</v>
+        <v>889</v>
       </c>
       <c r="E70" s="26" t="s">
-        <v>692</v>
+        <v>703</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>879</v>
+        <v>890</v>
       </c>
       <c r="G70" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H70" s="26" t="s">
-        <v>880</v>
+        <v>891</v>
       </c>
       <c r="I70" s="26" t="s">
         <v>86</v>
@@ -12861,22 +12904,22 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="25" t="s">
-        <v>881</v>
+        <v>892</v>
       </c>
       <c r="B71" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C71" s="26" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>882</v>
+        <v>893</v>
       </c>
       <c r="E71" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>883</v>
+        <v>894</v>
       </c>
       <c r="G71" s="26" t="s">
         <v>78</v>
@@ -12888,7 +12931,7 @@
         <v>22</v>
       </c>
       <c r="J71" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K71" s="26" t="s">
         <v>29</v>
@@ -12900,22 +12943,22 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="25" t="s">
-        <v>884</v>
+        <v>895</v>
       </c>
       <c r="B72" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C72" s="26" t="s">
-        <v>461</v>
+        <v>472</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>885</v>
+        <v>896</v>
       </c>
       <c r="E72" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>886</v>
+        <v>897</v>
       </c>
       <c r="G72" s="26" t="s">
         <v>78</v>
@@ -12939,22 +12982,22 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="25" t="s">
-        <v>887</v>
+        <v>898</v>
       </c>
       <c r="B73" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C73" s="26" t="s">
-        <v>888</v>
+        <v>899</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>889</v>
+        <v>900</v>
       </c>
       <c r="E73" s="26" t="s">
-        <v>890</v>
+        <v>901</v>
       </c>
       <c r="F73" s="26" t="s">
-        <v>891</v>
+        <v>902</v>
       </c>
       <c r="G73" s="26" t="s">
         <v>78</v>
@@ -12978,34 +13021,34 @@
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="25" t="s">
-        <v>892</v>
+        <v>903</v>
       </c>
       <c r="B74" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C74" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D74" s="27" t="s">
-        <v>893</v>
+        <v>904</v>
       </c>
       <c r="E74" s="26" t="s">
-        <v>894</v>
+        <v>905</v>
       </c>
       <c r="F74" s="26" t="s">
-        <v>895</v>
+        <v>906</v>
       </c>
       <c r="G74" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H74" s="26" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="I74" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J74" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K74" s="26" t="s">
         <v>29</v>
@@ -13017,25 +13060,25 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="25" t="s">
-        <v>896</v>
+        <v>907</v>
       </c>
       <c r="B75" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C75" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D75" s="27" t="s">
-        <v>897</v>
+        <v>908</v>
       </c>
       <c r="E75" s="26" t="s">
-        <v>898</v>
+        <v>909</v>
       </c>
       <c r="F75" s="26" t="s">
-        <v>819</v>
+        <v>830</v>
       </c>
       <c r="G75" s="26" t="s">
-        <v>899</v>
+        <v>910</v>
       </c>
       <c r="H75" s="26" t="s">
         <v>85</v>
@@ -13056,22 +13099,22 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="25" t="s">
-        <v>900</v>
+        <v>911</v>
       </c>
       <c r="B76" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C76" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D76" s="27" t="s">
-        <v>901</v>
+        <v>912</v>
       </c>
       <c r="E76" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>902</v>
+        <v>913</v>
       </c>
       <c r="G76" s="26" t="s">
         <v>78</v>
@@ -13095,28 +13138,28 @@
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="25" t="s">
-        <v>903</v>
+        <v>914</v>
       </c>
       <c r="B77" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C77" s="26" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="D77" s="27" t="s">
-        <v>905</v>
+        <v>916</v>
       </c>
       <c r="E77" s="26" t="s">
-        <v>692</v>
+        <v>703</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>906</v>
+        <v>917</v>
       </c>
       <c r="G77" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H77" s="26" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="I77" s="26" t="s">
         <v>102</v>
@@ -13134,22 +13177,22 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="25" t="s">
-        <v>907</v>
+        <v>918</v>
       </c>
       <c r="B78" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C78" s="26" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="D78" s="27" t="s">
-        <v>908</v>
+        <v>919</v>
       </c>
       <c r="E78" s="26" t="s">
-        <v>909</v>
+        <v>920</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>910</v>
+        <v>921</v>
       </c>
       <c r="G78" s="26" t="s">
         <v>78</v>
@@ -13161,7 +13204,7 @@
         <v>22</v>
       </c>
       <c r="J78" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K78" s="26" t="s">
         <v>29</v>
@@ -13170,33 +13213,33 @@
         <v>22</v>
       </c>
       <c r="M78" s="26" t="s">
-        <v>911</v>
+        <v>922</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="25" t="s">
-        <v>912</v>
+        <v>923</v>
       </c>
       <c r="B79" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C79" s="26" t="s">
-        <v>904</v>
+        <v>915</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>913</v>
+        <v>924</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>914</v>
+        <v>925</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>915</v>
+        <v>926</v>
       </c>
       <c r="G79" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H79" s="26" t="s">
-        <v>456</v>
+        <v>467</v>
       </c>
       <c r="I79" s="26" t="s">
         <v>102</v>
@@ -13214,22 +13257,22 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="25" t="s">
-        <v>916</v>
+        <v>927</v>
       </c>
       <c r="B80" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C80" s="26" t="s">
-        <v>917</v>
+        <v>928</v>
       </c>
       <c r="D80" s="27" t="s">
-        <v>918</v>
+        <v>929</v>
       </c>
       <c r="E80" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F80" s="26" t="s">
-        <v>919</v>
+        <v>930</v>
       </c>
       <c r="G80" s="26" t="s">
         <v>78</v>
@@ -13241,7 +13284,7 @@
         <v>22</v>
       </c>
       <c r="J80" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K80" s="26" t="s">
         <v>29</v>
@@ -13253,28 +13296,28 @@
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="25" t="s">
-        <v>920</v>
+        <v>931</v>
       </c>
       <c r="B81" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C81" s="26" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>921</v>
+        <v>932</v>
       </c>
       <c r="E81" s="26" t="s">
-        <v>692</v>
+        <v>703</v>
       </c>
       <c r="F81" s="26" t="s">
-        <v>922</v>
+        <v>933</v>
       </c>
       <c r="G81" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H81" s="26" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="I81" s="26" t="s">
         <v>102</v>
@@ -13292,22 +13335,22 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="25" t="s">
-        <v>923</v>
+        <v>934</v>
       </c>
       <c r="B82" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C82" s="26" t="s">
-        <v>516</v>
+        <v>527</v>
       </c>
       <c r="D82" s="27" t="s">
-        <v>924</v>
+        <v>935</v>
       </c>
       <c r="E82" s="26" t="s">
-        <v>925</v>
+        <v>936</v>
       </c>
       <c r="F82" s="26" t="s">
-        <v>926</v>
+        <v>937</v>
       </c>
       <c r="G82" s="26" t="s">
         <v>100</v>
@@ -13331,19 +13374,19 @@
     </row>
     <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="25" t="s">
-        <v>927</v>
+        <v>938</v>
       </c>
       <c r="B83" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C83" s="26" t="s">
-        <v>928</v>
+        <v>939</v>
       </c>
       <c r="D83" s="27" t="s">
-        <v>929</v>
+        <v>940</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>875</v>
+        <v>886</v>
       </c>
       <c r="F83" s="26" t="s">
         <v>16</v>
@@ -13352,13 +13395,13 @@
         <v>78</v>
       </c>
       <c r="H83" s="26" t="s">
-        <v>734</v>
+        <v>745</v>
       </c>
       <c r="I83" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J83" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K83" s="26" t="s">
         <v>31</v>
@@ -13370,19 +13413,19 @@
     </row>
     <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="25" t="s">
-        <v>930</v>
+        <v>941</v>
       </c>
       <c r="B84" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C84" s="26" t="s">
-        <v>504</v>
+        <v>515</v>
       </c>
       <c r="D84" s="27" t="s">
-        <v>931</v>
+        <v>942</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>932</v>
+        <v>943</v>
       </c>
       <c r="F84" s="26" t="s">
         <v>124</v>
@@ -13391,7 +13434,7 @@
         <v>100</v>
       </c>
       <c r="H84" s="26" t="s">
-        <v>933</v>
+        <v>944</v>
       </c>
       <c r="I84" s="26" t="s">
         <v>102</v>
@@ -13406,27 +13449,27 @@
         <v>20</v>
       </c>
       <c r="M84" s="26" t="s">
-        <v>934</v>
+        <v>945</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="25" t="s">
-        <v>935</v>
+        <v>946</v>
       </c>
       <c r="B85" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C85" s="26" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
       <c r="D85" s="27" t="s">
-        <v>936</v>
+        <v>947</v>
       </c>
       <c r="E85" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F85" s="26" t="s">
-        <v>937</v>
+        <v>948</v>
       </c>
       <c r="G85" s="26" t="s">
         <v>78</v>
@@ -13450,28 +13493,28 @@
     </row>
     <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="25" t="s">
-        <v>938</v>
+        <v>949</v>
       </c>
       <c r="B86" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C86" s="26" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="D86" s="27" t="s">
-        <v>939</v>
+        <v>950</v>
       </c>
       <c r="E86" s="26" t="s">
-        <v>940</v>
+        <v>951</v>
       </c>
       <c r="F86" s="26" t="s">
-        <v>941</v>
+        <v>952</v>
       </c>
       <c r="G86" s="26" t="s">
-        <v>942</v>
+        <v>953</v>
       </c>
       <c r="H86" s="26" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="I86" s="26" t="s">
         <v>86</v>
@@ -13489,28 +13532,28 @@
     </row>
     <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="25" t="s">
-        <v>943</v>
+        <v>954</v>
       </c>
       <c r="B87" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C87" s="26" t="s">
-        <v>405</v>
+        <v>414</v>
       </c>
       <c r="D87" s="27" t="s">
-        <v>944</v>
+        <v>955</v>
       </c>
       <c r="E87" s="26" t="s">
-        <v>945</v>
+        <v>956</v>
       </c>
       <c r="F87" s="26" t="s">
-        <v>411</v>
+        <v>420</v>
       </c>
       <c r="G87" s="26" t="s">
-        <v>946</v>
+        <v>957</v>
       </c>
       <c r="H87" s="26" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="I87" s="26" t="s">
         <v>86</v>
@@ -13525,33 +13568,33 @@
         <v>18</v>
       </c>
       <c r="M87" s="26" t="s">
-        <v>947</v>
+        <v>958</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="25" t="s">
-        <v>948</v>
+        <v>959</v>
       </c>
       <c r="B88" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C88" s="26" t="s">
-        <v>949</v>
+        <v>960</v>
       </c>
       <c r="D88" s="27" t="s">
-        <v>950</v>
+        <v>961</v>
       </c>
       <c r="E88" s="26" t="s">
-        <v>745</v>
+        <v>756</v>
       </c>
       <c r="F88" s="26" t="s">
-        <v>951</v>
+        <v>962</v>
       </c>
       <c r="G88" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H88" s="26" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="I88" s="26" t="s">
         <v>102</v>
@@ -13569,22 +13612,22 @@
     </row>
     <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="25" t="s">
-        <v>952</v>
+        <v>963</v>
       </c>
       <c r="B89" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C89" s="26" t="s">
-        <v>949</v>
+        <v>960</v>
       </c>
       <c r="D89" s="27" t="s">
-        <v>953</v>
+        <v>964</v>
       </c>
       <c r="E89" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F89" s="26" t="s">
-        <v>954</v>
+        <v>965</v>
       </c>
       <c r="G89" s="26" t="s">
         <v>78</v>
@@ -13596,7 +13639,7 @@
         <v>22</v>
       </c>
       <c r="J89" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K89" s="26" t="s">
         <v>29</v>
@@ -13608,28 +13651,28 @@
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="25" t="s">
-        <v>955</v>
+        <v>966</v>
       </c>
       <c r="B90" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C90" s="26" t="s">
-        <v>949</v>
+        <v>960</v>
       </c>
       <c r="D90" s="27" t="s">
-        <v>956</v>
+        <v>967</v>
       </c>
       <c r="E90" s="26" t="s">
-        <v>957</v>
+        <v>968</v>
       </c>
       <c r="F90" s="26" t="s">
-        <v>958</v>
+        <v>969</v>
       </c>
       <c r="G90" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H90" s="26" t="s">
-        <v>418</v>
+        <v>427</v>
       </c>
       <c r="I90" s="26" t="s">
         <v>102</v>
@@ -13647,22 +13690,22 @@
     </row>
     <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="25" t="s">
-        <v>959</v>
+        <v>970</v>
       </c>
       <c r="B91" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>949</v>
+        <v>960</v>
       </c>
       <c r="D91" s="27" t="s">
-        <v>960</v>
+        <v>971</v>
       </c>
       <c r="E91" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F91" s="26" t="s">
-        <v>961</v>
+        <v>972</v>
       </c>
       <c r="G91" s="26" t="s">
         <v>78</v>
@@ -13674,7 +13717,7 @@
         <v>22</v>
       </c>
       <c r="J91" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K91" s="26" t="s">
         <v>29</v>
@@ -13683,39 +13726,39 @@
         <v>22</v>
       </c>
       <c r="M91" s="26" t="s">
-        <v>962</v>
+        <v>973</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="25" t="s">
-        <v>963</v>
+        <v>974</v>
       </c>
       <c r="B92" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C92" s="26" t="s">
-        <v>964</v>
+        <v>975</v>
       </c>
       <c r="D92" s="27" t="s">
-        <v>965</v>
+        <v>976</v>
       </c>
       <c r="E92" s="26" t="s">
-        <v>966</v>
+        <v>977</v>
       </c>
       <c r="F92" s="26" t="s">
-        <v>967</v>
+        <v>978</v>
       </c>
       <c r="G92" s="26" t="s">
         <v>148</v>
       </c>
       <c r="H92" s="26" t="s">
-        <v>968</v>
+        <v>979</v>
       </c>
       <c r="I92" s="26" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="J92" s="26" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="K92" s="26" t="s">
         <v>29</v>
@@ -13727,19 +13770,19 @@
     </row>
     <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="25" t="s">
-        <v>969</v>
+        <v>980</v>
       </c>
       <c r="B93" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C93" s="26" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="D93" s="27" t="s">
-        <v>970</v>
+        <v>981</v>
       </c>
       <c r="E93" s="26" t="s">
-        <v>971</v>
+        <v>982</v>
       </c>
       <c r="F93" s="26" t="s">
         <v>124</v>
@@ -13763,27 +13806,27 @@
         <v>20</v>
       </c>
       <c r="M93" s="26" t="s">
-        <v>972</v>
+        <v>983</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="25" t="s">
-        <v>973</v>
+        <v>984</v>
       </c>
       <c r="B94" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C94" s="26" t="s">
-        <v>437</v>
+        <v>448</v>
       </c>
       <c r="D94" s="27" t="s">
-        <v>974</v>
+        <v>985</v>
       </c>
       <c r="E94" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F94" s="26" t="s">
-        <v>975</v>
+        <v>986</v>
       </c>
       <c r="G94" s="26" t="s">
         <v>140</v>
@@ -13804,27 +13847,27 @@
         <v>14</v>
       </c>
       <c r="M94" s="26" t="s">
-        <v>976</v>
+        <v>987</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="25" t="s">
-        <v>977</v>
+        <v>988</v>
       </c>
       <c r="B95" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C95" s="26" t="s">
-        <v>978</v>
+        <v>989</v>
       </c>
       <c r="D95" s="27" t="s">
-        <v>979</v>
+        <v>990</v>
       </c>
       <c r="E95" s="26" t="s">
-        <v>980</v>
+        <v>991</v>
       </c>
       <c r="F95" s="26" t="s">
-        <v>981</v>
+        <v>992</v>
       </c>
       <c r="G95" s="26" t="s">
         <v>140</v>
@@ -13848,19 +13891,19 @@
     </row>
     <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="25" t="s">
-        <v>982</v>
+        <v>993</v>
       </c>
       <c r="B96" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C96" s="26" t="s">
-        <v>978</v>
+        <v>989</v>
       </c>
       <c r="D96" s="27" t="s">
-        <v>983</v>
+        <v>994</v>
       </c>
       <c r="E96" s="26" t="s">
-        <v>971</v>
+        <v>982</v>
       </c>
       <c r="F96" s="26" t="s">
         <v>124</v>
@@ -13887,22 +13930,22 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="25" t="s">
-        <v>984</v>
+        <v>995</v>
       </c>
       <c r="B97" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C97" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D97" s="27" t="s">
-        <v>985</v>
+        <v>996</v>
       </c>
       <c r="E97" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F97" s="26" t="s">
-        <v>986</v>
+        <v>997</v>
       </c>
       <c r="G97" s="26" t="s">
         <v>140</v>
@@ -13923,27 +13966,27 @@
         <v>14</v>
       </c>
       <c r="M97" s="26" t="s">
-        <v>987</v>
+        <v>998</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="25" t="s">
-        <v>988</v>
+        <v>999</v>
       </c>
       <c r="B98" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C98" s="26" t="s">
-        <v>917</v>
+        <v>928</v>
       </c>
       <c r="D98" s="27" t="s">
-        <v>989</v>
+        <v>1000</v>
       </c>
       <c r="E98" s="26" t="s">
-        <v>990</v>
+        <v>1001</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>991</v>
+        <v>1002</v>
       </c>
       <c r="G98" s="26" t="s">
         <v>100</v>
@@ -13955,7 +13998,7 @@
         <v>22</v>
       </c>
       <c r="J98" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K98" s="26" t="s">
         <v>29</v>
@@ -13967,22 +14010,22 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="25" t="s">
-        <v>992</v>
+        <v>1003</v>
       </c>
       <c r="B99" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C99" s="26" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D99" s="27" t="s">
-        <v>993</v>
+        <v>1004</v>
       </c>
       <c r="E99" s="26" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="F99" s="26" t="s">
-        <v>994</v>
+        <v>1005</v>
       </c>
       <c r="G99" s="26" t="s">
         <v>140</v>
@@ -13994,7 +14037,7 @@
         <v>22</v>
       </c>
       <c r="J99" s="26" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K99" s="26" t="s">
         <v>29</v>
@@ -14006,22 +14049,22 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="25" t="s">
-        <v>995</v>
+        <v>1006</v>
       </c>
       <c r="B100" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C100" s="26" t="s">
-        <v>996</v>
+        <v>1007</v>
       </c>
       <c r="D100" s="27" t="s">
-        <v>997</v>
+        <v>1008</v>
       </c>
       <c r="E100" s="26" t="s">
-        <v>453</v>
+        <v>464</v>
       </c>
       <c r="F100" s="26" t="s">
-        <v>998</v>
+        <v>1009</v>
       </c>
       <c r="G100" s="26" t="s">
         <v>100</v>
@@ -14045,28 +14088,28 @@
     </row>
     <row r="101" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="25" t="s">
-        <v>999</v>
+        <v>1010</v>
       </c>
       <c r="B101" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>520</v>
+        <v>531</v>
       </c>
       <c r="D101" s="27" t="s">
-        <v>1000</v>
+        <v>1011</v>
       </c>
       <c r="E101" s="26" t="s">
-        <v>1001</v>
+        <v>1012</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>1002</v>
+        <v>1013</v>
       </c>
       <c r="G101" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H101" s="26" t="s">
-        <v>524</v>
+        <v>535</v>
       </c>
       <c r="I101" s="26" t="s">
         <v>79</v>
@@ -14081,7 +14124,7 @@
         <v>14</v>
       </c>
       <c r="M101" s="26" t="s">
-        <v>1003</v>
+        <v>1014</v>
       </c>
     </row>
   </sheetData>
@@ -14153,12 +14196,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1004</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1005</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14174,10 +14217,10 @@
         <v>65</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>1006</v>
+        <v>1017</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>1007</v>
+        <v>1018</v>
       </c>
       <c r="D5" s="24" t="s">
         <v>67</v>
@@ -14191,56 +14234,56 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>1008</v>
+        <v>1019</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>1009</v>
+        <v>1020</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>1010</v>
+        <v>1021</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>1011</v>
+        <v>1022</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>1012</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>1013</v>
+        <v>1024</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>1014</v>
+        <v>1025</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>1015</v>
+        <v>1026</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>1016</v>
+        <v>1027</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>1017</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>1013</v>
+        <v>1024</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>1018</v>
+        <v>1029</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>1019</v>
+        <v>1030</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>1020</v>
+        <v>1031</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>29</v>
@@ -14249,33 +14292,33 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>1021</v>
+        <v>1032</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>1022</v>
+        <v>1033</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>1023</v>
+        <v>1034</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>1024</v>
+        <v>1035</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>1025</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>1026</v>
+        <v>1037</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>1027</v>
+        <v>1038</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>1028</v>
+        <v>1039</v>
       </c>
       <c r="D10" s="26" t="s">
         <v>22</v>
@@ -14284,61 +14327,61 @@
         <v>27</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>1029</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>1030</v>
+        <v>1041</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>1031</v>
+        <v>1042</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>1032</v>
+        <v>1043</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>1033</v>
+        <v>1044</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>1034</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>1030</v>
+        <v>1041</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>1035</v>
+        <v>1046</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>1036</v>
+        <v>1047</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>1037</v>
+        <v>1048</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1038</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>1030</v>
+        <v>1041</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>1039</v>
+        <v>1050</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>1040</v>
+        <v>1051</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>1041</v>
+        <v>1052</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>31</v>
@@ -14347,36 +14390,36 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>1030</v>
+        <v>1041</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>1042</v>
+        <v>1053</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>1043</v>
+        <v>1054</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>1044</v>
+        <v>1055</v>
       </c>
       <c r="E14" s="26" t="s">
         <v>31</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>1045</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>1046</v>
+        <v>1057</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>1047</v>
+        <v>1058</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>1048</v>
+        <v>1059</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>1049</v>
+        <v>1060</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>27</v>
@@ -14385,16 +14428,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>1046</v>
+        <v>1057</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>1050</v>
+        <v>1061</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>1051</v>
+        <v>1062</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>1052</v>
+        <v>1063</v>
       </c>
       <c r="E16" s="26" t="s">
         <v>31</v>
@@ -14403,16 +14446,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>1046</v>
+        <v>1057</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>1053</v>
+        <v>1064</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>1054</v>
+        <v>1065</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>1055</v>
+        <v>1066</v>
       </c>
       <c r="E17" s="26" t="s">
         <v>33</v>
@@ -14456,12 +14499,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1056</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1057</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14477,19 +14520,19 @@
         <v>67</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>1058</v>
+        <v>1069</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>1059</v>
+        <v>1070</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>1060</v>
+        <v>1071</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>1061</v>
+        <v>1072</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>1062</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14497,59 +14540,59 @@
         <v>98</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>1063</v>
+        <v>1074</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>1065</v>
+        <v>1076</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>1066</v>
+        <v>1077</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>1068</v>
+        <v>1079</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>1069</v>
+        <v>1080</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>1070</v>
+        <v>1081</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>1066</v>
+        <v>1077</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>1071</v>
+        <v>1082</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>1072</v>
+        <v>1083</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>1073</v>
+        <v>1084</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>1066</v>
+        <v>1077</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14557,279 +14600,279 @@
         <v>76</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>1074</v>
+        <v>1085</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>1075</v>
+        <v>1086</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>1066</v>
+        <v>1077</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>1076</v>
+        <v>1087</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>1077</v>
+        <v>1088</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="D10" s="26" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E10" s="29" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F10" s="26" t="s">
         <v>1078</v>
-      </c>
-      <c r="E10" s="29" t="s">
-        <v>1079</v>
-      </c>
-      <c r="F10" s="26" t="s">
-        <v>1067</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>416</v>
+        <v>425</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>1080</v>
+        <v>1091</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>1081</v>
+        <v>1092</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>1066</v>
+        <v>1077</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>1082</v>
+        <v>1093</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>1083</v>
+        <v>1094</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>1066</v>
+        <v>1077</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>537</v>
+        <v>548</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>1069</v>
+        <v>1080</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>1084</v>
+        <v>1095</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>1066</v>
+        <v>1077</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>1085</v>
+        <v>1096</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>1080</v>
+        <v>1091</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="D14" s="26" t="s">
         <v>124</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>1079</v>
+        <v>1090</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>561</v>
+        <v>572</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>562</v>
+        <v>573</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>1086</v>
+        <v>1097</v>
       </c>
       <c r="E15" s="29" t="s">
-        <v>1079</v>
+        <v>1090</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>1087</v>
+        <v>1098</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>1088</v>
+        <v>1099</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>1089</v>
+        <v>1100</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>1090</v>
+        <v>1101</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>1091</v>
+        <v>1102</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>1092</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>1093</v>
+        <v>1104</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>1080</v>
+        <v>1091</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>1094</v>
+        <v>1105</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>1095</v>
+        <v>1106</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>1079</v>
+        <v>1090</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>1096</v>
+        <v>1107</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>1080</v>
+        <v>1091</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>1094</v>
+        <v>1105</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>1097</v>
+        <v>1108</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>1079</v>
+        <v>1090</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>1098</v>
+        <v>1109</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>1080</v>
+        <v>1091</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>1099</v>
+        <v>1110</v>
       </c>
       <c r="D19" s="26" t="s">
-        <v>1100</v>
+        <v>1111</v>
       </c>
       <c r="E19" s="29" t="s">
-        <v>1079</v>
+        <v>1090</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>1092</v>
+        <v>1103</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>1101</v>
+        <v>1112</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>1080</v>
+        <v>1091</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>1102</v>
+        <v>1113</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>1066</v>
+        <v>1077</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>1103</v>
+        <v>1114</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>1104</v>
+        <v>1115</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>1105</v>
+        <v>1116</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>1079</v>
+        <v>1090</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>1106</v>
+        <v>1117</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>1080</v>
+        <v>1091</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>1099</v>
+        <v>1110</v>
       </c>
       <c r="D22" s="26" t="s">
-        <v>1107</v>
+        <v>1118</v>
       </c>
       <c r="E22" s="29" t="s">
-        <v>1079</v>
+        <v>1090</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>1108</v>
+        <v>1119</v>
       </c>
     </row>
   </sheetData>

--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -4424,7 +4424,7 @@
       </c>
       <c r="I7" s="16" t="n">
         <f aca="false">COUNTIF(Brasil!$L$6:$L$130,H7)</f>
-        <v>63</v>
+        <v>70</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4456,7 +4456,7 @@
       </c>
       <c r="I8" s="16" t="n">
         <f aca="false">COUNTIF(Brasil!$L$6:$L$130,H8)</f>
-        <v>26</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5820,7 +5820,7 @@
         <v>27</v>
       </c>
       <c r="L21" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M21" s="26" t="s">
         <v>160</v>
@@ -5861,7 +5861,7 @@
         <v>27</v>
       </c>
       <c r="L22" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M22" s="26" t="s">
         <v>167</v>
@@ -5902,7 +5902,7 @@
         <v>27</v>
       </c>
       <c r="L23" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M23" s="26" t="s">
         <v>171</v>
@@ -5984,7 +5984,7 @@
         <v>27</v>
       </c>
       <c r="L25" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M25" s="26" t="s">
         <v>180</v>
@@ -7990,7 +7990,7 @@
         <v>27</v>
       </c>
       <c r="L75" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M75" s="26" t="s">
         <v>390</v>
@@ -8031,7 +8031,7 @@
         <v>27</v>
       </c>
       <c r="L76" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M76" s="26" t="s">
         <v>394</v>
@@ -8470,7 +8470,7 @@
         <v>27</v>
       </c>
       <c r="L87" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M87" s="26" t="s">
         <v>439</v>

--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3059" uniqueCount="1120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3060" uniqueCount="1121">
   <si>
     <t xml:space="preserve">Argus — Catálogo de Dados</t>
   </si>
@@ -2265,7 +2265,7 @@
     <t xml:space="preserve">BEA API</t>
   </si>
   <si>
-    <t xml:space="preserve">NIPA T10206 (a confirmar)</t>
+    <t xml:space="preserve">NIPA T10206</t>
   </si>
   <si>
     <t xml:space="preserve">US$ bi</t>
@@ -2400,7 +2400,7 @@
     <t xml:space="preserve">GACDFSA e equivalentes</t>
   </si>
   <si>
-    <t xml:space="preserve">Substituto gratuito do ISM</t>
+    <t xml:space="preserve">Código GACDFSA não existe no FRED (HTTP 400 na validação de 2026-10-04); localizar o código correto</t>
   </si>
   <si>
     <t xml:space="preserve">US-040</t>
@@ -2652,7 +2652,7 @@
     <t xml:space="preserve">NAR / FRED</t>
   </si>
   <si>
-    <t xml:space="preserve">FIXHAI (a confirmar)</t>
+    <t xml:space="preserve">FIXHAI</t>
   </si>
   <si>
     <t xml:space="preserve">US-061</t>
@@ -2694,7 +2694,7 @@
     <t xml:space="preserve">FRED (Z.1)</t>
   </si>
   <si>
-    <t xml:space="preserve">TNWBSHNO (a confirmar)</t>
+    <t xml:space="preserve">TNWBSHNO</t>
   </si>
   <si>
     <t xml:space="preserve">US-065</t>
@@ -2967,10 +2967,13 @@
     <t xml:space="preserve">FRED (EIA)</t>
   </si>
   <si>
-    <t xml:space="preserve">WCSSTUS1 (a confirmar)</t>
+    <t xml:space="preserve">WCSSTUS1</t>
   </si>
   <si>
     <t xml:space="preserve">Mil barris</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Código WCSSTUS1 não existe no FRED (HTTP 400 na validação de 2026-10-04); localizar o código correto</t>
   </si>
   <si>
     <t xml:space="preserve">US-088</t>
@@ -4424,7 +4427,7 @@
       </c>
       <c r="I7" s="16" t="n">
         <f aca="false">COUNTIF(Brasil!$L$6:$L$130,H7)</f>
-        <v>70</v>
+        <v>71</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4456,7 +4459,7 @@
       </c>
       <c r="I8" s="16" t="n">
         <f aca="false">COUNTIF(Brasil!$L$6:$L$130,H8)</f>
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4804,7 +4807,7 @@
       </c>
       <c r="I22" s="16" t="n">
         <f aca="false">COUNTIF(EUA!$L$6:$L$101,H22)</f>
-        <v>4</v>
+        <v>50</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4836,7 +4839,7 @@
       </c>
       <c r="I23" s="16" t="n">
         <f aca="false">COUNTIF(EUA!$L$6:$L$101,H23)</f>
-        <v>56</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4868,7 +4871,7 @@
       </c>
       <c r="I24" s="16" t="n">
         <f aca="false">COUNTIF(EUA!$L$6:$L$101,H24)</f>
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -8749,7 +8752,7 @@
         <v>27</v>
       </c>
       <c r="L94" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M94" s="26"/>
     </row>
@@ -10364,7 +10367,7 @@
         <v>29</v>
       </c>
       <c r="L6" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M6" s="26"/>
     </row>
@@ -10403,7 +10406,7 @@
         <v>29</v>
       </c>
       <c r="L7" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M7" s="26"/>
     </row>
@@ -10442,7 +10445,7 @@
         <v>29</v>
       </c>
       <c r="L8" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M8" s="26"/>
     </row>
@@ -10481,7 +10484,7 @@
         <v>29</v>
       </c>
       <c r="L9" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M9" s="26"/>
     </row>
@@ -10559,7 +10562,7 @@
         <v>29</v>
       </c>
       <c r="L11" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M11" s="26"/>
     </row>
@@ -10598,7 +10601,7 @@
         <v>29</v>
       </c>
       <c r="L12" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M12" s="26"/>
     </row>
@@ -10756,7 +10759,7 @@
         <v>29</v>
       </c>
       <c r="L16" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M16" s="26"/>
     </row>
@@ -10795,7 +10798,7 @@
         <v>29</v>
       </c>
       <c r="L17" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M17" s="26"/>
     </row>
@@ -10955,7 +10958,7 @@
         <v>29</v>
       </c>
       <c r="L21" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M21" s="26"/>
     </row>
@@ -11035,7 +11038,7 @@
         <v>29</v>
       </c>
       <c r="L23" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M23" s="26"/>
     </row>
@@ -11074,7 +11077,7 @@
         <v>29</v>
       </c>
       <c r="L24" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M24" s="26"/>
     </row>
@@ -11113,7 +11116,7 @@
         <v>29</v>
       </c>
       <c r="L25" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M25" s="26"/>
     </row>
@@ -11152,7 +11155,7 @@
         <v>29</v>
       </c>
       <c r="L26" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M26" s="26"/>
     </row>
@@ -11191,7 +11194,7 @@
         <v>29</v>
       </c>
       <c r="L27" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M27" s="26" t="s">
         <v>715</v>
@@ -11273,7 +11276,7 @@
         <v>29</v>
       </c>
       <c r="L29" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M29" s="26" t="s">
         <v>723</v>
@@ -11392,7 +11395,7 @@
         <v>29</v>
       </c>
       <c r="L32" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M32" s="26"/>
     </row>
@@ -11550,7 +11553,7 @@
         <v>29</v>
       </c>
       <c r="L36" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M36" s="26"/>
     </row>
@@ -11589,7 +11592,7 @@
         <v>29</v>
       </c>
       <c r="L37" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M37" s="26"/>
     </row>
@@ -11706,7 +11709,7 @@
         <v>29</v>
       </c>
       <c r="L40" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M40" s="26"/>
     </row>
@@ -11745,7 +11748,7 @@
         <v>29</v>
       </c>
       <c r="L41" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M41" s="26" t="s">
         <v>775</v>
@@ -11786,7 +11789,7 @@
         <v>29</v>
       </c>
       <c r="L42" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M42" s="26" t="s">
         <v>723</v>
@@ -11833,7 +11836,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="25" t="s">
         <v>786</v>
       </c>
@@ -11868,7 +11871,7 @@
         <v>29</v>
       </c>
       <c r="L44" s="26" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="M44" s="26" t="s">
         <v>789</v>
@@ -11909,7 +11912,7 @@
         <v>29</v>
       </c>
       <c r="L45" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M45" s="26"/>
     </row>
@@ -11948,7 +11951,7 @@
         <v>29</v>
       </c>
       <c r="L46" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M46" s="26"/>
     </row>
@@ -12069,7 +12072,7 @@
         <v>29</v>
       </c>
       <c r="L49" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M49" s="26"/>
     </row>
@@ -12108,7 +12111,7 @@
         <v>29</v>
       </c>
       <c r="L50" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M50" s="26"/>
     </row>
@@ -12227,7 +12230,7 @@
         <v>29</v>
       </c>
       <c r="L53" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M53" s="26"/>
     </row>
@@ -12266,7 +12269,7 @@
         <v>29</v>
       </c>
       <c r="L54" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M54" s="26"/>
     </row>
@@ -12346,7 +12349,7 @@
         <v>29</v>
       </c>
       <c r="L56" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M56" s="26"/>
     </row>
@@ -12385,7 +12388,7 @@
         <v>29</v>
       </c>
       <c r="L57" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M57" s="26"/>
     </row>
@@ -12424,7 +12427,7 @@
         <v>29</v>
       </c>
       <c r="L58" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M58" s="26"/>
     </row>
@@ -12502,7 +12505,7 @@
         <v>29</v>
       </c>
       <c r="L60" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M60" s="26" t="s">
         <v>850</v>
@@ -12543,7 +12546,7 @@
         <v>29</v>
       </c>
       <c r="L61" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M61" s="26"/>
     </row>
@@ -12623,7 +12626,7 @@
         <v>29</v>
       </c>
       <c r="L63" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M63" s="26"/>
     </row>
@@ -12779,7 +12782,7 @@
         <v>29</v>
       </c>
       <c r="L67" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M67" s="26" t="s">
         <v>880</v>
@@ -12859,7 +12862,7 @@
         <v>29</v>
       </c>
       <c r="L69" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M69" s="26"/>
     </row>
@@ -12898,7 +12901,7 @@
         <v>29</v>
       </c>
       <c r="L70" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M70" s="26"/>
     </row>
@@ -12976,7 +12979,7 @@
         <v>29</v>
       </c>
       <c r="L72" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M72" s="26"/>
     </row>
@@ -13054,7 +13057,7 @@
         <v>29</v>
       </c>
       <c r="L74" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M74" s="26"/>
     </row>
@@ -13132,7 +13135,7 @@
         <v>29</v>
       </c>
       <c r="L76" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M76" s="26"/>
     </row>
@@ -13329,7 +13332,7 @@
         <v>29</v>
       </c>
       <c r="L81" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M81" s="26"/>
     </row>
@@ -13487,7 +13490,7 @@
         <v>29</v>
       </c>
       <c r="L85" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M85" s="26"/>
     </row>
@@ -13606,7 +13609,7 @@
         <v>29</v>
       </c>
       <c r="L88" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M88" s="26"/>
     </row>
@@ -13729,7 +13732,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="25" t="s">
         <v>974</v>
       </c>
@@ -13764,13 +13767,15 @@
         <v>29</v>
       </c>
       <c r="L92" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="M92" s="26"/>
+        <v>16</v>
+      </c>
+      <c r="M92" s="26" t="s">
+        <v>980</v>
+      </c>
     </row>
     <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="25" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="B93" s="26" t="s">
         <v>60</v>
@@ -13779,10 +13784,10 @@
         <v>448</v>
       </c>
       <c r="D93" s="27" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
       <c r="E93" s="26" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F93" s="26" t="s">
         <v>124</v>
@@ -13806,12 +13811,12 @@
         <v>20</v>
       </c>
       <c r="M93" s="26" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="25" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="B94" s="26" t="s">
         <v>60</v>
@@ -13820,13 +13825,13 @@
         <v>448</v>
       </c>
       <c r="D94" s="27" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="E94" s="26" t="s">
         <v>464</v>
       </c>
       <c r="F94" s="26" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
       <c r="G94" s="26" t="s">
         <v>140</v>
@@ -13844,30 +13849,30 @@
         <v>29</v>
       </c>
       <c r="L94" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M94" s="26" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="25" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="B95" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C95" s="26" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="D95" s="27" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="E95" s="26" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
       <c r="F95" s="26" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="G95" s="26" t="s">
         <v>140</v>
@@ -13885,25 +13890,25 @@
         <v>29</v>
       </c>
       <c r="L95" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M95" s="26"/>
     </row>
     <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="25" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="B96" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C96" s="26" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="D96" s="27" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="E96" s="26" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="F96" s="26" t="s">
         <v>124</v>
@@ -13930,7 +13935,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="25" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="B97" s="26" t="s">
         <v>61</v>
@@ -13939,13 +13944,13 @@
         <v>358</v>
       </c>
       <c r="D97" s="27" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
       <c r="E97" s="26" t="s">
         <v>464</v>
       </c>
       <c r="F97" s="26" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="G97" s="26" t="s">
         <v>140</v>
@@ -13963,15 +13968,15 @@
         <v>29</v>
       </c>
       <c r="L97" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M97" s="26" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="25" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="B98" s="26" t="s">
         <v>61</v>
@@ -13980,13 +13985,13 @@
         <v>928</v>
       </c>
       <c r="D98" s="27" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="E98" s="26" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="G98" s="26" t="s">
         <v>100</v>
@@ -14010,7 +14015,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="25" t="s">
-        <v>1003</v>
+        <v>1004</v>
       </c>
       <c r="B99" s="26" t="s">
         <v>61</v>
@@ -14019,13 +14024,13 @@
         <v>358</v>
       </c>
       <c r="D99" s="27" t="s">
-        <v>1004</v>
+        <v>1005</v>
       </c>
       <c r="E99" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F99" s="26" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="G99" s="26" t="s">
         <v>140</v>
@@ -14049,22 +14054,22 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="25" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B100" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C100" s="26" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D100" s="27" t="s">
-        <v>1008</v>
+        <v>1009</v>
       </c>
       <c r="E100" s="26" t="s">
         <v>464</v>
       </c>
       <c r="F100" s="26" t="s">
-        <v>1009</v>
+        <v>1010</v>
       </c>
       <c r="G100" s="26" t="s">
         <v>100</v>
@@ -14082,13 +14087,13 @@
         <v>29</v>
       </c>
       <c r="L100" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M100" s="26"/>
     </row>
     <row r="101" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="25" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B101" s="26" t="s">
         <v>61</v>
@@ -14097,13 +14102,13 @@
         <v>531</v>
       </c>
       <c r="D101" s="27" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="E101" s="26" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="G101" s="26" t="s">
         <v>140</v>
@@ -14124,7 +14129,7 @@
         <v>14</v>
       </c>
       <c r="M101" s="26" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
     </row>
   </sheetData>
@@ -14196,12 +14201,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14217,10 +14222,10 @@
         <v>65</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="D5" s="24" t="s">
         <v>67</v>
@@ -14234,56 +14239,56 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>1019</v>
+        <v>1020</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>1020</v>
+        <v>1021</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>1021</v>
+        <v>1022</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>29</v>
@@ -14292,33 +14297,33 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>1036</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="D10" s="26" t="s">
         <v>22</v>
@@ -14327,61 +14332,61 @@
         <v>27</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>1040</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>1045</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1049</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>31</v>
@@ -14390,36 +14395,36 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="E14" s="26" t="s">
         <v>31</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>27</v>
@@ -14428,16 +14433,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="E16" s="26" t="s">
         <v>31</v>
@@ -14446,16 +14451,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="E17" s="26" t="s">
         <v>33</v>
@@ -14499,12 +14504,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1067</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1068</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14520,19 +14525,19 @@
         <v>67</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>1073</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14540,59 +14545,59 @@
         <v>98</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B7" s="26" t="s">
+        <v>1081</v>
+      </c>
+      <c r="C7" s="26" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D7" s="26" t="s">
+        <v>1082</v>
+      </c>
+      <c r="E7" s="28" t="s">
+        <v>1078</v>
+      </c>
+      <c r="F7" s="26" t="s">
         <v>1079</v>
-      </c>
-      <c r="B7" s="26" t="s">
-        <v>1080</v>
-      </c>
-      <c r="C7" s="26" t="s">
-        <v>1075</v>
-      </c>
-      <c r="D7" s="26" t="s">
-        <v>1081</v>
-      </c>
-      <c r="E7" s="28" t="s">
-        <v>1077</v>
-      </c>
-      <c r="F7" s="26" t="s">
-        <v>1078</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14600,39 +14605,39 @@
         <v>76</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14640,19 +14645,19 @@
         <v>425</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14660,19 +14665,19 @@
         <v>291</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14680,39 +14685,39 @@
         <v>548</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D14" s="26" t="s">
         <v>124</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14723,156 +14728,156 @@
         <v>573</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="E15" s="29" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B17" s="26" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C17" s="26" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D17" s="26" t="s">
+        <v>1107</v>
+      </c>
+      <c r="E17" s="29" t="s">
         <v>1091</v>
       </c>
-      <c r="C17" s="26" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D17" s="26" t="s">
-        <v>1106</v>
-      </c>
-      <c r="E17" s="29" t="s">
-        <v>1090</v>
-      </c>
       <c r="F17" s="26" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="B18" s="26" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C18" s="26" t="s">
+        <v>1106</v>
+      </c>
+      <c r="D18" s="26" t="s">
+        <v>1109</v>
+      </c>
+      <c r="E18" s="29" t="s">
         <v>1091</v>
       </c>
-      <c r="C18" s="26" t="s">
-        <v>1105</v>
-      </c>
-      <c r="D18" s="26" t="s">
-        <v>1108</v>
-      </c>
-      <c r="E18" s="29" t="s">
-        <v>1090</v>
-      </c>
       <c r="F18" s="26" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="B19" s="26" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C19" s="26" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>1112</v>
+      </c>
+      <c r="E19" s="29" t="s">
         <v>1091</v>
       </c>
-      <c r="C19" s="26" t="s">
-        <v>1110</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>1111</v>
-      </c>
-      <c r="E19" s="29" t="s">
-        <v>1090</v>
-      </c>
       <c r="F19" s="26" t="s">
-        <v>1103</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>1078</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B22" s="26" t="s">
+        <v>1092</v>
+      </c>
+      <c r="C22" s="26" t="s">
+        <v>1111</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E22" s="29" t="s">
         <v>1091</v>
       </c>
-      <c r="C22" s="26" t="s">
-        <v>1110</v>
-      </c>
-      <c r="D22" s="26" t="s">
-        <v>1118</v>
-      </c>
-      <c r="E22" s="29" t="s">
-        <v>1090</v>
-      </c>
       <c r="F22" s="26" t="s">
-        <v>1119</v>
+        <v>1120</v>
       </c>
     </row>
   </sheetData>

--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -16,10 +16,10 @@
     <sheet name="Fontes" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Brasil!$A$5:$M$130</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Brasil!$A$5:$M$131</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Central!$A$5:$F$17</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">EUA!$A$5:$M$101</definedName>
-    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Fontes!$A$5:$F$22</definedName>
+    <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Fontes!$A$5:$F$25</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3060" uniqueCount="1121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3092" uniqueCount="1136">
   <si>
     <t xml:space="preserve">Argus — Catálogo de Dados</t>
   </si>
@@ -744,6 +744,9 @@
     <t xml:space="preserve">16121</t>
   </si>
   <si>
+    <t xml:space="preserve">Há dois códigos com título EX2: 16121 ("ex2") e 27838 ("EX2"); confirmar qual é a série vigente antes da Fase 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">BR-033</t>
   </si>
   <si>
@@ -759,7 +762,22 @@
     <t xml:space="preserve">Núcleos EX3 e P55</t>
   </si>
   <si>
-    <t xml:space="preserve">Não encontrados no portal do BCB por "núcleo ex3" nem "p55" (busca de 2026-10-04); localizar no SGS</t>
+    <t xml:space="preserve">27839 / 28750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Títulos SGS: "Núcleo por exclusão - EX3" (27839) e "Núcleo Percentil 55" (28750); sondagem 2026-10-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BR-126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Núcleo ex-alimentação e energia (EX-FE)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">28751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Título SGS 28751: "Núcleo Ex-alimentação e energia (EX-FE)"; comparável ao core dos EUA</t>
   </si>
   <si>
     <t xml:space="preserve">BR-035</t>
@@ -1053,16 +1071,16 @@
     <t xml:space="preserve">Comunicados e atas (texto)</t>
   </si>
   <si>
-    <t xml:space="preserve">BCB site</t>
-  </si>
-  <si>
-    <t xml:space="preserve">API do site (não documentada) + RSS</t>
+    <t xml:space="preserve">BCB site (API Copom)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">api/servico/sitebcb/copom/comunicados · /atas</t>
   </si>
   <si>
     <t xml:space="preserve">Texto</t>
   </si>
   <si>
-    <t xml:space="preserve">Base para o agregador e, depois, análise de linguagem</t>
+    <t xml:space="preserve">API do site, não documentada; respondeu com a 281ª reunião (set/2026). Teste de contrato obrigatório</t>
   </si>
   <si>
     <t xml:space="preserve">BR-059</t>
@@ -1248,10 +1266,10 @@
     <t xml:space="preserve">Receitas e despesas do Governo Central (RTN)</t>
   </si>
   <si>
-    <t xml:space="preserve">RTN (xlsx/CKAN)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Abertura por rubrica; despesa real deflacionada</t>
+    <t xml:space="preserve">CKAN resultado-do-tesouro-nacional (XLSX série histórica)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Planilha atualizada em 2026-08-27; layout mutável, teste de contrato obrigatório</t>
   </si>
   <si>
     <t xml:space="preserve">BR-075</t>
@@ -1311,13 +1329,13 @@
     <t xml:space="preserve">ComexStat (MDIC)</t>
   </si>
   <si>
-    <t xml:space="preserve">API ComexStat</t>
+    <t xml:space="preserve">POST api-comexstat.mdic.gov.br/general</t>
   </si>
   <si>
     <t xml:space="preserve">US$ mi</t>
   </si>
   <si>
-    <t xml:space="preserve">Também semanal</t>
+    <t xml:space="preserve">Dados até 2026-08 (sondagem 2026-10-04). Também semanal</t>
   </si>
   <si>
     <t xml:space="preserve">BR-080</t>
@@ -1326,6 +1344,9 @@
     <t xml:space="preserve">Exportações por produto e destino (China, EUA, UE)</t>
   </si>
   <si>
+    <t xml:space="preserve">POST api-comexstat.mdic.gov.br/general (por NCM/país)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Exposição a China e tarifas</t>
   </si>
   <si>
@@ -1632,16 +1653,16 @@
     <t xml:space="preserve">Ibovespa</t>
   </si>
   <si>
-    <t xml:space="preserve">FMP / B3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">^BVSP</t>
+    <t xml:space="preserve">B3 (oficial) / Yahoo (alternativa)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B3 IndexCall/GetPortfolioDay IBOV · Yahoo ^BVSP</t>
   </si>
   <si>
     <t xml:space="preserve">Pontos</t>
   </si>
   <si>
-    <t xml:space="preserve">Faixa da aba Central</t>
+    <t xml:space="preserve">FMP grátis não inclui Ibovespa (HTTP 402); SGS 7 descontinuada em 2019</t>
   </si>
   <si>
     <t xml:space="preserve">BR-107</t>
@@ -3369,7 +3390,7 @@
     <t xml:space="preserve">Chave</t>
   </si>
   <si>
-    <t xml:space="preserve">Grátis 250 chamadas/dia; Starter US$ 22/mês</t>
+    <t xml:space="preserve">Grátis 250 chamadas/dia, só ações dos EUA: Ibovespa e EWZ dão HTTP 402. Fora do MVP</t>
   </si>
   <si>
     <t xml:space="preserve">GDELT</t>
@@ -3394,6 +3415,30 @@
   </si>
   <si>
     <t xml:space="preserve">Pago por uso</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B3 (IndexCall)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JSON (sistemaswebb3-listados.b3.com.br)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Endpoint do site da B3, não documentado; fechamentos diários por ano</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yahoo Finance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JSON (query1.finance.yahoo.com)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não oficial; só como alternativa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JSON (www.bcb.gov.br/api/servico/sitebcb)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Não documentada; comunicados e atas do Copom</t>
   </si>
 </sst>
 </file>
@@ -4403,19 +4448,19 @@
         <v>45</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A7,Brasil!$K$6:$K$130,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A7,Brasil!$K$6:$K$131,"MVP")</f>
         <v>10</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A7,Brasil!$K$6:$K$130,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A7,Brasil!$K$6:$K$131,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A7,Brasil!$K$6:$K$130,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A7,Brasil!$K$6:$K$131,"v2")</f>
         <v>4</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A7,Brasil!$K$6:$K$130,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A7,Brasil!$K$6:$K$131,"v3")</f>
         <v>0</v>
       </c>
       <c r="F7" s="6" t="n">
@@ -4426,8 +4471,8 @@
         <v>12</v>
       </c>
       <c r="I7" s="16" t="n">
-        <f aca="false">COUNTIF(Brasil!$L$6:$L$130,H7)</f>
-        <v>71</v>
+        <f aca="false">COUNTIF(Brasil!$L$6:$L$131,H7)</f>
+        <v>78</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4435,19 +4480,19 @@
         <v>46</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A8,Brasil!$K$6:$K$130,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A8,Brasil!$K$6:$K$131,"MVP")</f>
         <v>7</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A8,Brasil!$K$6:$K$130,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A8,Brasil!$K$6:$K$131,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A8,Brasil!$K$6:$K$130,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A8,Brasil!$K$6:$K$131,"v2")</f>
         <v>3</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A8,Brasil!$K$6:$K$130,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A8,Brasil!$K$6:$K$131,"v3")</f>
         <v>0</v>
       </c>
       <c r="F8" s="6" t="n">
@@ -4458,8 +4503,8 @@
         <v>14</v>
       </c>
       <c r="I8" s="16" t="n">
-        <f aca="false">COUNTIF(Brasil!$L$6:$L$130,H8)</f>
-        <v>18</v>
+        <f aca="false">COUNTIF(Brasil!$L$6:$L$131,H8)</f>
+        <v>13</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4467,31 +4512,31 @@
         <v>47</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A9,Brasil!$K$6:$K$130,"MVP")</f>
-        <v>21</v>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A9,Brasil!$K$6:$K$131,"MVP")</f>
+        <v>22</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A9,Brasil!$K$6:$K$130,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A9,Brasil!$K$6:$K$131,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A9,Brasil!$K$6:$K$130,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A9,Brasil!$K$6:$K$131,"v2")</f>
         <v>4</v>
       </c>
       <c r="E9" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A9,Brasil!$K$6:$K$130,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A9,Brasil!$K$6:$K$131,"v3")</f>
         <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
         <f aca="false">SUM(B9:E9)</f>
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H9" s="19" t="s">
         <v>16</v>
       </c>
       <c r="I9" s="16" t="n">
-        <f aca="false">COUNTIF(Brasil!$L$6:$L$130,H9)</f>
-        <v>7</v>
+        <f aca="false">COUNTIF(Brasil!$L$6:$L$131,H9)</f>
+        <v>6</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4499,19 +4544,19 @@
         <v>48</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A10,Brasil!$K$6:$K$130,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A10,Brasil!$K$6:$K$131,"MVP")</f>
         <v>15</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A10,Brasil!$K$6:$K$130,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A10,Brasil!$K$6:$K$131,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A10,Brasil!$K$6:$K$130,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A10,Brasil!$K$6:$K$131,"v2")</f>
         <v>4</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A10,Brasil!$K$6:$K$130,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A10,Brasil!$K$6:$K$131,"v3")</f>
         <v>0</v>
       </c>
       <c r="F10" s="6" t="n">
@@ -4522,7 +4567,7 @@
         <v>18</v>
       </c>
       <c r="I10" s="16" t="n">
-        <f aca="false">COUNTIF(Brasil!$L$6:$L$130,H10)</f>
+        <f aca="false">COUNTIF(Brasil!$L$6:$L$131,H10)</f>
         <v>9</v>
       </c>
     </row>
@@ -4531,19 +4576,19 @@
         <v>49</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A11,Brasil!$K$6:$K$130,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A11,Brasil!$K$6:$K$131,"MVP")</f>
         <v>8</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A11,Brasil!$K$6:$K$130,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A11,Brasil!$K$6:$K$131,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A11,Brasil!$K$6:$K$130,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A11,Brasil!$K$6:$K$131,"v2")</f>
         <v>2</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A11,Brasil!$K$6:$K$130,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A11,Brasil!$K$6:$K$131,"v3")</f>
         <v>0</v>
       </c>
       <c r="F11" s="6" t="n">
@@ -4554,7 +4599,7 @@
         <v>20</v>
       </c>
       <c r="I11" s="16" t="n">
-        <f aca="false">COUNTIF(Brasil!$L$6:$L$130,H11)</f>
+        <f aca="false">COUNTIF(Brasil!$L$6:$L$131,H11)</f>
         <v>1</v>
       </c>
     </row>
@@ -4563,19 +4608,19 @@
         <v>50</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A12,Brasil!$K$6:$K$130,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A12,Brasil!$K$6:$K$131,"MVP")</f>
         <v>10</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A12,Brasil!$K$6:$K$130,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A12,Brasil!$K$6:$K$131,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A12,Brasil!$K$6:$K$130,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A12,Brasil!$K$6:$K$131,"v2")</f>
         <v>2</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A12,Brasil!$K$6:$K$130,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A12,Brasil!$K$6:$K$131,"v3")</f>
         <v>0</v>
       </c>
       <c r="F12" s="6" t="n">
@@ -4586,7 +4631,7 @@
         <v>22</v>
       </c>
       <c r="I12" s="16" t="n">
-        <f aca="false">COUNTIF(Brasil!$L$6:$L$130,H12)</f>
+        <f aca="false">COUNTIF(Brasil!$L$6:$L$131,H12)</f>
         <v>13</v>
       </c>
     </row>
@@ -4595,19 +4640,19 @@
         <v>51</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A13,Brasil!$K$6:$K$130,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A13,Brasil!$K$6:$K$131,"MVP")</f>
         <v>7</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A13,Brasil!$K$6:$K$130,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A13,Brasil!$K$6:$K$131,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A13,Brasil!$K$6:$K$130,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A13,Brasil!$K$6:$K$131,"v2")</f>
         <v>2</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A13,Brasil!$K$6:$K$130,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A13,Brasil!$K$6:$K$131,"v3")</f>
         <v>0</v>
       </c>
       <c r="F13" s="6" t="n">
@@ -4618,7 +4663,7 @@
         <v>24</v>
       </c>
       <c r="I13" s="16" t="n">
-        <f aca="false">COUNTIF(Brasil!$L$6:$L$130,H13)</f>
+        <f aca="false">COUNTIF(Brasil!$L$6:$L$131,H13)</f>
         <v>6</v>
       </c>
     </row>
@@ -4627,19 +4672,19 @@
         <v>52</v>
       </c>
       <c r="B14" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A14,Brasil!$K$6:$K$130,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A14,Brasil!$K$6:$K$131,"MVP")</f>
         <v>1</v>
       </c>
       <c r="C14" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A14,Brasil!$K$6:$K$130,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A14,Brasil!$K$6:$K$131,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D14" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A14,Brasil!$K$6:$K$130,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A14,Brasil!$K$6:$K$131,"v2")</f>
         <v>4</v>
       </c>
       <c r="E14" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A14,Brasil!$K$6:$K$130,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A14,Brasil!$K$6:$K$131,"v3")</f>
         <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
@@ -4652,19 +4697,19 @@
         <v>53</v>
       </c>
       <c r="B15" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A15,Brasil!$K$6:$K$130,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A15,Brasil!$K$6:$K$131,"MVP")</f>
         <v>1</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A15,Brasil!$K$6:$K$130,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A15,Brasil!$K$6:$K$131,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D15" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A15,Brasil!$K$6:$K$130,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A15,Brasil!$K$6:$K$131,"v2")</f>
         <v>4</v>
       </c>
       <c r="E15" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A15,Brasil!$K$6:$K$130,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A15,Brasil!$K$6:$K$131,"v3")</f>
         <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
@@ -4677,19 +4722,19 @@
         <v>54</v>
       </c>
       <c r="B16" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A16,Brasil!$K$6:$K$130,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A16,Brasil!$K$6:$K$131,"MVP")</f>
         <v>0</v>
       </c>
       <c r="C16" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A16,Brasil!$K$6:$K$130,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A16,Brasil!$K$6:$K$131,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D16" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A16,Brasil!$K$6:$K$130,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A16,Brasil!$K$6:$K$131,"v2")</f>
         <v>4</v>
       </c>
       <c r="E16" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A16,Brasil!$K$6:$K$130,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A16,Brasil!$K$6:$K$131,"v3")</f>
         <v>0</v>
       </c>
       <c r="F16" s="6" t="n">
@@ -4702,19 +4747,19 @@
         <v>55</v>
       </c>
       <c r="B17" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A17,Brasil!$K$6:$K$130,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A17,Brasil!$K$6:$K$131,"MVP")</f>
         <v>3</v>
       </c>
       <c r="C17" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A17,Brasil!$K$6:$K$130,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A17,Brasil!$K$6:$K$131,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D17" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A17,Brasil!$K$6:$K$130,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A17,Brasil!$K$6:$K$131,"v2")</f>
         <v>6</v>
       </c>
       <c r="E17" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$130,$A17,Brasil!$K$6:$K$130,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A17,Brasil!$K$6:$K$131,"v3")</f>
         <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
@@ -4728,7 +4773,7 @@
       </c>
       <c r="B18" s="6" t="n">
         <f aca="false">SUM(B7:B17)</f>
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C18" s="6" t="n">
         <f aca="false">SUM(C7:C17)</f>
@@ -4744,7 +4789,7 @@
       </c>
       <c r="F18" s="6" t="n">
         <f aca="false">SUM(F7:F17)</f>
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5093,7 +5138,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M130"/>
+  <dimension ref="A1:M131"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -6436,7 +6481,7 @@
       </c>
       <c r="M36" s="26"/>
     </row>
-    <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="37" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="25" t="s">
         <v>234</v>
       </c>
@@ -6473,11 +6518,13 @@
       <c r="L37" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M37" s="26"/>
+      <c r="M37" s="26" t="s">
+        <v>237</v>
+      </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="25" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B38" s="26" t="s">
         <v>47</v>
@@ -6486,13 +6533,13 @@
         <v>225</v>
       </c>
       <c r="D38" s="27" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E38" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F38" s="26" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G38" s="26" t="s">
         <v>100</v>
@@ -6516,7 +6563,7 @@
     </row>
     <row r="39" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="25" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B39" s="26" t="s">
         <v>47</v>
@@ -6525,13 +6572,13 @@
         <v>225</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="E39" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>16</v>
+        <v>243</v>
       </c>
       <c r="G39" s="26" t="s">
         <v>100</v>
@@ -6549,30 +6596,30 @@
         <v>27</v>
       </c>
       <c r="L39" s="26" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M39" s="26" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="25" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B40" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="E40" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G40" s="26" t="s">
         <v>100</v>
@@ -6592,26 +6639,28 @@
       <c r="L40" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M40" s="26"/>
+      <c r="M40" s="26" t="s">
+        <v>248</v>
+      </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="25" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B41" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D41" s="27" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E41" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="G41" s="26" t="s">
         <v>100</v>
@@ -6635,22 +6684,22 @@
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="25" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="B42" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D42" s="27" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="E42" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="G42" s="26" t="s">
         <v>100</v>
@@ -6674,22 +6723,22 @@
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="25" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="B43" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D43" s="27" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E43" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="G43" s="26" t="s">
         <v>100</v>
@@ -6713,22 +6762,22 @@
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="25" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="B44" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
       <c r="E44" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="G44" s="26" t="s">
         <v>100</v>
@@ -6743,82 +6792,82 @@
         <v>211</v>
       </c>
       <c r="K44" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L44" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M44" s="26"/>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="25" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="B45" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="E45" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="G45" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H45" s="26" t="s">
-        <v>85</v>
+        <v>209</v>
       </c>
       <c r="I45" s="26" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="J45" s="26" t="s">
-        <v>87</v>
+        <v>211</v>
       </c>
       <c r="K45" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L45" s="26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M45" s="26"/>
     </row>
-    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="25" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B46" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E46" s="26" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G46" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H46" s="26" t="s">
-        <v>265</v>
+        <v>85</v>
       </c>
       <c r="I46" s="26" t="s">
-        <v>210</v>
+        <v>86</v>
       </c>
       <c r="J46" s="26" t="s">
-        <v>211</v>
+        <v>87</v>
       </c>
       <c r="K46" s="26" t="s">
         <v>27</v>
@@ -6826,69 +6875,67 @@
       <c r="L46" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M46" s="26" t="s">
-        <v>266</v>
-      </c>
+      <c r="M46" s="26"/>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="25" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B47" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>200</v>
+        <v>76</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="G47" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H47" s="26" t="s">
-        <v>209</v>
+        <v>271</v>
       </c>
       <c r="I47" s="26" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="J47" s="26" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="K47" s="26" t="s">
         <v>27</v>
       </c>
       <c r="L47" s="26" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M47" s="26" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="25" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B48" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="D48" s="27" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="E48" s="26" t="s">
-        <v>98</v>
+        <v>200</v>
       </c>
       <c r="F48" s="26" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="G48" s="26" t="s">
         <v>100</v>
@@ -6897,39 +6944,39 @@
         <v>209</v>
       </c>
       <c r="I48" s="26" t="s">
-        <v>210</v>
+        <v>22</v>
       </c>
       <c r="J48" s="26" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="K48" s="26" t="s">
         <v>27</v>
       </c>
       <c r="L48" s="26" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="M48" s="26" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="25" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B49" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E49" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F49" s="26" t="s">
-        <v>16</v>
+        <v>280</v>
       </c>
       <c r="G49" s="26" t="s">
         <v>100</v>
@@ -6944,84 +6991,84 @@
         <v>211</v>
       </c>
       <c r="K49" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L49" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="M49" s="26"/>
+        <v>12</v>
+      </c>
+      <c r="M49" s="26" t="s">
+        <v>281</v>
+      </c>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="25" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="B50" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="D50" s="27" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="E50" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F50" s="26" t="s">
-        <v>280</v>
+        <v>16</v>
       </c>
       <c r="G50" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H50" s="26" t="s">
-        <v>79</v>
+        <v>209</v>
       </c>
       <c r="I50" s="26" t="s">
-        <v>79</v>
+        <v>210</v>
       </c>
       <c r="J50" s="26" t="s">
-        <v>80</v>
+        <v>211</v>
       </c>
       <c r="K50" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L50" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="M50" s="26" t="s">
-        <v>281</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="M50" s="26"/>
     </row>
     <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="B51" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>144</v>
+        <v>278</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E51" s="26" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="F51" s="26" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="G51" s="26" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="H51" s="26" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I51" s="26" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="J51" s="26" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K51" s="26" t="s">
         <v>27</v>
@@ -7029,11 +7076,13 @@
       <c r="L51" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M51" s="26"/>
+      <c r="M51" s="26" t="s">
+        <v>287</v>
+      </c>
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="25" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="B52" s="26" t="s">
         <v>47</v>
@@ -7042,16 +7091,16 @@
         <v>144</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="E52" s="26" t="s">
         <v>146</v>
       </c>
       <c r="F52" s="26" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G52" s="26" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H52" s="26" t="s">
         <v>85</v>
@@ -7068,13 +7117,11 @@
       <c r="L52" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M52" s="26" t="s">
-        <v>288</v>
-      </c>
+      <c r="M52" s="26"/>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="25" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B53" s="26" t="s">
         <v>47</v>
@@ -7083,13 +7130,13 @@
         <v>144</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>291</v>
+        <v>146</v>
       </c>
       <c r="F53" s="26" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="G53" s="26" t="s">
         <v>140</v>
@@ -7104,24 +7151,24 @@
         <v>87</v>
       </c>
       <c r="K53" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L53" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M53" s="26" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="25" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B54" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C54" s="26" t="s">
-        <v>295</v>
+        <v>144</v>
       </c>
       <c r="D54" s="27" t="s">
         <v>296</v>
@@ -7130,10 +7177,10 @@
         <v>297</v>
       </c>
       <c r="F54" s="26" t="s">
-        <v>24</v>
+        <v>298</v>
       </c>
       <c r="G54" s="26" t="s">
-        <v>298</v>
+        <v>140</v>
       </c>
       <c r="H54" s="26" t="s">
         <v>85</v>
@@ -7145,21 +7192,21 @@
         <v>87</v>
       </c>
       <c r="K54" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L54" s="26" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="M54" s="26" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="25" t="s">
         <v>300</v>
       </c>
       <c r="B55" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C55" s="26" t="s">
         <v>301</v>
@@ -7168,16 +7215,16 @@
         <v>302</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>98</v>
+        <v>303</v>
       </c>
       <c r="F55" s="26" t="s">
-        <v>303</v>
+        <v>24</v>
       </c>
       <c r="G55" s="26" t="s">
-        <v>140</v>
+        <v>304</v>
       </c>
       <c r="H55" s="26" t="s">
-        <v>304</v>
+        <v>85</v>
       </c>
       <c r="I55" s="26" t="s">
         <v>86</v>
@@ -7189,13 +7236,13 @@
         <v>27</v>
       </c>
       <c r="L55" s="26" t="s">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="M55" s="26" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="25" t="s">
         <v>306</v>
       </c>
@@ -7203,22 +7250,22 @@
         <v>48</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D56" s="27" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="E56" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F56" s="26" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="G56" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H56" s="26" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="I56" s="26" t="s">
         <v>86</v>
@@ -7227,39 +7274,39 @@
         <v>87</v>
       </c>
       <c r="K56" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L56" s="26" t="s">
         <v>12</v>
       </c>
       <c r="M56" s="26" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="25" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B57" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="E57" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F57" s="26" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="G57" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H57" s="26" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="I57" s="26" t="s">
         <v>86</v>
@@ -7268,39 +7315,39 @@
         <v>87</v>
       </c>
       <c r="K57" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L57" s="26" t="s">
         <v>12</v>
       </c>
       <c r="M57" s="26" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="25" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B58" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E58" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F58" s="26" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="G58" s="26" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H58" s="26" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="I58" s="26" t="s">
         <v>86</v>
@@ -7315,33 +7362,33 @@
         <v>12</v>
       </c>
       <c r="M58" s="26" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="25" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="B59" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D59" s="27" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E59" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F59" s="26" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="G59" s="26" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="H59" s="26" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="I59" s="26" t="s">
         <v>86</v>
@@ -7350,160 +7397,160 @@
         <v>87</v>
       </c>
       <c r="K59" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L59" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="M59" s="26"/>
+        <v>12</v>
+      </c>
+      <c r="M59" s="26" t="s">
+        <v>324</v>
+      </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="25" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="B60" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C60" s="26" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>200</v>
+        <v>98</v>
       </c>
       <c r="F60" s="26" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="G60" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H60" s="26" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="I60" s="26" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="J60" s="26" t="s">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="K60" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L60" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="M60" s="26" t="s">
-        <v>325</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="M60" s="26"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="25" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B61" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>144</v>
+        <v>307</v>
       </c>
       <c r="D61" s="27" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E61" s="26" t="s">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="F61" s="26" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="G61" s="26" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="H61" s="26" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="I61" s="26" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="J61" s="26" t="s">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="K61" s="26" t="s">
         <v>27</v>
       </c>
       <c r="L61" s="26" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="M61" s="26" t="s">
-        <v>329</v>
-      </c>
-    </row>
-    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="25" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B62" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C62" s="26" t="s">
-        <v>331</v>
+        <v>144</v>
       </c>
       <c r="D62" s="27" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="E62" s="26" t="s">
-        <v>333</v>
+        <v>146</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>24</v>
+        <v>334</v>
       </c>
       <c r="G62" s="26" t="s">
-        <v>334</v>
+        <v>148</v>
       </c>
       <c r="H62" s="26" t="s">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="I62" s="26" t="s">
-        <v>336</v>
+        <v>86</v>
       </c>
       <c r="J62" s="26" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="K62" s="26" t="s">
         <v>27</v>
       </c>
       <c r="L62" s="26" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M62" s="26" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="25" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B63" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C63" s="26" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="D63" s="27" t="s">
+        <v>338</v>
+      </c>
+      <c r="E63" s="26" t="s">
         <v>339</v>
       </c>
-      <c r="E63" s="26" t="s">
+      <c r="F63" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="G63" s="26" t="s">
         <v>340</v>
       </c>
-      <c r="F63" s="26" t="s">
+      <c r="H63" s="26" t="s">
         <v>341</v>
-      </c>
-      <c r="G63" s="26" t="s">
-        <v>334</v>
-      </c>
-      <c r="H63" s="26" t="s">
-        <v>342</v>
       </c>
       <c r="I63" s="26" t="s">
         <v>342</v>
@@ -7515,13 +7562,13 @@
         <v>27</v>
       </c>
       <c r="L63" s="26" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="M63" s="26" t="s">
         <v>343</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="25" t="s">
         <v>344</v>
       </c>
@@ -7529,28 +7576,28 @@
         <v>48</v>
       </c>
       <c r="C64" s="26" t="s">
+        <v>337</v>
+      </c>
+      <c r="D64" s="27" t="s">
         <v>345</v>
       </c>
-      <c r="D64" s="27" t="s">
+      <c r="E64" s="26" t="s">
         <v>346</v>
-      </c>
-      <c r="E64" s="26" t="s">
-        <v>98</v>
       </c>
       <c r="F64" s="26" t="s">
         <v>347</v>
       </c>
       <c r="G64" s="26" t="s">
-        <v>100</v>
+        <v>340</v>
       </c>
       <c r="H64" s="26" t="s">
         <v>348</v>
       </c>
       <c r="I64" s="26" t="s">
-        <v>165</v>
+        <v>348</v>
       </c>
       <c r="J64" s="26" t="s">
-        <v>166</v>
+        <v>124</v>
       </c>
       <c r="K64" s="26" t="s">
         <v>27</v>
@@ -7570,22 +7617,22 @@
         <v>48</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D65" s="27" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="E65" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="G65" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H65" s="26" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="I65" s="26" t="s">
         <v>165</v>
@@ -7600,33 +7647,33 @@
         <v>12</v>
       </c>
       <c r="M65" s="26" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="25" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="B66" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C66" s="26" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D66" s="27" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E66" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F66" s="26" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="G66" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H66" s="26" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="I66" s="26" t="s">
         <v>165</v>
@@ -7640,32 +7687,34 @@
       <c r="L66" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M66" s="26"/>
+      <c r="M66" s="26" t="s">
+        <v>359</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="25" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="B67" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C67" s="26" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E67" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="G67" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H67" s="26" t="s">
-        <v>101</v>
+        <v>354</v>
       </c>
       <c r="I67" s="26" t="s">
         <v>165</v>
@@ -7683,22 +7732,22 @@
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="25" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B68" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C68" s="26" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D68" s="27" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="E68" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="G68" s="26" t="s">
         <v>100</v>
@@ -7718,28 +7767,26 @@
       <c r="L68" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M68" s="26" t="s">
-        <v>364</v>
-      </c>
+      <c r="M68" s="26"/>
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="25" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B69" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D69" s="27" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E69" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="G69" s="26" t="s">
         <v>100</v>
@@ -7748,10 +7795,10 @@
         <v>101</v>
       </c>
       <c r="I69" s="26" t="s">
-        <v>102</v>
+        <v>165</v>
       </c>
       <c r="J69" s="26" t="s">
-        <v>103</v>
+        <v>166</v>
       </c>
       <c r="K69" s="26" t="s">
         <v>27</v>
@@ -7759,38 +7806,40 @@
       <c r="L69" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M69" s="26"/>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M69" s="26" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="25" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="B70" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C70" s="26" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D70" s="27" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="E70" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="G70" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H70" s="26" t="s">
-        <v>304</v>
+        <v>101</v>
       </c>
       <c r="I70" s="26" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="J70" s="26" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="K70" s="26" t="s">
         <v>27</v>
@@ -7802,28 +7851,28 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="25" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B71" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C71" s="26" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="E71" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="G71" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H71" s="26" t="s">
-        <v>202</v>
+        <v>310</v>
       </c>
       <c r="I71" s="26" t="s">
         <v>86</v>
@@ -7841,28 +7890,28 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="25" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="B72" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C72" s="26" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="E72" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="G72" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H72" s="26" t="s">
-        <v>304</v>
+        <v>202</v>
       </c>
       <c r="I72" s="26" t="s">
         <v>86</v>
@@ -7871,117 +7920,117 @@
         <v>87</v>
       </c>
       <c r="K72" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L72" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M72" s="26"/>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="25" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B73" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C73" s="26" t="s">
-        <v>378</v>
+        <v>364</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E73" s="26" t="s">
-        <v>200</v>
+        <v>98</v>
       </c>
       <c r="F73" s="26" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="G73" s="26" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="H73" s="26" t="s">
-        <v>79</v>
+        <v>310</v>
       </c>
       <c r="I73" s="26" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="J73" s="26" t="s">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="K73" s="26" t="s">
         <v>31</v>
       </c>
       <c r="L73" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="M73" s="26"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="25" t="s">
+        <v>383</v>
+      </c>
+      <c r="B74" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C74" s="26" t="s">
+        <v>384</v>
+      </c>
+      <c r="D74" s="27" t="s">
+        <v>385</v>
+      </c>
+      <c r="E74" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="F74" s="26" t="s">
+        <v>386</v>
+      </c>
+      <c r="G74" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="H74" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="I74" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="M73" s="26" t="s">
-        <v>381</v>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="25" t="s">
-        <v>382</v>
-      </c>
-      <c r="B74" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C74" s="26" t="s">
-        <v>383</v>
-      </c>
-      <c r="D74" s="27" t="s">
-        <v>384</v>
-      </c>
-      <c r="E74" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="F74" s="26" t="s">
-        <v>385</v>
-      </c>
-      <c r="G74" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="H74" s="26" t="s">
-        <v>386</v>
-      </c>
-      <c r="I74" s="26" t="s">
-        <v>86</v>
-      </c>
       <c r="J74" s="26" t="s">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="K74" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L74" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="M74" s="26"/>
+        <v>22</v>
+      </c>
+      <c r="M74" s="26" t="s">
+        <v>387</v>
+      </c>
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="25" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B75" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C75" s="26" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="D75" s="27" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E75" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F75" s="26" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="G75" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H75" s="26" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="I75" s="26" t="s">
         <v>86</v>
@@ -7995,34 +8044,32 @@
       <c r="L75" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M75" s="26" t="s">
-        <v>390</v>
-      </c>
+      <c r="M75" s="26"/>
     </row>
     <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="25" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="B76" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C76" s="26" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="D76" s="27" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E76" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="G76" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H76" s="26" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="I76" s="26" t="s">
         <v>86</v>
@@ -8037,33 +8084,33 @@
         <v>12</v>
       </c>
       <c r="M76" s="26" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="25" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="B77" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C77" s="26" t="s">
-        <v>396</v>
+        <v>389</v>
       </c>
       <c r="D77" s="27" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="E77" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="G77" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H77" s="26" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="I77" s="26" t="s">
         <v>86</v>
@@ -8077,32 +8124,34 @@
       <c r="L77" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M77" s="26"/>
+      <c r="M77" s="26" t="s">
+        <v>400</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="25" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B78" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C78" s="26" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="D78" s="27" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="E78" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="G78" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H78" s="26" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="I78" s="26" t="s">
         <v>86</v>
@@ -8118,110 +8167,110 @@
       </c>
       <c r="M78" s="26"/>
     </row>
-    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="25" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B79" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C79" s="26" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>291</v>
+        <v>98</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="G79" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H79" s="26" t="s">
-        <v>101</v>
+        <v>392</v>
       </c>
       <c r="I79" s="26" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="J79" s="26" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="K79" s="26" t="s">
         <v>27</v>
       </c>
       <c r="L79" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="M79" s="26" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>12</v>
+      </c>
+      <c r="M79" s="26"/>
+    </row>
+    <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="25" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B80" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C80" s="26" t="s">
-        <v>403</v>
+        <v>409</v>
       </c>
       <c r="D80" s="27" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E80" s="26" t="s">
-        <v>409</v>
+        <v>297</v>
       </c>
       <c r="F80" s="26" t="s">
-        <v>24</v>
+        <v>411</v>
       </c>
       <c r="G80" s="26" t="s">
-        <v>298</v>
+        <v>100</v>
       </c>
       <c r="H80" s="26" t="s">
-        <v>386</v>
+        <v>101</v>
       </c>
       <c r="I80" s="26" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="J80" s="26" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="K80" s="26" t="s">
         <v>27</v>
       </c>
       <c r="L80" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="M80" s="26"/>
+        <v>12</v>
+      </c>
+      <c r="M80" s="26" t="s">
+        <v>412</v>
+      </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="25" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="B81" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C81" s="26" t="s">
-        <v>396</v>
+        <v>409</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="E81" s="26" t="s">
-        <v>291</v>
+        <v>415</v>
       </c>
       <c r="F81" s="26" t="s">
-        <v>412</v>
+        <v>24</v>
       </c>
       <c r="G81" s="26" t="s">
-        <v>100</v>
+        <v>304</v>
       </c>
       <c r="H81" s="26" t="s">
-        <v>85</v>
+        <v>392</v>
       </c>
       <c r="I81" s="26" t="s">
         <v>86</v>
@@ -8230,37 +8279,37 @@
         <v>87</v>
       </c>
       <c r="K81" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L81" s="26" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="M81" s="26"/>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="25" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="B82" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C82" s="26" t="s">
-        <v>414</v>
+        <v>402</v>
       </c>
       <c r="D82" s="27" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E82" s="26" t="s">
-        <v>146</v>
+        <v>297</v>
       </c>
       <c r="F82" s="26" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="G82" s="26" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="H82" s="26" t="s">
-        <v>386</v>
+        <v>85</v>
       </c>
       <c r="I82" s="26" t="s">
         <v>86</v>
@@ -8269,37 +8318,37 @@
         <v>87</v>
       </c>
       <c r="K82" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L82" s="26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M82" s="26"/>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="25" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B83" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C83" s="26" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="D83" s="27" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>419</v>
+        <v>146</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="G83" s="26" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="H83" s="26" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="I83" s="26" t="s">
         <v>86</v>
@@ -8308,24 +8357,22 @@
         <v>87</v>
       </c>
       <c r="K83" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L83" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="M83" s="26" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>12</v>
+      </c>
+      <c r="M83" s="26"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="25" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="B84" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C84" s="26" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="D84" s="27" t="s">
         <v>424</v>
@@ -8340,48 +8387,48 @@
         <v>100</v>
       </c>
       <c r="H84" s="26" t="s">
+        <v>392</v>
+      </c>
+      <c r="I84" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="J84" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="K84" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="L84" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="M84" s="26" t="s">
         <v>427</v>
-      </c>
-      <c r="I84" s="26" t="s">
-        <v>102</v>
-      </c>
-      <c r="J84" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="K84" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="L84" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="M84" s="26" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="25" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B85" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C85" s="26" t="s">
-        <v>423</v>
+        <v>429</v>
       </c>
       <c r="D85" s="27" t="s">
         <v>430</v>
       </c>
       <c r="E85" s="26" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="F85" s="26" t="s">
-        <v>426</v>
+        <v>432</v>
       </c>
       <c r="G85" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H85" s="26" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="I85" s="26" t="s">
         <v>102</v>
@@ -8393,36 +8440,36 @@
         <v>27</v>
       </c>
       <c r="L85" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M85" s="26" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="25" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="B86" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C86" s="26" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D86" s="27" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E86" s="26" t="s">
-        <v>98</v>
+        <v>431</v>
       </c>
       <c r="F86" s="26" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="G86" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H86" s="26" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="I86" s="26" t="s">
         <v>102</v>
@@ -8436,38 +8483,40 @@
       <c r="L86" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M86" s="26"/>
+      <c r="M86" s="26" t="s">
+        <v>438</v>
+      </c>
     </row>
     <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="25" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="B87" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C87" s="26" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="D87" s="27" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="E87" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F87" s="26" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="G87" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H87" s="26" t="s">
-        <v>386</v>
+        <v>433</v>
       </c>
       <c r="I87" s="26" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="J87" s="26" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="K87" s="26" t="s">
         <v>27</v>
@@ -8475,40 +8524,38 @@
       <c r="L87" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M87" s="26" t="s">
-        <v>439</v>
-      </c>
+      <c r="M87" s="26"/>
     </row>
     <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="25" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="B88" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C88" s="26" t="s">
-        <v>433</v>
+        <v>440</v>
       </c>
       <c r="D88" s="27" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="E88" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F88" s="26" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="G88" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H88" s="26" t="s">
-        <v>427</v>
+        <v>392</v>
       </c>
       <c r="I88" s="26" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="J88" s="26" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="K88" s="26" t="s">
         <v>27</v>
@@ -8516,38 +8563,40 @@
       <c r="L88" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M88" s="26"/>
+      <c r="M88" s="26" t="s">
+        <v>446</v>
+      </c>
     </row>
     <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="25" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="B89" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C89" s="26" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="D89" s="27" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E89" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F89" s="26" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="G89" s="26" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="H89" s="26" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="I89" s="26" t="s">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="J89" s="26" t="s">
-        <v>166</v>
+        <v>103</v>
       </c>
       <c r="K89" s="26" t="s">
         <v>27</v>
@@ -8555,40 +8604,38 @@
       <c r="L89" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M89" s="26" t="s">
-        <v>310</v>
-      </c>
+      <c r="M89" s="26"/>
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="25" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B90" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C90" s="26" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D90" s="27" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="E90" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F90" s="26" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="G90" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H90" s="26" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="I90" s="26" t="s">
-        <v>79</v>
+        <v>165</v>
       </c>
       <c r="J90" s="26" t="s">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="K90" s="26" t="s">
         <v>27</v>
@@ -8597,33 +8644,33 @@
         <v>12</v>
       </c>
       <c r="M90" s="26" t="s">
-        <v>452</v>
+        <v>316</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="25" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B91" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="D91" s="27" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E91" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F91" s="26" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="G91" s="26" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H91" s="26" t="s">
-        <v>79</v>
+        <v>458</v>
       </c>
       <c r="I91" s="26" t="s">
         <v>79</v>
@@ -8637,110 +8684,112 @@
       <c r="L91" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M91" s="26"/>
+      <c r="M91" s="26" t="s">
+        <v>459</v>
+      </c>
     </row>
     <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="25" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B92" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C92" s="26" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="D92" s="27" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="E92" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F92" s="26" t="s">
-        <v>16</v>
+        <v>462</v>
       </c>
       <c r="G92" s="26" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="H92" s="26" t="s">
-        <v>427</v>
+        <v>79</v>
       </c>
       <c r="I92" s="26" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="J92" s="26" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="K92" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L92" s="26" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M92" s="26"/>
     </row>
     <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="25" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="B93" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C93" s="26" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="D93" s="27" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="E93" s="26" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="F93" s="26" t="s">
-        <v>460</v>
+        <v>16</v>
       </c>
       <c r="G93" s="26" t="s">
         <v>148</v>
       </c>
       <c r="H93" s="26" t="s">
-        <v>451</v>
+        <v>433</v>
       </c>
       <c r="I93" s="26" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="J93" s="26" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="K93" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L93" s="26" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M93" s="26"/>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="25" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B94" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C94" s="26" t="s">
-        <v>462</v>
+        <v>455</v>
       </c>
       <c r="D94" s="27" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="E94" s="26" t="s">
-        <v>464</v>
+        <v>146</v>
       </c>
       <c r="F94" s="26" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="G94" s="26" t="s">
-        <v>466</v>
+        <v>148</v>
       </c>
       <c r="H94" s="26" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="I94" s="26" t="s">
         <v>79</v>
@@ -8764,22 +8813,22 @@
         <v>50</v>
       </c>
       <c r="C95" s="26" t="s">
-        <v>462</v>
+        <v>469</v>
       </c>
       <c r="D95" s="27" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="E95" s="26" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="F95" s="26" t="s">
-        <v>16</v>
+        <v>472</v>
       </c>
       <c r="G95" s="26" t="s">
-        <v>100</v>
+        <v>473</v>
       </c>
       <c r="H95" s="26" t="s">
-        <v>79</v>
+        <v>474</v>
       </c>
       <c r="I95" s="26" t="s">
         <v>79</v>
@@ -8788,72 +8837,70 @@
         <v>80</v>
       </c>
       <c r="K95" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L95" s="26" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M95" s="26"/>
     </row>
     <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="25" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="B96" s="26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C96" s="26" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="D96" s="27" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="E96" s="26" t="s">
-        <v>98</v>
+        <v>477</v>
       </c>
       <c r="F96" s="26" t="s">
-        <v>474</v>
+        <v>16</v>
       </c>
       <c r="G96" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H96" s="26" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I96" s="26" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="J96" s="26" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K96" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L96" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="M96" s="26" t="s">
-        <v>475</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="M96" s="26"/>
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="25" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="B97" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C97" s="26" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="D97" s="27" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="E97" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F97" s="26" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="G97" s="26" t="s">
         <v>100</v>
@@ -8874,39 +8921,39 @@
         <v>12</v>
       </c>
       <c r="M97" s="26" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="25" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B98" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C98" s="26" t="s">
-        <v>358</v>
+        <v>479</v>
       </c>
       <c r="D98" s="27" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="E98" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="G98" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H98" s="26" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="I98" s="26" t="s">
-        <v>165</v>
+        <v>86</v>
       </c>
       <c r="J98" s="26" t="s">
-        <v>166</v>
+        <v>87</v>
       </c>
       <c r="K98" s="26" t="s">
         <v>27</v>
@@ -8914,26 +8961,28 @@
       <c r="L98" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M98" s="26"/>
+      <c r="M98" s="26" t="s">
+        <v>486</v>
+      </c>
     </row>
     <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="25" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="B99" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C99" s="26" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D99" s="27" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="E99" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F99" s="26" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="G99" s="26" t="s">
         <v>100</v>
@@ -8957,22 +9006,22 @@
     </row>
     <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="25" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B100" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C100" s="26" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D100" s="27" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="E100" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F100" s="26" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="G100" s="26" t="s">
         <v>100</v>
@@ -8994,36 +9043,36 @@
       </c>
       <c r="M100" s="26"/>
     </row>
-    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="101" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="25" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B101" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D101" s="27" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="E101" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="G101" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H101" s="26" t="s">
-        <v>85</v>
+        <v>101</v>
       </c>
       <c r="I101" s="26" t="s">
-        <v>86</v>
+        <v>165</v>
       </c>
       <c r="J101" s="26" t="s">
-        <v>87</v>
+        <v>166</v>
       </c>
       <c r="K101" s="26" t="s">
         <v>27</v>
@@ -9035,186 +9084,186 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="25" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="B102" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C102" s="26" t="s">
-        <v>493</v>
+        <v>364</v>
       </c>
       <c r="D102" s="27" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="E102" s="26" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F102" s="26" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
       <c r="G102" s="26" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H102" s="26" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="I102" s="26" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="J102" s="26" t="s">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="K102" s="26" t="s">
         <v>27</v>
       </c>
       <c r="L102" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="M102" s="26" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>12</v>
+      </c>
+      <c r="M102" s="26"/>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="25" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="B103" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C103" s="26" t="s">
-        <v>127</v>
+        <v>500</v>
       </c>
       <c r="D103" s="27" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="E103" s="26" t="s">
-        <v>129</v>
+        <v>76</v>
       </c>
       <c r="F103" s="26" t="s">
+        <v>502</v>
+      </c>
+      <c r="G103" s="26" t="s">
         <v>124</v>
       </c>
-      <c r="G103" s="26" t="s">
-        <v>100</v>
-      </c>
       <c r="H103" s="26" t="s">
-        <v>79</v>
+        <v>124</v>
       </c>
       <c r="I103" s="26" t="s">
-        <v>79</v>
+        <v>22</v>
       </c>
       <c r="J103" s="26" t="s">
-        <v>80</v>
+        <v>203</v>
       </c>
       <c r="K103" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L103" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="M103" s="26"/>
+        <v>22</v>
+      </c>
+      <c r="M103" s="26" t="s">
+        <v>503</v>
+      </c>
     </row>
     <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="25" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
       <c r="B104" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C104" s="26" t="s">
-        <v>500</v>
+        <v>127</v>
       </c>
       <c r="D104" s="27" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="E104" s="26" t="s">
-        <v>98</v>
+        <v>129</v>
       </c>
       <c r="F104" s="26" t="s">
-        <v>16</v>
+        <v>124</v>
       </c>
       <c r="G104" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H104" s="26" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="I104" s="26" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="J104" s="26" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="K104" s="26" t="s">
         <v>31</v>
       </c>
       <c r="L104" s="26" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="M104" s="26"/>
     </row>
     <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="25" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="B105" s="26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C105" s="26" t="s">
-        <v>358</v>
+        <v>507</v>
       </c>
       <c r="D105" s="27" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
       <c r="E105" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F105" s="26" t="s">
-        <v>504</v>
+        <v>16</v>
       </c>
       <c r="G105" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H105" s="26" t="s">
-        <v>505</v>
+        <v>101</v>
       </c>
       <c r="I105" s="26" t="s">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="J105" s="26" t="s">
-        <v>166</v>
+        <v>103</v>
       </c>
       <c r="K105" s="26" t="s">
         <v>31</v>
       </c>
       <c r="L105" s="26" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M105" s="26"/>
     </row>
     <row r="106" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="25" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="B106" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C106" s="26" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D106" s="27" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="E106" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F106" s="26" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="G106" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H106" s="26" t="s">
-        <v>101</v>
+        <v>512</v>
       </c>
       <c r="I106" s="26" t="s">
         <v>165</v>
@@ -9232,22 +9281,22 @@
     </row>
     <row r="107" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="25" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B107" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C107" s="26" t="s">
-        <v>510</v>
+        <v>364</v>
       </c>
       <c r="D107" s="27" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="E107" s="26" t="s">
-        <v>512</v>
+        <v>98</v>
       </c>
       <c r="F107" s="26" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="G107" s="26" t="s">
         <v>100</v>
@@ -9256,43 +9305,43 @@
         <v>101</v>
       </c>
       <c r="I107" s="26" t="s">
-        <v>102</v>
+        <v>165</v>
       </c>
       <c r="J107" s="26" t="s">
-        <v>103</v>
+        <v>166</v>
       </c>
       <c r="K107" s="26" t="s">
         <v>31</v>
       </c>
       <c r="L107" s="26" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M107" s="26"/>
     </row>
     <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="25" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B108" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C108" s="26" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="D108" s="27" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E108" s="26" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="F108" s="26" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="G108" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H108" s="26" t="s">
-        <v>195</v>
+        <v>101</v>
       </c>
       <c r="I108" s="26" t="s">
         <v>102</v>
@@ -9306,34 +9355,32 @@
       <c r="L108" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="M108" s="26" t="s">
-        <v>519</v>
-      </c>
+      <c r="M108" s="26"/>
     </row>
     <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="25" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B109" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C109" s="26" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="D109" s="27" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="E109" s="26" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F109" s="26" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="G109" s="26" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="H109" s="26" t="s">
-        <v>101</v>
+        <v>195</v>
       </c>
       <c r="I109" s="26" t="s">
         <v>102</v>
@@ -9342,80 +9389,80 @@
         <v>103</v>
       </c>
       <c r="K109" s="26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L109" s="26" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="M109" s="26" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="25" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B110" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C110" s="26" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="D110" s="27" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="E110" s="26" t="s">
-        <v>76</v>
+        <v>530</v>
       </c>
       <c r="F110" s="26" t="s">
-        <v>77</v>
+        <v>531</v>
       </c>
       <c r="G110" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H110" s="26" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="I110" s="26" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="J110" s="26" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="K110" s="26" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="L110" s="26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M110" s="26" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="25" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="B111" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C111" s="26" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D111" s="27" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E111" s="26" t="s">
-        <v>533</v>
+        <v>76</v>
       </c>
       <c r="F111" s="26" t="s">
-        <v>534</v>
+        <v>77</v>
       </c>
       <c r="G111" s="26" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="H111" s="26" t="s">
-        <v>535</v>
+        <v>79</v>
       </c>
       <c r="I111" s="26" t="s">
         <v>79</v>
@@ -9427,13 +9474,13 @@
         <v>27</v>
       </c>
       <c r="L111" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M111" s="26" t="s">
         <v>536</v>
       </c>
     </row>
-    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="112" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="25" t="s">
         <v>537</v>
       </c>
@@ -9441,63 +9488,63 @@
         <v>53</v>
       </c>
       <c r="C112" s="26" t="s">
-        <v>301</v>
+        <v>538</v>
       </c>
       <c r="D112" s="27" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="E112" s="26" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="G112" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H112" s="26" t="s">
-        <v>304</v>
+        <v>542</v>
       </c>
       <c r="I112" s="26" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="J112" s="26" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K112" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L112" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M112" s="26" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="25" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B113" s="26" t="s">
         <v>53</v>
       </c>
       <c r="C113" s="26" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="D113" s="27" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="E113" s="26" t="s">
-        <v>291</v>
+        <v>546</v>
       </c>
       <c r="F113" s="26" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="G113" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H113" s="26" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="I113" s="26" t="s">
         <v>86</v>
@@ -9511,32 +9558,34 @@
       <c r="L113" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="M113" s="26"/>
+      <c r="M113" s="26" t="s">
+        <v>548</v>
+      </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="25" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="B114" s="26" t="s">
         <v>53</v>
       </c>
       <c r="C114" s="26" t="s">
-        <v>546</v>
+        <v>307</v>
       </c>
       <c r="D114" s="27" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E114" s="26" t="s">
-        <v>548</v>
+        <v>297</v>
       </c>
       <c r="F114" s="26" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="G114" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H114" s="26" t="s">
-        <v>335</v>
+        <v>310</v>
       </c>
       <c r="I114" s="26" t="s">
         <v>86</v>
@@ -9550,34 +9599,32 @@
       <c r="L114" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="M114" s="26" t="s">
-        <v>550</v>
-      </c>
+      <c r="M114" s="26"/>
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="25" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B115" s="26" t="s">
         <v>53</v>
       </c>
       <c r="C115" s="26" t="s">
-        <v>546</v>
+        <v>553</v>
       </c>
       <c r="D115" s="27" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="E115" s="26" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="F115" s="26" t="s">
-        <v>124</v>
+        <v>556</v>
       </c>
       <c r="G115" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H115" s="26" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="I115" s="26" t="s">
         <v>86</v>
@@ -9589,119 +9636,121 @@
         <v>31</v>
       </c>
       <c r="L115" s="26" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="M115" s="26" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="25" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="B116" s="26" t="s">
         <v>53</v>
       </c>
       <c r="C116" s="26" t="s">
-        <v>102</v>
+        <v>553</v>
       </c>
       <c r="D116" s="27" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="E116" s="26" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
       <c r="F116" s="26" t="s">
-        <v>558</v>
+        <v>124</v>
       </c>
       <c r="G116" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H116" s="26" t="s">
-        <v>101</v>
+        <v>341</v>
       </c>
       <c r="I116" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="J116" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="K116" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="L116" s="26" t="s">
+        <v>20</v>
+      </c>
+      <c r="M116" s="26" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="25" t="s">
+        <v>562</v>
+      </c>
+      <c r="B117" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C117" s="26" t="s">
         <v>102</v>
       </c>
-      <c r="J116" s="26" t="s">
-        <v>103</v>
-      </c>
-      <c r="K116" s="26" t="s">
-        <v>33</v>
-      </c>
-      <c r="L116" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="M116" s="26" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A117" s="25" t="s">
-        <v>560</v>
-      </c>
-      <c r="B117" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="C117" s="26" t="s">
-        <v>561</v>
-      </c>
       <c r="D117" s="27" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="E117" s="26" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="F117" s="26" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="G117" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H117" s="26" t="s">
-        <v>342</v>
+        <v>101</v>
       </c>
       <c r="I117" s="26" t="s">
-        <v>336</v>
+        <v>102</v>
       </c>
       <c r="J117" s="26" t="s">
-        <v>124</v>
+        <v>103</v>
       </c>
       <c r="K117" s="26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L117" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="M117" s="26"/>
+        <v>18</v>
+      </c>
+      <c r="M117" s="26" t="s">
+        <v>566</v>
+      </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="25" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B118" s="26" t="s">
         <v>54</v>
       </c>
       <c r="C118" s="26" t="s">
-        <v>561</v>
+        <v>568</v>
       </c>
       <c r="D118" s="27" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="E118" s="26" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="F118" s="26" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="G118" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H118" s="26" t="s">
+        <v>348</v>
+      </c>
+      <c r="I118" s="26" t="s">
         <v>342</v>
-      </c>
-      <c r="I118" s="26" t="s">
-        <v>336</v>
       </c>
       <c r="J118" s="26" t="s">
         <v>124</v>
@@ -9716,31 +9765,31 @@
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="25" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="B119" s="26" t="s">
         <v>54</v>
       </c>
       <c r="C119" s="26" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="D119" s="27" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="E119" s="26" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="F119" s="26" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="G119" s="26" t="s">
-        <v>574</v>
+        <v>140</v>
       </c>
       <c r="H119" s="26" t="s">
-        <v>575</v>
+        <v>348</v>
       </c>
       <c r="I119" s="26" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="J119" s="26" t="s">
         <v>124</v>
@@ -9753,7 +9802,7 @@
       </c>
       <c r="M119" s="26"/>
     </row>
-    <row r="120" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="25" t="s">
         <v>576</v>
       </c>
@@ -9770,66 +9819,64 @@
         <v>579</v>
       </c>
       <c r="F120" s="26" t="s">
-        <v>24</v>
+        <v>580</v>
       </c>
       <c r="G120" s="26" t="s">
-        <v>100</v>
+        <v>581</v>
       </c>
       <c r="H120" s="26" t="s">
-        <v>85</v>
+        <v>582</v>
       </c>
       <c r="I120" s="26" t="s">
-        <v>86</v>
+        <v>342</v>
       </c>
       <c r="J120" s="26" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="K120" s="26" t="s">
         <v>31</v>
       </c>
       <c r="L120" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="M120" s="26" t="s">
-        <v>580</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="M120" s="26"/>
     </row>
     <row r="121" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="25" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B121" s="26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C121" s="26" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="D121" s="27" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E121" s="26" t="s">
-        <v>200</v>
+        <v>586</v>
       </c>
       <c r="F121" s="26" t="s">
-        <v>584</v>
+        <v>24</v>
       </c>
       <c r="G121" s="26" t="s">
-        <v>585</v>
+        <v>100</v>
       </c>
       <c r="H121" s="26" t="s">
-        <v>586</v>
+        <v>85</v>
       </c>
       <c r="I121" s="26" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="J121" s="26" t="s">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="K121" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L121" s="26" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M121" s="26" t="s">
         <v>587</v>
@@ -9855,10 +9902,10 @@
         <v>591</v>
       </c>
       <c r="G122" s="26" t="s">
-        <v>148</v>
+        <v>592</v>
       </c>
       <c r="H122" s="26" t="s">
-        <v>304</v>
+        <v>593</v>
       </c>
       <c r="I122" s="26" t="s">
         <v>22</v>
@@ -9873,33 +9920,33 @@
         <v>22</v>
       </c>
       <c r="M122" s="26" t="s">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="25" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B123" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C123" s="26" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="D123" s="27" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="E123" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F123" s="26" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="G123" s="26" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H123" s="26" t="s">
-        <v>202</v>
+        <v>310</v>
       </c>
       <c r="I123" s="26" t="s">
         <v>22</v>
@@ -9913,110 +9960,112 @@
       <c r="L123" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="M123" s="26"/>
+      <c r="M123" s="26" t="s">
+        <v>599</v>
+      </c>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="25" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B124" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C124" s="26" t="s">
-        <v>589</v>
+        <v>596</v>
       </c>
       <c r="D124" s="27" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="E124" s="26" t="s">
-        <v>598</v>
+        <v>200</v>
       </c>
       <c r="F124" s="26" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="G124" s="26" t="s">
-        <v>78</v>
+        <v>140</v>
       </c>
       <c r="H124" s="26" t="s">
-        <v>85</v>
+        <v>202</v>
       </c>
       <c r="I124" s="26" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="J124" s="26" t="s">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="K124" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L124" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M124" s="26"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="25" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="B125" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C125" s="26" t="s">
-        <v>601</v>
+        <v>596</v>
       </c>
       <c r="D125" s="27" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="E125" s="26" t="s">
-        <v>200</v>
+        <v>605</v>
       </c>
       <c r="F125" s="26" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="G125" s="26" t="s">
-        <v>100</v>
+        <v>78</v>
       </c>
       <c r="H125" s="26" t="s">
-        <v>304</v>
+        <v>85</v>
       </c>
       <c r="I125" s="26" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="J125" s="26" t="s">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="K125" s="26" t="s">
         <v>31</v>
       </c>
       <c r="L125" s="26" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="M125" s="26"/>
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="25" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="B126" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C126" s="26" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="D126" s="27" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E126" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F126" s="26" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="G126" s="26" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="H126" s="26" t="s">
-        <v>85</v>
+        <v>310</v>
       </c>
       <c r="I126" s="26" t="s">
         <v>22</v>
@@ -10030,28 +10079,26 @@
       <c r="L126" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="M126" s="26" t="s">
-        <v>607</v>
-      </c>
+      <c r="M126" s="26"/>
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="25" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="B127" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C127" s="26" t="s">
-        <v>601</v>
+        <v>608</v>
       </c>
       <c r="D127" s="27" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="E127" s="26" t="s">
-        <v>610</v>
+        <v>200</v>
       </c>
       <c r="F127" s="26" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="G127" s="26" t="s">
         <v>78</v>
@@ -10071,87 +10118,87 @@
       <c r="L127" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="M127" s="26"/>
-    </row>
-    <row r="128" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M127" s="26" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="25" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="B128" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C128" s="26" t="s">
-        <v>331</v>
+        <v>608</v>
       </c>
       <c r="D128" s="27" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
       <c r="E128" s="26" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="F128" s="26" t="s">
-        <v>24</v>
+        <v>618</v>
       </c>
       <c r="G128" s="26" t="s">
-        <v>334</v>
+        <v>78</v>
       </c>
       <c r="H128" s="26" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="I128" s="26" t="s">
-        <v>336</v>
+        <v>22</v>
       </c>
       <c r="J128" s="26" t="s">
-        <v>124</v>
+        <v>203</v>
       </c>
       <c r="K128" s="26" t="s">
         <v>31</v>
       </c>
       <c r="L128" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M128" s="26"/>
     </row>
-    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="129" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="25" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="B129" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C129" s="26" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="D129" s="27" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="E129" s="26" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="F129" s="26" t="s">
-        <v>618</v>
+        <v>24</v>
       </c>
       <c r="G129" s="26" t="s">
-        <v>619</v>
+        <v>340</v>
       </c>
       <c r="H129" s="26" t="s">
-        <v>620</v>
+        <v>124</v>
       </c>
       <c r="I129" s="26" t="s">
-        <v>22</v>
+        <v>342</v>
       </c>
       <c r="J129" s="26" t="s">
-        <v>203</v>
+        <v>124</v>
       </c>
       <c r="K129" s="26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L129" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="M129" s="26" t="s">
-        <v>621</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="M129" s="26"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="25" t="s">
@@ -10161,22 +10208,22 @@
         <v>55</v>
       </c>
       <c r="C130" s="26" t="s">
+        <v>337</v>
+      </c>
+      <c r="D130" s="27" t="s">
         <v>623</v>
       </c>
-      <c r="D130" s="27" t="s">
+      <c r="E130" s="26" t="s">
         <v>624</v>
-      </c>
-      <c r="E130" s="26" t="s">
-        <v>200</v>
       </c>
       <c r="F130" s="26" t="s">
         <v>625</v>
       </c>
       <c r="G130" s="26" t="s">
-        <v>124</v>
+        <v>626</v>
       </c>
       <c r="H130" s="26" t="s">
-        <v>124</v>
+        <v>627</v>
       </c>
       <c r="I130" s="26" t="s">
         <v>22</v>
@@ -10185,16 +10232,57 @@
         <v>203</v>
       </c>
       <c r="K130" s="26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L130" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="M130" s="26"/>
+      <c r="M130" s="26" t="s">
+        <v>628</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="25" t="s">
+        <v>629</v>
+      </c>
+      <c r="B131" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C131" s="26" t="s">
+        <v>630</v>
+      </c>
+      <c r="D131" s="27" t="s">
+        <v>631</v>
+      </c>
+      <c r="E131" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="F131" s="26" t="s">
+        <v>632</v>
+      </c>
+      <c r="G131" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="H131" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="I131" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J131" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K131" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="L131" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="M131" s="26"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:M130"/>
-  <conditionalFormatting sqref="L6:L330">
+  <autoFilter ref="A5:M131"/>
+  <conditionalFormatting sqref="L6:L331">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$L6="Verificado"</formula>
     </cfRule>
@@ -10217,17 +10305,17 @@
       <formula>$L6="Curado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K330">
+  <conditionalFormatting sqref="K6:K331">
     <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
       <formula>$K6="MVP"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K6:K330" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K6:K331" type="list">
       <formula1>"MVP,EUA,v2,v3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L6:L330" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L6:L331" type="list">
       <formula1>"Verificado,Confirmar,A mapear,Sem API,Pago,Derivado,Curado"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10268,12 +10356,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>626</v>
+        <v>633</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>627</v>
+        <v>634</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10334,28 +10422,28 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>628</v>
+        <v>635</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>629</v>
+        <v>636</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>630</v>
+        <v>637</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>632</v>
+        <v>639</v>
       </c>
       <c r="G6" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="I6" s="26" t="s">
         <v>165</v>
@@ -10373,22 +10461,22 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>634</v>
+        <v>641</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>636</v>
+        <v>643</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>637</v>
+        <v>644</v>
       </c>
       <c r="G7" s="26" t="s">
         <v>100</v>
@@ -10412,22 +10500,22 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>638</v>
+        <v>645</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>635</v>
+        <v>642</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>639</v>
+        <v>646</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>640</v>
+        <v>647</v>
       </c>
       <c r="G8" s="26" t="s">
         <v>100</v>
@@ -10451,22 +10539,22 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>641</v>
+        <v>648</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>642</v>
+        <v>649</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>643</v>
+        <v>650</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>644</v>
+        <v>651</v>
       </c>
       <c r="G9" s="26" t="s">
         <v>100</v>
@@ -10490,28 +10578,28 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>645</v>
+        <v>652</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>647</v>
+        <v>654</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>648</v>
+        <v>655</v>
       </c>
       <c r="G10" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="I10" s="26" t="s">
         <v>22</v>
@@ -10529,28 +10617,28 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>650</v>
+        <v>657</v>
       </c>
       <c r="B11" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>646</v>
+        <v>653</v>
       </c>
       <c r="D11" s="27" t="s">
-        <v>651</v>
+        <v>658</v>
       </c>
       <c r="E11" s="26" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>652</v>
+        <v>659</v>
       </c>
       <c r="G11" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="I11" s="26" t="s">
         <v>102</v>
@@ -10568,28 +10656,28 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>653</v>
+        <v>660</v>
       </c>
       <c r="B12" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>654</v>
+        <v>661</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>655</v>
+        <v>662</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>656</v>
+        <v>663</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>657</v>
+        <v>664</v>
       </c>
       <c r="G12" s="26" t="s">
         <v>148</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="I12" s="26" t="s">
         <v>102</v>
@@ -10607,19 +10695,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>658</v>
+        <v>665</v>
       </c>
       <c r="B13" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>660</v>
+        <v>667</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>661</v>
+        <v>668</v>
       </c>
       <c r="F13" s="26" t="s">
         <v>124</v>
@@ -10643,27 +10731,27 @@
         <v>20</v>
       </c>
       <c r="M13" s="26" t="s">
-        <v>662</v>
+        <v>669</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>663</v>
+        <v>670</v>
       </c>
       <c r="B14" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>659</v>
+        <v>666</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>664</v>
+        <v>671</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>666</v>
+        <v>673</v>
       </c>
       <c r="G14" s="26" t="s">
         <v>100</v>
@@ -10687,7 +10775,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>667</v>
+        <v>674</v>
       </c>
       <c r="B15" s="26" t="s">
         <v>46</v>
@@ -10696,13 +10784,13 @@
         <v>198</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>668</v>
+        <v>675</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>669</v>
+        <v>676</v>
       </c>
       <c r="G15" s="26" t="s">
         <v>100</v>
@@ -10726,22 +10814,22 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>670</v>
+        <v>677</v>
       </c>
       <c r="B16" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>672</v>
+        <v>679</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>673</v>
+        <v>680</v>
       </c>
       <c r="G16" s="26" t="s">
         <v>78</v>
@@ -10765,28 +10853,28 @@
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>674</v>
+        <v>681</v>
       </c>
       <c r="B17" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>675</v>
+        <v>682</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>676</v>
+        <v>683</v>
       </c>
       <c r="G17" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="I17" s="26" t="s">
         <v>79</v>
@@ -10804,22 +10892,22 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>677</v>
+        <v>684</v>
       </c>
       <c r="B18" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>678</v>
+        <v>685</v>
       </c>
       <c r="E18" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>679</v>
+        <v>686</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>100</v>
@@ -10843,22 +10931,22 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>680</v>
+        <v>687</v>
       </c>
       <c r="B19" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>671</v>
+        <v>678</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>681</v>
+        <v>688</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>682</v>
+        <v>689</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>683</v>
+        <v>690</v>
       </c>
       <c r="G19" s="26" t="s">
         <v>100</v>
@@ -10879,12 +10967,12 @@
         <v>18</v>
       </c>
       <c r="M19" s="26" t="s">
-        <v>684</v>
+        <v>691</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>685</v>
+        <v>692</v>
       </c>
       <c r="B20" s="26" t="s">
         <v>46</v>
@@ -10893,13 +10981,13 @@
         <v>198</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>686</v>
+        <v>693</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>687</v>
+        <v>694</v>
       </c>
       <c r="G20" s="26" t="s">
         <v>100</v>
@@ -10920,27 +11008,27 @@
         <v>12</v>
       </c>
       <c r="M20" s="26" t="s">
-        <v>688</v>
+        <v>695</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>689</v>
+        <v>696</v>
       </c>
       <c r="B21" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>692</v>
+        <v>699</v>
       </c>
       <c r="G21" s="26" t="s">
         <v>100</v>
@@ -10964,22 +11052,22 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>693</v>
+        <v>700</v>
       </c>
       <c r="B22" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>694</v>
+        <v>701</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>695</v>
+        <v>702</v>
       </c>
       <c r="G22" s="26" t="s">
         <v>100</v>
@@ -11000,27 +11088,27 @@
         <v>12</v>
       </c>
       <c r="M22" s="26" t="s">
-        <v>696</v>
+        <v>703</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>697</v>
+        <v>704</v>
       </c>
       <c r="B23" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>690</v>
+        <v>697</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>698</v>
+        <v>705</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>699</v>
+        <v>706</v>
       </c>
       <c r="G23" s="26" t="s">
         <v>100</v>
@@ -11044,22 +11132,22 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="25" t="s">
-        <v>700</v>
+        <v>707</v>
       </c>
       <c r="B24" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>702</v>
+        <v>709</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>704</v>
+        <v>711</v>
       </c>
       <c r="G24" s="26" t="s">
         <v>100</v>
@@ -11083,22 +11171,22 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="25" t="s">
-        <v>705</v>
+        <v>712</v>
       </c>
       <c r="B25" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>701</v>
+        <v>708</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>706</v>
+        <v>713</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>707</v>
+        <v>714</v>
       </c>
       <c r="G25" s="26" t="s">
         <v>100</v>
@@ -11122,22 +11210,22 @@
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="25" t="s">
-        <v>708</v>
+        <v>715</v>
       </c>
       <c r="B26" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>709</v>
+        <v>716</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>710</v>
+        <v>717</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>631</v>
+        <v>638</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>711</v>
+        <v>718</v>
       </c>
       <c r="G26" s="26" t="s">
         <v>100</v>
@@ -11161,7 +11249,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="25" t="s">
-        <v>712</v>
+        <v>719</v>
       </c>
       <c r="B27" s="26" t="s">
         <v>47</v>
@@ -11170,13 +11258,13 @@
         <v>144</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>713</v>
+        <v>720</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>714</v>
+        <v>721</v>
       </c>
       <c r="G27" s="26" t="s">
         <v>140</v>
@@ -11197,12 +11285,12 @@
         <v>12</v>
       </c>
       <c r="M27" s="26" t="s">
-        <v>715</v>
+        <v>722</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="25" t="s">
-        <v>716</v>
+        <v>723</v>
       </c>
       <c r="B28" s="26" t="s">
         <v>47</v>
@@ -11211,10 +11299,10 @@
         <v>144</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>717</v>
+        <v>724</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="F28" s="26" t="s">
         <v>124</v>
@@ -11238,12 +11326,12 @@
         <v>20</v>
       </c>
       <c r="M28" s="26" t="s">
-        <v>719</v>
+        <v>726</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="25" t="s">
-        <v>720</v>
+        <v>727</v>
       </c>
       <c r="B29" s="26" t="s">
         <v>47</v>
@@ -11252,13 +11340,13 @@
         <v>144</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>721</v>
+        <v>728</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>722</v>
+        <v>729</v>
       </c>
       <c r="G29" s="26" t="s">
         <v>100</v>
@@ -11279,27 +11367,27 @@
         <v>12</v>
       </c>
       <c r="M29" s="26" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="25" t="s">
-        <v>724</v>
+        <v>731</v>
       </c>
       <c r="B30" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="D30" s="27" t="s">
-        <v>726</v>
+        <v>733</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>727</v>
+        <v>734</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="G30" s="26" t="s">
         <v>100</v>
@@ -11323,19 +11411,19 @@
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="25" t="s">
-        <v>729</v>
+        <v>736</v>
       </c>
       <c r="B31" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>725</v>
+        <v>732</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>730</v>
+        <v>737</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>731</v>
+        <v>738</v>
       </c>
       <c r="F31" s="26" t="s">
         <v>124</v>
@@ -11344,7 +11432,7 @@
         <v>148</v>
       </c>
       <c r="H31" s="26" t="s">
-        <v>732</v>
+        <v>739</v>
       </c>
       <c r="I31" s="26" t="s">
         <v>79</v>
@@ -11362,7 +11450,7 @@
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="25" t="s">
-        <v>733</v>
+        <v>740</v>
       </c>
       <c r="B32" s="26" t="s">
         <v>45</v>
@@ -11371,19 +11459,19 @@
         <v>74</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>734</v>
+        <v>741</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>735</v>
+        <v>742</v>
       </c>
       <c r="G32" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H32" s="26" t="s">
-        <v>736</v>
+        <v>743</v>
       </c>
       <c r="I32" s="26" t="s">
         <v>79</v>
@@ -11401,7 +11489,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="25" t="s">
-        <v>737</v>
+        <v>744</v>
       </c>
       <c r="B33" s="26" t="s">
         <v>45</v>
@@ -11410,19 +11498,19 @@
         <v>74</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>738</v>
+        <v>745</v>
       </c>
       <c r="E33" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>739</v>
+        <v>746</v>
       </c>
       <c r="G33" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H33" s="26" t="s">
-        <v>740</v>
+        <v>747</v>
       </c>
       <c r="I33" s="26" t="s">
         <v>22</v>
@@ -11440,7 +11528,7 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="25" t="s">
-        <v>741</v>
+        <v>748</v>
       </c>
       <c r="B34" s="26" t="s">
         <v>45</v>
@@ -11449,19 +11537,19 @@
         <v>74</v>
       </c>
       <c r="D34" s="27" t="s">
-        <v>742</v>
+        <v>749</v>
       </c>
       <c r="E34" s="26" t="s">
-        <v>743</v>
+        <v>750</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>744</v>
+        <v>751</v>
       </c>
       <c r="G34" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H34" s="26" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="I34" s="26" t="s">
         <v>79</v>
@@ -11479,7 +11567,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="25" t="s">
-        <v>746</v>
+        <v>753</v>
       </c>
       <c r="B35" s="26" t="s">
         <v>45</v>
@@ -11488,19 +11576,19 @@
         <v>74</v>
       </c>
       <c r="D35" s="27" t="s">
-        <v>747</v>
+        <v>754</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>748</v>
+        <v>755</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>749</v>
+        <v>756</v>
       </c>
       <c r="G35" s="26" t="s">
-        <v>750</v>
+        <v>757</v>
       </c>
       <c r="H35" s="26" t="s">
-        <v>751</v>
+        <v>758</v>
       </c>
       <c r="I35" s="26" t="s">
         <v>86</v>
@@ -11515,33 +11603,33 @@
         <v>12</v>
       </c>
       <c r="M35" s="26" t="s">
-        <v>752</v>
+        <v>759</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="25" t="s">
-        <v>753</v>
+        <v>760</v>
       </c>
       <c r="B36" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="D36" s="27" t="s">
-        <v>755</v>
+        <v>762</v>
       </c>
       <c r="E36" s="26" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>757</v>
+        <v>764</v>
       </c>
       <c r="G36" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H36" s="26" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="I36" s="26" t="s">
         <v>102</v>
@@ -11559,28 +11647,28 @@
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="25" t="s">
-        <v>758</v>
+        <v>765</v>
       </c>
       <c r="B37" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>754</v>
+        <v>761</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>759</v>
+        <v>766</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>760</v>
+        <v>767</v>
       </c>
       <c r="G37" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H37" s="26" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="I37" s="26" t="s">
         <v>102</v>
@@ -11598,19 +11686,19 @@
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="25" t="s">
-        <v>761</v>
+        <v>768</v>
       </c>
       <c r="B38" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="D38" s="27" t="s">
+        <v>770</v>
+      </c>
+      <c r="E38" s="26" t="s">
         <v>763</v>
-      </c>
-      <c r="E38" s="26" t="s">
-        <v>756</v>
       </c>
       <c r="F38" s="26" t="s">
         <v>16</v>
@@ -11619,7 +11707,7 @@
         <v>100</v>
       </c>
       <c r="H38" s="26" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="I38" s="26" t="s">
         <v>102</v>
@@ -11637,28 +11725,28 @@
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="25" t="s">
-        <v>764</v>
+        <v>771</v>
       </c>
       <c r="B39" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>765</v>
+        <v>772</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>766</v>
+        <v>773</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>767</v>
+        <v>774</v>
       </c>
       <c r="G39" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H39" s="26" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="I39" s="26" t="s">
         <v>102</v>
@@ -11676,28 +11764,28 @@
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="25" t="s">
-        <v>768</v>
+        <v>775</v>
       </c>
       <c r="B40" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>770</v>
+        <v>777</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>771</v>
+        <v>778</v>
       </c>
       <c r="G40" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H40" s="26" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="I40" s="26" t="s">
         <v>102</v>
@@ -11715,28 +11803,28 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="25" t="s">
-        <v>772</v>
+        <v>779</v>
       </c>
       <c r="B41" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>769</v>
+        <v>776</v>
       </c>
       <c r="D41" s="27" t="s">
-        <v>773</v>
+        <v>780</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>774</v>
+        <v>781</v>
       </c>
       <c r="G41" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H41" s="26" t="s">
-        <v>649</v>
+        <v>656</v>
       </c>
       <c r="I41" s="26" t="s">
         <v>86</v>
@@ -11751,27 +11839,27 @@
         <v>12</v>
       </c>
       <c r="M41" s="26" t="s">
-        <v>775</v>
+        <v>782</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="25" t="s">
-        <v>776</v>
+        <v>783</v>
       </c>
       <c r="B42" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>777</v>
+        <v>784</v>
       </c>
       <c r="D42" s="27" t="s">
-        <v>778</v>
+        <v>785</v>
       </c>
       <c r="E42" s="26" t="s">
-        <v>779</v>
+        <v>786</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>780</v>
+        <v>787</v>
       </c>
       <c r="G42" s="26" t="s">
         <v>100</v>
@@ -11792,24 +11880,24 @@
         <v>12</v>
       </c>
       <c r="M42" s="26" t="s">
-        <v>723</v>
+        <v>730</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="25" t="s">
-        <v>781</v>
+        <v>788</v>
       </c>
       <c r="B43" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="D43" s="27" t="s">
-        <v>783</v>
+        <v>790</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>784</v>
+        <v>791</v>
       </c>
       <c r="F43" s="26" t="s">
         <v>124</v>
@@ -11833,27 +11921,27 @@
         <v>20</v>
       </c>
       <c r="M43" s="26" t="s">
-        <v>785</v>
+        <v>792</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="25" t="s">
-        <v>786</v>
+        <v>793</v>
       </c>
       <c r="B44" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>782</v>
+        <v>789</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>787</v>
+        <v>794</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>788</v>
+        <v>795</v>
       </c>
       <c r="G44" s="26" t="s">
         <v>100</v>
@@ -11874,12 +11962,12 @@
         <v>16</v>
       </c>
       <c r="M44" s="26" t="s">
-        <v>789</v>
+        <v>796</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="25" t="s">
-        <v>790</v>
+        <v>797</v>
       </c>
       <c r="B45" s="26" t="s">
         <v>56</v>
@@ -11888,13 +11976,13 @@
         <v>54</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>791</v>
+        <v>798</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>792</v>
+        <v>799</v>
       </c>
       <c r="G45" s="26" t="s">
         <v>140</v>
@@ -11918,28 +12006,28 @@
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="25" t="s">
-        <v>793</v>
+        <v>800</v>
       </c>
       <c r="B46" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>794</v>
+        <v>801</v>
       </c>
       <c r="E46" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>795</v>
+        <v>802</v>
       </c>
       <c r="G46" s="26" t="s">
         <v>148</v>
       </c>
       <c r="H46" s="26" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="I46" s="26" t="s">
         <v>165</v>
@@ -11957,31 +12045,31 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="25" t="s">
-        <v>796</v>
+        <v>803</v>
       </c>
       <c r="B47" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>797</v>
+        <v>804</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>798</v>
+        <v>805</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>799</v>
+        <v>806</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>800</v>
+        <v>807</v>
       </c>
       <c r="G47" s="26" t="s">
-        <v>619</v>
+        <v>626</v>
       </c>
       <c r="H47" s="26" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="I47" s="26" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="J47" s="26" t="s">
         <v>124</v>
@@ -11993,27 +12081,27 @@
         <v>14</v>
       </c>
       <c r="M47" s="26" t="s">
-        <v>801</v>
+        <v>808</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="25" t="s">
-        <v>802</v>
+        <v>809</v>
       </c>
       <c r="B48" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="D48" s="27" t="s">
-        <v>803</v>
+        <v>810</v>
       </c>
       <c r="E48" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F48" s="26" t="s">
-        <v>804</v>
+        <v>811</v>
       </c>
       <c r="G48" s="26" t="s">
         <v>78</v>
@@ -12034,27 +12122,27 @@
         <v>12</v>
       </c>
       <c r="M48" s="26" t="s">
-        <v>805</v>
+        <v>812</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="25" t="s">
-        <v>806</v>
+        <v>813</v>
       </c>
       <c r="B49" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>808</v>
+        <v>815</v>
       </c>
       <c r="E49" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F49" s="26" t="s">
-        <v>809</v>
+        <v>816</v>
       </c>
       <c r="G49" s="26" t="s">
         <v>140</v>
@@ -12078,22 +12166,22 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="25" t="s">
-        <v>810</v>
+        <v>817</v>
       </c>
       <c r="B50" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="D50" s="27" t="s">
-        <v>811</v>
+        <v>818</v>
       </c>
       <c r="E50" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F50" s="26" t="s">
-        <v>812</v>
+        <v>819</v>
       </c>
       <c r="G50" s="26" t="s">
         <v>140</v>
@@ -12117,19 +12205,19 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="25" t="s">
-        <v>813</v>
+        <v>820</v>
       </c>
       <c r="B51" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>807</v>
+        <v>814</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>814</v>
+        <v>821</v>
       </c>
       <c r="E51" s="26" t="s">
-        <v>718</v>
+        <v>725</v>
       </c>
       <c r="F51" s="26" t="s">
         <v>124</v>
@@ -12156,19 +12244,19 @@
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="25" t="s">
-        <v>815</v>
+        <v>822</v>
       </c>
       <c r="B52" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>816</v>
+        <v>823</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>817</v>
+        <v>824</v>
       </c>
       <c r="E52" s="26" t="s">
-        <v>818</v>
+        <v>825</v>
       </c>
       <c r="F52" s="26" t="s">
         <v>124</v>
@@ -12192,27 +12280,27 @@
         <v>20</v>
       </c>
       <c r="M52" s="26" t="s">
-        <v>819</v>
+        <v>826</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="25" t="s">
-        <v>820</v>
+        <v>827</v>
       </c>
       <c r="B53" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>821</v>
+        <v>828</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>822</v>
+        <v>829</v>
       </c>
       <c r="F53" s="26" t="s">
-        <v>823</v>
+        <v>830</v>
       </c>
       <c r="G53" s="26" t="s">
         <v>148</v>
@@ -12236,28 +12324,28 @@
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="25" t="s">
-        <v>824</v>
+        <v>831</v>
       </c>
       <c r="B54" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C54" s="26" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D54" s="27" t="s">
-        <v>825</v>
+        <v>832</v>
       </c>
       <c r="E54" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F54" s="26" t="s">
-        <v>826</v>
+        <v>833</v>
       </c>
       <c r="G54" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H54" s="26" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="I54" s="26" t="s">
         <v>165</v>
@@ -12275,28 +12363,28 @@
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="25" t="s">
-        <v>827</v>
+        <v>834</v>
       </c>
       <c r="B55" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="D55" s="27" t="s">
-        <v>828</v>
+        <v>835</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>829</v>
+        <v>836</v>
       </c>
       <c r="F55" s="26" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="G55" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H55" s="26" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="I55" s="26" t="s">
         <v>165</v>
@@ -12311,27 +12399,27 @@
         <v>18</v>
       </c>
       <c r="M55" s="26" t="s">
-        <v>831</v>
+        <v>838</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="25" t="s">
-        <v>832</v>
+        <v>839</v>
       </c>
       <c r="B56" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="D56" s="27" t="s">
-        <v>833</v>
+        <v>840</v>
       </c>
       <c r="E56" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F56" s="26" t="s">
-        <v>834</v>
+        <v>841</v>
       </c>
       <c r="G56" s="26" t="s">
         <v>148</v>
@@ -12355,22 +12443,22 @@
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="25" t="s">
-        <v>835</v>
+        <v>842</v>
       </c>
       <c r="B57" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>836</v>
+        <v>843</v>
       </c>
       <c r="E57" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F57" s="26" t="s">
-        <v>837</v>
+        <v>844</v>
       </c>
       <c r="G57" s="26" t="s">
         <v>148</v>
@@ -12394,22 +12482,22 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="25" t="s">
-        <v>838</v>
+        <v>845</v>
       </c>
       <c r="B58" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>839</v>
+        <v>846</v>
       </c>
       <c r="E58" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F58" s="26" t="s">
-        <v>840</v>
+        <v>847</v>
       </c>
       <c r="G58" s="26" t="s">
         <v>78</v>
@@ -12433,22 +12521,22 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="25" t="s">
-        <v>841</v>
+        <v>848</v>
       </c>
       <c r="B59" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="D59" s="27" t="s">
-        <v>842</v>
+        <v>849</v>
       </c>
       <c r="E59" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F59" s="26" t="s">
-        <v>843</v>
+        <v>850</v>
       </c>
       <c r="G59" s="26" t="s">
         <v>78</v>
@@ -12472,28 +12560,28 @@
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="25" t="s">
-        <v>844</v>
+        <v>851</v>
       </c>
       <c r="B60" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C60" s="26" t="s">
-        <v>845</v>
+        <v>852</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>846</v>
+        <v>853</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F60" s="26" t="s">
-        <v>847</v>
+        <v>854</v>
       </c>
       <c r="G60" s="26" t="s">
-        <v>848</v>
+        <v>855</v>
       </c>
       <c r="H60" s="26" t="s">
-        <v>849</v>
+        <v>856</v>
       </c>
       <c r="I60" s="26" t="s">
         <v>79</v>
@@ -12508,33 +12596,33 @@
         <v>12</v>
       </c>
       <c r="M60" s="26" t="s">
-        <v>850</v>
+        <v>857</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="25" t="s">
-        <v>851</v>
+        <v>858</v>
       </c>
       <c r="B61" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>852</v>
+        <v>859</v>
       </c>
       <c r="D61" s="27" t="s">
-        <v>853</v>
+        <v>860</v>
       </c>
       <c r="E61" s="26" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="F61" s="26" t="s">
-        <v>854</v>
+        <v>861</v>
       </c>
       <c r="G61" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H61" s="26" t="s">
-        <v>855</v>
+        <v>862</v>
       </c>
       <c r="I61" s="26" t="s">
         <v>102</v>
@@ -12552,28 +12640,28 @@
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="25" t="s">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="B62" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C62" s="26" t="s">
-        <v>762</v>
+        <v>769</v>
       </c>
       <c r="D62" s="27" t="s">
-        <v>857</v>
+        <v>864</v>
       </c>
       <c r="E62" s="26" t="s">
-        <v>858</v>
+        <v>865</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>859</v>
+        <v>866</v>
       </c>
       <c r="G62" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H62" s="26" t="s">
-        <v>633</v>
+        <v>640</v>
       </c>
       <c r="I62" s="26" t="s">
         <v>102</v>
@@ -12588,27 +12676,27 @@
         <v>20</v>
       </c>
       <c r="M62" s="26" t="s">
-        <v>860</v>
+        <v>867</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="25" t="s">
-        <v>861</v>
+        <v>868</v>
       </c>
       <c r="B63" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C63" s="26" t="s">
-        <v>862</v>
+        <v>869</v>
       </c>
       <c r="D63" s="27" t="s">
-        <v>863</v>
+        <v>870</v>
       </c>
       <c r="E63" s="26" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="F63" s="26" t="s">
-        <v>864</v>
+        <v>871</v>
       </c>
       <c r="G63" s="26" t="s">
         <v>78</v>
@@ -12632,22 +12720,22 @@
     </row>
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="25" t="s">
-        <v>865</v>
+        <v>872</v>
       </c>
       <c r="B64" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C64" s="26" t="s">
-        <v>866</v>
+        <v>873</v>
       </c>
       <c r="D64" s="27" t="s">
-        <v>867</v>
+        <v>874</v>
       </c>
       <c r="E64" s="26" t="s">
-        <v>868</v>
+        <v>875</v>
       </c>
       <c r="F64" s="26" t="s">
-        <v>728</v>
+        <v>735</v>
       </c>
       <c r="G64" s="26" t="s">
         <v>100</v>
@@ -12671,22 +12759,22 @@
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="25" t="s">
-        <v>869</v>
+        <v>876</v>
       </c>
       <c r="B65" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>870</v>
+        <v>877</v>
       </c>
       <c r="D65" s="27" t="s">
-        <v>871</v>
+        <v>878</v>
       </c>
       <c r="E65" s="26" t="s">
-        <v>872</v>
+        <v>879</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>873</v>
+        <v>880</v>
       </c>
       <c r="G65" s="26" t="s">
         <v>100</v>
@@ -12710,19 +12798,19 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="25" t="s">
-        <v>874</v>
+        <v>881</v>
       </c>
       <c r="B66" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C66" s="26" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D66" s="27" t="s">
-        <v>875</v>
+        <v>882</v>
       </c>
       <c r="E66" s="26" t="s">
-        <v>876</v>
+        <v>883</v>
       </c>
       <c r="F66" s="26" t="s">
         <v>124</v>
@@ -12749,7 +12837,7 @@
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="25" t="s">
-        <v>877</v>
+        <v>884</v>
       </c>
       <c r="B67" s="26" t="s">
         <v>58</v>
@@ -12758,13 +12846,13 @@
         <v>127</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>878</v>
+        <v>885</v>
       </c>
       <c r="E67" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>879</v>
+        <v>886</v>
       </c>
       <c r="G67" s="26" t="s">
         <v>100</v>
@@ -12785,12 +12873,12 @@
         <v>12</v>
       </c>
       <c r="M67" s="26" t="s">
-        <v>880</v>
+        <v>887</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="25" t="s">
-        <v>881</v>
+        <v>888</v>
       </c>
       <c r="B68" s="26" t="s">
         <v>58</v>
@@ -12799,13 +12887,13 @@
         <v>127</v>
       </c>
       <c r="D68" s="27" t="s">
-        <v>882</v>
+        <v>889</v>
       </c>
       <c r="E68" s="26" t="s">
-        <v>665</v>
+        <v>672</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>883</v>
+        <v>890</v>
       </c>
       <c r="G68" s="26" t="s">
         <v>100</v>
@@ -12829,28 +12917,28 @@
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="25" t="s">
-        <v>884</v>
+        <v>891</v>
       </c>
       <c r="B69" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="D69" s="27" t="s">
-        <v>885</v>
+        <v>892</v>
       </c>
       <c r="E69" s="26" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>887</v>
+        <v>894</v>
       </c>
       <c r="G69" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H69" s="26" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="I69" s="26" t="s">
         <v>165</v>
@@ -12868,28 +12956,28 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="25" t="s">
-        <v>888</v>
+        <v>895</v>
       </c>
       <c r="B70" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C70" s="26" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="D70" s="27" t="s">
-        <v>889</v>
+        <v>896</v>
       </c>
       <c r="E70" s="26" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>890</v>
+        <v>897</v>
       </c>
       <c r="G70" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H70" s="26" t="s">
-        <v>891</v>
+        <v>898</v>
       </c>
       <c r="I70" s="26" t="s">
         <v>86</v>
@@ -12907,22 +12995,22 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="25" t="s">
-        <v>892</v>
+        <v>899</v>
       </c>
       <c r="B71" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C71" s="26" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>893</v>
+        <v>900</v>
       </c>
       <c r="E71" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>894</v>
+        <v>901</v>
       </c>
       <c r="G71" s="26" t="s">
         <v>78</v>
@@ -12946,22 +13034,22 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="25" t="s">
-        <v>895</v>
+        <v>902</v>
       </c>
       <c r="B72" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C72" s="26" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>896</v>
+        <v>903</v>
       </c>
       <c r="E72" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>897</v>
+        <v>904</v>
       </c>
       <c r="G72" s="26" t="s">
         <v>78</v>
@@ -12985,22 +13073,22 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="25" t="s">
-        <v>898</v>
+        <v>905</v>
       </c>
       <c r="B73" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C73" s="26" t="s">
-        <v>899</v>
+        <v>906</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>900</v>
+        <v>907</v>
       </c>
       <c r="E73" s="26" t="s">
-        <v>901</v>
+        <v>908</v>
       </c>
       <c r="F73" s="26" t="s">
-        <v>902</v>
+        <v>909</v>
       </c>
       <c r="G73" s="26" t="s">
         <v>78</v>
@@ -13024,28 +13112,28 @@
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="25" t="s">
-        <v>903</v>
+        <v>910</v>
       </c>
       <c r="B74" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C74" s="26" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D74" s="27" t="s">
-        <v>904</v>
+        <v>911</v>
       </c>
       <c r="E74" s="26" t="s">
-        <v>905</v>
+        <v>912</v>
       </c>
       <c r="F74" s="26" t="s">
-        <v>906</v>
+        <v>913</v>
       </c>
       <c r="G74" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H74" s="26" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="I74" s="26" t="s">
         <v>165</v>
@@ -13063,25 +13151,25 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="25" t="s">
-        <v>907</v>
+        <v>914</v>
       </c>
       <c r="B75" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C75" s="26" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D75" s="27" t="s">
-        <v>908</v>
+        <v>915</v>
       </c>
       <c r="E75" s="26" t="s">
-        <v>909</v>
+        <v>916</v>
       </c>
       <c r="F75" s="26" t="s">
-        <v>830</v>
+        <v>837</v>
       </c>
       <c r="G75" s="26" t="s">
-        <v>910</v>
+        <v>917</v>
       </c>
       <c r="H75" s="26" t="s">
         <v>85</v>
@@ -13102,22 +13190,22 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="25" t="s">
-        <v>911</v>
+        <v>918</v>
       </c>
       <c r="B76" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C76" s="26" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D76" s="27" t="s">
-        <v>912</v>
+        <v>919</v>
       </c>
       <c r="E76" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>913</v>
+        <v>920</v>
       </c>
       <c r="G76" s="26" t="s">
         <v>78</v>
@@ -13141,28 +13229,28 @@
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="25" t="s">
-        <v>914</v>
+        <v>921</v>
       </c>
       <c r="B77" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C77" s="26" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="D77" s="27" t="s">
-        <v>916</v>
+        <v>923</v>
       </c>
       <c r="E77" s="26" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>917</v>
+        <v>924</v>
       </c>
       <c r="G77" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H77" s="26" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="I77" s="26" t="s">
         <v>102</v>
@@ -13180,22 +13268,22 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="25" t="s">
-        <v>918</v>
+        <v>925</v>
       </c>
       <c r="B78" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C78" s="26" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="D78" s="27" t="s">
-        <v>919</v>
+        <v>926</v>
       </c>
       <c r="E78" s="26" t="s">
-        <v>920</v>
+        <v>927</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>921</v>
+        <v>928</v>
       </c>
       <c r="G78" s="26" t="s">
         <v>78</v>
@@ -13216,33 +13304,33 @@
         <v>22</v>
       </c>
       <c r="M78" s="26" t="s">
-        <v>922</v>
+        <v>929</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="25" t="s">
-        <v>923</v>
+        <v>930</v>
       </c>
       <c r="B79" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C79" s="26" t="s">
-        <v>915</v>
+        <v>922</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>926</v>
+        <v>933</v>
       </c>
       <c r="G79" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H79" s="26" t="s">
-        <v>467</v>
+        <v>474</v>
       </c>
       <c r="I79" s="26" t="s">
         <v>102</v>
@@ -13260,22 +13348,22 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="25" t="s">
-        <v>927</v>
+        <v>934</v>
       </c>
       <c r="B80" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C80" s="26" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="D80" s="27" t="s">
-        <v>929</v>
+        <v>936</v>
       </c>
       <c r="E80" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F80" s="26" t="s">
-        <v>930</v>
+        <v>937</v>
       </c>
       <c r="G80" s="26" t="s">
         <v>78</v>
@@ -13299,28 +13387,28 @@
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="25" t="s">
-        <v>931</v>
+        <v>938</v>
       </c>
       <c r="B81" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C81" s="26" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>932</v>
+        <v>939</v>
       </c>
       <c r="E81" s="26" t="s">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="F81" s="26" t="s">
-        <v>933</v>
+        <v>940</v>
       </c>
       <c r="G81" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H81" s="26" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="I81" s="26" t="s">
         <v>102</v>
@@ -13338,22 +13426,22 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="25" t="s">
-        <v>934</v>
+        <v>941</v>
       </c>
       <c r="B82" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C82" s="26" t="s">
-        <v>527</v>
+        <v>534</v>
       </c>
       <c r="D82" s="27" t="s">
-        <v>935</v>
+        <v>942</v>
       </c>
       <c r="E82" s="26" t="s">
-        <v>936</v>
+        <v>943</v>
       </c>
       <c r="F82" s="26" t="s">
-        <v>937</v>
+        <v>944</v>
       </c>
       <c r="G82" s="26" t="s">
         <v>100</v>
@@ -13377,19 +13465,19 @@
     </row>
     <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="25" t="s">
-        <v>938</v>
+        <v>945</v>
       </c>
       <c r="B83" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C83" s="26" t="s">
-        <v>939</v>
+        <v>946</v>
       </c>
       <c r="D83" s="27" t="s">
-        <v>940</v>
+        <v>947</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>886</v>
+        <v>893</v>
       </c>
       <c r="F83" s="26" t="s">
         <v>16</v>
@@ -13398,7 +13486,7 @@
         <v>78</v>
       </c>
       <c r="H83" s="26" t="s">
-        <v>745</v>
+        <v>752</v>
       </c>
       <c r="I83" s="26" t="s">
         <v>165</v>
@@ -13416,19 +13504,19 @@
     </row>
     <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="25" t="s">
-        <v>941</v>
+        <v>948</v>
       </c>
       <c r="B84" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C84" s="26" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="D84" s="27" t="s">
-        <v>942</v>
+        <v>949</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>943</v>
+        <v>950</v>
       </c>
       <c r="F84" s="26" t="s">
         <v>124</v>
@@ -13437,7 +13525,7 @@
         <v>100</v>
       </c>
       <c r="H84" s="26" t="s">
-        <v>944</v>
+        <v>951</v>
       </c>
       <c r="I84" s="26" t="s">
         <v>102</v>
@@ -13452,27 +13540,27 @@
         <v>20</v>
       </c>
       <c r="M84" s="26" t="s">
-        <v>945</v>
+        <v>952</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="25" t="s">
-        <v>946</v>
+        <v>953</v>
       </c>
       <c r="B85" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C85" s="26" t="s">
-        <v>396</v>
+        <v>402</v>
       </c>
       <c r="D85" s="27" t="s">
-        <v>947</v>
+        <v>954</v>
       </c>
       <c r="E85" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F85" s="26" t="s">
-        <v>948</v>
+        <v>955</v>
       </c>
       <c r="G85" s="26" t="s">
         <v>78</v>
@@ -13496,28 +13584,28 @@
     </row>
     <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="25" t="s">
-        <v>949</v>
+        <v>956</v>
       </c>
       <c r="B86" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C86" s="26" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="D86" s="27" t="s">
-        <v>950</v>
+        <v>957</v>
       </c>
       <c r="E86" s="26" t="s">
-        <v>951</v>
+        <v>958</v>
       </c>
       <c r="F86" s="26" t="s">
-        <v>952</v>
+        <v>959</v>
       </c>
       <c r="G86" s="26" t="s">
-        <v>953</v>
+        <v>960</v>
       </c>
       <c r="H86" s="26" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="I86" s="26" t="s">
         <v>86</v>
@@ -13535,28 +13623,28 @@
     </row>
     <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="25" t="s">
-        <v>954</v>
+        <v>961</v>
       </c>
       <c r="B87" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C87" s="26" t="s">
-        <v>414</v>
+        <v>420</v>
       </c>
       <c r="D87" s="27" t="s">
-        <v>955</v>
+        <v>962</v>
       </c>
       <c r="E87" s="26" t="s">
-        <v>956</v>
+        <v>963</v>
       </c>
       <c r="F87" s="26" t="s">
-        <v>420</v>
+        <v>426</v>
       </c>
       <c r="G87" s="26" t="s">
-        <v>957</v>
+        <v>964</v>
       </c>
       <c r="H87" s="26" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="I87" s="26" t="s">
         <v>86</v>
@@ -13571,33 +13659,33 @@
         <v>18</v>
       </c>
       <c r="M87" s="26" t="s">
-        <v>958</v>
+        <v>965</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="25" t="s">
-        <v>959</v>
+        <v>966</v>
       </c>
       <c r="B88" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C88" s="26" t="s">
-        <v>960</v>
+        <v>967</v>
       </c>
       <c r="D88" s="27" t="s">
-        <v>961</v>
+        <v>968</v>
       </c>
       <c r="E88" s="26" t="s">
-        <v>756</v>
+        <v>763</v>
       </c>
       <c r="F88" s="26" t="s">
-        <v>962</v>
+        <v>969</v>
       </c>
       <c r="G88" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H88" s="26" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="I88" s="26" t="s">
         <v>102</v>
@@ -13615,22 +13703,22 @@
     </row>
     <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="25" t="s">
-        <v>963</v>
+        <v>970</v>
       </c>
       <c r="B89" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C89" s="26" t="s">
-        <v>960</v>
+        <v>967</v>
       </c>
       <c r="D89" s="27" t="s">
-        <v>964</v>
+        <v>971</v>
       </c>
       <c r="E89" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F89" s="26" t="s">
-        <v>965</v>
+        <v>972</v>
       </c>
       <c r="G89" s="26" t="s">
         <v>78</v>
@@ -13654,28 +13742,28 @@
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="25" t="s">
-        <v>966</v>
+        <v>973</v>
       </c>
       <c r="B90" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C90" s="26" t="s">
-        <v>960</v>
+        <v>967</v>
       </c>
       <c r="D90" s="27" t="s">
-        <v>967</v>
+        <v>974</v>
       </c>
       <c r="E90" s="26" t="s">
-        <v>968</v>
+        <v>975</v>
       </c>
       <c r="F90" s="26" t="s">
-        <v>969</v>
+        <v>976</v>
       </c>
       <c r="G90" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H90" s="26" t="s">
-        <v>427</v>
+        <v>433</v>
       </c>
       <c r="I90" s="26" t="s">
         <v>102</v>
@@ -13693,22 +13781,22 @@
     </row>
     <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="25" t="s">
-        <v>970</v>
+        <v>977</v>
       </c>
       <c r="B91" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>960</v>
+        <v>967</v>
       </c>
       <c r="D91" s="27" t="s">
-        <v>971</v>
+        <v>978</v>
       </c>
       <c r="E91" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F91" s="26" t="s">
-        <v>972</v>
+        <v>979</v>
       </c>
       <c r="G91" s="26" t="s">
         <v>78</v>
@@ -13729,33 +13817,33 @@
         <v>22</v>
       </c>
       <c r="M91" s="26" t="s">
-        <v>973</v>
+        <v>980</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="25" t="s">
-        <v>974</v>
+        <v>981</v>
       </c>
       <c r="B92" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C92" s="26" t="s">
-        <v>975</v>
+        <v>982</v>
       </c>
       <c r="D92" s="27" t="s">
-        <v>976</v>
+        <v>983</v>
       </c>
       <c r="E92" s="26" t="s">
-        <v>977</v>
+        <v>984</v>
       </c>
       <c r="F92" s="26" t="s">
-        <v>978</v>
+        <v>985</v>
       </c>
       <c r="G92" s="26" t="s">
         <v>148</v>
       </c>
       <c r="H92" s="26" t="s">
-        <v>979</v>
+        <v>986</v>
       </c>
       <c r="I92" s="26" t="s">
         <v>165</v>
@@ -13770,24 +13858,24 @@
         <v>16</v>
       </c>
       <c r="M92" s="26" t="s">
-        <v>980</v>
+        <v>987</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="25" t="s">
-        <v>981</v>
+        <v>988</v>
       </c>
       <c r="B93" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C93" s="26" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="D93" s="27" t="s">
-        <v>982</v>
+        <v>989</v>
       </c>
       <c r="E93" s="26" t="s">
-        <v>983</v>
+        <v>990</v>
       </c>
       <c r="F93" s="26" t="s">
         <v>124</v>
@@ -13811,27 +13899,27 @@
         <v>20</v>
       </c>
       <c r="M93" s="26" t="s">
-        <v>984</v>
+        <v>991</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="25" t="s">
-        <v>985</v>
+        <v>992</v>
       </c>
       <c r="B94" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C94" s="26" t="s">
-        <v>448</v>
+        <v>455</v>
       </c>
       <c r="D94" s="27" t="s">
-        <v>986</v>
+        <v>993</v>
       </c>
       <c r="E94" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F94" s="26" t="s">
-        <v>987</v>
+        <v>994</v>
       </c>
       <c r="G94" s="26" t="s">
         <v>140</v>
@@ -13852,27 +13940,27 @@
         <v>12</v>
       </c>
       <c r="M94" s="26" t="s">
-        <v>988</v>
+        <v>995</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="25" t="s">
-        <v>989</v>
+        <v>996</v>
       </c>
       <c r="B95" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C95" s="26" t="s">
-        <v>990</v>
+        <v>997</v>
       </c>
       <c r="D95" s="27" t="s">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="E95" s="26" t="s">
-        <v>992</v>
+        <v>999</v>
       </c>
       <c r="F95" s="26" t="s">
-        <v>993</v>
+        <v>1000</v>
       </c>
       <c r="G95" s="26" t="s">
         <v>140</v>
@@ -13896,19 +13984,19 @@
     </row>
     <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="25" t="s">
-        <v>994</v>
+        <v>1001</v>
       </c>
       <c r="B96" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C96" s="26" t="s">
+        <v>997</v>
+      </c>
+      <c r="D96" s="27" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E96" s="26" t="s">
         <v>990</v>
-      </c>
-      <c r="D96" s="27" t="s">
-        <v>995</v>
-      </c>
-      <c r="E96" s="26" t="s">
-        <v>983</v>
       </c>
       <c r="F96" s="26" t="s">
         <v>124</v>
@@ -13935,22 +14023,22 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="25" t="s">
-        <v>996</v>
+        <v>1003</v>
       </c>
       <c r="B97" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C97" s="26" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D97" s="27" t="s">
-        <v>997</v>
+        <v>1004</v>
       </c>
       <c r="E97" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F97" s="26" t="s">
-        <v>998</v>
+        <v>1005</v>
       </c>
       <c r="G97" s="26" t="s">
         <v>140</v>
@@ -13971,27 +14059,27 @@
         <v>12</v>
       </c>
       <c r="M97" s="26" t="s">
-        <v>999</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="25" t="s">
-        <v>1000</v>
+        <v>1007</v>
       </c>
       <c r="B98" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C98" s="26" t="s">
-        <v>928</v>
+        <v>935</v>
       </c>
       <c r="D98" s="27" t="s">
-        <v>1001</v>
+        <v>1008</v>
       </c>
       <c r="E98" s="26" t="s">
-        <v>1002</v>
+        <v>1009</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>1003</v>
+        <v>1010</v>
       </c>
       <c r="G98" s="26" t="s">
         <v>100</v>
@@ -14015,22 +14103,22 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="25" t="s">
-        <v>1004</v>
+        <v>1011</v>
       </c>
       <c r="B99" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C99" s="26" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="D99" s="27" t="s">
-        <v>1005</v>
+        <v>1012</v>
       </c>
       <c r="E99" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F99" s="26" t="s">
-        <v>1006</v>
+        <v>1013</v>
       </c>
       <c r="G99" s="26" t="s">
         <v>140</v>
@@ -14054,22 +14142,22 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="25" t="s">
-        <v>1007</v>
+        <v>1014</v>
       </c>
       <c r="B100" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C100" s="26" t="s">
-        <v>1008</v>
+        <v>1015</v>
       </c>
       <c r="D100" s="27" t="s">
-        <v>1009</v>
+        <v>1016</v>
       </c>
       <c r="E100" s="26" t="s">
-        <v>464</v>
+        <v>471</v>
       </c>
       <c r="F100" s="26" t="s">
-        <v>1010</v>
+        <v>1017</v>
       </c>
       <c r="G100" s="26" t="s">
         <v>100</v>
@@ -14093,28 +14181,28 @@
     </row>
     <row r="101" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="25" t="s">
-        <v>1011</v>
+        <v>1018</v>
       </c>
       <c r="B101" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>531</v>
+        <v>538</v>
       </c>
       <c r="D101" s="27" t="s">
-        <v>1012</v>
+        <v>1019</v>
       </c>
       <c r="E101" s="26" t="s">
-        <v>1013</v>
+        <v>1020</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>1014</v>
+        <v>1021</v>
       </c>
       <c r="G101" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H101" s="26" t="s">
-        <v>535</v>
+        <v>542</v>
       </c>
       <c r="I101" s="26" t="s">
         <v>79</v>
@@ -14129,7 +14217,7 @@
         <v>14</v>
       </c>
       <c r="M101" s="26" t="s">
-        <v>1015</v>
+        <v>1022</v>
       </c>
     </row>
   </sheetData>
@@ -14201,12 +14289,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1016</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1017</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14222,10 +14310,10 @@
         <v>65</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>1018</v>
+        <v>1025</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>1019</v>
+        <v>1026</v>
       </c>
       <c r="D5" s="24" t="s">
         <v>67</v>
@@ -14239,56 +14327,56 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>1020</v>
+        <v>1027</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>1021</v>
+        <v>1028</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>1022</v>
+        <v>1029</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>1023</v>
+        <v>1030</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>1024</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>1025</v>
+        <v>1032</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>1026</v>
+        <v>1033</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>1027</v>
+        <v>1034</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>1028</v>
+        <v>1035</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>1029</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>1025</v>
+        <v>1032</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>1030</v>
+        <v>1037</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>1031</v>
+        <v>1038</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>1032</v>
+        <v>1039</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>29</v>
@@ -14297,33 +14385,33 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>1033</v>
+        <v>1040</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>1034</v>
+        <v>1041</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>1035</v>
+        <v>1042</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>1036</v>
+        <v>1043</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>1037</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>1038</v>
+        <v>1045</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>1039</v>
+        <v>1046</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>1040</v>
+        <v>1047</v>
       </c>
       <c r="D10" s="26" t="s">
         <v>22</v>
@@ -14332,61 +14420,61 @@
         <v>27</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>1041</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>1042</v>
+        <v>1049</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>1043</v>
+        <v>1050</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>1044</v>
+        <v>1051</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>1045</v>
+        <v>1052</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>1046</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>1042</v>
+        <v>1049</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>1047</v>
+        <v>1054</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>1048</v>
+        <v>1055</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>1049</v>
+        <v>1056</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1050</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>1042</v>
+        <v>1049</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>1051</v>
+        <v>1058</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>1052</v>
+        <v>1059</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>1053</v>
+        <v>1060</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>31</v>
@@ -14395,36 +14483,36 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>1042</v>
+        <v>1049</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>1054</v>
+        <v>1061</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>1055</v>
+        <v>1062</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>1056</v>
+        <v>1063</v>
       </c>
       <c r="E14" s="26" t="s">
         <v>31</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>1057</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>1059</v>
+        <v>1066</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>1060</v>
+        <v>1067</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>1061</v>
+        <v>1068</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>27</v>
@@ -14433,16 +14521,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>1062</v>
+        <v>1069</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>1063</v>
+        <v>1070</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>1064</v>
+        <v>1071</v>
       </c>
       <c r="E16" s="26" t="s">
         <v>31</v>
@@ -14451,16 +14539,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>1058</v>
+        <v>1065</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>1065</v>
+        <v>1072</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>1066</v>
+        <v>1073</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>1067</v>
+        <v>1074</v>
       </c>
       <c r="E17" s="26" t="s">
         <v>33</v>
@@ -14491,7 +14579,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="32"/>
@@ -14504,12 +14592,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1068</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1069</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14525,19 +14613,19 @@
         <v>67</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>1070</v>
+        <v>1077</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>1071</v>
+        <v>1078</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>1072</v>
+        <v>1079</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>1073</v>
+        <v>1080</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>1074</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14545,59 +14633,59 @@
         <v>98</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>1075</v>
+        <v>1082</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>1077</v>
+        <v>1084</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>1080</v>
+        <v>1087</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>1081</v>
+        <v>1088</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>1082</v>
+        <v>1089</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
+        <v>1090</v>
+      </c>
+      <c r="B8" s="26" t="s">
+        <v>1091</v>
+      </c>
+      <c r="C8" s="26" t="s">
         <v>1083</v>
       </c>
-      <c r="B8" s="26" t="s">
-        <v>1084</v>
-      </c>
-      <c r="C8" s="26" t="s">
-        <v>1076</v>
-      </c>
       <c r="D8" s="26" t="s">
+        <v>1092</v>
+      </c>
+      <c r="E8" s="28" t="s">
         <v>1085</v>
       </c>
-      <c r="E8" s="28" t="s">
-        <v>1078</v>
-      </c>
       <c r="F8" s="26" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14605,283 +14693,343 @@
         <v>76</v>
       </c>
       <c r="B9" s="26" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C9" s="26" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D9" s="26" t="s">
+        <v>1094</v>
+      </c>
+      <c r="E9" s="28" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F9" s="26" t="s">
         <v>1086</v>
-      </c>
-      <c r="C9" s="26" t="s">
-        <v>1076</v>
-      </c>
-      <c r="D9" s="26" t="s">
-        <v>1087</v>
-      </c>
-      <c r="E9" s="28" t="s">
-        <v>1078</v>
-      </c>
-      <c r="F9" s="26" t="s">
-        <v>1079</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>1088</v>
+        <v>1095</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>1089</v>
+        <v>1096</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>1090</v>
+        <v>1097</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>425</v>
+        <v>431</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>1093</v>
+        <v>1100</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>1094</v>
+        <v>1101</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>1095</v>
+        <v>1102</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>548</v>
+        <v>555</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>1081</v>
+        <v>1088</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>1096</v>
+        <v>1103</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>1097</v>
+        <v>1104</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="D14" s="26" t="s">
         <v>124</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>572</v>
+        <v>579</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>573</v>
+        <v>580</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="D15" s="26" t="s">
+        <v>1105</v>
+      </c>
+      <c r="E15" s="29" t="s">
         <v>1098</v>
       </c>
-      <c r="E15" s="29" t="s">
-        <v>1091</v>
-      </c>
       <c r="F15" s="26" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>1099</v>
+        <v>1106</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>1100</v>
+        <v>1107</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>1101</v>
+        <v>1108</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>1102</v>
+        <v>1109</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>1103</v>
+        <v>1110</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>1104</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>1105</v>
+        <v>1112</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>1106</v>
+        <v>1113</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>1107</v>
+        <v>1114</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>1108</v>
+        <v>1115</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>1106</v>
+        <v>1113</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>1109</v>
+        <v>1116</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>1079</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>1110</v>
+        <v>1117</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
       <c r="C19" s="26" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>1119</v>
+      </c>
+      <c r="E19" s="29" t="s">
+        <v>1098</v>
+      </c>
+      <c r="F19" s="26" t="s">
         <v>1111</v>
-      </c>
-      <c r="D19" s="26" t="s">
-        <v>1112</v>
-      </c>
-      <c r="E19" s="29" t="s">
-        <v>1091</v>
-      </c>
-      <c r="F19" s="26" t="s">
-        <v>1104</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>1113</v>
+        <v>1120</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>1092</v>
+        <v>1099</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>1114</v>
+        <v>1121</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>1078</v>
+        <v>1085</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>1115</v>
+        <v>1122</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>1116</v>
+        <v>1123</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>1076</v>
+        <v>1083</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>1117</v>
+        <v>1124</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>1079</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
+        <v>1125</v>
+      </c>
+      <c r="B22" s="26" t="s">
+        <v>1099</v>
+      </c>
+      <c r="C22" s="26" t="s">
         <v>1118</v>
       </c>
-      <c r="B22" s="26" t="s">
-        <v>1092</v>
-      </c>
-      <c r="C22" s="26" t="s">
-        <v>1111</v>
-      </c>
       <c r="D22" s="26" t="s">
-        <v>1119</v>
+        <v>1126</v>
       </c>
       <c r="E22" s="29" t="s">
-        <v>1091</v>
+        <v>1098</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>1120</v>
+        <v>1127</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="26" t="s">
+        <v>1128</v>
+      </c>
+      <c r="B23" s="26" t="s">
+        <v>1129</v>
+      </c>
+      <c r="C23" s="26" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D23" s="26" t="s">
+        <v>1130</v>
+      </c>
+      <c r="E23" s="28" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F23" s="26" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="26" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B24" s="26" t="s">
+        <v>1132</v>
+      </c>
+      <c r="C24" s="26" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D24" s="26" t="s">
+        <v>1133</v>
+      </c>
+      <c r="E24" s="30" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F24" s="26" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="26" t="s">
+        <v>346</v>
+      </c>
+      <c r="B25" s="26" t="s">
+        <v>1134</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D25" s="26" t="s">
+        <v>1135</v>
+      </c>
+      <c r="E25" s="28" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F25" s="26" t="s">
+        <v>1086</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:F22"/>
+  <autoFilter ref="A5:F25"/>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>

--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -16,7 +16,7 @@
     <sheet name="Fontes" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Brasil!$A$5:$M$131</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">Brasil!$A$5:$M$136</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Central!$A$5:$F$17</definedName>
     <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">EUA!$A$5:$M$101</definedName>
     <definedName function="false" hidden="true" localSheetId="5" name="_xlnm._FilterDatabase" vbProcedure="false">Fontes!$A$5:$F$25</definedName>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3092" uniqueCount="1136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3157" uniqueCount="1156">
   <si>
     <t xml:space="preserve">Argus — Catálogo de Dados</t>
   </si>
@@ -778,6 +778,66 @@
   </si>
   <si>
     <t xml:space="preserve">Título SGS 28751: "Núcleo Ex-alimentação e energia (EX-FE)"; comparável ao core dos EUA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BR-127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Média dos 5 núcleos do Copom (EX0, EX3, MS, DP, P55)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">média(11427, 27839, 4466, 16122, 28750)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Leitura-síntese citada pelo Copom; recalcular e conferir contra o RPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BR-128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mediana ponderada do IPCA (P50)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f(t7060): subitens ordenados por variação, peso acumulado = 50%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complementa o P55 oficial; documentar metodologia em docs/metodologia</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BR-129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bens industriais subjacentes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f(t7060): metodologia BCB (industriais ex-voláteis)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Par de serviços subjacentes; conferir contra boxes do RPM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BR-130</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Serviços intensivos em trabalho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f(t7060): subitens de serviços com alto peso de mão de obra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lista de subitens curada a partir da classificação do BCB; ligação com Mercado de Trabalho</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BR-131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preços rígidos × flexíveis (sticky/flexible)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">f(t7060 + classificação por frequência de reajuste)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Estilo Fed de Atlanta; exige montar a classificação de subitens</t>
   </si>
   <si>
     <t xml:space="preserve">BR-035</t>
@@ -4448,19 +4508,19 @@
         <v>45</v>
       </c>
       <c r="B7" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A7,Brasil!$K$6:$K$131,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A7,Brasil!$K$6:$K$136,"MVP")</f>
         <v>10</v>
       </c>
       <c r="C7" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A7,Brasil!$K$6:$K$131,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A7,Brasil!$K$6:$K$136,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D7" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A7,Brasil!$K$6:$K$131,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A7,Brasil!$K$6:$K$136,"v2")</f>
         <v>4</v>
       </c>
       <c r="E7" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A7,Brasil!$K$6:$K$131,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A7,Brasil!$K$6:$K$136,"v3")</f>
         <v>0</v>
       </c>
       <c r="F7" s="6" t="n">
@@ -4471,7 +4531,7 @@
         <v>12</v>
       </c>
       <c r="I7" s="16" t="n">
-        <f aca="false">COUNTIF(Brasil!$L$6:$L$131,H7)</f>
+        <f aca="false">COUNTIF(Brasil!$L$6:$L$136,H7)</f>
         <v>78</v>
       </c>
     </row>
@@ -4480,19 +4540,19 @@
         <v>46</v>
       </c>
       <c r="B8" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A8,Brasil!$K$6:$K$131,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A8,Brasil!$K$6:$K$136,"MVP")</f>
         <v>7</v>
       </c>
       <c r="C8" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A8,Brasil!$K$6:$K$131,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A8,Brasil!$K$6:$K$136,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D8" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A8,Brasil!$K$6:$K$131,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A8,Brasil!$K$6:$K$136,"v2")</f>
         <v>3</v>
       </c>
       <c r="E8" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A8,Brasil!$K$6:$K$131,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A8,Brasil!$K$6:$K$136,"v3")</f>
         <v>0</v>
       </c>
       <c r="F8" s="6" t="n">
@@ -4503,7 +4563,7 @@
         <v>14</v>
       </c>
       <c r="I8" s="16" t="n">
-        <f aca="false">COUNTIF(Brasil!$L$6:$L$131,H8)</f>
+        <f aca="false">COUNTIF(Brasil!$L$6:$L$136,H8)</f>
         <v>13</v>
       </c>
     </row>
@@ -4512,30 +4572,30 @@
         <v>47</v>
       </c>
       <c r="B9" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A9,Brasil!$K$6:$K$131,"MVP")</f>
-        <v>22</v>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A9,Brasil!$K$6:$K$136,"MVP")</f>
+        <v>26</v>
       </c>
       <c r="C9" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A9,Brasil!$K$6:$K$131,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A9,Brasil!$K$6:$K$136,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D9" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A9,Brasil!$K$6:$K$131,"v2")</f>
-        <v>4</v>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A9,Brasil!$K$6:$K$136,"v2")</f>
+        <v>5</v>
       </c>
       <c r="E9" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A9,Brasil!$K$6:$K$131,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A9,Brasil!$K$6:$K$136,"v3")</f>
         <v>0</v>
       </c>
       <c r="F9" s="6" t="n">
         <f aca="false">SUM(B9:E9)</f>
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H9" s="19" t="s">
         <v>16</v>
       </c>
       <c r="I9" s="16" t="n">
-        <f aca="false">COUNTIF(Brasil!$L$6:$L$131,H9)</f>
+        <f aca="false">COUNTIF(Brasil!$L$6:$L$136,H9)</f>
         <v>6</v>
       </c>
     </row>
@@ -4544,19 +4604,19 @@
         <v>48</v>
       </c>
       <c r="B10" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A10,Brasil!$K$6:$K$131,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A10,Brasil!$K$6:$K$136,"MVP")</f>
         <v>15</v>
       </c>
       <c r="C10" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A10,Brasil!$K$6:$K$131,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A10,Brasil!$K$6:$K$136,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D10" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A10,Brasil!$K$6:$K$131,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A10,Brasil!$K$6:$K$136,"v2")</f>
         <v>4</v>
       </c>
       <c r="E10" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A10,Brasil!$K$6:$K$131,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A10,Brasil!$K$6:$K$136,"v3")</f>
         <v>0</v>
       </c>
       <c r="F10" s="6" t="n">
@@ -4567,7 +4627,7 @@
         <v>18</v>
       </c>
       <c r="I10" s="16" t="n">
-        <f aca="false">COUNTIF(Brasil!$L$6:$L$131,H10)</f>
+        <f aca="false">COUNTIF(Brasil!$L$6:$L$136,H10)</f>
         <v>9</v>
       </c>
     </row>
@@ -4576,19 +4636,19 @@
         <v>49</v>
       </c>
       <c r="B11" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A11,Brasil!$K$6:$K$131,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A11,Brasil!$K$6:$K$136,"MVP")</f>
         <v>8</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A11,Brasil!$K$6:$K$131,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A11,Brasil!$K$6:$K$136,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A11,Brasil!$K$6:$K$131,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A11,Brasil!$K$6:$K$136,"v2")</f>
         <v>2</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A11,Brasil!$K$6:$K$131,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A11,Brasil!$K$6:$K$136,"v3")</f>
         <v>0</v>
       </c>
       <c r="F11" s="6" t="n">
@@ -4599,7 +4659,7 @@
         <v>20</v>
       </c>
       <c r="I11" s="16" t="n">
-        <f aca="false">COUNTIF(Brasil!$L$6:$L$131,H11)</f>
+        <f aca="false">COUNTIF(Brasil!$L$6:$L$136,H11)</f>
         <v>1</v>
       </c>
     </row>
@@ -4608,19 +4668,19 @@
         <v>50</v>
       </c>
       <c r="B12" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A12,Brasil!$K$6:$K$131,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A12,Brasil!$K$6:$K$136,"MVP")</f>
         <v>10</v>
       </c>
       <c r="C12" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A12,Brasil!$K$6:$K$131,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A12,Brasil!$K$6:$K$136,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D12" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A12,Brasil!$K$6:$K$131,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A12,Brasil!$K$6:$K$136,"v2")</f>
         <v>2</v>
       </c>
       <c r="E12" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A12,Brasil!$K$6:$K$131,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A12,Brasil!$K$6:$K$136,"v3")</f>
         <v>0</v>
       </c>
       <c r="F12" s="6" t="n">
@@ -4631,8 +4691,8 @@
         <v>22</v>
       </c>
       <c r="I12" s="16" t="n">
-        <f aca="false">COUNTIF(Brasil!$L$6:$L$131,H12)</f>
-        <v>13</v>
+        <f aca="false">COUNTIF(Brasil!$L$6:$L$136,H12)</f>
+        <v>18</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4640,19 +4700,19 @@
         <v>51</v>
       </c>
       <c r="B13" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A13,Brasil!$K$6:$K$131,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A13,Brasil!$K$6:$K$136,"MVP")</f>
         <v>7</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A13,Brasil!$K$6:$K$131,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A13,Brasil!$K$6:$K$136,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A13,Brasil!$K$6:$K$131,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A13,Brasil!$K$6:$K$136,"v2")</f>
         <v>2</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A13,Brasil!$K$6:$K$131,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A13,Brasil!$K$6:$K$136,"v3")</f>
         <v>0</v>
       </c>
       <c r="F13" s="6" t="n">
@@ -4663,7 +4723,7 @@
         <v>24</v>
       </c>
       <c r="I13" s="16" t="n">
-        <f aca="false">COUNTIF(Brasil!$L$6:$L$131,H13)</f>
+        <f aca="false">COUNTIF(Brasil!$L$6:$L$136,H13)</f>
         <v>6</v>
       </c>
     </row>
@@ -4672,19 +4732,19 @@
         <v>52</v>
       </c>
       <c r="B14" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A14,Brasil!$K$6:$K$131,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A14,Brasil!$K$6:$K$136,"MVP")</f>
         <v>1</v>
       </c>
       <c r="C14" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A14,Brasil!$K$6:$K$131,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A14,Brasil!$K$6:$K$136,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D14" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A14,Brasil!$K$6:$K$131,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A14,Brasil!$K$6:$K$136,"v2")</f>
         <v>4</v>
       </c>
       <c r="E14" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A14,Brasil!$K$6:$K$131,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A14,Brasil!$K$6:$K$136,"v3")</f>
         <v>1</v>
       </c>
       <c r="F14" s="6" t="n">
@@ -4697,19 +4757,19 @@
         <v>53</v>
       </c>
       <c r="B15" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A15,Brasil!$K$6:$K$131,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A15,Brasil!$K$6:$K$136,"MVP")</f>
         <v>1</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A15,Brasil!$K$6:$K$131,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A15,Brasil!$K$6:$K$136,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D15" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A15,Brasil!$K$6:$K$131,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A15,Brasil!$K$6:$K$136,"v2")</f>
         <v>4</v>
       </c>
       <c r="E15" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A15,Brasil!$K$6:$K$131,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A15,Brasil!$K$6:$K$136,"v3")</f>
         <v>1</v>
       </c>
       <c r="F15" s="6" t="n">
@@ -4722,19 +4782,19 @@
         <v>54</v>
       </c>
       <c r="B16" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A16,Brasil!$K$6:$K$131,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A16,Brasil!$K$6:$K$136,"MVP")</f>
         <v>0</v>
       </c>
       <c r="C16" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A16,Brasil!$K$6:$K$131,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A16,Brasil!$K$6:$K$136,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D16" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A16,Brasil!$K$6:$K$131,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A16,Brasil!$K$6:$K$136,"v2")</f>
         <v>4</v>
       </c>
       <c r="E16" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A16,Brasil!$K$6:$K$131,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A16,Brasil!$K$6:$K$136,"v3")</f>
         <v>0</v>
       </c>
       <c r="F16" s="6" t="n">
@@ -4747,19 +4807,19 @@
         <v>55</v>
       </c>
       <c r="B17" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A17,Brasil!$K$6:$K$131,"MVP")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A17,Brasil!$K$6:$K$136,"MVP")</f>
         <v>3</v>
       </c>
       <c r="C17" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A17,Brasil!$K$6:$K$131,"EUA")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A17,Brasil!$K$6:$K$136,"EUA")</f>
         <v>0</v>
       </c>
       <c r="D17" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A17,Brasil!$K$6:$K$131,"v2")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A17,Brasil!$K$6:$K$136,"v2")</f>
         <v>6</v>
       </c>
       <c r="E17" s="16" t="n">
-        <f aca="false">COUNTIFS(Brasil!$B$6:$B$131,$A17,Brasil!$K$6:$K$131,"v3")</f>
+        <f aca="false">COUNTIFS(Brasil!$B$6:$B$136,$A17,Brasil!$K$6:$K$136,"v3")</f>
         <v>1</v>
       </c>
       <c r="F17" s="6" t="n">
@@ -4773,7 +4833,7 @@
       </c>
       <c r="B18" s="6" t="n">
         <f aca="false">SUM(B7:B17)</f>
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="C18" s="6" t="n">
         <f aca="false">SUM(C7:C17)</f>
@@ -4781,7 +4841,7 @@
       </c>
       <c r="D18" s="6" t="n">
         <f aca="false">SUM(D7:D17)</f>
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E18" s="6" t="n">
         <f aca="false">SUM(E7:E17)</f>
@@ -4789,7 +4849,7 @@
       </c>
       <c r="F18" s="6" t="n">
         <f aca="false">SUM(F7:F17)</f>
-        <v>126</v>
+        <v>131</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5138,7 +5198,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M131"/>
+  <dimension ref="A1:M136"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
@@ -6651,16 +6711,16 @@
         <v>47</v>
       </c>
       <c r="C41" s="26" t="s">
+        <v>225</v>
+      </c>
+      <c r="D41" s="27" t="s">
         <v>250</v>
       </c>
-      <c r="D41" s="27" t="s">
+      <c r="E41" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="F41" s="26" t="s">
         <v>251</v>
-      </c>
-      <c r="E41" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="F41" s="26" t="s">
-        <v>252</v>
       </c>
       <c r="G41" s="26" t="s">
         <v>100</v>
@@ -6669,7 +6729,7 @@
         <v>209</v>
       </c>
       <c r="I41" s="26" t="s">
-        <v>210</v>
+        <v>22</v>
       </c>
       <c r="J41" s="26" t="s">
         <v>211</v>
@@ -6678,9 +6738,11 @@
         <v>27</v>
       </c>
       <c r="L41" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="M41" s="26"/>
+        <v>22</v>
+      </c>
+      <c r="M41" s="26" t="s">
+        <v>252</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="25" t="s">
@@ -6690,13 +6752,13 @@
         <v>47</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="D42" s="27" t="s">
         <v>254</v>
       </c>
       <c r="E42" s="26" t="s">
-        <v>98</v>
+        <v>200</v>
       </c>
       <c r="F42" s="26" t="s">
         <v>255</v>
@@ -6708,7 +6770,7 @@
         <v>209</v>
       </c>
       <c r="I42" s="26" t="s">
-        <v>210</v>
+        <v>22</v>
       </c>
       <c r="J42" s="26" t="s">
         <v>211</v>
@@ -6717,28 +6779,30 @@
         <v>27</v>
       </c>
       <c r="L42" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="M42" s="26"/>
+        <v>22</v>
+      </c>
+      <c r="M42" s="26" t="s">
+        <v>256</v>
+      </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="25" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B43" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="D43" s="27" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>98</v>
+        <v>200</v>
       </c>
       <c r="F43" s="26" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G43" s="26" t="s">
         <v>100</v>
@@ -6747,7 +6811,7 @@
         <v>209</v>
       </c>
       <c r="I43" s="26" t="s">
-        <v>210</v>
+        <v>22</v>
       </c>
       <c r="J43" s="26" t="s">
         <v>211</v>
@@ -6756,28 +6820,30 @@
         <v>27</v>
       </c>
       <c r="L43" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="M43" s="26"/>
+        <v>22</v>
+      </c>
+      <c r="M43" s="26" t="s">
+        <v>260</v>
+      </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B44" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>98</v>
+        <v>200</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="G44" s="26" t="s">
         <v>100</v>
@@ -6786,7 +6852,7 @@
         <v>209</v>
       </c>
       <c r="I44" s="26" t="s">
-        <v>210</v>
+        <v>22</v>
       </c>
       <c r="J44" s="26" t="s">
         <v>211</v>
@@ -6795,28 +6861,30 @@
         <v>27</v>
       </c>
       <c r="L44" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="M44" s="26"/>
+        <v>22</v>
+      </c>
+      <c r="M44" s="26" t="s">
+        <v>264</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="25" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="B45" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C45" s="26" t="s">
-        <v>250</v>
+        <v>225</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>98</v>
+        <v>200</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="G45" s="26" t="s">
         <v>100</v>
@@ -6825,7 +6893,7 @@
         <v>209</v>
       </c>
       <c r="I45" s="26" t="s">
-        <v>210</v>
+        <v>22</v>
       </c>
       <c r="J45" s="26" t="s">
         <v>211</v>
@@ -6834,40 +6902,42 @@
         <v>31</v>
       </c>
       <c r="L45" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="M45" s="26"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>22</v>
+      </c>
+      <c r="M45" s="26" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="25" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B46" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E46" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="G46" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H46" s="26" t="s">
-        <v>85</v>
+        <v>209</v>
       </c>
       <c r="I46" s="26" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="J46" s="26" t="s">
-        <v>87</v>
+        <v>211</v>
       </c>
       <c r="K46" s="26" t="s">
         <v>27</v>
@@ -6879,28 +6949,28 @@
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="25" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="B47" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="G47" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H47" s="26" t="s">
-        <v>271</v>
+        <v>209</v>
       </c>
       <c r="I47" s="26" t="s">
         <v>210</v>
@@ -6914,28 +6984,26 @@
       <c r="L47" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M47" s="26" t="s">
-        <v>272</v>
-      </c>
+      <c r="M47" s="26"/>
     </row>
     <row r="48" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="25" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="B48" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="D48" s="27" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="E48" s="26" t="s">
-        <v>200</v>
+        <v>98</v>
       </c>
       <c r="F48" s="26" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G48" s="26" t="s">
         <v>100</v>
@@ -6944,39 +7012,37 @@
         <v>209</v>
       </c>
       <c r="I48" s="26" t="s">
-        <v>22</v>
+        <v>210</v>
       </c>
       <c r="J48" s="26" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
       <c r="K48" s="26" t="s">
         <v>27</v>
       </c>
       <c r="L48" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="M48" s="26" t="s">
-        <v>276</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="M48" s="26"/>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="25" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="B49" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="E49" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F49" s="26" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="G49" s="26" t="s">
         <v>100</v>
@@ -6996,9 +7062,7 @@
       <c r="L49" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M49" s="26" t="s">
-        <v>281</v>
-      </c>
+      <c r="M49" s="26"/>
     </row>
     <row r="50" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="25" t="s">
@@ -7008,7 +7072,7 @@
         <v>47</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="D50" s="27" t="s">
         <v>283</v>
@@ -7017,7 +7081,7 @@
         <v>98</v>
       </c>
       <c r="F50" s="26" t="s">
-        <v>16</v>
+        <v>284</v>
       </c>
       <c r="G50" s="26" t="s">
         <v>100</v>
@@ -7035,40 +7099,40 @@
         <v>31</v>
       </c>
       <c r="L50" s="26" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="M50" s="26"/>
     </row>
-    <row r="51" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="25" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B51" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="E51" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F51" s="26" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="G51" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H51" s="26" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="I51" s="26" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="J51" s="26" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="K51" s="26" t="s">
         <v>27</v>
@@ -7076,9 +7140,7 @@
       <c r="L51" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M51" s="26" t="s">
-        <v>287</v>
-      </c>
+      <c r="M51" s="26"/>
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="25" t="s">
@@ -7088,28 +7150,28 @@
         <v>47</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>144</v>
+        <v>270</v>
       </c>
       <c r="D52" s="27" t="s">
         <v>289</v>
       </c>
       <c r="E52" s="26" t="s">
-        <v>146</v>
+        <v>76</v>
       </c>
       <c r="F52" s="26" t="s">
         <v>290</v>
       </c>
       <c r="G52" s="26" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="H52" s="26" t="s">
-        <v>85</v>
+        <v>291</v>
       </c>
       <c r="I52" s="26" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="J52" s="26" t="s">
-        <v>87</v>
+        <v>211</v>
       </c>
       <c r="K52" s="26" t="s">
         <v>27</v>
@@ -7117,161 +7179,161 @@
       <c r="L52" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M52" s="26"/>
+      <c r="M52" s="26" t="s">
+        <v>292</v>
+      </c>
     </row>
     <row r="53" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="25" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="B53" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>144</v>
+        <v>270</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>146</v>
+        <v>200</v>
       </c>
       <c r="F53" s="26" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="G53" s="26" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="H53" s="26" t="s">
-        <v>85</v>
+        <v>209</v>
       </c>
       <c r="I53" s="26" t="s">
-        <v>86</v>
+        <v>22</v>
       </c>
       <c r="J53" s="26" t="s">
-        <v>87</v>
+        <v>203</v>
       </c>
       <c r="K53" s="26" t="s">
         <v>27</v>
       </c>
       <c r="L53" s="26" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="M53" s="26" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="25" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B54" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C54" s="26" t="s">
-        <v>144</v>
+        <v>298</v>
       </c>
       <c r="D54" s="27" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="E54" s="26" t="s">
-        <v>297</v>
+        <v>98</v>
       </c>
       <c r="F54" s="26" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="G54" s="26" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="H54" s="26" t="s">
-        <v>85</v>
+        <v>209</v>
       </c>
       <c r="I54" s="26" t="s">
-        <v>86</v>
+        <v>210</v>
       </c>
       <c r="J54" s="26" t="s">
-        <v>87</v>
+        <v>211</v>
       </c>
       <c r="K54" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L54" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M54" s="26" t="s">
-        <v>299</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="25" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="B55" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D55" s="27" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>303</v>
+        <v>98</v>
       </c>
       <c r="F55" s="26" t="s">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="G55" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="H55" s="26" t="s">
+        <v>209</v>
+      </c>
+      <c r="I55" s="26" t="s">
+        <v>210</v>
+      </c>
+      <c r="J55" s="26" t="s">
+        <v>211</v>
+      </c>
+      <c r="K55" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="L55" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="M55" s="26"/>
+    </row>
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="25" t="s">
         <v>304</v>
       </c>
-      <c r="H55" s="26" t="s">
-        <v>85</v>
-      </c>
-      <c r="I55" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="J55" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="K55" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="L55" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="M55" s="26" t="s">
+      <c r="B56" s="26" t="s">
+        <v>47</v>
+      </c>
+      <c r="C56" s="26" t="s">
+        <v>298</v>
+      </c>
+      <c r="D56" s="27" t="s">
         <v>305</v>
-      </c>
-    </row>
-    <row r="56" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="25" t="s">
-        <v>306</v>
-      </c>
-      <c r="B56" s="26" t="s">
-        <v>48</v>
-      </c>
-      <c r="C56" s="26" t="s">
-        <v>307</v>
-      </c>
-      <c r="D56" s="27" t="s">
-        <v>308</v>
       </c>
       <c r="E56" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F56" s="26" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="G56" s="26" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="H56" s="26" t="s">
-        <v>310</v>
+        <v>79</v>
       </c>
       <c r="I56" s="26" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="J56" s="26" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K56" s="26" t="s">
         <v>27</v>
@@ -7280,33 +7342,33 @@
         <v>12</v>
       </c>
       <c r="M56" s="26" t="s">
-        <v>311</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="25" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B57" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>307</v>
+        <v>144</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E57" s="26" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="F57" s="26" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="G57" s="26" t="s">
-        <v>140</v>
+        <v>148</v>
       </c>
       <c r="H57" s="26" t="s">
-        <v>315</v>
+        <v>85</v>
       </c>
       <c r="I57" s="26" t="s">
         <v>86</v>
@@ -7315,39 +7377,37 @@
         <v>87</v>
       </c>
       <c r="K57" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L57" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M57" s="26" t="s">
-        <v>316</v>
-      </c>
+      <c r="M57" s="26"/>
     </row>
     <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="25" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B58" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>307</v>
+        <v>144</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="E58" s="26" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="F58" s="26" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="G58" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H58" s="26" t="s">
-        <v>310</v>
+        <v>85</v>
       </c>
       <c r="I58" s="26" t="s">
         <v>86</v>
@@ -7362,33 +7422,33 @@
         <v>12</v>
       </c>
       <c r="M58" s="26" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="25" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="B59" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>307</v>
+        <v>144</v>
       </c>
       <c r="D59" s="27" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="E59" s="26" t="s">
-        <v>98</v>
+        <v>317</v>
       </c>
       <c r="F59" s="26" t="s">
-        <v>323</v>
+        <v>318</v>
       </c>
       <c r="G59" s="26" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H59" s="26" t="s">
-        <v>310</v>
+        <v>85</v>
       </c>
       <c r="I59" s="26" t="s">
         <v>86</v>
@@ -7397,39 +7457,39 @@
         <v>87</v>
       </c>
       <c r="K59" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L59" s="26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M59" s="26" t="s">
-        <v>324</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="25" t="s">
-        <v>325</v>
+        <v>320</v>
       </c>
       <c r="B60" s="26" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C60" s="26" t="s">
-        <v>307</v>
+        <v>321</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>98</v>
+        <v>323</v>
       </c>
       <c r="F60" s="26" t="s">
-        <v>327</v>
+        <v>24</v>
       </c>
       <c r="G60" s="26" t="s">
-        <v>140</v>
+        <v>324</v>
       </c>
       <c r="H60" s="26" t="s">
-        <v>310</v>
+        <v>85</v>
       </c>
       <c r="I60" s="26" t="s">
         <v>86</v>
@@ -7438,49 +7498,51 @@
         <v>87</v>
       </c>
       <c r="K60" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L60" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="M60" s="26"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>24</v>
+      </c>
+      <c r="M60" s="26" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="25" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B61" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>307</v>
+        <v>327</v>
       </c>
       <c r="D61" s="27" t="s">
+        <v>328</v>
+      </c>
+      <c r="E61" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="F61" s="26" t="s">
         <v>329</v>
-      </c>
-      <c r="E61" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="F61" s="26" t="s">
-        <v>330</v>
       </c>
       <c r="G61" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H61" s="26" t="s">
-        <v>310</v>
+        <v>330</v>
       </c>
       <c r="I61" s="26" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="J61" s="26" t="s">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="K61" s="26" t="s">
         <v>27</v>
       </c>
       <c r="L61" s="26" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M61" s="26" t="s">
         <v>331</v>
@@ -7494,22 +7556,22 @@
         <v>48</v>
       </c>
       <c r="C62" s="26" t="s">
-        <v>144</v>
+        <v>327</v>
       </c>
       <c r="D62" s="27" t="s">
         <v>333</v>
       </c>
       <c r="E62" s="26" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="F62" s="26" t="s">
         <v>334</v>
       </c>
       <c r="G62" s="26" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="H62" s="26" t="s">
-        <v>310</v>
+        <v>335</v>
       </c>
       <c r="I62" s="26" t="s">
         <v>86</v>
@@ -7518,86 +7580,86 @@
         <v>87</v>
       </c>
       <c r="K62" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L62" s="26" t="s">
         <v>12</v>
       </c>
       <c r="M62" s="26" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="25" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B63" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C63" s="26" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="D63" s="27" t="s">
         <v>338</v>
       </c>
       <c r="E63" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="F63" s="26" t="s">
         <v>339</v>
       </c>
-      <c r="F63" s="26" t="s">
-        <v>24</v>
-      </c>
       <c r="G63" s="26" t="s">
-        <v>340</v>
+        <v>140</v>
       </c>
       <c r="H63" s="26" t="s">
-        <v>341</v>
+        <v>330</v>
       </c>
       <c r="I63" s="26" t="s">
-        <v>342</v>
+        <v>86</v>
       </c>
       <c r="J63" s="26" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="K63" s="26" t="s">
         <v>27</v>
       </c>
       <c r="L63" s="26" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="M63" s="26" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="64" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="25" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="B64" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C64" s="26" t="s">
-        <v>337</v>
+        <v>327</v>
       </c>
       <c r="D64" s="27" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E64" s="26" t="s">
-        <v>346</v>
+        <v>98</v>
       </c>
       <c r="F64" s="26" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G64" s="26" t="s">
-        <v>340</v>
+        <v>100</v>
       </c>
       <c r="H64" s="26" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="I64" s="26" t="s">
-        <v>348</v>
+        <v>86</v>
       </c>
       <c r="J64" s="26" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="K64" s="26" t="s">
         <v>27</v>
@@ -7606,121 +7668,119 @@
         <v>12</v>
       </c>
       <c r="M64" s="26" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="25" t="s">
-        <v>350</v>
+        <v>345</v>
       </c>
       <c r="B65" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>351</v>
+        <v>327</v>
       </c>
       <c r="D65" s="27" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="E65" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="G65" s="26" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H65" s="26" t="s">
-        <v>354</v>
+        <v>330</v>
       </c>
       <c r="I65" s="26" t="s">
-        <v>165</v>
+        <v>86</v>
       </c>
       <c r="J65" s="26" t="s">
-        <v>166</v>
+        <v>87</v>
       </c>
       <c r="K65" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L65" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="M65" s="26" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>14</v>
+      </c>
+      <c r="M65" s="26"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="25" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="B66" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C66" s="26" t="s">
-        <v>351</v>
+        <v>327</v>
       </c>
       <c r="D66" s="27" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
       <c r="E66" s="26" t="s">
-        <v>98</v>
+        <v>200</v>
       </c>
       <c r="F66" s="26" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="G66" s="26" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H66" s="26" t="s">
-        <v>354</v>
+        <v>330</v>
       </c>
       <c r="I66" s="26" t="s">
-        <v>165</v>
+        <v>22</v>
       </c>
       <c r="J66" s="26" t="s">
-        <v>166</v>
+        <v>203</v>
       </c>
       <c r="K66" s="26" t="s">
         <v>27</v>
       </c>
       <c r="L66" s="26" t="s">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="M66" s="26" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="25" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="B67" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C67" s="26" t="s">
-        <v>351</v>
+        <v>144</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
       <c r="E67" s="26" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="G67" s="26" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="H67" s="26" t="s">
-        <v>354</v>
+        <v>330</v>
       </c>
       <c r="I67" s="26" t="s">
-        <v>165</v>
+        <v>86</v>
       </c>
       <c r="J67" s="26" t="s">
-        <v>166</v>
+        <v>87</v>
       </c>
       <c r="K67" s="26" t="s">
         <v>27</v>
@@ -7728,77 +7788,81 @@
       <c r="L67" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M67" s="26"/>
+      <c r="M67" s="26" t="s">
+        <v>355</v>
+      </c>
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="25" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="B68" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C68" s="26" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="D68" s="27" t="s">
-        <v>365</v>
+        <v>358</v>
       </c>
       <c r="E68" s="26" t="s">
-        <v>98</v>
+        <v>359</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>366</v>
+        <v>24</v>
       </c>
       <c r="G68" s="26" t="s">
-        <v>100</v>
+        <v>360</v>
       </c>
       <c r="H68" s="26" t="s">
-        <v>101</v>
+        <v>361</v>
       </c>
       <c r="I68" s="26" t="s">
-        <v>165</v>
+        <v>362</v>
       </c>
       <c r="J68" s="26" t="s">
-        <v>166</v>
+        <v>124</v>
       </c>
       <c r="K68" s="26" t="s">
         <v>27</v>
       </c>
       <c r="L68" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="M68" s="26"/>
-    </row>
-    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>24</v>
+      </c>
+      <c r="M68" s="26" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="25" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="B69" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>364</v>
+        <v>357</v>
       </c>
       <c r="D69" s="27" t="s">
+        <v>365</v>
+      </c>
+      <c r="E69" s="26" t="s">
+        <v>366</v>
+      </c>
+      <c r="F69" s="26" t="s">
+        <v>367</v>
+      </c>
+      <c r="G69" s="26" t="s">
+        <v>360</v>
+      </c>
+      <c r="H69" s="26" t="s">
         <v>368</v>
       </c>
-      <c r="E69" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="F69" s="26" t="s">
-        <v>369</v>
-      </c>
-      <c r="G69" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="H69" s="26" t="s">
-        <v>101</v>
-      </c>
       <c r="I69" s="26" t="s">
-        <v>165</v>
+        <v>368</v>
       </c>
       <c r="J69" s="26" t="s">
-        <v>166</v>
+        <v>124</v>
       </c>
       <c r="K69" s="26" t="s">
         <v>27</v>
@@ -7807,18 +7871,18 @@
         <v>12</v>
       </c>
       <c r="M69" s="26" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="25" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B70" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C70" s="26" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="D70" s="27" t="s">
         <v>372</v>
@@ -7833,13 +7897,13 @@
         <v>100</v>
       </c>
       <c r="H70" s="26" t="s">
-        <v>101</v>
+        <v>374</v>
       </c>
       <c r="I70" s="26" t="s">
-        <v>102</v>
+        <v>165</v>
       </c>
       <c r="J70" s="26" t="s">
-        <v>103</v>
+        <v>166</v>
       </c>
       <c r="K70" s="26" t="s">
         <v>27</v>
@@ -7847,38 +7911,40 @@
       <c r="L70" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M70" s="26"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M70" s="26" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="25" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B71" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C71" s="26" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E71" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="G71" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H71" s="26" t="s">
-        <v>310</v>
+        <v>374</v>
       </c>
       <c r="I71" s="26" t="s">
-        <v>86</v>
+        <v>165</v>
       </c>
       <c r="J71" s="26" t="s">
-        <v>87</v>
+        <v>166</v>
       </c>
       <c r="K71" s="26" t="s">
         <v>27</v>
@@ -7886,38 +7952,40 @@
       <c r="L71" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M71" s="26"/>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M71" s="26" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="25" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="B72" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C72" s="26" t="s">
-        <v>364</v>
+        <v>371</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="E72" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="G72" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H72" s="26" t="s">
-        <v>202</v>
+        <v>374</v>
       </c>
       <c r="I72" s="26" t="s">
-        <v>86</v>
+        <v>165</v>
       </c>
       <c r="J72" s="26" t="s">
-        <v>87</v>
+        <v>166</v>
       </c>
       <c r="K72" s="26" t="s">
         <v>27</v>
@@ -7927,48 +7995,48 @@
       </c>
       <c r="M72" s="26"/>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="25" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B73" s="26" t="s">
         <v>48</v>
       </c>
       <c r="C73" s="26" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="E73" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F73" s="26" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="G73" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H73" s="26" t="s">
-        <v>310</v>
+        <v>101</v>
       </c>
       <c r="I73" s="26" t="s">
-        <v>86</v>
+        <v>165</v>
       </c>
       <c r="J73" s="26" t="s">
-        <v>87</v>
+        <v>166</v>
       </c>
       <c r="K73" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L73" s="26" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="M73" s="26"/>
     </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="25" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B74" s="26" t="s">
         <v>48</v>
@@ -7977,66 +8045,66 @@
         <v>384</v>
       </c>
       <c r="D74" s="27" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="E74" s="26" t="s">
-        <v>200</v>
+        <v>98</v>
       </c>
       <c r="F74" s="26" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="G74" s="26" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="H74" s="26" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="I74" s="26" t="s">
-        <v>22</v>
+        <v>165</v>
       </c>
       <c r="J74" s="26" t="s">
-        <v>203</v>
+        <v>166</v>
       </c>
       <c r="K74" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L74" s="26" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M74" s="26" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="25" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="B75" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C75" s="26" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="D75" s="27" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E75" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F75" s="26" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="G75" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H75" s="26" t="s">
-        <v>392</v>
+        <v>101</v>
       </c>
       <c r="I75" s="26" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="J75" s="26" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="K75" s="26" t="s">
         <v>27</v>
@@ -8046,30 +8114,30 @@
       </c>
       <c r="M75" s="26"/>
     </row>
-    <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="25" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B76" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C76" s="26" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="D76" s="27" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="E76" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="G76" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H76" s="26" t="s">
-        <v>392</v>
+        <v>330</v>
       </c>
       <c r="I76" s="26" t="s">
         <v>86</v>
@@ -8083,19 +8151,17 @@
       <c r="L76" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M76" s="26" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M76" s="26"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="25" t="s">
         <v>397</v>
       </c>
       <c r="B77" s="26" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C77" s="26" t="s">
-        <v>389</v>
+        <v>384</v>
       </c>
       <c r="D77" s="27" t="s">
         <v>398</v>
@@ -8110,7 +8176,7 @@
         <v>100</v>
       </c>
       <c r="H77" s="26" t="s">
-        <v>392</v>
+        <v>202</v>
       </c>
       <c r="I77" s="26" t="s">
         <v>86</v>
@@ -8124,34 +8190,32 @@
       <c r="L77" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M77" s="26" t="s">
-        <v>400</v>
-      </c>
+      <c r="M77" s="26"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="B78" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C78" s="26" t="s">
+        <v>384</v>
+      </c>
+      <c r="D78" s="27" t="s">
         <v>401</v>
-      </c>
-      <c r="B78" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C78" s="26" t="s">
-        <v>402</v>
-      </c>
-      <c r="D78" s="27" t="s">
-        <v>403</v>
       </c>
       <c r="E78" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="G78" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H78" s="26" t="s">
-        <v>392</v>
+        <v>330</v>
       </c>
       <c r="I78" s="26" t="s">
         <v>86</v>
@@ -8160,51 +8224,53 @@
         <v>87</v>
       </c>
       <c r="K78" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L78" s="26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M78" s="26"/>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="25" t="s">
+        <v>403</v>
+      </c>
+      <c r="B79" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C79" s="26" t="s">
+        <v>404</v>
+      </c>
+      <c r="D79" s="27" t="s">
         <v>405</v>
       </c>
-      <c r="B79" s="26" t="s">
-        <v>49</v>
-      </c>
-      <c r="C79" s="26" t="s">
-        <v>402</v>
-      </c>
-      <c r="D79" s="27" t="s">
+      <c r="E79" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="F79" s="26" t="s">
         <v>406</v>
       </c>
-      <c r="E79" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="F79" s="26" t="s">
+      <c r="G79" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="H79" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="I79" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J79" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K79" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="L79" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="M79" s="26" t="s">
         <v>407</v>
       </c>
-      <c r="G79" s="26" t="s">
-        <v>100</v>
-      </c>
-      <c r="H79" s="26" t="s">
-        <v>392</v>
-      </c>
-      <c r="I79" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="J79" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="K79" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="L79" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="M79" s="26"/>
     </row>
     <row r="80" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="25" t="s">
@@ -8220,7 +8286,7 @@
         <v>410</v>
       </c>
       <c r="E80" s="26" t="s">
-        <v>297</v>
+        <v>98</v>
       </c>
       <c r="F80" s="26" t="s">
         <v>411</v>
@@ -8229,13 +8295,13 @@
         <v>100</v>
       </c>
       <c r="H80" s="26" t="s">
-        <v>101</v>
+        <v>412</v>
       </c>
       <c r="I80" s="26" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="J80" s="26" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="K80" s="26" t="s">
         <v>27</v>
@@ -8243,11 +8309,9 @@
       <c r="L80" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M80" s="26" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M80" s="26"/>
+    </row>
+    <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="25" t="s">
         <v>413</v>
       </c>
@@ -8261,16 +8325,16 @@
         <v>414</v>
       </c>
       <c r="E81" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="F81" s="26" t="s">
         <v>415</v>
       </c>
-      <c r="F81" s="26" t="s">
-        <v>24</v>
-      </c>
       <c r="G81" s="26" t="s">
-        <v>304</v>
+        <v>100</v>
       </c>
       <c r="H81" s="26" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="I81" s="26" t="s">
         <v>86</v>
@@ -8282,34 +8346,36 @@
         <v>27</v>
       </c>
       <c r="L81" s="26" t="s">
-        <v>24</v>
-      </c>
-      <c r="M81" s="26"/>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>12</v>
+      </c>
+      <c r="M81" s="26" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="25" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="B82" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C82" s="26" t="s">
-        <v>402</v>
+        <v>409</v>
       </c>
       <c r="D82" s="27" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E82" s="26" t="s">
-        <v>297</v>
+        <v>98</v>
       </c>
       <c r="F82" s="26" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="G82" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H82" s="26" t="s">
-        <v>85</v>
+        <v>412</v>
       </c>
       <c r="I82" s="26" t="s">
         <v>86</v>
@@ -8318,37 +8384,39 @@
         <v>87</v>
       </c>
       <c r="K82" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L82" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="M82" s="26"/>
+        <v>12</v>
+      </c>
+      <c r="M82" s="26" t="s">
+        <v>420</v>
+      </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="25" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="B83" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C83" s="26" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D83" s="27" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="F83" s="26" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="G83" s="26" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="H83" s="26" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="I83" s="26" t="s">
         <v>86</v>
@@ -8366,28 +8434,28 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="25" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B84" s="26" t="s">
         <v>49</v>
       </c>
       <c r="C84" s="26" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="D84" s="27" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>425</v>
+        <v>98</v>
       </c>
       <c r="F84" s="26" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="G84" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H84" s="26" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="I84" s="26" t="s">
         <v>86</v>
@@ -8396,21 +8464,19 @@
         <v>87</v>
       </c>
       <c r="K84" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L84" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="M84" s="26" t="s">
-        <v>427</v>
-      </c>
+        <v>12</v>
+      </c>
+      <c r="M84" s="26"/>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="25" t="s">
         <v>428</v>
       </c>
       <c r="B85" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C85" s="26" t="s">
         <v>429</v>
@@ -8419,16 +8485,16 @@
         <v>430</v>
       </c>
       <c r="E85" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="F85" s="26" t="s">
         <v>431</v>
-      </c>
-      <c r="F85" s="26" t="s">
-        <v>432</v>
       </c>
       <c r="G85" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H85" s="26" t="s">
-        <v>433</v>
+        <v>101</v>
       </c>
       <c r="I85" s="26" t="s">
         <v>102</v>
@@ -8443,113 +8509,111 @@
         <v>12</v>
       </c>
       <c r="M85" s="26" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="25" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="B86" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C86" s="26" t="s">
         <v>429</v>
       </c>
       <c r="D86" s="27" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="E86" s="26" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="F86" s="26" t="s">
-        <v>437</v>
+        <v>24</v>
       </c>
       <c r="G86" s="26" t="s">
-        <v>100</v>
+        <v>324</v>
       </c>
       <c r="H86" s="26" t="s">
-        <v>433</v>
+        <v>412</v>
       </c>
       <c r="I86" s="26" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="J86" s="26" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="K86" s="26" t="s">
         <v>27</v>
       </c>
       <c r="L86" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="M86" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="M86" s="26"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="25" t="s">
+        <v>436</v>
+      </c>
+      <c r="B87" s="26" t="s">
+        <v>49</v>
+      </c>
+      <c r="C87" s="26" t="s">
+        <v>422</v>
+      </c>
+      <c r="D87" s="27" t="s">
+        <v>437</v>
+      </c>
+      <c r="E87" s="26" t="s">
+        <v>317</v>
+      </c>
+      <c r="F87" s="26" t="s">
         <v>438</v>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="25" t="s">
-        <v>439</v>
-      </c>
-      <c r="B87" s="26" t="s">
-        <v>50</v>
-      </c>
-      <c r="C87" s="26" t="s">
-        <v>440</v>
-      </c>
-      <c r="D87" s="27" t="s">
-        <v>441</v>
-      </c>
-      <c r="E87" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="F87" s="26" t="s">
-        <v>442</v>
       </c>
       <c r="G87" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H87" s="26" t="s">
-        <v>433</v>
+        <v>85</v>
       </c>
       <c r="I87" s="26" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="J87" s="26" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="K87" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L87" s="26" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="M87" s="26"/>
     </row>
-    <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="25" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="B88" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C88" s="26" t="s">
         <v>440</v>
       </c>
       <c r="D88" s="27" t="s">
-        <v>444</v>
+        <v>441</v>
       </c>
       <c r="E88" s="26" t="s">
-        <v>98</v>
+        <v>146</v>
       </c>
       <c r="F88" s="26" t="s">
-        <v>445</v>
+        <v>442</v>
       </c>
       <c r="G88" s="26" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="H88" s="26" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="I88" s="26" t="s">
         <v>86</v>
@@ -8563,79 +8627,79 @@
       <c r="L88" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M88" s="26" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M88" s="26"/>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="25" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B89" s="26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C89" s="26" t="s">
         <v>440</v>
       </c>
       <c r="D89" s="27" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E89" s="26" t="s">
-        <v>98</v>
+        <v>445</v>
       </c>
       <c r="F89" s="26" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="G89" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H89" s="26" t="s">
-        <v>433</v>
+        <v>412</v>
       </c>
       <c r="I89" s="26" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="J89" s="26" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="K89" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L89" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="M89" s="26"/>
+        <v>18</v>
+      </c>
+      <c r="M89" s="26" t="s">
+        <v>447</v>
+      </c>
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="25" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="B90" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C90" s="26" t="s">
+        <v>449</v>
+      </c>
+      <c r="D90" s="27" t="s">
+        <v>450</v>
+      </c>
+      <c r="E90" s="26" t="s">
         <v>451</v>
       </c>
-      <c r="D90" s="27" t="s">
+      <c r="F90" s="26" t="s">
         <v>452</v>
       </c>
-      <c r="E90" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="F90" s="26" t="s">
+      <c r="G90" s="26" t="s">
+        <v>100</v>
+      </c>
+      <c r="H90" s="26" t="s">
         <v>453</v>
       </c>
-      <c r="G90" s="26" t="s">
-        <v>140</v>
-      </c>
-      <c r="H90" s="26" t="s">
-        <v>433</v>
-      </c>
       <c r="I90" s="26" t="s">
-        <v>165</v>
+        <v>102</v>
       </c>
       <c r="J90" s="26" t="s">
-        <v>166</v>
+        <v>103</v>
       </c>
       <c r="K90" s="26" t="s">
         <v>27</v>
@@ -8644,39 +8708,39 @@
         <v>12</v>
       </c>
       <c r="M90" s="26" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="25" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B91" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="D91" s="27" t="s">
         <v>456</v>
       </c>
       <c r="E91" s="26" t="s">
-        <v>98</v>
+        <v>451</v>
       </c>
       <c r="F91" s="26" t="s">
         <v>457</v>
       </c>
       <c r="G91" s="26" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="H91" s="26" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="I91" s="26" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="J91" s="26" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="K91" s="26" t="s">
         <v>27</v>
@@ -8685,18 +8749,18 @@
         <v>12</v>
       </c>
       <c r="M91" s="26" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B92" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C92" s="26" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="D92" s="27" t="s">
         <v>461</v>
@@ -8711,13 +8775,13 @@
         <v>100</v>
       </c>
       <c r="H92" s="26" t="s">
-        <v>79</v>
+        <v>453</v>
       </c>
       <c r="I92" s="26" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="J92" s="26" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="K92" s="26" t="s">
         <v>27</v>
@@ -8735,7 +8799,7 @@
         <v>50</v>
       </c>
       <c r="C93" s="26" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="D93" s="27" t="s">
         <v>464</v>
@@ -8744,58 +8808,60 @@
         <v>98</v>
       </c>
       <c r="F93" s="26" t="s">
-        <v>16</v>
+        <v>465</v>
       </c>
       <c r="G93" s="26" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="H93" s="26" t="s">
-        <v>433</v>
+        <v>412</v>
       </c>
       <c r="I93" s="26" t="s">
-        <v>102</v>
+        <v>86</v>
       </c>
       <c r="J93" s="26" t="s">
-        <v>103</v>
+        <v>87</v>
       </c>
       <c r="K93" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L93" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="M93" s="26"/>
+        <v>12</v>
+      </c>
+      <c r="M93" s="26" t="s">
+        <v>466</v>
+      </c>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="25" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B94" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C94" s="26" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="D94" s="27" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E94" s="26" t="s">
-        <v>146</v>
+        <v>98</v>
       </c>
       <c r="F94" s="26" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="G94" s="26" t="s">
-        <v>148</v>
+        <v>100</v>
       </c>
       <c r="H94" s="26" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
       <c r="I94" s="26" t="s">
-        <v>79</v>
+        <v>102</v>
       </c>
       <c r="J94" s="26" t="s">
-        <v>80</v>
+        <v>103</v>
       </c>
       <c r="K94" s="26" t="s">
         <v>27</v>
@@ -8807,34 +8873,34 @@
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="25" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="B95" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C95" s="26" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="D95" s="27" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E95" s="26" t="s">
-        <v>471</v>
+        <v>98</v>
       </c>
       <c r="F95" s="26" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="G95" s="26" t="s">
-        <v>473</v>
+        <v>140</v>
       </c>
       <c r="H95" s="26" t="s">
-        <v>474</v>
+        <v>453</v>
       </c>
       <c r="I95" s="26" t="s">
-        <v>79</v>
+        <v>165</v>
       </c>
       <c r="J95" s="26" t="s">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="K95" s="26" t="s">
         <v>27</v>
@@ -8842,32 +8908,34 @@
       <c r="L95" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M95" s="26"/>
+      <c r="M95" s="26" t="s">
+        <v>336</v>
+      </c>
     </row>
     <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="25" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B96" s="26" t="s">
         <v>50</v>
       </c>
       <c r="C96" s="26" t="s">
-        <v>469</v>
+        <v>475</v>
       </c>
       <c r="D96" s="27" t="s">
         <v>476</v>
       </c>
       <c r="E96" s="26" t="s">
+        <v>98</v>
+      </c>
+      <c r="F96" s="26" t="s">
         <v>477</v>
       </c>
-      <c r="F96" s="26" t="s">
-        <v>16</v>
-      </c>
       <c r="G96" s="26" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H96" s="26" t="s">
-        <v>79</v>
+        <v>478</v>
       </c>
       <c r="I96" s="26" t="s">
         <v>79</v>
@@ -8876,43 +8944,45 @@
         <v>80</v>
       </c>
       <c r="K96" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L96" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="M96" s="26"/>
+        <v>12</v>
+      </c>
+      <c r="M96" s="26" t="s">
+        <v>479</v>
+      </c>
     </row>
     <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="25" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B97" s="26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C97" s="26" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="D97" s="27" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="E97" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F97" s="26" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="G97" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H97" s="26" t="s">
-        <v>85</v>
+        <v>79</v>
       </c>
       <c r="I97" s="26" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="J97" s="26" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K97" s="26" t="s">
         <v>27</v>
@@ -8920,19 +8990,17 @@
       <c r="L97" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M97" s="26" t="s">
-        <v>482</v>
-      </c>
+      <c r="M97" s="26"/>
     </row>
     <row r="98" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="25" t="s">
         <v>483</v>
       </c>
       <c r="B98" s="26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C98" s="26" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="D98" s="27" t="s">
         <v>484</v>
@@ -8941,60 +9009,58 @@
         <v>98</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>485</v>
+        <v>16</v>
       </c>
       <c r="G98" s="26" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="H98" s="26" t="s">
-        <v>85</v>
+        <v>453</v>
       </c>
       <c r="I98" s="26" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="J98" s="26" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="K98" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L98" s="26" t="s">
-        <v>12</v>
-      </c>
-      <c r="M98" s="26" t="s">
-        <v>486</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="M98" s="26"/>
     </row>
     <row r="99" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="B99" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C99" s="26" t="s">
+        <v>475</v>
+      </c>
+      <c r="D99" s="27" t="s">
+        <v>486</v>
+      </c>
+      <c r="E99" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="F99" s="26" t="s">
         <v>487</v>
       </c>
-      <c r="B99" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C99" s="26" t="s">
-        <v>364</v>
-      </c>
-      <c r="D99" s="27" t="s">
-        <v>488</v>
-      </c>
-      <c r="E99" s="26" t="s">
-        <v>98</v>
-      </c>
-      <c r="F99" s="26" t="s">
-        <v>489</v>
-      </c>
       <c r="G99" s="26" t="s">
-        <v>100</v>
+        <v>148</v>
       </c>
       <c r="H99" s="26" t="s">
-        <v>101</v>
+        <v>478</v>
       </c>
       <c r="I99" s="26" t="s">
-        <v>165</v>
+        <v>79</v>
       </c>
       <c r="J99" s="26" t="s">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="K99" s="26" t="s">
         <v>27</v>
@@ -9006,34 +9072,34 @@
     </row>
     <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="25" t="s">
+        <v>488</v>
+      </c>
+      <c r="B100" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C100" s="26" t="s">
+        <v>489</v>
+      </c>
+      <c r="D100" s="27" t="s">
         <v>490</v>
       </c>
-      <c r="B100" s="26" t="s">
-        <v>51</v>
-      </c>
-      <c r="C100" s="26" t="s">
-        <v>364</v>
-      </c>
-      <c r="D100" s="27" t="s">
+      <c r="E100" s="26" t="s">
         <v>491</v>
-      </c>
-      <c r="E100" s="26" t="s">
-        <v>98</v>
       </c>
       <c r="F100" s="26" t="s">
         <v>492</v>
       </c>
       <c r="G100" s="26" t="s">
-        <v>100</v>
+        <v>493</v>
       </c>
       <c r="H100" s="26" t="s">
-        <v>101</v>
+        <v>494</v>
       </c>
       <c r="I100" s="26" t="s">
-        <v>165</v>
+        <v>79</v>
       </c>
       <c r="J100" s="26" t="s">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="K100" s="26" t="s">
         <v>27</v>
@@ -9045,61 +9111,61 @@
     </row>
     <row r="101" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="25" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="B101" s="26" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>364</v>
+        <v>489</v>
       </c>
       <c r="D101" s="27" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E101" s="26" t="s">
-        <v>98</v>
+        <v>497</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>495</v>
+        <v>16</v>
       </c>
       <c r="G101" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H101" s="26" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
       <c r="I101" s="26" t="s">
-        <v>165</v>
+        <v>79</v>
       </c>
       <c r="J101" s="26" t="s">
-        <v>166</v>
+        <v>80</v>
       </c>
       <c r="K101" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L101" s="26" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="M101" s="26"/>
     </row>
-    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="102" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="25" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B102" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C102" s="26" t="s">
-        <v>364</v>
+        <v>499</v>
       </c>
       <c r="D102" s="27" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="E102" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F102" s="26" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="G102" s="26" t="s">
         <v>100</v>
@@ -9119,106 +9185,108 @@
       <c r="L102" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M102" s="26"/>
-    </row>
-    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M102" s="26" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="25" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B103" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C103" s="26" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D103" s="27" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="E103" s="26" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F103" s="26" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="G103" s="26" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H103" s="26" t="s">
-        <v>124</v>
+        <v>85</v>
       </c>
       <c r="I103" s="26" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="J103" s="26" t="s">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="K103" s="26" t="s">
         <v>27</v>
       </c>
       <c r="L103" s="26" t="s">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="M103" s="26" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="25" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="B104" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C104" s="26" t="s">
-        <v>127</v>
+        <v>384</v>
       </c>
       <c r="D104" s="27" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="E104" s="26" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="F104" s="26" t="s">
-        <v>124</v>
+        <v>509</v>
       </c>
       <c r="G104" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H104" s="26" t="s">
-        <v>79</v>
+        <v>101</v>
       </c>
       <c r="I104" s="26" t="s">
-        <v>79</v>
+        <v>165</v>
       </c>
       <c r="J104" s="26" t="s">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="K104" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L104" s="26" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M104" s="26"/>
     </row>
     <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="25" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B105" s="26" t="s">
         <v>51</v>
       </c>
       <c r="C105" s="26" t="s">
-        <v>507</v>
+        <v>384</v>
       </c>
       <c r="D105" s="27" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="E105" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F105" s="26" t="s">
-        <v>16</v>
+        <v>512</v>
       </c>
       <c r="G105" s="26" t="s">
         <v>100</v>
@@ -9227,43 +9295,43 @@
         <v>101</v>
       </c>
       <c r="I105" s="26" t="s">
-        <v>102</v>
+        <v>165</v>
       </c>
       <c r="J105" s="26" t="s">
-        <v>103</v>
+        <v>166</v>
       </c>
       <c r="K105" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L105" s="26" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="M105" s="26"/>
     </row>
     <row r="106" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="25" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B106" s="26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C106" s="26" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="D106" s="27" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="E106" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F106" s="26" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="G106" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H106" s="26" t="s">
-        <v>512</v>
+        <v>101</v>
       </c>
       <c r="I106" s="26" t="s">
         <v>165</v>
@@ -9272,121 +9340,123 @@
         <v>166</v>
       </c>
       <c r="K106" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L106" s="26" t="s">
         <v>12</v>
       </c>
       <c r="M106" s="26"/>
     </row>
-    <row r="107" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="25" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="B107" s="26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C107" s="26" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="D107" s="27" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="E107" s="26" t="s">
         <v>98</v>
       </c>
       <c r="F107" s="26" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="G107" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H107" s="26" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="I107" s="26" t="s">
-        <v>165</v>
+        <v>86</v>
       </c>
       <c r="J107" s="26" t="s">
-        <v>166</v>
+        <v>87</v>
       </c>
       <c r="K107" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L107" s="26" t="s">
         <v>12</v>
       </c>
       <c r="M107" s="26"/>
     </row>
-    <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="25" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="B108" s="26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C108" s="26" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D108" s="27" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E108" s="26" t="s">
-        <v>519</v>
+        <v>76</v>
       </c>
       <c r="F108" s="26" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="G108" s="26" t="s">
-        <v>100</v>
+        <v>124</v>
       </c>
       <c r="H108" s="26" t="s">
-        <v>101</v>
+        <v>124</v>
       </c>
       <c r="I108" s="26" t="s">
-        <v>102</v>
+        <v>22</v>
       </c>
       <c r="J108" s="26" t="s">
-        <v>103</v>
+        <v>203</v>
       </c>
       <c r="K108" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L108" s="26" t="s">
-        <v>18</v>
-      </c>
-      <c r="M108" s="26"/>
+        <v>22</v>
+      </c>
+      <c r="M108" s="26" t="s">
+        <v>523</v>
+      </c>
     </row>
     <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="25" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="B109" s="26" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="C109" s="26" t="s">
-        <v>522</v>
+        <v>127</v>
       </c>
       <c r="D109" s="27" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="E109" s="26" t="s">
-        <v>524</v>
+        <v>129</v>
       </c>
       <c r="F109" s="26" t="s">
-        <v>525</v>
+        <v>124</v>
       </c>
       <c r="G109" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H109" s="26" t="s">
-        <v>195</v>
+        <v>79</v>
       </c>
       <c r="I109" s="26" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="J109" s="26" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="K109" s="26" t="s">
         <v>31</v>
@@ -9394,31 +9464,29 @@
       <c r="L109" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="M109" s="26" t="s">
-        <v>526</v>
-      </c>
+      <c r="M109" s="26"/>
     </row>
     <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A110" s="25" t="s">
+        <v>526</v>
+      </c>
+      <c r="B110" s="26" t="s">
+        <v>51</v>
+      </c>
+      <c r="C110" s="26" t="s">
         <v>527</v>
       </c>
-      <c r="B110" s="26" t="s">
-        <v>52</v>
-      </c>
-      <c r="C110" s="26" t="s">
+      <c r="D110" s="27" t="s">
         <v>528</v>
       </c>
-      <c r="D110" s="27" t="s">
-        <v>529</v>
-      </c>
       <c r="E110" s="26" t="s">
-        <v>530</v>
+        <v>98</v>
       </c>
       <c r="F110" s="26" t="s">
-        <v>531</v>
+        <v>16</v>
       </c>
       <c r="G110" s="26" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="H110" s="26" t="s">
         <v>101</v>
@@ -9430,330 +9498,324 @@
         <v>103</v>
       </c>
       <c r="K110" s="26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L110" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="M110" s="26" t="s">
-        <v>532</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="M110" s="26"/>
     </row>
     <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="25" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="B111" s="26" t="s">
         <v>52</v>
       </c>
       <c r="C111" s="26" t="s">
-        <v>534</v>
+        <v>384</v>
       </c>
       <c r="D111" s="27" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="E111" s="26" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="F111" s="26" t="s">
-        <v>77</v>
+        <v>531</v>
       </c>
       <c r="G111" s="26" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="H111" s="26" t="s">
-        <v>79</v>
+        <v>532</v>
       </c>
       <c r="I111" s="26" t="s">
-        <v>79</v>
+        <v>165</v>
       </c>
       <c r="J111" s="26" t="s">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="K111" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L111" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M111" s="26" t="s">
-        <v>536</v>
-      </c>
+      <c r="M111" s="26"/>
     </row>
     <row r="112" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A112" s="25" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="B112" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C112" s="26" t="s">
-        <v>538</v>
+        <v>384</v>
       </c>
       <c r="D112" s="27" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="E112" s="26" t="s">
-        <v>540</v>
+        <v>98</v>
       </c>
       <c r="F112" s="26" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="G112" s="26" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="H112" s="26" t="s">
-        <v>542</v>
+        <v>101</v>
       </c>
       <c r="I112" s="26" t="s">
-        <v>79</v>
+        <v>165</v>
       </c>
       <c r="J112" s="26" t="s">
-        <v>80</v>
+        <v>166</v>
       </c>
       <c r="K112" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L112" s="26" t="s">
         <v>12</v>
       </c>
-      <c r="M112" s="26" t="s">
-        <v>543</v>
-      </c>
-    </row>
-    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M112" s="26"/>
+    </row>
+    <row r="113" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="25" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
       <c r="B113" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C113" s="26" t="s">
-        <v>307</v>
+        <v>537</v>
       </c>
       <c r="D113" s="27" t="s">
-        <v>545</v>
+        <v>538</v>
       </c>
       <c r="E113" s="26" t="s">
-        <v>546</v>
+        <v>539</v>
       </c>
       <c r="F113" s="26" t="s">
-        <v>547</v>
+        <v>540</v>
       </c>
       <c r="G113" s="26" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="H113" s="26" t="s">
-        <v>310</v>
+        <v>101</v>
       </c>
       <c r="I113" s="26" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="J113" s="26" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="K113" s="26" t="s">
         <v>31</v>
       </c>
       <c r="L113" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="M113" s="26" t="s">
-        <v>548</v>
-      </c>
-    </row>
-    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>18</v>
+      </c>
+      <c r="M113" s="26"/>
+    </row>
+    <row r="114" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="25" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="B114" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C114" s="26" t="s">
-        <v>307</v>
+        <v>542</v>
       </c>
       <c r="D114" s="27" t="s">
-        <v>550</v>
+        <v>543</v>
       </c>
       <c r="E114" s="26" t="s">
-        <v>297</v>
+        <v>544</v>
       </c>
       <c r="F114" s="26" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="G114" s="26" t="s">
-        <v>140</v>
+        <v>100</v>
       </c>
       <c r="H114" s="26" t="s">
-        <v>310</v>
+        <v>195</v>
       </c>
       <c r="I114" s="26" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="J114" s="26" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="K114" s="26" t="s">
         <v>31</v>
       </c>
       <c r="L114" s="26" t="s">
-        <v>14</v>
-      </c>
-      <c r="M114" s="26"/>
-    </row>
-    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>18</v>
+      </c>
+      <c r="M114" s="26" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="25" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="B115" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C115" s="26" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="D115" s="27" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="E115" s="26" t="s">
-        <v>555</v>
+        <v>550</v>
       </c>
       <c r="F115" s="26" t="s">
-        <v>556</v>
+        <v>551</v>
       </c>
       <c r="G115" s="26" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="H115" s="26" t="s">
-        <v>341</v>
+        <v>101</v>
       </c>
       <c r="I115" s="26" t="s">
-        <v>86</v>
+        <v>102</v>
       </c>
       <c r="J115" s="26" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="K115" s="26" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="L115" s="26" t="s">
         <v>14</v>
       </c>
       <c r="M115" s="26" t="s">
-        <v>557</v>
-      </c>
-    </row>
-    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="25" t="s">
-        <v>558</v>
+        <v>553</v>
       </c>
       <c r="B116" s="26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="C116" s="26" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="D116" s="27" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="E116" s="26" t="s">
-        <v>560</v>
+        <v>76</v>
       </c>
       <c r="F116" s="26" t="s">
-        <v>124</v>
+        <v>77</v>
       </c>
       <c r="G116" s="26" t="s">
-        <v>140</v>
+        <v>78</v>
       </c>
       <c r="H116" s="26" t="s">
-        <v>341</v>
+        <v>79</v>
       </c>
       <c r="I116" s="26" t="s">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="J116" s="26" t="s">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="K116" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L116" s="26" t="s">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="M116" s="26" t="s">
-        <v>561</v>
+        <v>556</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A117" s="25" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="B117" s="26" t="s">
         <v>53</v>
       </c>
       <c r="C117" s="26" t="s">
-        <v>102</v>
+        <v>558</v>
       </c>
       <c r="D117" s="27" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="E117" s="26" t="s">
-        <v>564</v>
+        <v>560</v>
       </c>
       <c r="F117" s="26" t="s">
-        <v>565</v>
+        <v>561</v>
       </c>
       <c r="G117" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H117" s="26" t="s">
-        <v>101</v>
+        <v>562</v>
       </c>
       <c r="I117" s="26" t="s">
-        <v>102</v>
+        <v>79</v>
       </c>
       <c r="J117" s="26" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="K117" s="26" t="s">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="L117" s="26" t="s">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="M117" s="26" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="25" t="s">
+        <v>564</v>
+      </c>
+      <c r="B118" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C118" s="26" t="s">
+        <v>327</v>
+      </c>
+      <c r="D118" s="27" t="s">
+        <v>565</v>
+      </c>
+      <c r="E118" s="26" t="s">
+        <v>566</v>
+      </c>
+      <c r="F118" s="26" t="s">
         <v>567</v>
-      </c>
-      <c r="B118" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="C118" s="26" t="s">
-        <v>568</v>
-      </c>
-      <c r="D118" s="27" t="s">
-        <v>569</v>
-      </c>
-      <c r="E118" s="26" t="s">
-        <v>570</v>
-      </c>
-      <c r="F118" s="26" t="s">
-        <v>571</v>
       </c>
       <c r="G118" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H118" s="26" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="I118" s="26" t="s">
-        <v>342</v>
+        <v>86</v>
       </c>
       <c r="J118" s="26" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="K118" s="26" t="s">
         <v>31</v>
@@ -9761,38 +9823,40 @@
       <c r="L118" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="M118" s="26"/>
+      <c r="M118" s="26" t="s">
+        <v>568</v>
+      </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="25" t="s">
-        <v>572</v>
+        <v>569</v>
       </c>
       <c r="B119" s="26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C119" s="26" t="s">
-        <v>568</v>
+        <v>327</v>
       </c>
       <c r="D119" s="27" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="E119" s="26" t="s">
-        <v>574</v>
+        <v>317</v>
       </c>
       <c r="F119" s="26" t="s">
-        <v>575</v>
+        <v>571</v>
       </c>
       <c r="G119" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H119" s="26" t="s">
-        <v>348</v>
+        <v>330</v>
       </c>
       <c r="I119" s="26" t="s">
-        <v>342</v>
+        <v>86</v>
       </c>
       <c r="J119" s="26" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="K119" s="26" t="s">
         <v>31</v>
@@ -9804,34 +9868,34 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="25" t="s">
+        <v>572</v>
+      </c>
+      <c r="B120" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C120" s="26" t="s">
+        <v>573</v>
+      </c>
+      <c r="D120" s="27" t="s">
+        <v>574</v>
+      </c>
+      <c r="E120" s="26" t="s">
+        <v>575</v>
+      </c>
+      <c r="F120" s="26" t="s">
         <v>576</v>
       </c>
-      <c r="B120" s="26" t="s">
-        <v>54</v>
-      </c>
-      <c r="C120" s="26" t="s">
-        <v>577</v>
-      </c>
-      <c r="D120" s="27" t="s">
-        <v>578</v>
-      </c>
-      <c r="E120" s="26" t="s">
-        <v>579</v>
-      </c>
-      <c r="F120" s="26" t="s">
-        <v>580</v>
-      </c>
       <c r="G120" s="26" t="s">
-        <v>581</v>
+        <v>140</v>
       </c>
       <c r="H120" s="26" t="s">
-        <v>582</v>
+        <v>361</v>
       </c>
       <c r="I120" s="26" t="s">
-        <v>342</v>
+        <v>86</v>
       </c>
       <c r="J120" s="26" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="K120" s="26" t="s">
         <v>31</v>
@@ -9839,32 +9903,34 @@
       <c r="L120" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="M120" s="26"/>
-    </row>
-    <row r="121" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M120" s="26" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="25" t="s">
-        <v>583</v>
+        <v>578</v>
       </c>
       <c r="B121" s="26" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C121" s="26" t="s">
-        <v>584</v>
+        <v>573</v>
       </c>
       <c r="D121" s="27" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
       <c r="E121" s="26" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="F121" s="26" t="s">
-        <v>24</v>
+        <v>124</v>
       </c>
       <c r="G121" s="26" t="s">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="H121" s="26" t="s">
-        <v>85</v>
+        <v>361</v>
       </c>
       <c r="I121" s="26" t="s">
         <v>86</v>
@@ -9876,235 +9942,235 @@
         <v>31</v>
       </c>
       <c r="L121" s="26" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="M121" s="26" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="25" t="s">
+        <v>582</v>
+      </c>
+      <c r="B122" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C122" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="D122" s="27" t="s">
+        <v>583</v>
+      </c>
+      <c r="E122" s="26" t="s">
+        <v>584</v>
+      </c>
+      <c r="F122" s="26" t="s">
+        <v>585</v>
+      </c>
+      <c r="G122" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="H122" s="26" t="s">
+        <v>101</v>
+      </c>
+      <c r="I122" s="26" t="s">
+        <v>102</v>
+      </c>
+      <c r="J122" s="26" t="s">
+        <v>103</v>
+      </c>
+      <c r="K122" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L122" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="M122" s="26" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="25" t="s">
+        <v>587</v>
+      </c>
+      <c r="B123" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C123" s="26" t="s">
         <v>588</v>
       </c>
-      <c r="B122" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C122" s="26" t="s">
+      <c r="D123" s="27" t="s">
         <v>589</v>
       </c>
-      <c r="D122" s="27" t="s">
+      <c r="E123" s="26" t="s">
         <v>590</v>
       </c>
-      <c r="E122" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="F122" s="26" t="s">
+      <c r="F123" s="26" t="s">
         <v>591</v>
       </c>
-      <c r="G122" s="26" t="s">
-        <v>592</v>
-      </c>
-      <c r="H122" s="26" t="s">
-        <v>593</v>
-      </c>
-      <c r="I122" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="J122" s="26" t="s">
-        <v>203</v>
-      </c>
-      <c r="K122" s="26" t="s">
-        <v>27</v>
-      </c>
-      <c r="L122" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="M122" s="26" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="123" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A123" s="25" t="s">
-        <v>595</v>
-      </c>
-      <c r="B123" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C123" s="26" t="s">
-        <v>596</v>
-      </c>
-      <c r="D123" s="27" t="s">
-        <v>597</v>
-      </c>
-      <c r="E123" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="F123" s="26" t="s">
-        <v>598</v>
-      </c>
       <c r="G123" s="26" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="H123" s="26" t="s">
-        <v>310</v>
+        <v>368</v>
       </c>
       <c r="I123" s="26" t="s">
-        <v>22</v>
+        <v>362</v>
       </c>
       <c r="J123" s="26" t="s">
-        <v>203</v>
+        <v>124</v>
       </c>
       <c r="K123" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L123" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="M123" s="26" t="s">
-        <v>599</v>
-      </c>
+        <v>14</v>
+      </c>
+      <c r="M123" s="26"/>
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="25" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="B124" s="26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C124" s="26" t="s">
-        <v>596</v>
+        <v>588</v>
       </c>
       <c r="D124" s="27" t="s">
-        <v>601</v>
+        <v>593</v>
       </c>
       <c r="E124" s="26" t="s">
-        <v>200</v>
+        <v>594</v>
       </c>
       <c r="F124" s="26" t="s">
-        <v>602</v>
+        <v>595</v>
       </c>
       <c r="G124" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H124" s="26" t="s">
-        <v>202</v>
+        <v>368</v>
       </c>
       <c r="I124" s="26" t="s">
-        <v>22</v>
+        <v>362</v>
       </c>
       <c r="J124" s="26" t="s">
-        <v>203</v>
+        <v>124</v>
       </c>
       <c r="K124" s="26" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="L124" s="26" t="s">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="M124" s="26"/>
     </row>
     <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="25" t="s">
-        <v>603</v>
+        <v>596</v>
       </c>
       <c r="B125" s="26" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="C125" s="26" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="D125" s="27" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="E125" s="26" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="F125" s="26" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="G125" s="26" t="s">
-        <v>78</v>
+        <v>601</v>
       </c>
       <c r="H125" s="26" t="s">
-        <v>85</v>
+        <v>602</v>
       </c>
       <c r="I125" s="26" t="s">
-        <v>86</v>
+        <v>362</v>
       </c>
       <c r="J125" s="26" t="s">
-        <v>87</v>
+        <v>124</v>
       </c>
       <c r="K125" s="26" t="s">
         <v>31</v>
       </c>
       <c r="L125" s="26" t="s">
+        <v>14</v>
+      </c>
+      <c r="M125" s="26"/>
+    </row>
+    <row r="126" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="25" t="s">
+        <v>603</v>
+      </c>
+      <c r="B126" s="26" t="s">
+        <v>54</v>
+      </c>
+      <c r="C126" s="26" t="s">
+        <v>604</v>
+      </c>
+      <c r="D126" s="27" t="s">
+        <v>605</v>
+      </c>
+      <c r="E126" s="26" t="s">
+        <v>606</v>
+      </c>
+      <c r="F126" s="26" t="s">
         <v>24</v>
-      </c>
-      <c r="M125" s="26"/>
-    </row>
-    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A126" s="25" t="s">
-        <v>607</v>
-      </c>
-      <c r="B126" s="26" t="s">
-        <v>55</v>
-      </c>
-      <c r="C126" s="26" t="s">
-        <v>608</v>
-      </c>
-      <c r="D126" s="27" t="s">
-        <v>609</v>
-      </c>
-      <c r="E126" s="26" t="s">
-        <v>200</v>
-      </c>
-      <c r="F126" s="26" t="s">
-        <v>610</v>
       </c>
       <c r="G126" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H126" s="26" t="s">
-        <v>310</v>
+        <v>85</v>
       </c>
       <c r="I126" s="26" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="J126" s="26" t="s">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="K126" s="26" t="s">
         <v>31</v>
       </c>
       <c r="L126" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="M126" s="26"/>
-    </row>
-    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>24</v>
+      </c>
+      <c r="M126" s="26" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="25" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="B127" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C127" s="26" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="D127" s="27" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="E127" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F127" s="26" t="s">
+        <v>611</v>
+      </c>
+      <c r="G127" s="26" t="s">
+        <v>612</v>
+      </c>
+      <c r="H127" s="26" t="s">
         <v>613</v>
-      </c>
-      <c r="G127" s="26" t="s">
-        <v>78</v>
-      </c>
-      <c r="H127" s="26" t="s">
-        <v>85</v>
       </c>
       <c r="I127" s="26" t="s">
         <v>22</v>
@@ -10113,7 +10179,7 @@
         <v>203</v>
       </c>
       <c r="K127" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L127" s="26" t="s">
         <v>22</v>
@@ -10122,7 +10188,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="128" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A128" s="25" t="s">
         <v>615</v>
       </c>
@@ -10130,22 +10196,22 @@
         <v>55</v>
       </c>
       <c r="C128" s="26" t="s">
-        <v>608</v>
+        <v>616</v>
       </c>
       <c r="D128" s="27" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="E128" s="26" t="s">
-        <v>617</v>
+        <v>200</v>
       </c>
       <c r="F128" s="26" t="s">
         <v>618</v>
       </c>
       <c r="G128" s="26" t="s">
-        <v>78</v>
+        <v>148</v>
       </c>
       <c r="H128" s="26" t="s">
-        <v>85</v>
+        <v>330</v>
       </c>
       <c r="I128" s="26" t="s">
         <v>22</v>
@@ -10154,117 +10220,117 @@
         <v>203</v>
       </c>
       <c r="K128" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L128" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="M128" s="26"/>
-    </row>
-    <row r="129" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="M128" s="26" t="s">
+        <v>619</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="25" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="B129" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C129" s="26" t="s">
-        <v>337</v>
+        <v>616</v>
       </c>
       <c r="D129" s="27" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="E129" s="26" t="s">
-        <v>621</v>
+        <v>200</v>
       </c>
       <c r="F129" s="26" t="s">
-        <v>24</v>
+        <v>622</v>
       </c>
       <c r="G129" s="26" t="s">
-        <v>340</v>
+        <v>140</v>
       </c>
       <c r="H129" s="26" t="s">
-        <v>124</v>
+        <v>202</v>
       </c>
       <c r="I129" s="26" t="s">
-        <v>342</v>
+        <v>22</v>
       </c>
       <c r="J129" s="26" t="s">
-        <v>124</v>
+        <v>203</v>
       </c>
       <c r="K129" s="26" t="s">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="L129" s="26" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="M129" s="26"/>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="25" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B130" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C130" s="26" t="s">
-        <v>337</v>
+        <v>616</v>
       </c>
       <c r="D130" s="27" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="E130" s="26" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="F130" s="26" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="G130" s="26" t="s">
-        <v>626</v>
+        <v>78</v>
       </c>
       <c r="H130" s="26" t="s">
-        <v>627</v>
+        <v>85</v>
       </c>
       <c r="I130" s="26" t="s">
-        <v>22</v>
+        <v>86</v>
       </c>
       <c r="J130" s="26" t="s">
-        <v>203</v>
+        <v>87</v>
       </c>
       <c r="K130" s="26" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="L130" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="M130" s="26" t="s">
-        <v>628</v>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="M130" s="26"/>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="25" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B131" s="26" t="s">
         <v>55</v>
       </c>
       <c r="C131" s="26" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="D131" s="27" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E131" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F131" s="26" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="G131" s="26" t="s">
-        <v>124</v>
+        <v>100</v>
       </c>
       <c r="H131" s="26" t="s">
-        <v>124</v>
+        <v>330</v>
       </c>
       <c r="I131" s="26" t="s">
         <v>22</v>
@@ -10280,9 +10346,208 @@
       </c>
       <c r="M131" s="26"/>
     </row>
+    <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="25" t="s">
+        <v>631</v>
+      </c>
+      <c r="B132" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C132" s="26" t="s">
+        <v>628</v>
+      </c>
+      <c r="D132" s="27" t="s">
+        <v>632</v>
+      </c>
+      <c r="E132" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="F132" s="26" t="s">
+        <v>633</v>
+      </c>
+      <c r="G132" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="H132" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="I132" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J132" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K132" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="L132" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="M132" s="26" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="25" t="s">
+        <v>635</v>
+      </c>
+      <c r="B133" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C133" s="26" t="s">
+        <v>628</v>
+      </c>
+      <c r="D133" s="27" t="s">
+        <v>636</v>
+      </c>
+      <c r="E133" s="26" t="s">
+        <v>637</v>
+      </c>
+      <c r="F133" s="26" t="s">
+        <v>638</v>
+      </c>
+      <c r="G133" s="26" t="s">
+        <v>78</v>
+      </c>
+      <c r="H133" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="I133" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J133" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K133" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="L133" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="M133" s="26"/>
+    </row>
+    <row r="134" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="25" t="s">
+        <v>639</v>
+      </c>
+      <c r="B134" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C134" s="26" t="s">
+        <v>357</v>
+      </c>
+      <c r="D134" s="27" t="s">
+        <v>640</v>
+      </c>
+      <c r="E134" s="26" t="s">
+        <v>641</v>
+      </c>
+      <c r="F134" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="G134" s="26" t="s">
+        <v>360</v>
+      </c>
+      <c r="H134" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="I134" s="26" t="s">
+        <v>362</v>
+      </c>
+      <c r="J134" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="K134" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="L134" s="26" t="s">
+        <v>24</v>
+      </c>
+      <c r="M134" s="26"/>
+    </row>
+    <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A135" s="25" t="s">
+        <v>642</v>
+      </c>
+      <c r="B135" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C135" s="26" t="s">
+        <v>357</v>
+      </c>
+      <c r="D135" s="27" t="s">
+        <v>643</v>
+      </c>
+      <c r="E135" s="26" t="s">
+        <v>644</v>
+      </c>
+      <c r="F135" s="26" t="s">
+        <v>645</v>
+      </c>
+      <c r="G135" s="26" t="s">
+        <v>646</v>
+      </c>
+      <c r="H135" s="26" t="s">
+        <v>647</v>
+      </c>
+      <c r="I135" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J135" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K135" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="L135" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="M135" s="26" t="s">
+        <v>648</v>
+      </c>
+    </row>
+    <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A136" s="25" t="s">
+        <v>649</v>
+      </c>
+      <c r="B136" s="26" t="s">
+        <v>55</v>
+      </c>
+      <c r="C136" s="26" t="s">
+        <v>650</v>
+      </c>
+      <c r="D136" s="27" t="s">
+        <v>651</v>
+      </c>
+      <c r="E136" s="26" t="s">
+        <v>200</v>
+      </c>
+      <c r="F136" s="26" t="s">
+        <v>652</v>
+      </c>
+      <c r="G136" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="H136" s="26" t="s">
+        <v>124</v>
+      </c>
+      <c r="I136" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="J136" s="26" t="s">
+        <v>203</v>
+      </c>
+      <c r="K136" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="L136" s="26" t="s">
+        <v>22</v>
+      </c>
+      <c r="M136" s="26"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:M131"/>
-  <conditionalFormatting sqref="L6:L331">
+  <autoFilter ref="A5:M136"/>
+  <conditionalFormatting sqref="L6:L336">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$L6="Verificado"</formula>
     </cfRule>
@@ -10305,17 +10570,17 @@
       <formula>$L6="Curado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K331">
+  <conditionalFormatting sqref="K6:K336">
     <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
       <formula>$K6="MVP"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K6:K331" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K6:K336" type="list">
       <formula1>"MVP,EUA,v2,v3"</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L6:L331" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="L6:L336" type="list">
       <formula1>"Verificado,Confirmar,A mapear,Sem API,Pago,Derivado,Curado"</formula1>
       <formula2>0</formula2>
     </dataValidation>
@@ -10356,12 +10621,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>633</v>
+        <v>653</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>634</v>
+        <v>654</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -10422,28 +10687,28 @@
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="25" t="s">
-        <v>635</v>
+        <v>655</v>
       </c>
       <c r="B6" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>636</v>
+        <v>656</v>
       </c>
       <c r="D6" s="27" t="s">
-        <v>637</v>
+        <v>657</v>
       </c>
       <c r="E6" s="26" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>639</v>
+        <v>659</v>
       </c>
       <c r="G6" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H6" s="26" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="I6" s="26" t="s">
         <v>165</v>
@@ -10461,22 +10726,22 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="25" t="s">
-        <v>641</v>
+        <v>661</v>
       </c>
       <c r="B7" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>642</v>
+        <v>662</v>
       </c>
       <c r="D7" s="27" t="s">
-        <v>643</v>
+        <v>663</v>
       </c>
       <c r="E7" s="26" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>644</v>
+        <v>664</v>
       </c>
       <c r="G7" s="26" t="s">
         <v>100</v>
@@ -10500,22 +10765,22 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="25" t="s">
-        <v>645</v>
+        <v>665</v>
       </c>
       <c r="B8" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>642</v>
+        <v>662</v>
       </c>
       <c r="D8" s="27" t="s">
-        <v>646</v>
+        <v>666</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>647</v>
+        <v>667</v>
       </c>
       <c r="G8" s="26" t="s">
         <v>100</v>
@@ -10539,22 +10804,22 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="25" t="s">
-        <v>648</v>
+        <v>668</v>
       </c>
       <c r="B9" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>649</v>
+        <v>669</v>
       </c>
       <c r="D9" s="27" t="s">
-        <v>650</v>
+        <v>670</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>651</v>
+        <v>671</v>
       </c>
       <c r="G9" s="26" t="s">
         <v>100</v>
@@ -10578,28 +10843,28 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="25" t="s">
-        <v>652</v>
+        <v>672</v>
       </c>
       <c r="B10" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>653</v>
+        <v>673</v>
       </c>
       <c r="D10" s="27" t="s">
-        <v>654</v>
+        <v>674</v>
       </c>
       <c r="E10" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>655</v>
+        <v>675</v>
       </c>
       <c r="G10" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H10" s="26" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="I10" s="26" t="s">
         <v>22</v>
@@ -10617,28 +10882,28 @@
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="25" t="s">
-        <v>657</v>
+        <v>677</v>
       </c>
       <c r="B11" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>653</v>
+        <v>673</v>
       </c>
       <c r="D11" s="27" t="s">
+        <v>678</v>
+      </c>
+      <c r="E11" s="26" t="s">
         <v>658</v>
       </c>
-      <c r="E11" s="26" t="s">
-        <v>638</v>
-      </c>
       <c r="F11" s="26" t="s">
-        <v>659</v>
+        <v>679</v>
       </c>
       <c r="G11" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H11" s="26" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="I11" s="26" t="s">
         <v>102</v>
@@ -10656,28 +10921,28 @@
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="25" t="s">
-        <v>660</v>
+        <v>680</v>
       </c>
       <c r="B12" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>661</v>
+        <v>681</v>
       </c>
       <c r="D12" s="27" t="s">
-        <v>662</v>
+        <v>682</v>
       </c>
       <c r="E12" s="26" t="s">
-        <v>663</v>
+        <v>683</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>664</v>
+        <v>684</v>
       </c>
       <c r="G12" s="26" t="s">
         <v>148</v>
       </c>
       <c r="H12" s="26" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="I12" s="26" t="s">
         <v>102</v>
@@ -10695,19 +10960,19 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="25" t="s">
-        <v>665</v>
+        <v>685</v>
       </c>
       <c r="B13" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="D13" s="27" t="s">
-        <v>667</v>
+        <v>687</v>
       </c>
       <c r="E13" s="26" t="s">
-        <v>668</v>
+        <v>688</v>
       </c>
       <c r="F13" s="26" t="s">
         <v>124</v>
@@ -10731,27 +10996,27 @@
         <v>20</v>
       </c>
       <c r="M13" s="26" t="s">
-        <v>669</v>
+        <v>689</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="25" t="s">
-        <v>670</v>
+        <v>690</v>
       </c>
       <c r="B14" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>666</v>
+        <v>686</v>
       </c>
       <c r="D14" s="27" t="s">
-        <v>671</v>
+        <v>691</v>
       </c>
       <c r="E14" s="26" t="s">
-        <v>672</v>
+        <v>692</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G14" s="26" t="s">
         <v>100</v>
@@ -10775,7 +11040,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="25" t="s">
-        <v>674</v>
+        <v>694</v>
       </c>
       <c r="B15" s="26" t="s">
         <v>46</v>
@@ -10784,13 +11049,13 @@
         <v>198</v>
       </c>
       <c r="D15" s="27" t="s">
-        <v>675</v>
+        <v>695</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>676</v>
+        <v>696</v>
       </c>
       <c r="G15" s="26" t="s">
         <v>100</v>
@@ -10814,22 +11079,22 @@
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="25" t="s">
-        <v>677</v>
+        <v>697</v>
       </c>
       <c r="B16" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>678</v>
+        <v>698</v>
       </c>
       <c r="D16" s="27" t="s">
-        <v>679</v>
+        <v>699</v>
       </c>
       <c r="E16" s="26" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>680</v>
+        <v>700</v>
       </c>
       <c r="G16" s="26" t="s">
         <v>78</v>
@@ -10853,28 +11118,28 @@
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="25" t="s">
-        <v>681</v>
+        <v>701</v>
       </c>
       <c r="B17" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>678</v>
+        <v>698</v>
       </c>
       <c r="D17" s="27" t="s">
-        <v>682</v>
+        <v>702</v>
       </c>
       <c r="E17" s="26" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>683</v>
+        <v>703</v>
       </c>
       <c r="G17" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H17" s="26" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="I17" s="26" t="s">
         <v>79</v>
@@ -10892,22 +11157,22 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="25" t="s">
-        <v>684</v>
+        <v>704</v>
       </c>
       <c r="B18" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>678</v>
+        <v>698</v>
       </c>
       <c r="D18" s="27" t="s">
-        <v>685</v>
+        <v>705</v>
       </c>
       <c r="E18" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>686</v>
+        <v>706</v>
       </c>
       <c r="G18" s="26" t="s">
         <v>100</v>
@@ -10931,22 +11196,22 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="25" t="s">
-        <v>687</v>
+        <v>707</v>
       </c>
       <c r="B19" s="26" t="s">
         <v>46</v>
       </c>
       <c r="C19" s="26" t="s">
-        <v>678</v>
+        <v>698</v>
       </c>
       <c r="D19" s="27" t="s">
-        <v>688</v>
+        <v>708</v>
       </c>
       <c r="E19" s="26" t="s">
-        <v>689</v>
+        <v>709</v>
       </c>
       <c r="F19" s="26" t="s">
-        <v>690</v>
+        <v>710</v>
       </c>
       <c r="G19" s="26" t="s">
         <v>100</v>
@@ -10967,12 +11232,12 @@
         <v>18</v>
       </c>
       <c r="M19" s="26" t="s">
-        <v>691</v>
+        <v>711</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="25" t="s">
-        <v>692</v>
+        <v>712</v>
       </c>
       <c r="B20" s="26" t="s">
         <v>46</v>
@@ -10981,13 +11246,13 @@
         <v>198</v>
       </c>
       <c r="D20" s="27" t="s">
-        <v>693</v>
+        <v>713</v>
       </c>
       <c r="E20" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>694</v>
+        <v>714</v>
       </c>
       <c r="G20" s="26" t="s">
         <v>100</v>
@@ -11008,27 +11273,27 @@
         <v>12</v>
       </c>
       <c r="M20" s="26" t="s">
-        <v>695</v>
+        <v>715</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="25" t="s">
-        <v>696</v>
+        <v>716</v>
       </c>
       <c r="B21" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>697</v>
+        <v>717</v>
       </c>
       <c r="D21" s="27" t="s">
-        <v>698</v>
+        <v>718</v>
       </c>
       <c r="E21" s="26" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>699</v>
+        <v>719</v>
       </c>
       <c r="G21" s="26" t="s">
         <v>100</v>
@@ -11052,22 +11317,22 @@
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="25" t="s">
-        <v>700</v>
+        <v>720</v>
       </c>
       <c r="B22" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C22" s="26" t="s">
-        <v>697</v>
+        <v>717</v>
       </c>
       <c r="D22" s="27" t="s">
-        <v>701</v>
+        <v>721</v>
       </c>
       <c r="E22" s="26" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="F22" s="26" t="s">
-        <v>702</v>
+        <v>722</v>
       </c>
       <c r="G22" s="26" t="s">
         <v>100</v>
@@ -11088,27 +11353,27 @@
         <v>12</v>
       </c>
       <c r="M22" s="26" t="s">
-        <v>703</v>
+        <v>723</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="25" t="s">
-        <v>704</v>
+        <v>724</v>
       </c>
       <c r="B23" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>697</v>
+        <v>717</v>
       </c>
       <c r="D23" s="27" t="s">
-        <v>705</v>
+        <v>725</v>
       </c>
       <c r="E23" s="26" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>706</v>
+        <v>726</v>
       </c>
       <c r="G23" s="26" t="s">
         <v>100</v>
@@ -11132,22 +11397,22 @@
     </row>
     <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="25" t="s">
-        <v>707</v>
+        <v>727</v>
       </c>
       <c r="B24" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>708</v>
+        <v>728</v>
       </c>
       <c r="D24" s="27" t="s">
-        <v>709</v>
+        <v>729</v>
       </c>
       <c r="E24" s="26" t="s">
-        <v>710</v>
+        <v>730</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>711</v>
+        <v>731</v>
       </c>
       <c r="G24" s="26" t="s">
         <v>100</v>
@@ -11171,22 +11436,22 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="25" t="s">
-        <v>712</v>
+        <v>732</v>
       </c>
       <c r="B25" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>708</v>
+        <v>728</v>
       </c>
       <c r="D25" s="27" t="s">
-        <v>713</v>
+        <v>733</v>
       </c>
       <c r="E25" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>714</v>
+        <v>734</v>
       </c>
       <c r="G25" s="26" t="s">
         <v>100</v>
@@ -11210,22 +11475,22 @@
     </row>
     <row r="26" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="25" t="s">
-        <v>715</v>
+        <v>735</v>
       </c>
       <c r="B26" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>716</v>
+        <v>736</v>
       </c>
       <c r="D26" s="27" t="s">
-        <v>717</v>
+        <v>737</v>
       </c>
       <c r="E26" s="26" t="s">
-        <v>638</v>
+        <v>658</v>
       </c>
       <c r="F26" s="26" t="s">
-        <v>718</v>
+        <v>738</v>
       </c>
       <c r="G26" s="26" t="s">
         <v>100</v>
@@ -11249,7 +11514,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="25" t="s">
-        <v>719</v>
+        <v>739</v>
       </c>
       <c r="B27" s="26" t="s">
         <v>47</v>
@@ -11258,13 +11523,13 @@
         <v>144</v>
       </c>
       <c r="D27" s="27" t="s">
-        <v>720</v>
+        <v>740</v>
       </c>
       <c r="E27" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F27" s="26" t="s">
-        <v>721</v>
+        <v>741</v>
       </c>
       <c r="G27" s="26" t="s">
         <v>140</v>
@@ -11285,12 +11550,12 @@
         <v>12</v>
       </c>
       <c r="M27" s="26" t="s">
-        <v>722</v>
+        <v>742</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="25" t="s">
-        <v>723</v>
+        <v>743</v>
       </c>
       <c r="B28" s="26" t="s">
         <v>47</v>
@@ -11299,10 +11564,10 @@
         <v>144</v>
       </c>
       <c r="D28" s="27" t="s">
-        <v>724</v>
+        <v>744</v>
       </c>
       <c r="E28" s="26" t="s">
-        <v>725</v>
+        <v>745</v>
       </c>
       <c r="F28" s="26" t="s">
         <v>124</v>
@@ -11326,12 +11591,12 @@
         <v>20</v>
       </c>
       <c r="M28" s="26" t="s">
-        <v>726</v>
+        <v>746</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="25" t="s">
-        <v>727</v>
+        <v>747</v>
       </c>
       <c r="B29" s="26" t="s">
         <v>47</v>
@@ -11340,13 +11605,13 @@
         <v>144</v>
       </c>
       <c r="D29" s="27" t="s">
-        <v>728</v>
+        <v>748</v>
       </c>
       <c r="E29" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F29" s="26" t="s">
-        <v>729</v>
+        <v>749</v>
       </c>
       <c r="G29" s="26" t="s">
         <v>100</v>
@@ -11367,27 +11632,27 @@
         <v>12</v>
       </c>
       <c r="M29" s="26" t="s">
-        <v>730</v>
+        <v>750</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="25" t="s">
-        <v>731</v>
+        <v>751</v>
       </c>
       <c r="B30" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C30" s="26" t="s">
-        <v>732</v>
+        <v>752</v>
       </c>
       <c r="D30" s="27" t="s">
-        <v>733</v>
+        <v>753</v>
       </c>
       <c r="E30" s="26" t="s">
-        <v>734</v>
+        <v>754</v>
       </c>
       <c r="F30" s="26" t="s">
-        <v>735</v>
+        <v>755</v>
       </c>
       <c r="G30" s="26" t="s">
         <v>100</v>
@@ -11411,19 +11676,19 @@
     </row>
     <row r="31" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="25" t="s">
-        <v>736</v>
+        <v>756</v>
       </c>
       <c r="B31" s="26" t="s">
         <v>47</v>
       </c>
       <c r="C31" s="26" t="s">
-        <v>732</v>
+        <v>752</v>
       </c>
       <c r="D31" s="27" t="s">
-        <v>737</v>
+        <v>757</v>
       </c>
       <c r="E31" s="26" t="s">
-        <v>738</v>
+        <v>758</v>
       </c>
       <c r="F31" s="26" t="s">
         <v>124</v>
@@ -11432,7 +11697,7 @@
         <v>148</v>
       </c>
       <c r="H31" s="26" t="s">
-        <v>739</v>
+        <v>759</v>
       </c>
       <c r="I31" s="26" t="s">
         <v>79</v>
@@ -11450,7 +11715,7 @@
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="25" t="s">
-        <v>740</v>
+        <v>760</v>
       </c>
       <c r="B32" s="26" t="s">
         <v>45</v>
@@ -11459,19 +11724,19 @@
         <v>74</v>
       </c>
       <c r="D32" s="27" t="s">
-        <v>741</v>
+        <v>761</v>
       </c>
       <c r="E32" s="26" t="s">
-        <v>710</v>
+        <v>730</v>
       </c>
       <c r="F32" s="26" t="s">
-        <v>742</v>
+        <v>762</v>
       </c>
       <c r="G32" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H32" s="26" t="s">
-        <v>743</v>
+        <v>763</v>
       </c>
       <c r="I32" s="26" t="s">
         <v>79</v>
@@ -11489,7 +11754,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="25" t="s">
-        <v>744</v>
+        <v>764</v>
       </c>
       <c r="B33" s="26" t="s">
         <v>45</v>
@@ -11498,19 +11763,19 @@
         <v>74</v>
       </c>
       <c r="D33" s="27" t="s">
-        <v>745</v>
+        <v>765</v>
       </c>
       <c r="E33" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F33" s="26" t="s">
-        <v>746</v>
+        <v>766</v>
       </c>
       <c r="G33" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H33" s="26" t="s">
-        <v>747</v>
+        <v>767</v>
       </c>
       <c r="I33" s="26" t="s">
         <v>22</v>
@@ -11528,7 +11793,7 @@
     </row>
     <row r="34" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="25" t="s">
-        <v>748</v>
+        <v>768</v>
       </c>
       <c r="B34" s="26" t="s">
         <v>45</v>
@@ -11537,19 +11802,19 @@
         <v>74</v>
       </c>
       <c r="D34" s="27" t="s">
-        <v>749</v>
+        <v>769</v>
       </c>
       <c r="E34" s="26" t="s">
-        <v>750</v>
+        <v>770</v>
       </c>
       <c r="F34" s="26" t="s">
-        <v>751</v>
+        <v>771</v>
       </c>
       <c r="G34" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H34" s="26" t="s">
-        <v>752</v>
+        <v>772</v>
       </c>
       <c r="I34" s="26" t="s">
         <v>79</v>
@@ -11567,7 +11832,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="25" t="s">
-        <v>753</v>
+        <v>773</v>
       </c>
       <c r="B35" s="26" t="s">
         <v>45</v>
@@ -11576,19 +11841,19 @@
         <v>74</v>
       </c>
       <c r="D35" s="27" t="s">
-        <v>754</v>
+        <v>774</v>
       </c>
       <c r="E35" s="26" t="s">
-        <v>755</v>
+        <v>775</v>
       </c>
       <c r="F35" s="26" t="s">
-        <v>756</v>
+        <v>776</v>
       </c>
       <c r="G35" s="26" t="s">
-        <v>757</v>
+        <v>777</v>
       </c>
       <c r="H35" s="26" t="s">
-        <v>758</v>
+        <v>778</v>
       </c>
       <c r="I35" s="26" t="s">
         <v>86</v>
@@ -11603,33 +11868,33 @@
         <v>12</v>
       </c>
       <c r="M35" s="26" t="s">
-        <v>759</v>
+        <v>779</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="25" t="s">
-        <v>760</v>
+        <v>780</v>
       </c>
       <c r="B36" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C36" s="26" t="s">
-        <v>761</v>
+        <v>781</v>
       </c>
       <c r="D36" s="27" t="s">
-        <v>762</v>
+        <v>782</v>
       </c>
       <c r="E36" s="26" t="s">
-        <v>763</v>
+        <v>783</v>
       </c>
       <c r="F36" s="26" t="s">
-        <v>764</v>
+        <v>784</v>
       </c>
       <c r="G36" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H36" s="26" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="I36" s="26" t="s">
         <v>102</v>
@@ -11647,28 +11912,28 @@
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="25" t="s">
-        <v>765</v>
+        <v>785</v>
       </c>
       <c r="B37" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C37" s="26" t="s">
-        <v>761</v>
+        <v>781</v>
       </c>
       <c r="D37" s="27" t="s">
-        <v>766</v>
+        <v>786</v>
       </c>
       <c r="E37" s="26" t="s">
-        <v>710</v>
+        <v>730</v>
       </c>
       <c r="F37" s="26" t="s">
-        <v>767</v>
+        <v>787</v>
       </c>
       <c r="G37" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H37" s="26" t="s">
-        <v>752</v>
+        <v>772</v>
       </c>
       <c r="I37" s="26" t="s">
         <v>102</v>
@@ -11686,19 +11951,19 @@
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="25" t="s">
-        <v>768</v>
+        <v>788</v>
       </c>
       <c r="B38" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C38" s="26" t="s">
-        <v>769</v>
+        <v>789</v>
       </c>
       <c r="D38" s="27" t="s">
-        <v>770</v>
+        <v>790</v>
       </c>
       <c r="E38" s="26" t="s">
-        <v>763</v>
+        <v>783</v>
       </c>
       <c r="F38" s="26" t="s">
         <v>16</v>
@@ -11707,7 +11972,7 @@
         <v>100</v>
       </c>
       <c r="H38" s="26" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="I38" s="26" t="s">
         <v>102</v>
@@ -11725,28 +11990,28 @@
     </row>
     <row r="39" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="25" t="s">
-        <v>771</v>
+        <v>791</v>
       </c>
       <c r="B39" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C39" s="26" t="s">
-        <v>769</v>
+        <v>789</v>
       </c>
       <c r="D39" s="27" t="s">
-        <v>772</v>
+        <v>792</v>
       </c>
       <c r="E39" s="26" t="s">
-        <v>773</v>
+        <v>793</v>
       </c>
       <c r="F39" s="26" t="s">
-        <v>774</v>
+        <v>794</v>
       </c>
       <c r="G39" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H39" s="26" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="I39" s="26" t="s">
         <v>102</v>
@@ -11764,28 +12029,28 @@
     </row>
     <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="25" t="s">
-        <v>775</v>
+        <v>795</v>
       </c>
       <c r="B40" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C40" s="26" t="s">
-        <v>776</v>
+        <v>796</v>
       </c>
       <c r="D40" s="27" t="s">
-        <v>777</v>
+        <v>797</v>
       </c>
       <c r="E40" s="26" t="s">
-        <v>710</v>
+        <v>730</v>
       </c>
       <c r="F40" s="26" t="s">
-        <v>778</v>
+        <v>798</v>
       </c>
       <c r="G40" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H40" s="26" t="s">
-        <v>752</v>
+        <v>772</v>
       </c>
       <c r="I40" s="26" t="s">
         <v>102</v>
@@ -11803,28 +12068,28 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="25" t="s">
-        <v>779</v>
+        <v>799</v>
       </c>
       <c r="B41" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C41" s="26" t="s">
-        <v>776</v>
+        <v>796</v>
       </c>
       <c r="D41" s="27" t="s">
-        <v>780</v>
+        <v>800</v>
       </c>
       <c r="E41" s="26" t="s">
-        <v>763</v>
+        <v>783</v>
       </c>
       <c r="F41" s="26" t="s">
-        <v>781</v>
+        <v>801</v>
       </c>
       <c r="G41" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H41" s="26" t="s">
-        <v>656</v>
+        <v>676</v>
       </c>
       <c r="I41" s="26" t="s">
         <v>86</v>
@@ -11839,27 +12104,27 @@
         <v>12</v>
       </c>
       <c r="M41" s="26" t="s">
-        <v>782</v>
+        <v>802</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="25" t="s">
-        <v>783</v>
+        <v>803</v>
       </c>
       <c r="B42" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C42" s="26" t="s">
-        <v>784</v>
+        <v>804</v>
       </c>
       <c r="D42" s="27" t="s">
-        <v>785</v>
+        <v>805</v>
       </c>
       <c r="E42" s="26" t="s">
-        <v>786</v>
+        <v>806</v>
       </c>
       <c r="F42" s="26" t="s">
-        <v>787</v>
+        <v>807</v>
       </c>
       <c r="G42" s="26" t="s">
         <v>100</v>
@@ -11880,24 +12145,24 @@
         <v>12</v>
       </c>
       <c r="M42" s="26" t="s">
-        <v>730</v>
+        <v>750</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="25" t="s">
-        <v>788</v>
+        <v>808</v>
       </c>
       <c r="B43" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C43" s="26" t="s">
-        <v>789</v>
+        <v>809</v>
       </c>
       <c r="D43" s="27" t="s">
-        <v>790</v>
+        <v>810</v>
       </c>
       <c r="E43" s="26" t="s">
-        <v>791</v>
+        <v>811</v>
       </c>
       <c r="F43" s="26" t="s">
         <v>124</v>
@@ -11921,27 +12186,27 @@
         <v>20</v>
       </c>
       <c r="M43" s="26" t="s">
-        <v>792</v>
+        <v>812</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="25" t="s">
-        <v>793</v>
+        <v>813</v>
       </c>
       <c r="B44" s="26" t="s">
         <v>45</v>
       </c>
       <c r="C44" s="26" t="s">
-        <v>789</v>
+        <v>809</v>
       </c>
       <c r="D44" s="27" t="s">
-        <v>794</v>
+        <v>814</v>
       </c>
       <c r="E44" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F44" s="26" t="s">
-        <v>795</v>
+        <v>815</v>
       </c>
       <c r="G44" s="26" t="s">
         <v>100</v>
@@ -11962,12 +12227,12 @@
         <v>16</v>
       </c>
       <c r="M44" s="26" t="s">
-        <v>796</v>
+        <v>816</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="25" t="s">
-        <v>797</v>
+        <v>817</v>
       </c>
       <c r="B45" s="26" t="s">
         <v>56</v>
@@ -11976,13 +12241,13 @@
         <v>54</v>
       </c>
       <c r="D45" s="27" t="s">
-        <v>798</v>
+        <v>818</v>
       </c>
       <c r="E45" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F45" s="26" t="s">
-        <v>799</v>
+        <v>819</v>
       </c>
       <c r="G45" s="26" t="s">
         <v>140</v>
@@ -12006,28 +12271,28 @@
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="25" t="s">
-        <v>800</v>
+        <v>820</v>
       </c>
       <c r="B46" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C46" s="26" t="s">
-        <v>479</v>
+        <v>499</v>
       </c>
       <c r="D46" s="27" t="s">
-        <v>801</v>
+        <v>821</v>
       </c>
       <c r="E46" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F46" s="26" t="s">
-        <v>802</v>
+        <v>822</v>
       </c>
       <c r="G46" s="26" t="s">
         <v>148</v>
       </c>
       <c r="H46" s="26" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="I46" s="26" t="s">
         <v>165</v>
@@ -12045,31 +12310,31 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="25" t="s">
-        <v>803</v>
+        <v>823</v>
       </c>
       <c r="B47" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C47" s="26" t="s">
-        <v>804</v>
+        <v>824</v>
       </c>
       <c r="D47" s="27" t="s">
-        <v>805</v>
+        <v>825</v>
       </c>
       <c r="E47" s="26" t="s">
-        <v>806</v>
+        <v>826</v>
       </c>
       <c r="F47" s="26" t="s">
-        <v>807</v>
+        <v>827</v>
       </c>
       <c r="G47" s="26" t="s">
-        <v>626</v>
+        <v>646</v>
       </c>
       <c r="H47" s="26" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="I47" s="26" t="s">
-        <v>348</v>
+        <v>368</v>
       </c>
       <c r="J47" s="26" t="s">
         <v>124</v>
@@ -12081,27 +12346,27 @@
         <v>14</v>
       </c>
       <c r="M47" s="26" t="s">
-        <v>808</v>
+        <v>828</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="25" t="s">
-        <v>809</v>
+        <v>829</v>
       </c>
       <c r="B48" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C48" s="26" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="D48" s="27" t="s">
-        <v>810</v>
+        <v>830</v>
       </c>
       <c r="E48" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F48" s="26" t="s">
-        <v>811</v>
+        <v>831</v>
       </c>
       <c r="G48" s="26" t="s">
         <v>78</v>
@@ -12122,27 +12387,27 @@
         <v>12</v>
       </c>
       <c r="M48" s="26" t="s">
-        <v>812</v>
+        <v>832</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="25" t="s">
-        <v>813</v>
+        <v>833</v>
       </c>
       <c r="B49" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C49" s="26" t="s">
-        <v>814</v>
+        <v>834</v>
       </c>
       <c r="D49" s="27" t="s">
-        <v>815</v>
+        <v>835</v>
       </c>
       <c r="E49" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F49" s="26" t="s">
-        <v>816</v>
+        <v>836</v>
       </c>
       <c r="G49" s="26" t="s">
         <v>140</v>
@@ -12166,22 +12431,22 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="25" t="s">
-        <v>817</v>
+        <v>837</v>
       </c>
       <c r="B50" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C50" s="26" t="s">
-        <v>814</v>
+        <v>834</v>
       </c>
       <c r="D50" s="27" t="s">
-        <v>818</v>
+        <v>838</v>
       </c>
       <c r="E50" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F50" s="26" t="s">
-        <v>819</v>
+        <v>839</v>
       </c>
       <c r="G50" s="26" t="s">
         <v>140</v>
@@ -12205,19 +12470,19 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="25" t="s">
-        <v>820</v>
+        <v>840</v>
       </c>
       <c r="B51" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C51" s="26" t="s">
-        <v>814</v>
+        <v>834</v>
       </c>
       <c r="D51" s="27" t="s">
-        <v>821</v>
+        <v>841</v>
       </c>
       <c r="E51" s="26" t="s">
-        <v>725</v>
+        <v>745</v>
       </c>
       <c r="F51" s="26" t="s">
         <v>124</v>
@@ -12244,19 +12509,19 @@
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="25" t="s">
-        <v>822</v>
+        <v>842</v>
       </c>
       <c r="B52" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C52" s="26" t="s">
-        <v>823</v>
+        <v>843</v>
       </c>
       <c r="D52" s="27" t="s">
-        <v>824</v>
+        <v>844</v>
       </c>
       <c r="E52" s="26" t="s">
-        <v>825</v>
+        <v>845</v>
       </c>
       <c r="F52" s="26" t="s">
         <v>124</v>
@@ -12280,27 +12545,27 @@
         <v>20</v>
       </c>
       <c r="M52" s="26" t="s">
-        <v>826</v>
+        <v>846</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="25" t="s">
-        <v>827</v>
+        <v>847</v>
       </c>
       <c r="B53" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C53" s="26" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="D53" s="27" t="s">
-        <v>828</v>
+        <v>848</v>
       </c>
       <c r="E53" s="26" t="s">
-        <v>829</v>
+        <v>849</v>
       </c>
       <c r="F53" s="26" t="s">
-        <v>830</v>
+        <v>850</v>
       </c>
       <c r="G53" s="26" t="s">
         <v>148</v>
@@ -12324,28 +12589,28 @@
     </row>
     <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="25" t="s">
-        <v>831</v>
+        <v>851</v>
       </c>
       <c r="B54" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C54" s="26" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="D54" s="27" t="s">
-        <v>832</v>
+        <v>852</v>
       </c>
       <c r="E54" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F54" s="26" t="s">
-        <v>833</v>
+        <v>853</v>
       </c>
       <c r="G54" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H54" s="26" t="s">
-        <v>752</v>
+        <v>772</v>
       </c>
       <c r="I54" s="26" t="s">
         <v>165</v>
@@ -12363,28 +12628,28 @@
     </row>
     <row r="55" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="25" t="s">
-        <v>834</v>
+        <v>854</v>
       </c>
       <c r="B55" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C55" s="26" t="s">
-        <v>351</v>
+        <v>371</v>
       </c>
       <c r="D55" s="27" t="s">
-        <v>835</v>
+        <v>855</v>
       </c>
       <c r="E55" s="26" t="s">
-        <v>836</v>
+        <v>856</v>
       </c>
       <c r="F55" s="26" t="s">
-        <v>837</v>
+        <v>857</v>
       </c>
       <c r="G55" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H55" s="26" t="s">
-        <v>752</v>
+        <v>772</v>
       </c>
       <c r="I55" s="26" t="s">
         <v>165</v>
@@ -12399,27 +12664,27 @@
         <v>18</v>
       </c>
       <c r="M55" s="26" t="s">
-        <v>838</v>
+        <v>858</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="25" t="s">
-        <v>839</v>
+        <v>859</v>
       </c>
       <c r="B56" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C56" s="26" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="D56" s="27" t="s">
-        <v>840</v>
+        <v>860</v>
       </c>
       <c r="E56" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F56" s="26" t="s">
-        <v>841</v>
+        <v>861</v>
       </c>
       <c r="G56" s="26" t="s">
         <v>148</v>
@@ -12443,22 +12708,22 @@
     </row>
     <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="25" t="s">
-        <v>842</v>
+        <v>862</v>
       </c>
       <c r="B57" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C57" s="26" t="s">
-        <v>384</v>
+        <v>404</v>
       </c>
       <c r="D57" s="27" t="s">
-        <v>843</v>
+        <v>863</v>
       </c>
       <c r="E57" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F57" s="26" t="s">
-        <v>844</v>
+        <v>864</v>
       </c>
       <c r="G57" s="26" t="s">
         <v>148</v>
@@ -12482,22 +12747,22 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="25" t="s">
-        <v>845</v>
+        <v>865</v>
       </c>
       <c r="B58" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C58" s="26" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="D58" s="27" t="s">
-        <v>846</v>
+        <v>866</v>
       </c>
       <c r="E58" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F58" s="26" t="s">
-        <v>847</v>
+        <v>867</v>
       </c>
       <c r="G58" s="26" t="s">
         <v>78</v>
@@ -12521,22 +12786,22 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="25" t="s">
-        <v>848</v>
+        <v>868</v>
       </c>
       <c r="B59" s="26" t="s">
         <v>56</v>
       </c>
       <c r="C59" s="26" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="D59" s="27" t="s">
-        <v>849</v>
+        <v>869</v>
       </c>
       <c r="E59" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F59" s="26" t="s">
-        <v>850</v>
+        <v>870</v>
       </c>
       <c r="G59" s="26" t="s">
         <v>78</v>
@@ -12560,28 +12825,28 @@
     </row>
     <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="25" t="s">
-        <v>851</v>
+        <v>871</v>
       </c>
       <c r="B60" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C60" s="26" t="s">
-        <v>852</v>
+        <v>872</v>
       </c>
       <c r="D60" s="27" t="s">
-        <v>853</v>
+        <v>873</v>
       </c>
       <c r="E60" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F60" s="26" t="s">
-        <v>854</v>
+        <v>874</v>
       </c>
       <c r="G60" s="26" t="s">
-        <v>855</v>
+        <v>875</v>
       </c>
       <c r="H60" s="26" t="s">
-        <v>856</v>
+        <v>876</v>
       </c>
       <c r="I60" s="26" t="s">
         <v>79</v>
@@ -12596,33 +12861,33 @@
         <v>12</v>
       </c>
       <c r="M60" s="26" t="s">
-        <v>857</v>
+        <v>877</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="25" t="s">
-        <v>858</v>
+        <v>878</v>
       </c>
       <c r="B61" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C61" s="26" t="s">
-        <v>859</v>
+        <v>879</v>
       </c>
       <c r="D61" s="27" t="s">
-        <v>860</v>
+        <v>880</v>
       </c>
       <c r="E61" s="26" t="s">
-        <v>763</v>
+        <v>783</v>
       </c>
       <c r="F61" s="26" t="s">
-        <v>861</v>
+        <v>881</v>
       </c>
       <c r="G61" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H61" s="26" t="s">
-        <v>862</v>
+        <v>882</v>
       </c>
       <c r="I61" s="26" t="s">
         <v>102</v>
@@ -12640,28 +12905,28 @@
     </row>
     <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="25" t="s">
-        <v>863</v>
+        <v>883</v>
       </c>
       <c r="B62" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C62" s="26" t="s">
-        <v>769</v>
+        <v>789</v>
       </c>
       <c r="D62" s="27" t="s">
-        <v>864</v>
+        <v>884</v>
       </c>
       <c r="E62" s="26" t="s">
-        <v>865</v>
+        <v>885</v>
       </c>
       <c r="F62" s="26" t="s">
-        <v>866</v>
+        <v>886</v>
       </c>
       <c r="G62" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H62" s="26" t="s">
-        <v>640</v>
+        <v>660</v>
       </c>
       <c r="I62" s="26" t="s">
         <v>102</v>
@@ -12676,27 +12941,27 @@
         <v>20</v>
       </c>
       <c r="M62" s="26" t="s">
-        <v>867</v>
+        <v>887</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="25" t="s">
-        <v>868</v>
+        <v>888</v>
       </c>
       <c r="B63" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C63" s="26" t="s">
-        <v>869</v>
+        <v>889</v>
       </c>
       <c r="D63" s="27" t="s">
-        <v>870</v>
+        <v>890</v>
       </c>
       <c r="E63" s="26" t="s">
-        <v>763</v>
+        <v>783</v>
       </c>
       <c r="F63" s="26" t="s">
-        <v>871</v>
+        <v>891</v>
       </c>
       <c r="G63" s="26" t="s">
         <v>78</v>
@@ -12720,22 +12985,22 @@
     </row>
     <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="25" t="s">
-        <v>872</v>
+        <v>892</v>
       </c>
       <c r="B64" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C64" s="26" t="s">
-        <v>873</v>
+        <v>893</v>
       </c>
       <c r="D64" s="27" t="s">
-        <v>874</v>
+        <v>894</v>
       </c>
       <c r="E64" s="26" t="s">
-        <v>875</v>
+        <v>895</v>
       </c>
       <c r="F64" s="26" t="s">
-        <v>735</v>
+        <v>755</v>
       </c>
       <c r="G64" s="26" t="s">
         <v>100</v>
@@ -12759,22 +13024,22 @@
     </row>
     <row r="65" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="25" t="s">
-        <v>876</v>
+        <v>896</v>
       </c>
       <c r="B65" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C65" s="26" t="s">
-        <v>877</v>
+        <v>897</v>
       </c>
       <c r="D65" s="27" t="s">
-        <v>878</v>
+        <v>898</v>
       </c>
       <c r="E65" s="26" t="s">
-        <v>879</v>
+        <v>899</v>
       </c>
       <c r="F65" s="26" t="s">
-        <v>880</v>
+        <v>900</v>
       </c>
       <c r="G65" s="26" t="s">
         <v>100</v>
@@ -12798,19 +13063,19 @@
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="25" t="s">
-        <v>881</v>
+        <v>901</v>
       </c>
       <c r="B66" s="26" t="s">
         <v>57</v>
       </c>
       <c r="C66" s="26" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="D66" s="27" t="s">
-        <v>882</v>
+        <v>902</v>
       </c>
       <c r="E66" s="26" t="s">
-        <v>883</v>
+        <v>903</v>
       </c>
       <c r="F66" s="26" t="s">
         <v>124</v>
@@ -12837,7 +13102,7 @@
     </row>
     <row r="67" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="25" t="s">
-        <v>884</v>
+        <v>904</v>
       </c>
       <c r="B67" s="26" t="s">
         <v>58</v>
@@ -12846,13 +13111,13 @@
         <v>127</v>
       </c>
       <c r="D67" s="27" t="s">
-        <v>885</v>
+        <v>905</v>
       </c>
       <c r="E67" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F67" s="26" t="s">
-        <v>886</v>
+        <v>906</v>
       </c>
       <c r="G67" s="26" t="s">
         <v>100</v>
@@ -12873,12 +13138,12 @@
         <v>12</v>
       </c>
       <c r="M67" s="26" t="s">
-        <v>887</v>
+        <v>907</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="25" t="s">
-        <v>888</v>
+        <v>908</v>
       </c>
       <c r="B68" s="26" t="s">
         <v>58</v>
@@ -12887,13 +13152,13 @@
         <v>127</v>
       </c>
       <c r="D68" s="27" t="s">
-        <v>889</v>
+        <v>909</v>
       </c>
       <c r="E68" s="26" t="s">
-        <v>672</v>
+        <v>692</v>
       </c>
       <c r="F68" s="26" t="s">
-        <v>890</v>
+        <v>910</v>
       </c>
       <c r="G68" s="26" t="s">
         <v>100</v>
@@ -12917,28 +13182,28 @@
     </row>
     <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="25" t="s">
-        <v>891</v>
+        <v>911</v>
       </c>
       <c r="B69" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C69" s="26" t="s">
-        <v>479</v>
+        <v>499</v>
       </c>
       <c r="D69" s="27" t="s">
-        <v>892</v>
+        <v>912</v>
       </c>
       <c r="E69" s="26" t="s">
-        <v>893</v>
+        <v>913</v>
       </c>
       <c r="F69" s="26" t="s">
-        <v>894</v>
+        <v>914</v>
       </c>
       <c r="G69" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H69" s="26" t="s">
-        <v>752</v>
+        <v>772</v>
       </c>
       <c r="I69" s="26" t="s">
         <v>165</v>
@@ -12956,28 +13221,28 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="25" t="s">
-        <v>895</v>
+        <v>915</v>
       </c>
       <c r="B70" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C70" s="26" t="s">
-        <v>500</v>
+        <v>520</v>
       </c>
       <c r="D70" s="27" t="s">
-        <v>896</v>
+        <v>916</v>
       </c>
       <c r="E70" s="26" t="s">
-        <v>710</v>
+        <v>730</v>
       </c>
       <c r="F70" s="26" t="s">
-        <v>897</v>
+        <v>917</v>
       </c>
       <c r="G70" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H70" s="26" t="s">
-        <v>898</v>
+        <v>918</v>
       </c>
       <c r="I70" s="26" t="s">
         <v>86</v>
@@ -12995,22 +13260,22 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="25" t="s">
-        <v>899</v>
+        <v>919</v>
       </c>
       <c r="B71" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C71" s="26" t="s">
-        <v>479</v>
+        <v>499</v>
       </c>
       <c r="D71" s="27" t="s">
-        <v>900</v>
+        <v>920</v>
       </c>
       <c r="E71" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F71" s="26" t="s">
-        <v>901</v>
+        <v>921</v>
       </c>
       <c r="G71" s="26" t="s">
         <v>78</v>
@@ -13034,22 +13299,22 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="25" t="s">
-        <v>902</v>
+        <v>922</v>
       </c>
       <c r="B72" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C72" s="26" t="s">
-        <v>479</v>
+        <v>499</v>
       </c>
       <c r="D72" s="27" t="s">
-        <v>903</v>
+        <v>923</v>
       </c>
       <c r="E72" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F72" s="26" t="s">
-        <v>904</v>
+        <v>924</v>
       </c>
       <c r="G72" s="26" t="s">
         <v>78</v>
@@ -13073,22 +13338,22 @@
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="25" t="s">
-        <v>905</v>
+        <v>925</v>
       </c>
       <c r="B73" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C73" s="26" t="s">
-        <v>906</v>
+        <v>926</v>
       </c>
       <c r="D73" s="27" t="s">
-        <v>907</v>
+        <v>927</v>
       </c>
       <c r="E73" s="26" t="s">
-        <v>908</v>
+        <v>928</v>
       </c>
       <c r="F73" s="26" t="s">
-        <v>909</v>
+        <v>929</v>
       </c>
       <c r="G73" s="26" t="s">
         <v>78</v>
@@ -13112,28 +13377,28 @@
     </row>
     <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="25" t="s">
-        <v>910</v>
+        <v>930</v>
       </c>
       <c r="B74" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C74" s="26" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="D74" s="27" t="s">
-        <v>911</v>
+        <v>931</v>
       </c>
       <c r="E74" s="26" t="s">
-        <v>912</v>
+        <v>932</v>
       </c>
       <c r="F74" s="26" t="s">
-        <v>913</v>
+        <v>933</v>
       </c>
       <c r="G74" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H74" s="26" t="s">
-        <v>752</v>
+        <v>772</v>
       </c>
       <c r="I74" s="26" t="s">
         <v>165</v>
@@ -13151,25 +13416,25 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="25" t="s">
-        <v>914</v>
+        <v>934</v>
       </c>
       <c r="B75" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C75" s="26" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="D75" s="27" t="s">
-        <v>915</v>
+        <v>935</v>
       </c>
       <c r="E75" s="26" t="s">
-        <v>916</v>
+        <v>936</v>
       </c>
       <c r="F75" s="26" t="s">
-        <v>837</v>
+        <v>857</v>
       </c>
       <c r="G75" s="26" t="s">
-        <v>917</v>
+        <v>937</v>
       </c>
       <c r="H75" s="26" t="s">
         <v>85</v>
@@ -13190,22 +13455,22 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="25" t="s">
-        <v>918</v>
+        <v>938</v>
       </c>
       <c r="B76" s="26" t="s">
         <v>58</v>
       </c>
       <c r="C76" s="26" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="D76" s="27" t="s">
-        <v>919</v>
+        <v>939</v>
       </c>
       <c r="E76" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F76" s="26" t="s">
-        <v>920</v>
+        <v>940</v>
       </c>
       <c r="G76" s="26" t="s">
         <v>78</v>
@@ -13229,28 +13494,28 @@
     </row>
     <row r="77" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="25" t="s">
-        <v>921</v>
+        <v>941</v>
       </c>
       <c r="B77" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C77" s="26" t="s">
-        <v>922</v>
+        <v>942</v>
       </c>
       <c r="D77" s="27" t="s">
-        <v>923</v>
+        <v>943</v>
       </c>
       <c r="E77" s="26" t="s">
-        <v>710</v>
+        <v>730</v>
       </c>
       <c r="F77" s="26" t="s">
-        <v>924</v>
+        <v>944</v>
       </c>
       <c r="G77" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H77" s="26" t="s">
-        <v>752</v>
+        <v>772</v>
       </c>
       <c r="I77" s="26" t="s">
         <v>102</v>
@@ -13268,22 +13533,22 @@
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="25" t="s">
-        <v>925</v>
+        <v>945</v>
       </c>
       <c r="B78" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C78" s="26" t="s">
-        <v>922</v>
+        <v>942</v>
       </c>
       <c r="D78" s="27" t="s">
-        <v>926</v>
+        <v>946</v>
       </c>
       <c r="E78" s="26" t="s">
-        <v>927</v>
+        <v>947</v>
       </c>
       <c r="F78" s="26" t="s">
-        <v>928</v>
+        <v>948</v>
       </c>
       <c r="G78" s="26" t="s">
         <v>78</v>
@@ -13304,33 +13569,33 @@
         <v>22</v>
       </c>
       <c r="M78" s="26" t="s">
-        <v>929</v>
+        <v>949</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="25" t="s">
-        <v>930</v>
+        <v>950</v>
       </c>
       <c r="B79" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C79" s="26" t="s">
-        <v>922</v>
+        <v>942</v>
       </c>
       <c r="D79" s="27" t="s">
-        <v>931</v>
+        <v>951</v>
       </c>
       <c r="E79" s="26" t="s">
-        <v>932</v>
+        <v>952</v>
       </c>
       <c r="F79" s="26" t="s">
-        <v>933</v>
+        <v>953</v>
       </c>
       <c r="G79" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H79" s="26" t="s">
-        <v>474</v>
+        <v>494</v>
       </c>
       <c r="I79" s="26" t="s">
         <v>102</v>
@@ -13348,22 +13613,22 @@
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="25" t="s">
-        <v>934</v>
+        <v>954</v>
       </c>
       <c r="B80" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C80" s="26" t="s">
-        <v>935</v>
+        <v>955</v>
       </c>
       <c r="D80" s="27" t="s">
-        <v>936</v>
+        <v>956</v>
       </c>
       <c r="E80" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F80" s="26" t="s">
-        <v>937</v>
+        <v>957</v>
       </c>
       <c r="G80" s="26" t="s">
         <v>78</v>
@@ -13387,28 +13652,28 @@
     </row>
     <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="25" t="s">
-        <v>938</v>
+        <v>958</v>
       </c>
       <c r="B81" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C81" s="26" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="D81" s="27" t="s">
-        <v>939</v>
+        <v>959</v>
       </c>
       <c r="E81" s="26" t="s">
-        <v>710</v>
+        <v>730</v>
       </c>
       <c r="F81" s="26" t="s">
-        <v>940</v>
+        <v>960</v>
       </c>
       <c r="G81" s="26" t="s">
         <v>78</v>
       </c>
       <c r="H81" s="26" t="s">
-        <v>752</v>
+        <v>772</v>
       </c>
       <c r="I81" s="26" t="s">
         <v>102</v>
@@ -13426,22 +13691,22 @@
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="25" t="s">
-        <v>941</v>
+        <v>961</v>
       </c>
       <c r="B82" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C82" s="26" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="D82" s="27" t="s">
-        <v>942</v>
+        <v>962</v>
       </c>
       <c r="E82" s="26" t="s">
-        <v>943</v>
+        <v>963</v>
       </c>
       <c r="F82" s="26" t="s">
-        <v>944</v>
+        <v>964</v>
       </c>
       <c r="G82" s="26" t="s">
         <v>100</v>
@@ -13465,19 +13730,19 @@
     </row>
     <row r="83" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="25" t="s">
-        <v>945</v>
+        <v>965</v>
       </c>
       <c r="B83" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C83" s="26" t="s">
-        <v>946</v>
+        <v>966</v>
       </c>
       <c r="D83" s="27" t="s">
-        <v>947</v>
+        <v>967</v>
       </c>
       <c r="E83" s="26" t="s">
-        <v>893</v>
+        <v>913</v>
       </c>
       <c r="F83" s="26" t="s">
         <v>16</v>
@@ -13486,7 +13751,7 @@
         <v>78</v>
       </c>
       <c r="H83" s="26" t="s">
-        <v>752</v>
+        <v>772</v>
       </c>
       <c r="I83" s="26" t="s">
         <v>165</v>
@@ -13504,19 +13769,19 @@
     </row>
     <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="25" t="s">
-        <v>948</v>
+        <v>968</v>
       </c>
       <c r="B84" s="26" t="s">
         <v>59</v>
       </c>
       <c r="C84" s="26" t="s">
-        <v>522</v>
+        <v>542</v>
       </c>
       <c r="D84" s="27" t="s">
-        <v>949</v>
+        <v>969</v>
       </c>
       <c r="E84" s="26" t="s">
-        <v>950</v>
+        <v>970</v>
       </c>
       <c r="F84" s="26" t="s">
         <v>124</v>
@@ -13525,7 +13790,7 @@
         <v>100</v>
       </c>
       <c r="H84" s="26" t="s">
-        <v>951</v>
+        <v>971</v>
       </c>
       <c r="I84" s="26" t="s">
         <v>102</v>
@@ -13540,27 +13805,27 @@
         <v>20</v>
       </c>
       <c r="M84" s="26" t="s">
-        <v>952</v>
+        <v>972</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="25" t="s">
-        <v>953</v>
+        <v>973</v>
       </c>
       <c r="B85" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C85" s="26" t="s">
-        <v>402</v>
+        <v>422</v>
       </c>
       <c r="D85" s="27" t="s">
-        <v>954</v>
+        <v>974</v>
       </c>
       <c r="E85" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F85" s="26" t="s">
-        <v>955</v>
+        <v>975</v>
       </c>
       <c r="G85" s="26" t="s">
         <v>78</v>
@@ -13584,28 +13849,28 @@
     </row>
     <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="25" t="s">
-        <v>956</v>
+        <v>976</v>
       </c>
       <c r="B86" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C86" s="26" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="D86" s="27" t="s">
-        <v>957</v>
+        <v>977</v>
       </c>
       <c r="E86" s="26" t="s">
-        <v>958</v>
+        <v>978</v>
       </c>
       <c r="F86" s="26" t="s">
-        <v>959</v>
+        <v>979</v>
       </c>
       <c r="G86" s="26" t="s">
-        <v>960</v>
+        <v>980</v>
       </c>
       <c r="H86" s="26" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="I86" s="26" t="s">
         <v>86</v>
@@ -13623,28 +13888,28 @@
     </row>
     <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="25" t="s">
-        <v>961</v>
+        <v>981</v>
       </c>
       <c r="B87" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C87" s="26" t="s">
-        <v>420</v>
+        <v>440</v>
       </c>
       <c r="D87" s="27" t="s">
-        <v>962</v>
+        <v>982</v>
       </c>
       <c r="E87" s="26" t="s">
-        <v>963</v>
+        <v>983</v>
       </c>
       <c r="F87" s="26" t="s">
-        <v>426</v>
+        <v>446</v>
       </c>
       <c r="G87" s="26" t="s">
-        <v>964</v>
+        <v>984</v>
       </c>
       <c r="H87" s="26" t="s">
-        <v>392</v>
+        <v>412</v>
       </c>
       <c r="I87" s="26" t="s">
         <v>86</v>
@@ -13659,33 +13924,33 @@
         <v>18</v>
       </c>
       <c r="M87" s="26" t="s">
-        <v>965</v>
+        <v>985</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="25" t="s">
-        <v>966</v>
+        <v>986</v>
       </c>
       <c r="B88" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C88" s="26" t="s">
-        <v>967</v>
+        <v>987</v>
       </c>
       <c r="D88" s="27" t="s">
-        <v>968</v>
+        <v>988</v>
       </c>
       <c r="E88" s="26" t="s">
-        <v>763</v>
+        <v>783</v>
       </c>
       <c r="F88" s="26" t="s">
-        <v>969</v>
+        <v>989</v>
       </c>
       <c r="G88" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H88" s="26" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="I88" s="26" t="s">
         <v>102</v>
@@ -13703,22 +13968,22 @@
     </row>
     <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="25" t="s">
-        <v>970</v>
+        <v>990</v>
       </c>
       <c r="B89" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C89" s="26" t="s">
-        <v>967</v>
+        <v>987</v>
       </c>
       <c r="D89" s="27" t="s">
-        <v>971</v>
+        <v>991</v>
       </c>
       <c r="E89" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F89" s="26" t="s">
-        <v>972</v>
+        <v>992</v>
       </c>
       <c r="G89" s="26" t="s">
         <v>78</v>
@@ -13742,28 +14007,28 @@
     </row>
     <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="25" t="s">
-        <v>973</v>
+        <v>993</v>
       </c>
       <c r="B90" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C90" s="26" t="s">
-        <v>967</v>
+        <v>987</v>
       </c>
       <c r="D90" s="27" t="s">
-        <v>974</v>
+        <v>994</v>
       </c>
       <c r="E90" s="26" t="s">
-        <v>975</v>
+        <v>995</v>
       </c>
       <c r="F90" s="26" t="s">
-        <v>976</v>
+        <v>996</v>
       </c>
       <c r="G90" s="26" t="s">
         <v>100</v>
       </c>
       <c r="H90" s="26" t="s">
-        <v>433</v>
+        <v>453</v>
       </c>
       <c r="I90" s="26" t="s">
         <v>102</v>
@@ -13781,22 +14046,22 @@
     </row>
     <row r="91" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="25" t="s">
-        <v>977</v>
+        <v>997</v>
       </c>
       <c r="B91" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C91" s="26" t="s">
-        <v>967</v>
+        <v>987</v>
       </c>
       <c r="D91" s="27" t="s">
-        <v>978</v>
+        <v>998</v>
       </c>
       <c r="E91" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F91" s="26" t="s">
-        <v>979</v>
+        <v>999</v>
       </c>
       <c r="G91" s="26" t="s">
         <v>78</v>
@@ -13817,33 +14082,33 @@
         <v>22</v>
       </c>
       <c r="M91" s="26" t="s">
-        <v>980</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="25" t="s">
-        <v>981</v>
+        <v>1001</v>
       </c>
       <c r="B92" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C92" s="26" t="s">
-        <v>982</v>
+        <v>1002</v>
       </c>
       <c r="D92" s="27" t="s">
-        <v>983</v>
+        <v>1003</v>
       </c>
       <c r="E92" s="26" t="s">
-        <v>984</v>
+        <v>1004</v>
       </c>
       <c r="F92" s="26" t="s">
-        <v>985</v>
+        <v>1005</v>
       </c>
       <c r="G92" s="26" t="s">
         <v>148</v>
       </c>
       <c r="H92" s="26" t="s">
-        <v>986</v>
+        <v>1006</v>
       </c>
       <c r="I92" s="26" t="s">
         <v>165</v>
@@ -13858,24 +14123,24 @@
         <v>16</v>
       </c>
       <c r="M92" s="26" t="s">
-        <v>987</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="25" t="s">
-        <v>988</v>
+        <v>1008</v>
       </c>
       <c r="B93" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C93" s="26" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="D93" s="27" t="s">
-        <v>989</v>
+        <v>1009</v>
       </c>
       <c r="E93" s="26" t="s">
-        <v>990</v>
+        <v>1010</v>
       </c>
       <c r="F93" s="26" t="s">
         <v>124</v>
@@ -13899,27 +14164,27 @@
         <v>20</v>
       </c>
       <c r="M93" s="26" t="s">
-        <v>991</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="25" t="s">
-        <v>992</v>
+        <v>1012</v>
       </c>
       <c r="B94" s="26" t="s">
         <v>60</v>
       </c>
       <c r="C94" s="26" t="s">
-        <v>455</v>
+        <v>475</v>
       </c>
       <c r="D94" s="27" t="s">
-        <v>993</v>
+        <v>1013</v>
       </c>
       <c r="E94" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F94" s="26" t="s">
-        <v>994</v>
+        <v>1014</v>
       </c>
       <c r="G94" s="26" t="s">
         <v>140</v>
@@ -13940,27 +14205,27 @@
         <v>12</v>
       </c>
       <c r="M94" s="26" t="s">
-        <v>995</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="25" t="s">
-        <v>996</v>
+        <v>1016</v>
       </c>
       <c r="B95" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C95" s="26" t="s">
-        <v>997</v>
+        <v>1017</v>
       </c>
       <c r="D95" s="27" t="s">
-        <v>998</v>
+        <v>1018</v>
       </c>
       <c r="E95" s="26" t="s">
-        <v>999</v>
+        <v>1019</v>
       </c>
       <c r="F95" s="26" t="s">
-        <v>1000</v>
+        <v>1020</v>
       </c>
       <c r="G95" s="26" t="s">
         <v>140</v>
@@ -13984,19 +14249,19 @@
     </row>
     <row r="96" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="25" t="s">
-        <v>1001</v>
+        <v>1021</v>
       </c>
       <c r="B96" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C96" s="26" t="s">
-        <v>997</v>
+        <v>1017</v>
       </c>
       <c r="D96" s="27" t="s">
-        <v>1002</v>
+        <v>1022</v>
       </c>
       <c r="E96" s="26" t="s">
-        <v>990</v>
+        <v>1010</v>
       </c>
       <c r="F96" s="26" t="s">
         <v>124</v>
@@ -14023,22 +14288,22 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="25" t="s">
-        <v>1003</v>
+        <v>1023</v>
       </c>
       <c r="B97" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C97" s="26" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="D97" s="27" t="s">
-        <v>1004</v>
+        <v>1024</v>
       </c>
       <c r="E97" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F97" s="26" t="s">
-        <v>1005</v>
+        <v>1025</v>
       </c>
       <c r="G97" s="26" t="s">
         <v>140</v>
@@ -14059,27 +14324,27 @@
         <v>12</v>
       </c>
       <c r="M97" s="26" t="s">
-        <v>1006</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="25" t="s">
-        <v>1007</v>
+        <v>1027</v>
       </c>
       <c r="B98" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C98" s="26" t="s">
-        <v>935</v>
+        <v>955</v>
       </c>
       <c r="D98" s="27" t="s">
-        <v>1008</v>
+        <v>1028</v>
       </c>
       <c r="E98" s="26" t="s">
-        <v>1009</v>
+        <v>1029</v>
       </c>
       <c r="F98" s="26" t="s">
-        <v>1010</v>
+        <v>1030</v>
       </c>
       <c r="G98" s="26" t="s">
         <v>100</v>
@@ -14103,22 +14368,22 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="25" t="s">
-        <v>1011</v>
+        <v>1031</v>
       </c>
       <c r="B99" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C99" s="26" t="s">
-        <v>364</v>
+        <v>384</v>
       </c>
       <c r="D99" s="27" t="s">
-        <v>1012</v>
+        <v>1032</v>
       </c>
       <c r="E99" s="26" t="s">
         <v>200</v>
       </c>
       <c r="F99" s="26" t="s">
-        <v>1013</v>
+        <v>1033</v>
       </c>
       <c r="G99" s="26" t="s">
         <v>140</v>
@@ -14142,22 +14407,22 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="25" t="s">
-        <v>1014</v>
+        <v>1034</v>
       </c>
       <c r="B100" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C100" s="26" t="s">
-        <v>1015</v>
+        <v>1035</v>
       </c>
       <c r="D100" s="27" t="s">
-        <v>1016</v>
+        <v>1036</v>
       </c>
       <c r="E100" s="26" t="s">
-        <v>471</v>
+        <v>491</v>
       </c>
       <c r="F100" s="26" t="s">
-        <v>1017</v>
+        <v>1037</v>
       </c>
       <c r="G100" s="26" t="s">
         <v>100</v>
@@ -14181,28 +14446,28 @@
     </row>
     <row r="101" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="25" t="s">
-        <v>1018</v>
+        <v>1038</v>
       </c>
       <c r="B101" s="26" t="s">
         <v>61</v>
       </c>
       <c r="C101" s="26" t="s">
-        <v>538</v>
+        <v>558</v>
       </c>
       <c r="D101" s="27" t="s">
-        <v>1019</v>
+        <v>1039</v>
       </c>
       <c r="E101" s="26" t="s">
-        <v>1020</v>
+        <v>1040</v>
       </c>
       <c r="F101" s="26" t="s">
-        <v>1021</v>
+        <v>1041</v>
       </c>
       <c r="G101" s="26" t="s">
         <v>140</v>
       </c>
       <c r="H101" s="26" t="s">
-        <v>542</v>
+        <v>562</v>
       </c>
       <c r="I101" s="26" t="s">
         <v>79</v>
@@ -14217,7 +14482,7 @@
         <v>14</v>
       </c>
       <c r="M101" s="26" t="s">
-        <v>1022</v>
+        <v>1042</v>
       </c>
     </row>
   </sheetData>
@@ -14289,12 +14554,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1023</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1024</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14310,10 +14575,10 @@
         <v>65</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>1025</v>
+        <v>1045</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>1026</v>
+        <v>1046</v>
       </c>
       <c r="D5" s="24" t="s">
         <v>67</v>
@@ -14327,56 +14592,56 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="26" t="s">
-        <v>1027</v>
+        <v>1047</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>1028</v>
+        <v>1048</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>1029</v>
+        <v>1049</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>1030</v>
+        <v>1050</v>
       </c>
       <c r="E6" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>1031</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>1032</v>
+        <v>1052</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>1033</v>
+        <v>1053</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>1034</v>
+        <v>1054</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>1035</v>
+        <v>1055</v>
       </c>
       <c r="E7" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>1036</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>1032</v>
+        <v>1052</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>1037</v>
+        <v>1057</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>1038</v>
+        <v>1058</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>1039</v>
+        <v>1059</v>
       </c>
       <c r="E8" s="26" t="s">
         <v>29</v>
@@ -14385,33 +14650,33 @@
     </row>
     <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="26" t="s">
-        <v>1040</v>
+        <v>1060</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>1041</v>
+        <v>1061</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>1042</v>
+        <v>1062</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>1043</v>
+        <v>1063</v>
       </c>
       <c r="E9" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>1044</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>1045</v>
+        <v>1065</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>1046</v>
+        <v>1066</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>1047</v>
+        <v>1067</v>
       </c>
       <c r="D10" s="26" t="s">
         <v>22</v>
@@ -14420,61 +14685,61 @@
         <v>27</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>1048</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>1049</v>
+        <v>1069</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>1050</v>
+        <v>1070</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>1051</v>
+        <v>1071</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>1052</v>
+        <v>1072</v>
       </c>
       <c r="E11" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>1053</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>1049</v>
+        <v>1069</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>1054</v>
+        <v>1074</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>1055</v>
+        <v>1075</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>1056</v>
+        <v>1076</v>
       </c>
       <c r="E12" s="26" t="s">
         <v>27</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1057</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>1049</v>
+        <v>1069</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>1058</v>
+        <v>1078</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>1059</v>
+        <v>1079</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>1060</v>
+        <v>1080</v>
       </c>
       <c r="E13" s="26" t="s">
         <v>31</v>
@@ -14483,36 +14748,36 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>1049</v>
+        <v>1069</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>1061</v>
+        <v>1081</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>1062</v>
+        <v>1082</v>
       </c>
       <c r="D14" s="26" t="s">
-        <v>1063</v>
+        <v>1083</v>
       </c>
       <c r="E14" s="26" t="s">
         <v>31</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>1064</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>1065</v>
+        <v>1085</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>1066</v>
+        <v>1086</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>1067</v>
+        <v>1087</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>1068</v>
+        <v>1088</v>
       </c>
       <c r="E15" s="26" t="s">
         <v>27</v>
@@ -14521,16 +14786,16 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>1065</v>
+        <v>1085</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>1069</v>
+        <v>1089</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>1070</v>
+        <v>1090</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>1071</v>
+        <v>1091</v>
       </c>
       <c r="E16" s="26" t="s">
         <v>31</v>
@@ -14539,16 +14804,16 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>1065</v>
+        <v>1085</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>1072</v>
+        <v>1092</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>1073</v>
+        <v>1093</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>1074</v>
+        <v>1094</v>
       </c>
       <c r="E17" s="26" t="s">
         <v>33</v>
@@ -14592,12 +14857,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>1075</v>
+        <v>1095</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>1076</v>
+        <v>1096</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -14613,19 +14878,19 @@
         <v>67</v>
       </c>
       <c r="B5" s="24" t="s">
-        <v>1077</v>
+        <v>1097</v>
       </c>
       <c r="C5" s="24" t="s">
-        <v>1078</v>
+        <v>1098</v>
       </c>
       <c r="D5" s="24" t="s">
-        <v>1079</v>
+        <v>1099</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>1080</v>
+        <v>1100</v>
       </c>
       <c r="F5" s="24" t="s">
-        <v>1081</v>
+        <v>1101</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14633,59 +14898,59 @@
         <v>98</v>
       </c>
       <c r="B6" s="26" t="s">
-        <v>1082</v>
+        <v>1102</v>
       </c>
       <c r="C6" s="26" t="s">
-        <v>1083</v>
+        <v>1103</v>
       </c>
       <c r="D6" s="26" t="s">
-        <v>1084</v>
+        <v>1104</v>
       </c>
       <c r="E6" s="28" t="s">
-        <v>1085</v>
+        <v>1105</v>
       </c>
       <c r="F6" s="26" t="s">
-        <v>1086</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="26" t="s">
-        <v>1087</v>
+        <v>1107</v>
       </c>
       <c r="B7" s="26" t="s">
-        <v>1088</v>
+        <v>1108</v>
       </c>
       <c r="C7" s="26" t="s">
-        <v>1083</v>
+        <v>1103</v>
       </c>
       <c r="D7" s="26" t="s">
-        <v>1089</v>
+        <v>1109</v>
       </c>
       <c r="E7" s="28" t="s">
-        <v>1085</v>
+        <v>1105</v>
       </c>
       <c r="F7" s="26" t="s">
-        <v>1086</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="26" t="s">
-        <v>1090</v>
+        <v>1110</v>
       </c>
       <c r="B8" s="26" t="s">
-        <v>1091</v>
+        <v>1111</v>
       </c>
       <c r="C8" s="26" t="s">
-        <v>1083</v>
+        <v>1103</v>
       </c>
       <c r="D8" s="26" t="s">
-        <v>1092</v>
+        <v>1112</v>
       </c>
       <c r="E8" s="28" t="s">
-        <v>1085</v>
+        <v>1105</v>
       </c>
       <c r="F8" s="26" t="s">
-        <v>1086</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14693,339 +14958,339 @@
         <v>76</v>
       </c>
       <c r="B9" s="26" t="s">
-        <v>1093</v>
+        <v>1113</v>
       </c>
       <c r="C9" s="26" t="s">
-        <v>1083</v>
+        <v>1103</v>
       </c>
       <c r="D9" s="26" t="s">
-        <v>1094</v>
+        <v>1114</v>
       </c>
       <c r="E9" s="28" t="s">
-        <v>1085</v>
+        <v>1105</v>
       </c>
       <c r="F9" s="26" t="s">
-        <v>1086</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="26" t="s">
-        <v>1095</v>
+        <v>1115</v>
       </c>
       <c r="B10" s="26" t="s">
-        <v>1096</v>
+        <v>1116</v>
       </c>
       <c r="C10" s="26" t="s">
-        <v>1083</v>
+        <v>1103</v>
       </c>
       <c r="D10" s="26" t="s">
-        <v>1097</v>
+        <v>1117</v>
       </c>
       <c r="E10" s="29" t="s">
-        <v>1098</v>
+        <v>1118</v>
       </c>
       <c r="F10" s="26" t="s">
-        <v>1086</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="26" t="s">
-        <v>431</v>
+        <v>451</v>
       </c>
       <c r="B11" s="26" t="s">
-        <v>1099</v>
+        <v>1119</v>
       </c>
       <c r="C11" s="26" t="s">
-        <v>1083</v>
+        <v>1103</v>
       </c>
       <c r="D11" s="26" t="s">
-        <v>1100</v>
+        <v>1120</v>
       </c>
       <c r="E11" s="28" t="s">
-        <v>1085</v>
+        <v>1105</v>
       </c>
       <c r="F11" s="26" t="s">
-        <v>1086</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="26" t="s">
-        <v>297</v>
+        <v>317</v>
       </c>
       <c r="B12" s="26" t="s">
-        <v>1101</v>
+        <v>1121</v>
       </c>
       <c r="C12" s="26" t="s">
-        <v>1083</v>
+        <v>1103</v>
       </c>
       <c r="D12" s="26" t="s">
-        <v>1102</v>
+        <v>1122</v>
       </c>
       <c r="E12" s="28" t="s">
-        <v>1085</v>
+        <v>1105</v>
       </c>
       <c r="F12" s="26" t="s">
-        <v>1086</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="26" t="s">
-        <v>555</v>
+        <v>575</v>
       </c>
       <c r="B13" s="26" t="s">
-        <v>1088</v>
+        <v>1108</v>
       </c>
       <c r="C13" s="26" t="s">
-        <v>1083</v>
+        <v>1103</v>
       </c>
       <c r="D13" s="26" t="s">
-        <v>1103</v>
+        <v>1123</v>
       </c>
       <c r="E13" s="28" t="s">
-        <v>1085</v>
+        <v>1105</v>
       </c>
       <c r="F13" s="26" t="s">
-        <v>1086</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="26" t="s">
-        <v>1104</v>
+        <v>1124</v>
       </c>
       <c r="B14" s="26" t="s">
-        <v>1099</v>
+        <v>1119</v>
       </c>
       <c r="C14" s="26" t="s">
-        <v>1083</v>
+        <v>1103</v>
       </c>
       <c r="D14" s="26" t="s">
         <v>124</v>
       </c>
       <c r="E14" s="29" t="s">
-        <v>1098</v>
+        <v>1118</v>
       </c>
       <c r="F14" s="26" t="s">
-        <v>1086</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="26" t="s">
-        <v>579</v>
+        <v>599</v>
       </c>
       <c r="B15" s="26" t="s">
-        <v>580</v>
+        <v>600</v>
       </c>
       <c r="C15" s="26" t="s">
-        <v>1083</v>
+        <v>1103</v>
       </c>
       <c r="D15" s="26" t="s">
-        <v>1105</v>
+        <v>1125</v>
       </c>
       <c r="E15" s="29" t="s">
-        <v>1098</v>
+        <v>1118</v>
       </c>
       <c r="F15" s="26" t="s">
-        <v>1086</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="26" t="s">
-        <v>1106</v>
+        <v>1126</v>
       </c>
       <c r="B16" s="26" t="s">
-        <v>1107</v>
+        <v>1127</v>
       </c>
       <c r="C16" s="26" t="s">
-        <v>1108</v>
+        <v>1128</v>
       </c>
       <c r="D16" s="26" t="s">
-        <v>1109</v>
+        <v>1129</v>
       </c>
       <c r="E16" s="30" t="s">
-        <v>1110</v>
+        <v>1130</v>
       </c>
       <c r="F16" s="26" t="s">
-        <v>1111</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="26" t="s">
-        <v>1112</v>
+        <v>1132</v>
       </c>
       <c r="B17" s="26" t="s">
-        <v>1099</v>
+        <v>1119</v>
       </c>
       <c r="C17" s="26" t="s">
-        <v>1113</v>
+        <v>1133</v>
       </c>
       <c r="D17" s="26" t="s">
-        <v>1114</v>
+        <v>1134</v>
       </c>
       <c r="E17" s="29" t="s">
-        <v>1098</v>
+        <v>1118</v>
       </c>
       <c r="F17" s="26" t="s">
-        <v>1086</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="26" t="s">
-        <v>1115</v>
+        <v>1135</v>
       </c>
       <c r="B18" s="26" t="s">
-        <v>1099</v>
+        <v>1119</v>
       </c>
       <c r="C18" s="26" t="s">
-        <v>1113</v>
+        <v>1133</v>
       </c>
       <c r="D18" s="26" t="s">
-        <v>1116</v>
+        <v>1136</v>
       </c>
       <c r="E18" s="29" t="s">
-        <v>1098</v>
+        <v>1118</v>
       </c>
       <c r="F18" s="26" t="s">
-        <v>1086</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="26" t="s">
-        <v>1117</v>
+        <v>1137</v>
       </c>
       <c r="B19" s="26" t="s">
-        <v>1099</v>
+        <v>1119</v>
       </c>
       <c r="C19" s="26" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D19" s="26" t="s">
+        <v>1139</v>
+      </c>
+      <c r="E19" s="29" t="s">
         <v>1118</v>
       </c>
-      <c r="D19" s="26" t="s">
-        <v>1119</v>
-      </c>
-      <c r="E19" s="29" t="s">
-        <v>1098</v>
-      </c>
       <c r="F19" s="26" t="s">
-        <v>1111</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="26" t="s">
-        <v>1120</v>
+        <v>1140</v>
       </c>
       <c r="B20" s="26" t="s">
-        <v>1099</v>
+        <v>1119</v>
       </c>
       <c r="C20" s="26" t="s">
-        <v>1083</v>
+        <v>1103</v>
       </c>
       <c r="D20" s="26" t="s">
-        <v>1121</v>
+        <v>1141</v>
       </c>
       <c r="E20" s="28" t="s">
-        <v>1085</v>
+        <v>1105</v>
       </c>
       <c r="F20" s="26" t="s">
-        <v>1086</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="26" t="s">
-        <v>1122</v>
+        <v>1142</v>
       </c>
       <c r="B21" s="26" t="s">
-        <v>1123</v>
+        <v>1143</v>
       </c>
       <c r="C21" s="26" t="s">
-        <v>1083</v>
+        <v>1103</v>
       </c>
       <c r="D21" s="26" t="s">
-        <v>1124</v>
+        <v>1144</v>
       </c>
       <c r="E21" s="29" t="s">
-        <v>1098</v>
+        <v>1118</v>
       </c>
       <c r="F21" s="26" t="s">
-        <v>1086</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="26" t="s">
-        <v>1125</v>
+        <v>1145</v>
       </c>
       <c r="B22" s="26" t="s">
-        <v>1099</v>
+        <v>1119</v>
       </c>
       <c r="C22" s="26" t="s">
+        <v>1138</v>
+      </c>
+      <c r="D22" s="26" t="s">
+        <v>1146</v>
+      </c>
+      <c r="E22" s="29" t="s">
         <v>1118</v>
       </c>
-      <c r="D22" s="26" t="s">
-        <v>1126</v>
-      </c>
-      <c r="E22" s="29" t="s">
-        <v>1098</v>
-      </c>
       <c r="F22" s="26" t="s">
-        <v>1127</v>
+        <v>1147</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="26" t="s">
-        <v>1128</v>
+        <v>1148</v>
       </c>
       <c r="B23" s="26" t="s">
-        <v>1129</v>
+        <v>1149</v>
       </c>
       <c r="C23" s="26" t="s">
-        <v>1083</v>
+        <v>1103</v>
       </c>
       <c r="D23" s="26" t="s">
-        <v>1130</v>
+        <v>1150</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>1085</v>
+        <v>1105</v>
       </c>
       <c r="F23" s="26" t="s">
-        <v>1086</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="26" t="s">
-        <v>1131</v>
+        <v>1151</v>
       </c>
       <c r="B24" s="26" t="s">
-        <v>1132</v>
+        <v>1152</v>
       </c>
       <c r="C24" s="26" t="s">
-        <v>1083</v>
+        <v>1103</v>
       </c>
       <c r="D24" s="26" t="s">
-        <v>1133</v>
+        <v>1153</v>
       </c>
       <c r="E24" s="30" t="s">
-        <v>1110</v>
+        <v>1130</v>
       </c>
       <c r="F24" s="26" t="s">
-        <v>1086</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="26" t="s">
-        <v>346</v>
+        <v>366</v>
       </c>
       <c r="B25" s="26" t="s">
-        <v>1134</v>
+        <v>1154</v>
       </c>
       <c r="C25" s="26" t="s">
-        <v>1083</v>
+        <v>1103</v>
       </c>
       <c r="D25" s="26" t="s">
-        <v>1135</v>
+        <v>1155</v>
       </c>
       <c r="E25" s="28" t="s">
-        <v>1085</v>
+        <v>1105</v>
       </c>
       <c r="F25" s="26" t="s">
-        <v>1086</v>
+        <v>1106</v>
       </c>
     </row>
   </sheetData>

--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -972,10 +972,10 @@
     <t xml:space="preserve">Focus — IPCA 12 meses à frente</t>
   </si>
   <si>
-    <t xml:space="preserve">ExpectativasMercadoInflacao12Meses</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Usado no juro real ex-ante</t>
+    <t xml:space="preserve">ExpectativasMercadoInflacao12Meses · Indicador='IPCA'</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Série suavizada; usada no juro real ex-ante</t>
   </si>
   <si>
     <t xml:space="preserve">BR-048</t>
@@ -1359,7 +1359,7 @@
     <t xml:space="preserve">Focus — primário e dívida líquida</t>
   </si>
   <si>
-    <t xml:space="preserve">ExpectativasMercadoAnuais</t>
+    <t xml:space="preserve">ExpectativasMercadoAnuais · Indicador='Resultado primário' ; Indicador='Dívida líquida do setor público'</t>
   </si>
   <si>
     <t xml:space="preserve">BR-078</t>
@@ -8590,7 +8590,7 @@
       </c>
       <c r="M87" s="26"/>
     </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="88" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="25" t="s">
         <v>439</v>
       </c>

--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -7424,7 +7424,7 @@
       </c>
       <c r="F90" s="26" t="inlineStr">
         <is>
-          <t>POST api-comexstat.mdic.gov.br/general</t>
+          <t>fluxo=export ; fluxo=import</t>
         </is>
       </c>
       <c r="G90" s="26" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="H90" s="26" t="inlineStr">
         <is>
-          <t>US$ mi</t>
+          <t>US$ FOB</t>
         </is>
       </c>
       <c r="I90" s="26" t="inlineStr">
@@ -7481,7 +7481,7 @@
       </c>
       <c r="D91" s="27" t="inlineStr">
         <is>
-          <t>Exportações por produto e destino (China, EUA, UE)</t>
+          <t>Exportações por destino (China, EUA, UE)</t>
         </is>
       </c>
       <c r="E91" s="26" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="F91" s="26" t="inlineStr">
         <is>
-          <t>POST api-comexstat.mdic.gov.br/general (por NCM/país)</t>
+          <t>fluxo=export/pais=160 ; fluxo=export/pais=249 ; fluxo=export/bloco=22</t>
         </is>
       </c>
       <c r="G91" s="26" t="inlineStr">
@@ -7501,7 +7501,7 @@
       </c>
       <c r="H91" s="26" t="inlineStr">
         <is>
-          <t>US$ mi</t>
+          <t>US$ FOB</t>
         </is>
       </c>
       <c r="I91" s="26" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="M91" s="26" t="inlineStr">
         <is>
-          <t>Exposição a China e tarifas</t>
+          <t>Exposição a China e tarifas; Abertura por produto (SH4/NCM) fica para a v2</t>
         </is>
       </c>
     </row>

--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -7096,12 +7096,12 @@
       </c>
       <c r="E85" s="26" t="inlineStr">
         <is>
-          <t>Tesouro Transparente</t>
+          <t>Tesouro Nacional (API RTN)</t>
         </is>
       </c>
       <c r="F85" s="26" t="inlineStr">
         <is>
-          <t>CKAN resultado-do-tesouro-nacional (XLSX série histórica)</t>
+          <t>rtn=10.01.1 ; rtn=10.02.1 ; rtn=10.01.2 ; rtn=10.03.1 ; rtn=10.04.1 ; rtn=10.08.1 ; rtn=10.09.1</t>
         </is>
       </c>
       <c r="G85" s="26" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="M85" s="26" t="inlineStr">
         <is>
-          <t>Planilha atualizada em 2026-08-27; layout mutável, teste de contrato obrigatório</t>
+          <t>API Séries Temporais do RTN (decisão 0010): receita total, transferências, receita líquida, despesa total, primário, juros e nominal; R$ milhões correntes</t>
         </is>
       </c>
     </row>
@@ -17522,7 +17522,7 @@
       </c>
       <c r="B12" s="26" t="inlineStr">
         <is>
-          <t>CKAN / CSV / xlsx</t>
+          <t>API Séries Temporais (RTN, JSON) · CKAN / xlsx</t>
         </is>
       </c>
       <c r="C12" s="26" t="inlineStr">
@@ -17532,12 +17532,12 @@
       </c>
       <c r="D12" s="26" t="inlineStr">
         <is>
-          <t>RTN e RMD em planilhas com layout mutável</t>
-        </is>
-      </c>
-      <c r="E12" s="28" t="inlineStr">
-        <is>
-          <t>Médio</t>
+          <t>RTN por API JSON paginada (decisão 0010); RMD ainda em planilha</t>
+        </is>
+      </c>
+      <c r="E12" s="29" t="inlineStr">
+        <is>
+          <t>Baixo</t>
         </is>
       </c>
       <c r="F12" s="26" t="inlineStr">

--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -9169,7 +9169,7 @@
       </c>
       <c r="F117" s="26" t="inlineStr">
         <is>
-          <t>B3 IndexCall/GetPortfolioDay IBOV · Yahoo ^BVSP</t>
+          <t>indice=IBOV · yahoo=^BVSP</t>
         </is>
       </c>
       <c r="G117" s="26" t="inlineStr">
@@ -9204,7 +9204,7 @@
       </c>
       <c r="M117" s="26" t="inlineStr">
         <is>
-          <t>FMP grátis não inclui Ibovespa (HTTP 402); SGS 7 descontinuada em 2019</t>
+          <t>Fechamento diário desde 1998 (antes, reescalonamentos ÷10 sem ajuste na fonte: v2). Yahoo cobre a janela recente se a B3 falhar; FMP grátis não inclui Ibovespa (HTTP 402)</t>
         </is>
       </c>
     </row>

--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F69" s="26" t="inlineStr">
         <is>
-          <t>api/servico/sitebcb/copom/comunicados · /atas</t>
+          <t>comunicados ; atas</t>
         </is>
       </c>
       <c r="G69" s="26" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="M69" s="26" t="inlineStr">
         <is>
-          <t>API do site, não documentada; respondeu com a 281ª reunião (set/2026). Teste de contrato obrigatório</t>
+          <t>API do site do BCB, não documentada (copom/comunicados, copom/atas e *_detalhes); texto convertido para texto puro na tabela events; comunicados desde a 46ª reunião (2000)</t>
         </is>
       </c>
     </row>

--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Fontes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Brasil'!$A$5:$M$136</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Brasil'!$A$5:$M$138</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'EUA'!$A$5:$M$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Central'!$A$5:$F$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Fontes'!$A$5:$F$25</definedName>
@@ -993,19 +993,19 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A7,Brasil!$K$6:$K$136,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A7,Brasil!$K$6:$K$138,"MVP")</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A7,Brasil!$K$6:$K$136,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A7,Brasil!$K$6:$K$138,"EUA")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A7,Brasil!$K$6:$K$136,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A7,Brasil!$K$6:$K$138,"v2")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A7,Brasil!$K$6:$K$136,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A7,Brasil!$K$6:$K$138,"v3")</f>
         <v/>
       </c>
       <c r="F7" s="6">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$136,H7)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$138,H7)</f>
         <v/>
       </c>
     </row>
@@ -1029,19 +1029,19 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A8,Brasil!$K$6:$K$136,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A8,Brasil!$K$6:$K$138,"MVP")</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A8,Brasil!$K$6:$K$136,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A8,Brasil!$K$6:$K$138,"EUA")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A8,Brasil!$K$6:$K$136,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A8,Brasil!$K$6:$K$138,"v2")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A8,Brasil!$K$6:$K$136,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A8,Brasil!$K$6:$K$138,"v3")</f>
         <v/>
       </c>
       <c r="F8" s="6">
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$136,H8)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$138,H8)</f>
         <v/>
       </c>
     </row>
@@ -1065,19 +1065,19 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A9,Brasil!$K$6:$K$136,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A9,Brasil!$K$6:$K$138,"MVP")</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A9,Brasil!$K$6:$K$136,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A9,Brasil!$K$6:$K$138,"EUA")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A9,Brasil!$K$6:$K$136,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A9,Brasil!$K$6:$K$138,"v2")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A9,Brasil!$K$6:$K$136,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A9,Brasil!$K$6:$K$138,"v3")</f>
         <v/>
       </c>
       <c r="F9" s="6">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$136,H9)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$138,H9)</f>
         <v/>
       </c>
     </row>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A10,Brasil!$K$6:$K$136,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A10,Brasil!$K$6:$K$138,"MVP")</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A10,Brasil!$K$6:$K$136,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A10,Brasil!$K$6:$K$138,"EUA")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A10,Brasil!$K$6:$K$136,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A10,Brasil!$K$6:$K$138,"v2")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A10,Brasil!$K$6:$K$136,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A10,Brasil!$K$6:$K$138,"v3")</f>
         <v/>
       </c>
       <c r="F10" s="6">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$136,H10)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$138,H10)</f>
         <v/>
       </c>
     </row>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A11,Brasil!$K$6:$K$136,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A11,Brasil!$K$6:$K$138,"MVP")</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A11,Brasil!$K$6:$K$136,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A11,Brasil!$K$6:$K$138,"EUA")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A11,Brasil!$K$6:$K$136,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A11,Brasil!$K$6:$K$138,"v2")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A11,Brasil!$K$6:$K$136,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A11,Brasil!$K$6:$K$138,"v3")</f>
         <v/>
       </c>
       <c r="F11" s="6">
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$136,H11)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$138,H11)</f>
         <v/>
       </c>
     </row>
@@ -1173,19 +1173,19 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A12,Brasil!$K$6:$K$136,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A12,Brasil!$K$6:$K$138,"MVP")</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A12,Brasil!$K$6:$K$136,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A12,Brasil!$K$6:$K$138,"EUA")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A12,Brasil!$K$6:$K$136,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A12,Brasil!$K$6:$K$138,"v2")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A12,Brasil!$K$6:$K$136,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A12,Brasil!$K$6:$K$138,"v3")</f>
         <v/>
       </c>
       <c r="F12" s="6">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$136,H12)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$138,H12)</f>
         <v/>
       </c>
     </row>
@@ -1209,19 +1209,19 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A13,Brasil!$K$6:$K$136,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A13,Brasil!$K$6:$K$138,"MVP")</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A13,Brasil!$K$6:$K$136,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A13,Brasil!$K$6:$K$138,"EUA")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A13,Brasil!$K$6:$K$136,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A13,Brasil!$K$6:$K$138,"v2")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A13,Brasil!$K$6:$K$136,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A13,Brasil!$K$6:$K$138,"v3")</f>
         <v/>
       </c>
       <c r="F13" s="6">
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$136,H13)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$138,H13)</f>
         <v/>
       </c>
     </row>
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A14,Brasil!$K$6:$K$136,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A14,Brasil!$K$6:$K$138,"MVP")</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A14,Brasil!$K$6:$K$136,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A14,Brasil!$K$6:$K$138,"EUA")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A14,Brasil!$K$6:$K$136,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A14,Brasil!$K$6:$K$138,"v2")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A14,Brasil!$K$6:$K$136,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A14,Brasil!$K$6:$K$138,"v3")</f>
         <v/>
       </c>
       <c r="F14" s="6">
@@ -1272,19 +1272,19 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A15,Brasil!$K$6:$K$136,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A15,Brasil!$K$6:$K$138,"MVP")</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A15,Brasil!$K$6:$K$136,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A15,Brasil!$K$6:$K$138,"EUA")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A15,Brasil!$K$6:$K$136,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A15,Brasil!$K$6:$K$138,"v2")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A15,Brasil!$K$6:$K$136,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A15,Brasil!$K$6:$K$138,"v3")</f>
         <v/>
       </c>
       <c r="F15" s="6">
@@ -1299,19 +1299,19 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A16,Brasil!$K$6:$K$136,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A16,Brasil!$K$6:$K$138,"MVP")</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A16,Brasil!$K$6:$K$136,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A16,Brasil!$K$6:$K$138,"EUA")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A16,Brasil!$K$6:$K$136,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A16,Brasil!$K$6:$K$138,"v2")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A16,Brasil!$K$6:$K$136,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A16,Brasil!$K$6:$K$138,"v3")</f>
         <v/>
       </c>
       <c r="F16" s="6">
@@ -1326,19 +1326,19 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A17,Brasil!$K$6:$K$136,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A17,Brasil!$K$6:$K$138,"MVP")</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A17,Brasil!$K$6:$K$136,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A17,Brasil!$K$6:$K$138,"EUA")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A17,Brasil!$K$6:$K$136,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A17,Brasil!$K$6:$K$138,"v2")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$136,$A17,Brasil!$K$6:$K$136,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$138,$A17,Brasil!$K$6:$K$138,"v3")</f>
         <v/>
       </c>
       <c r="F17" s="6">
@@ -1766,7 +1766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M136"/>
+  <dimension ref="A1:M138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10441,9 +10441,143 @@
       </c>
       <c r="M136" s="26" t="inlineStr"/>
     </row>
+    <row r="137">
+      <c r="A137" s="25" t="inlineStr">
+        <is>
+          <t>BR-132</t>
+        </is>
+      </c>
+      <c r="B137" s="26" t="inlineStr">
+        <is>
+          <t>Política Monetária</t>
+        </is>
+      </c>
+      <c r="C137" s="26" t="inlineStr">
+        <is>
+          <t>Expectativas</t>
+        </is>
+      </c>
+      <c r="D137" s="27" t="inlineStr">
+        <is>
+          <t>Focus — Selic fim de ano (ano corrente a +3)</t>
+        </is>
+      </c>
+      <c r="E137" s="26" t="inlineStr">
+        <is>
+          <t>BCB Olinda (Focus)</t>
+        </is>
+      </c>
+      <c r="F137" s="26" t="inlineStr">
+        <is>
+          <t>ExpectativasMercadoAnuais · Indicador='Selic'</t>
+        </is>
+      </c>
+      <c r="G137" s="26" t="inlineStr">
+        <is>
+          <t>Semanal</t>
+        </is>
+      </c>
+      <c r="H137" s="26" t="inlineStr">
+        <is>
+          <t>% a.a.</t>
+        </is>
+      </c>
+      <c r="I137" s="26" t="inlineStr">
+        <is>
+          <t>Taxa</t>
+        </is>
+      </c>
+      <c r="J137" s="26" t="inlineStr">
+        <is>
+          <t>Nível, Δ p.p. (MoM, YoY, 3/6/12m)</t>
+        </is>
+      </c>
+      <c r="K137" s="26" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="L137" s="26" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
+        </is>
+      </c>
+      <c r="M137" s="26" t="inlineStr">
+        <is>
+          <t>Insumo do juro neutro implícito (BR-117); sub-série por ano de referência</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="25" t="inlineStr">
+        <is>
+          <t>BR-133</t>
+        </is>
+      </c>
+      <c r="B138" s="26" t="inlineStr">
+        <is>
+          <t>Mercado de Trabalho</t>
+        </is>
+      </c>
+      <c r="C138" s="26" t="inlineStr">
+        <is>
+          <t>Formal</t>
+        </is>
+      </c>
+      <c r="D138" s="27" t="inlineStr">
+        <is>
+          <t>Saldo mensal do Novo CAGED (variação do estoque)</t>
+        </is>
+      </c>
+      <c r="E138" s="26" t="inlineStr">
+        <is>
+          <t>Argus</t>
+        </is>
+      </c>
+      <c r="F138" s="26" t="inlineStr">
+        <is>
+          <t>Δ(28763)</t>
+        </is>
+      </c>
+      <c r="G138" s="26" t="inlineStr">
+        <is>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="H138" s="26" t="inlineStr">
+        <is>
+          <t>Postos</t>
+        </is>
+      </c>
+      <c r="I138" s="26" t="inlineStr">
+        <is>
+          <t>Derivado</t>
+        </is>
+      </c>
+      <c r="J138" s="26" t="inlineStr">
+        <is>
+          <t>Nível, soma 3/12m, MoM % (SA), YoY %, real/nominal, % PIB</t>
+        </is>
+      </c>
+      <c r="K138" s="26" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="L138" s="26" t="inlineStr">
+        <is>
+          <t>Derivado</t>
+        </is>
+      </c>
+      <c r="M138" s="26" t="inlineStr">
+        <is>
+          <t>Variação mensal do estoque BR-022; só entre meses consecutivos</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:M136"/>
-  <conditionalFormatting sqref="L6:L336">
+  <autoFilter ref="A5:M138"/>
+  <conditionalFormatting sqref="L6:L338">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$L6="Verificado"</formula>
     </cfRule>
@@ -10466,16 +10600,16 @@
       <formula>$L6="Curado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K336">
+  <conditionalFormatting sqref="K6:K338">
     <cfRule type="expression" priority="8" dxfId="7">
       <formula>$K6="MVP"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="K6:K336" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K338" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"MVP,EUA,v2,v3"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L336" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L338" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Verificado,Confirmar,A mapear,Sem API,Pago,Derivado,Curado"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -10499,12 +10499,12 @@
       </c>
       <c r="L137" s="26" t="inlineStr">
         <is>
-          <t>Confirmar</t>
+          <t>Verificado</t>
         </is>
       </c>
       <c r="M137" s="26" t="inlineStr">
         <is>
-          <t>Insumo do juro neutro implícito (BR-117); sub-série por ano de referência</t>
+          <t>Insumo do juro neutro implícito (BR-117); sub-série por ano de referência; validador 2026-10-04: última pesquisa 2026-09-25</t>
         </is>
       </c>
     </row>

--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -3961,7 +3961,7 @@
       </c>
       <c r="F37" s="26" t="inlineStr">
         <is>
-          <t>16121</t>
+          <t>27838</t>
         </is>
       </c>
       <c r="G37" s="26" t="inlineStr">
@@ -3991,12 +3991,12 @@
       </c>
       <c r="L37" s="26" t="inlineStr">
         <is>
-          <t>Verificado</t>
+          <t>Confirmar</t>
         </is>
       </c>
       <c r="M37" s="26" t="inlineStr">
         <is>
-          <t>Há dois códigos com título EX2: 16121 ("ex2") e 27838 ("EX2"); confirmar qual é a série vigente antes da Fase 3</t>
+          <t>NT 57 (dez/2025, Tabela 11): EX1 = 16121 e EX2 = 27838; o título SGS de 16121 ('ex2') é enganoso</t>
         </is>
       </c>
     </row>
@@ -4349,17 +4349,17 @@
       </c>
       <c r="D43" s="27" t="inlineStr">
         <is>
-          <t>Bens industriais subjacentes</t>
+          <t>Bens industriais subjacentes (EX3 Industriais)</t>
         </is>
       </c>
       <c r="E43" s="26" t="inlineStr">
         <is>
-          <t>Argus</t>
+          <t>BCB SGS</t>
         </is>
       </c>
       <c r="F43" s="26" t="inlineStr">
         <is>
-          <t>f(t7060): metodologia BCB (industriais ex-voláteis)</t>
+          <t>29684</t>
         </is>
       </c>
       <c r="G43" s="26" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="I43" s="26" t="inlineStr">
         <is>
-          <t>Derivado</t>
+          <t>Var % mensal</t>
         </is>
       </c>
       <c r="J43" s="26" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L43" s="26" t="inlineStr">
         <is>
-          <t>Derivado</t>
+          <t>Confirmar</t>
         </is>
       </c>
       <c r="M43" s="26" t="inlineStr">
         <is>
-          <t>Par de serviços subjacentes; conferir contra boxes do RPM</t>
+          <t>Série oficial do BCB desde a NT 57 (dez/2025, Tabela 11): antes era cálculo próprio</t>
         </is>
       </c>
     </row>
@@ -4995,17 +4995,17 @@
       </c>
       <c r="D53" s="27" t="inlineStr">
         <is>
-          <t>Serviços subjacentes / supercore BR</t>
+          <t>Serviços subjacentes (EX3 Serviços)</t>
         </is>
       </c>
       <c r="E53" s="26" t="inlineStr">
         <is>
-          <t>Argus</t>
+          <t>BCB SGS</t>
         </is>
       </c>
       <c r="F53" s="26" t="inlineStr">
         <is>
-          <t>f(t7060)</t>
+          <t>29683</t>
         </is>
       </c>
       <c r="G53" s="26" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="I53" s="26" t="inlineStr">
         <is>
-          <t>Derivado</t>
+          <t>Var % mensal</t>
         </is>
       </c>
       <c r="J53" s="26" t="inlineStr">
         <is>
-          <t>Conforme definição da fórmula</t>
+          <t>Mensal, acum. 3/6/9/12m (encadeado), 3m/6m anualizado, YoY via 12m</t>
         </is>
       </c>
       <c r="K53" s="26" t="inlineStr">
@@ -5035,12 +5035,12 @@
       </c>
       <c r="L53" s="26" t="inlineStr">
         <is>
-          <t>Derivado</t>
+          <t>Confirmar</t>
         </is>
       </c>
       <c r="M53" s="26" t="inlineStr">
         <is>
-          <t>Recalcular com a metodologia do BCB e validar contra o RPM</t>
+          <t>Série oficial do BCB desde a NT 57 (dez/2025, Tabela 11): antes era cálculo próprio</t>
         </is>
       </c>
     </row>

--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -3991,12 +3991,12 @@
       </c>
       <c r="L37" s="26" t="inlineStr">
         <is>
-          <t>Confirmar</t>
+          <t>Verificado</t>
         </is>
       </c>
       <c r="M37" s="26" t="inlineStr">
         <is>
-          <t>NT 57 (dez/2025, Tabela 11): EX1 = 16121 e EX2 = 27838; o título SGS de 16121 ('ex2') é enganoso</t>
+          <t>NT 57 (dez/2025, Tabela 11): EX1 = 16121 e EX2 = 27838; o título SGS de 16121 ('ex2') é enganoso; validador 2026-10-04: título oficial confere</t>
         </is>
       </c>
     </row>
@@ -4327,7 +4327,7 @@
       </c>
       <c r="M42" s="26" t="inlineStr">
         <is>
-          <t>Complementa o P55 oficial; documentar metodologia em docs/metodologia</t>
+          <t>Método do P55 do BCB (NT 57) em 50%; o mesmo cálculo em 55% reproduz o SGS 28750 em 80 de 80 meses (2020-2026). Desde 2020 (tabela 7060)</t>
         </is>
       </c>
     </row>
@@ -4389,12 +4389,12 @@
       </c>
       <c r="L43" s="26" t="inlineStr">
         <is>
-          <t>Confirmar</t>
+          <t>Verificado</t>
         </is>
       </c>
       <c r="M43" s="26" t="inlineStr">
         <is>
-          <t>Série oficial do BCB desde a NT 57 (dez/2025, Tabela 11): antes era cálculo próprio</t>
+          <t>Série oficial do BCB desde a NT 57 (dez/2025, Tabela 11): antes era cálculo próprio; validador 2026-10-04: título oficial confere</t>
         </is>
       </c>
     </row>
@@ -5035,12 +5035,12 @@
       </c>
       <c r="L53" s="26" t="inlineStr">
         <is>
-          <t>Confirmar</t>
+          <t>Verificado</t>
         </is>
       </c>
       <c r="M53" s="26" t="inlineStr">
         <is>
-          <t>Série oficial do BCB desde a NT 57 (dez/2025, Tabela 11): antes era cálculo próprio</t>
+          <t>Série oficial do BCB desde a NT 57 (dez/2025, Tabela 11): antes era cálculo próprio; validador 2026-10-04: título oficial confere</t>
         </is>
       </c>
     </row>

--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -2306,7 +2306,7 @@
       </c>
       <c r="F12" s="26" t="inlineStr">
         <is>
-          <t>t8888/v12606,12607/c544=129314,129315,129316</t>
+          <t>t8888/v12606,12607/c544=129314,129315,129316 ; t8888/v11602,11604/c544=129314</t>
         </is>
       </c>
       <c r="G12" s="26" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="M12" s="26" t="inlineStr">
         <is>
-          <t>Tabela nova (base 2022); conferir na Fase 0</t>
+          <t>Tabela nova (base 2022); conferir na Fase 0; v11602 (YoY) e v11604 (12 meses) são as taxas oficiais, usadas para conferir o cálculo do site</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
       </c>
       <c r="F13" s="26" t="inlineStr">
         <is>
-          <t>t8880/v7169,7170/c11046=56733,56734 ; t8881/v7169,7170/c11046=56735,56736</t>
+          <t>t8880/v7169,7170/c11046=56733,56734 ; t8881/v7169,7170/c11046=56735,56736 ; t8880/v11708/c11046=56734</t>
         </is>
       </c>
       <c r="G13" s="26" t="inlineStr">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="M13" s="26" t="inlineStr">
         <is>
-          <t>Volume e receita nominal</t>
+          <t>Volume e receita nominal; t8880 v11708 (MoM SA oficial) confere o cálculo do site</t>
         </is>
       </c>
     </row>

--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Fontes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Brasil'!$A$5:$M$138</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Brasil'!$A$5:$M$139</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'EUA'!$A$5:$M$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Central'!$A$5:$F$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Fontes'!$A$5:$F$25</definedName>
@@ -993,19 +993,19 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A7,Brasil!$K$6:$K$138,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A7,Brasil!$K$6:$K$139,"MVP")</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A7,Brasil!$K$6:$K$138,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A7,Brasil!$K$6:$K$139,"EUA")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A7,Brasil!$K$6:$K$138,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A7,Brasil!$K$6:$K$139,"v2")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A7,Brasil!$K$6:$K$138,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A7,Brasil!$K$6:$K$139,"v3")</f>
         <v/>
       </c>
       <c r="F7" s="6">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$138,H7)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$139,H7)</f>
         <v/>
       </c>
     </row>
@@ -1029,19 +1029,19 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A8,Brasil!$K$6:$K$138,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A8,Brasil!$K$6:$K$139,"MVP")</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A8,Brasil!$K$6:$K$138,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A8,Brasil!$K$6:$K$139,"EUA")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A8,Brasil!$K$6:$K$138,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A8,Brasil!$K$6:$K$139,"v2")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A8,Brasil!$K$6:$K$138,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A8,Brasil!$K$6:$K$139,"v3")</f>
         <v/>
       </c>
       <c r="F8" s="6">
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$138,H8)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$139,H8)</f>
         <v/>
       </c>
     </row>
@@ -1065,19 +1065,19 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A9,Brasil!$K$6:$K$138,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A9,Brasil!$K$6:$K$139,"MVP")</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A9,Brasil!$K$6:$K$138,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A9,Brasil!$K$6:$K$139,"EUA")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A9,Brasil!$K$6:$K$138,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A9,Brasil!$K$6:$K$139,"v2")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A9,Brasil!$K$6:$K$138,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A9,Brasil!$K$6:$K$139,"v3")</f>
         <v/>
       </c>
       <c r="F9" s="6">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$138,H9)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$139,H9)</f>
         <v/>
       </c>
     </row>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A10,Brasil!$K$6:$K$138,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A10,Brasil!$K$6:$K$139,"MVP")</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A10,Brasil!$K$6:$K$138,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A10,Brasil!$K$6:$K$139,"EUA")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A10,Brasil!$K$6:$K$138,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A10,Brasil!$K$6:$K$139,"v2")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A10,Brasil!$K$6:$K$138,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A10,Brasil!$K$6:$K$139,"v3")</f>
         <v/>
       </c>
       <c r="F10" s="6">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$138,H10)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$139,H10)</f>
         <v/>
       </c>
     </row>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A11,Brasil!$K$6:$K$138,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A11,Brasil!$K$6:$K$139,"MVP")</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A11,Brasil!$K$6:$K$138,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A11,Brasil!$K$6:$K$139,"EUA")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A11,Brasil!$K$6:$K$138,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A11,Brasil!$K$6:$K$139,"v2")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A11,Brasil!$K$6:$K$138,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A11,Brasil!$K$6:$K$139,"v3")</f>
         <v/>
       </c>
       <c r="F11" s="6">
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$138,H11)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$139,H11)</f>
         <v/>
       </c>
     </row>
@@ -1173,19 +1173,19 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A12,Brasil!$K$6:$K$138,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A12,Brasil!$K$6:$K$139,"MVP")</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A12,Brasil!$K$6:$K$138,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A12,Brasil!$K$6:$K$139,"EUA")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A12,Brasil!$K$6:$K$138,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A12,Brasil!$K$6:$K$139,"v2")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A12,Brasil!$K$6:$K$138,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A12,Brasil!$K$6:$K$139,"v3")</f>
         <v/>
       </c>
       <c r="F12" s="6">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$138,H12)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$139,H12)</f>
         <v/>
       </c>
     </row>
@@ -1209,19 +1209,19 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A13,Brasil!$K$6:$K$138,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A13,Brasil!$K$6:$K$139,"MVP")</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A13,Brasil!$K$6:$K$138,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A13,Brasil!$K$6:$K$139,"EUA")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A13,Brasil!$K$6:$K$138,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A13,Brasil!$K$6:$K$139,"v2")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A13,Brasil!$K$6:$K$138,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A13,Brasil!$K$6:$K$139,"v3")</f>
         <v/>
       </c>
       <c r="F13" s="6">
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$138,H13)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$139,H13)</f>
         <v/>
       </c>
     </row>
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A14,Brasil!$K$6:$K$138,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A14,Brasil!$K$6:$K$139,"MVP")</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A14,Brasil!$K$6:$K$138,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A14,Brasil!$K$6:$K$139,"EUA")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A14,Brasil!$K$6:$K$138,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A14,Brasil!$K$6:$K$139,"v2")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A14,Brasil!$K$6:$K$138,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A14,Brasil!$K$6:$K$139,"v3")</f>
         <v/>
       </c>
       <c r="F14" s="6">
@@ -1272,19 +1272,19 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A15,Brasil!$K$6:$K$138,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A15,Brasil!$K$6:$K$139,"MVP")</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A15,Brasil!$K$6:$K$138,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A15,Brasil!$K$6:$K$139,"EUA")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A15,Brasil!$K$6:$K$138,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A15,Brasil!$K$6:$K$139,"v2")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A15,Brasil!$K$6:$K$138,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A15,Brasil!$K$6:$K$139,"v3")</f>
         <v/>
       </c>
       <c r="F15" s="6">
@@ -1299,19 +1299,19 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A16,Brasil!$K$6:$K$138,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A16,Brasil!$K$6:$K$139,"MVP")</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A16,Brasil!$K$6:$K$138,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A16,Brasil!$K$6:$K$139,"EUA")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A16,Brasil!$K$6:$K$138,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A16,Brasil!$K$6:$K$139,"v2")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A16,Brasil!$K$6:$K$138,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A16,Brasil!$K$6:$K$139,"v3")</f>
         <v/>
       </c>
       <c r="F16" s="6">
@@ -1326,19 +1326,19 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A17,Brasil!$K$6:$K$138,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A17,Brasil!$K$6:$K$139,"MVP")</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A17,Brasil!$K$6:$K$138,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A17,Brasil!$K$6:$K$139,"EUA")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A17,Brasil!$K$6:$K$138,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A17,Brasil!$K$6:$K$139,"v2")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$138,$A17,Brasil!$K$6:$K$138,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$139,$A17,Brasil!$K$6:$K$139,"v3")</f>
         <v/>
       </c>
       <c r="F17" s="6">
@@ -1766,7 +1766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M138"/>
+  <dimension ref="A1:M139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10575,9 +10575,76 @@
         </is>
       </c>
     </row>
+    <row r="139">
+      <c r="A139" s="25" t="inlineStr">
+        <is>
+          <t>BR-134</t>
+        </is>
+      </c>
+      <c r="B139" s="26" t="inlineStr">
+        <is>
+          <t>Inflação</t>
+        </is>
+      </c>
+      <c r="C139" s="26" t="inlineStr">
+        <is>
+          <t>Cheio</t>
+        </is>
+      </c>
+      <c r="D139" s="27" t="inlineStr">
+        <is>
+          <t>Meta para a inflação (CMN)</t>
+        </is>
+      </c>
+      <c r="E139" s="26" t="inlineStr">
+        <is>
+          <t>BCB SGS</t>
+        </is>
+      </c>
+      <c r="F139" s="26" t="inlineStr">
+        <is>
+          <t>13521</t>
+        </is>
+      </c>
+      <c r="G139" s="26" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="H139" s="26" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="I139" s="26" t="inlineStr">
+        <is>
+          <t>Taxa</t>
+        </is>
+      </c>
+      <c r="J139" s="26" t="inlineStr">
+        <is>
+          <t>Nível</t>
+        </is>
+      </c>
+      <c r="K139" s="26" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="L139" s="26" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="M139" s="26" t="inlineStr">
+        <is>
+          <t>Título oficial 'Meta para a inflação' conferido em 2026-10-15; valor central do ano (o intervalo de tolerância não está no SGS). Insumo da regra de Taylor e do desvio da meta</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:M138"/>
-  <conditionalFormatting sqref="L6:L338">
+  <autoFilter ref="A5:M139"/>
+  <conditionalFormatting sqref="L6:L339">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$L6="Verificado"</formula>
     </cfRule>
@@ -10600,16 +10667,16 @@
       <formula>$L6="Curado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K338">
+  <conditionalFormatting sqref="K6:K339">
     <cfRule type="expression" priority="8" dxfId="7">
       <formula>$K6="MVP"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="K6:K338" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K339" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"MVP,EUA,v2,v3"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L338" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L339" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Verificado,Confirmar,A mapear,Sem API,Pago,Derivado,Curado"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Fontes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Brasil'!$A$5:$M$139</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Brasil'!$A$5:$M$144</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'EUA'!$A$5:$M$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Central'!$A$5:$F$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Fontes'!$A$5:$F$25</definedName>
@@ -993,19 +993,19 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A7,Brasil!$K$6:$K$139,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A7,Brasil!$K$6:$K$144,"MVP")</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A7,Brasil!$K$6:$K$139,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A7,Brasil!$K$6:$K$144,"EUA")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A7,Brasil!$K$6:$K$139,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A7,Brasil!$K$6:$K$144,"v2")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A7,Brasil!$K$6:$K$139,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A7,Brasil!$K$6:$K$144,"v3")</f>
         <v/>
       </c>
       <c r="F7" s="6">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$139,H7)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$144,H7)</f>
         <v/>
       </c>
     </row>
@@ -1029,19 +1029,19 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A8,Brasil!$K$6:$K$139,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A8,Brasil!$K$6:$K$144,"MVP")</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A8,Brasil!$K$6:$K$139,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A8,Brasil!$K$6:$K$144,"EUA")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A8,Brasil!$K$6:$K$139,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A8,Brasil!$K$6:$K$144,"v2")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A8,Brasil!$K$6:$K$139,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A8,Brasil!$K$6:$K$144,"v3")</f>
         <v/>
       </c>
       <c r="F8" s="6">
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$139,H8)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$144,H8)</f>
         <v/>
       </c>
     </row>
@@ -1065,19 +1065,19 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A9,Brasil!$K$6:$K$139,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A9,Brasil!$K$6:$K$144,"MVP")</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A9,Brasil!$K$6:$K$139,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A9,Brasil!$K$6:$K$144,"EUA")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A9,Brasil!$K$6:$K$139,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A9,Brasil!$K$6:$K$144,"v2")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A9,Brasil!$K$6:$K$139,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A9,Brasil!$K$6:$K$144,"v3")</f>
         <v/>
       </c>
       <c r="F9" s="6">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$139,H9)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$144,H9)</f>
         <v/>
       </c>
     </row>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A10,Brasil!$K$6:$K$139,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A10,Brasil!$K$6:$K$144,"MVP")</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A10,Brasil!$K$6:$K$139,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A10,Brasil!$K$6:$K$144,"EUA")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A10,Brasil!$K$6:$K$139,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A10,Brasil!$K$6:$K$144,"v2")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A10,Brasil!$K$6:$K$139,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A10,Brasil!$K$6:$K$144,"v3")</f>
         <v/>
       </c>
       <c r="F10" s="6">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$139,H10)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$144,H10)</f>
         <v/>
       </c>
     </row>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A11,Brasil!$K$6:$K$139,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A11,Brasil!$K$6:$K$144,"MVP")</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A11,Brasil!$K$6:$K$139,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A11,Brasil!$K$6:$K$144,"EUA")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A11,Brasil!$K$6:$K$139,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A11,Brasil!$K$6:$K$144,"v2")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A11,Brasil!$K$6:$K$139,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A11,Brasil!$K$6:$K$144,"v3")</f>
         <v/>
       </c>
       <c r="F11" s="6">
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$139,H11)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$144,H11)</f>
         <v/>
       </c>
     </row>
@@ -1173,19 +1173,19 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A12,Brasil!$K$6:$K$139,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A12,Brasil!$K$6:$K$144,"MVP")</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A12,Brasil!$K$6:$K$139,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A12,Brasil!$K$6:$K$144,"EUA")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A12,Brasil!$K$6:$K$139,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A12,Brasil!$K$6:$K$144,"v2")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A12,Brasil!$K$6:$K$139,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A12,Brasil!$K$6:$K$144,"v3")</f>
         <v/>
       </c>
       <c r="F12" s="6">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$139,H12)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$144,H12)</f>
         <v/>
       </c>
     </row>
@@ -1209,19 +1209,19 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A13,Brasil!$K$6:$K$139,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A13,Brasil!$K$6:$K$144,"MVP")</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A13,Brasil!$K$6:$K$139,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A13,Brasil!$K$6:$K$144,"EUA")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A13,Brasil!$K$6:$K$139,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A13,Brasil!$K$6:$K$144,"v2")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A13,Brasil!$K$6:$K$139,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A13,Brasil!$K$6:$K$144,"v3")</f>
         <v/>
       </c>
       <c r="F13" s="6">
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$139,H13)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$144,H13)</f>
         <v/>
       </c>
     </row>
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A14,Brasil!$K$6:$K$139,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A14,Brasil!$K$6:$K$144,"MVP")</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A14,Brasil!$K$6:$K$139,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A14,Brasil!$K$6:$K$144,"EUA")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A14,Brasil!$K$6:$K$139,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A14,Brasil!$K$6:$K$144,"v2")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A14,Brasil!$K$6:$K$139,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A14,Brasil!$K$6:$K$144,"v3")</f>
         <v/>
       </c>
       <c r="F14" s="6">
@@ -1272,19 +1272,19 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A15,Brasil!$K$6:$K$139,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A15,Brasil!$K$6:$K$144,"MVP")</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A15,Brasil!$K$6:$K$139,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A15,Brasil!$K$6:$K$144,"EUA")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A15,Brasil!$K$6:$K$139,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A15,Brasil!$K$6:$K$144,"v2")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A15,Brasil!$K$6:$K$139,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A15,Brasil!$K$6:$K$144,"v3")</f>
         <v/>
       </c>
       <c r="F15" s="6">
@@ -1299,19 +1299,19 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A16,Brasil!$K$6:$K$139,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A16,Brasil!$K$6:$K$144,"MVP")</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A16,Brasil!$K$6:$K$139,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A16,Brasil!$K$6:$K$144,"EUA")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A16,Brasil!$K$6:$K$139,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A16,Brasil!$K$6:$K$144,"v2")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A16,Brasil!$K$6:$K$139,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A16,Brasil!$K$6:$K$144,"v3")</f>
         <v/>
       </c>
       <c r="F16" s="6">
@@ -1326,19 +1326,19 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A17,Brasil!$K$6:$K$139,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A17,Brasil!$K$6:$K$144,"MVP")</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A17,Brasil!$K$6:$K$139,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A17,Brasil!$K$6:$K$144,"EUA")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A17,Brasil!$K$6:$K$139,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A17,Brasil!$K$6:$K$144,"v2")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$139,$A17,Brasil!$K$6:$K$139,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$144,$A17,Brasil!$K$6:$K$144,"v3")</f>
         <v/>
       </c>
       <c r="F17" s="6">
@@ -1766,7 +1766,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M139"/>
+  <dimension ref="A1:M144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10642,9 +10642,344 @@
         </is>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" s="25" t="inlineStr">
+        <is>
+          <t>BR-135</t>
+        </is>
+      </c>
+      <c r="B140" s="26" t="inlineStr">
+        <is>
+          <t>Inflação</t>
+        </is>
+      </c>
+      <c r="C140" s="26" t="inlineStr">
+        <is>
+          <t>Aberturas</t>
+        </is>
+      </c>
+      <c r="D140" s="27" t="inlineStr">
+        <is>
+          <t>IPCA — Comercializáveis (tradables)</t>
+        </is>
+      </c>
+      <c r="E140" s="26" t="inlineStr">
+        <is>
+          <t>BCB SGS</t>
+        </is>
+      </c>
+      <c r="F140" s="26" t="inlineStr">
+        <is>
+          <t>4447</t>
+        </is>
+      </c>
+      <c r="G140" s="26" t="inlineStr">
+        <is>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="H140" s="26" t="inlineStr">
+        <is>
+          <t>% m/m</t>
+        </is>
+      </c>
+      <c r="I140" s="26" t="inlineStr">
+        <is>
+          <t>Var % mensal</t>
+        </is>
+      </c>
+      <c r="J140" s="26" t="inlineStr">
+        <is>
+          <t>Mensal, acum. 3/6/9/12m (encadeado), 3m/6m anualizado, YoY via 12m</t>
+        </is>
+      </c>
+      <c r="K140" s="26" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="L140" s="26" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="M140" s="26" t="inlineStr">
+        <is>
+          <t>Classificação do BCB; título oficial conferido no SGS em 2026-10-15. Preços formados no mercado internacional; reagem a câmbio e commodities</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="25" t="inlineStr">
+        <is>
+          <t>BR-136</t>
+        </is>
+      </c>
+      <c r="B141" s="26" t="inlineStr">
+        <is>
+          <t>Inflação</t>
+        </is>
+      </c>
+      <c r="C141" s="26" t="inlineStr">
+        <is>
+          <t>Aberturas</t>
+        </is>
+      </c>
+      <c r="D141" s="27" t="inlineStr">
+        <is>
+          <t>IPCA — Não comercializáveis</t>
+        </is>
+      </c>
+      <c r="E141" s="26" t="inlineStr">
+        <is>
+          <t>BCB SGS</t>
+        </is>
+      </c>
+      <c r="F141" s="26" t="inlineStr">
+        <is>
+          <t>4448</t>
+        </is>
+      </c>
+      <c r="G141" s="26" t="inlineStr">
+        <is>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="H141" s="26" t="inlineStr">
+        <is>
+          <t>% m/m</t>
+        </is>
+      </c>
+      <c r="I141" s="26" t="inlineStr">
+        <is>
+          <t>Var % mensal</t>
+        </is>
+      </c>
+      <c r="J141" s="26" t="inlineStr">
+        <is>
+          <t>Mensal, acum. 3/6/9/12m (encadeado), 3m/6m anualizado, YoY via 12m</t>
+        </is>
+      </c>
+      <c r="K141" s="26" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="L141" s="26" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="M141" s="26" t="inlineStr">
+        <is>
+          <t>Classificação do BCB; título oficial conferido no SGS em 2026-10-15. Preços formados no mercado doméstico; reagem a renda e demanda interna</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="25" t="inlineStr">
+        <is>
+          <t>BR-137</t>
+        </is>
+      </c>
+      <c r="B142" s="26" t="inlineStr">
+        <is>
+          <t>Inflação</t>
+        </is>
+      </c>
+      <c r="C142" s="26" t="inlineStr">
+        <is>
+          <t>Aberturas</t>
+        </is>
+      </c>
+      <c r="D142" s="27" t="inlineStr">
+        <is>
+          <t>IPCA — Bens duráveis</t>
+        </is>
+      </c>
+      <c r="E142" s="26" t="inlineStr">
+        <is>
+          <t>BCB SGS</t>
+        </is>
+      </c>
+      <c r="F142" s="26" t="inlineStr">
+        <is>
+          <t>10843</t>
+        </is>
+      </c>
+      <c r="G142" s="26" t="inlineStr">
+        <is>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="H142" s="26" t="inlineStr">
+        <is>
+          <t>% m/m</t>
+        </is>
+      </c>
+      <c r="I142" s="26" t="inlineStr">
+        <is>
+          <t>Var % mensal</t>
+        </is>
+      </c>
+      <c r="J142" s="26" t="inlineStr">
+        <is>
+          <t>Mensal, acum. 3/6/9/12m (encadeado), 3m/6m anualizado, YoY via 12m</t>
+        </is>
+      </c>
+      <c r="K142" s="26" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="L142" s="26" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="M142" s="26" t="inlineStr">
+        <is>
+          <t>Classificação do BCB; título oficial conferido no SGS em 2026-10-15. Compras em geral financiadas (veículos, eletrodomésticos); sensíveis a crédito, juros e câmbio</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="25" t="inlineStr">
+        <is>
+          <t>BR-138</t>
+        </is>
+      </c>
+      <c r="B143" s="26" t="inlineStr">
+        <is>
+          <t>Inflação</t>
+        </is>
+      </c>
+      <c r="C143" s="26" t="inlineStr">
+        <is>
+          <t>Aberturas</t>
+        </is>
+      </c>
+      <c r="D143" s="27" t="inlineStr">
+        <is>
+          <t>IPCA — Bens semiduráveis</t>
+        </is>
+      </c>
+      <c r="E143" s="26" t="inlineStr">
+        <is>
+          <t>BCB SGS</t>
+        </is>
+      </c>
+      <c r="F143" s="26" t="inlineStr">
+        <is>
+          <t>10842</t>
+        </is>
+      </c>
+      <c r="G143" s="26" t="inlineStr">
+        <is>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="H143" s="26" t="inlineStr">
+        <is>
+          <t>% m/m</t>
+        </is>
+      </c>
+      <c r="I143" s="26" t="inlineStr">
+        <is>
+          <t>Var % mensal</t>
+        </is>
+      </c>
+      <c r="J143" s="26" t="inlineStr">
+        <is>
+          <t>Mensal, acum. 3/6/9/12m (encadeado), 3m/6m anualizado, YoY via 12m</t>
+        </is>
+      </c>
+      <c r="K143" s="26" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="L143" s="26" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="M143" s="26" t="inlineStr">
+        <is>
+          <t>Classificação do BCB; título oficial conferido no SGS em 2026-10-15. Vestuário, calçados e similares</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="25" t="inlineStr">
+        <is>
+          <t>BR-139</t>
+        </is>
+      </c>
+      <c r="B144" s="26" t="inlineStr">
+        <is>
+          <t>Inflação</t>
+        </is>
+      </c>
+      <c r="C144" s="26" t="inlineStr">
+        <is>
+          <t>Aberturas</t>
+        </is>
+      </c>
+      <c r="D144" s="27" t="inlineStr">
+        <is>
+          <t>IPCA — Bens não duráveis</t>
+        </is>
+      </c>
+      <c r="E144" s="26" t="inlineStr">
+        <is>
+          <t>BCB SGS</t>
+        </is>
+      </c>
+      <c r="F144" s="26" t="inlineStr">
+        <is>
+          <t>10841</t>
+        </is>
+      </c>
+      <c r="G144" s="26" t="inlineStr">
+        <is>
+          <t>Mensal</t>
+        </is>
+      </c>
+      <c r="H144" s="26" t="inlineStr">
+        <is>
+          <t>% m/m</t>
+        </is>
+      </c>
+      <c r="I144" s="26" t="inlineStr">
+        <is>
+          <t>Var % mensal</t>
+        </is>
+      </c>
+      <c r="J144" s="26" t="inlineStr">
+        <is>
+          <t>Mensal, acum. 3/6/9/12m (encadeado), 3m/6m anualizado, YoY via 12m</t>
+        </is>
+      </c>
+      <c r="K144" s="26" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="L144" s="26" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="M144" s="26" t="inlineStr">
+        <is>
+          <t>Classificação do BCB; título oficial conferido no SGS em 2026-10-15. Alimentos, higiene, combustíveis e similares</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:M139"/>
-  <conditionalFormatting sqref="L6:L339">
+  <autoFilter ref="A5:M144"/>
+  <conditionalFormatting sqref="L6:L344">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$L6="Verificado"</formula>
     </cfRule>
@@ -10667,16 +11002,16 @@
       <formula>$L6="Curado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K339">
+  <conditionalFormatting sqref="K6:K344">
     <cfRule type="expression" priority="8" dxfId="7">
       <formula>$K6="MVP"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="K6:K339" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K344" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"MVP,EUA,v2,v3"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L339" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L344" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Verificado,Confirmar,A mapear,Sem API,Pago,Derivado,Curado"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Fontes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Brasil'!$A$5:$M$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Brasil'!$A$5:$M$145</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'EUA'!$A$5:$M$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Central'!$A$5:$F$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Fontes'!$A$5:$F$25</definedName>
@@ -898,7 +898,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I31"/>
+  <dimension ref="A1:I32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -993,19 +993,19 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A7,Brasil!$K$6:$K$144,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A7,Brasil!$K$6:$K$145,"MVP")</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A7,Brasil!$K$6:$K$144,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A7,Brasil!$K$6:$K$145,"EUA")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A7,Brasil!$K$6:$K$144,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A7,Brasil!$K$6:$K$145,"v2")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A7,Brasil!$K$6:$K$144,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A7,Brasil!$K$6:$K$145,"v3")</f>
         <v/>
       </c>
       <c r="F7" s="6">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$144,H7)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$145,H7)</f>
         <v/>
       </c>
     </row>
@@ -1029,19 +1029,19 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A8,Brasil!$K$6:$K$144,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A8,Brasil!$K$6:$K$145,"MVP")</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A8,Brasil!$K$6:$K$144,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A8,Brasil!$K$6:$K$145,"EUA")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A8,Brasil!$K$6:$K$144,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A8,Brasil!$K$6:$K$145,"v2")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A8,Brasil!$K$6:$K$144,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A8,Brasil!$K$6:$K$145,"v3")</f>
         <v/>
       </c>
       <c r="F8" s="6">
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$144,H8)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$145,H8)</f>
         <v/>
       </c>
     </row>
@@ -1065,19 +1065,19 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A9,Brasil!$K$6:$K$144,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A9,Brasil!$K$6:$K$145,"MVP")</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A9,Brasil!$K$6:$K$144,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A9,Brasil!$K$6:$K$145,"EUA")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A9,Brasil!$K$6:$K$144,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A9,Brasil!$K$6:$K$145,"v2")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A9,Brasil!$K$6:$K$144,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A9,Brasil!$K$6:$K$145,"v3")</f>
         <v/>
       </c>
       <c r="F9" s="6">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$144,H9)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$145,H9)</f>
         <v/>
       </c>
     </row>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A10,Brasil!$K$6:$K$144,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A10,Brasil!$K$6:$K$145,"MVP")</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A10,Brasil!$K$6:$K$144,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A10,Brasil!$K$6:$K$145,"EUA")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A10,Brasil!$K$6:$K$144,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A10,Brasil!$K$6:$K$145,"v2")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A10,Brasil!$K$6:$K$144,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A10,Brasil!$K$6:$K$145,"v3")</f>
         <v/>
       </c>
       <c r="F10" s="6">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$144,H10)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$145,H10)</f>
         <v/>
       </c>
     </row>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A11,Brasil!$K$6:$K$144,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A11,Brasil!$K$6:$K$145,"MVP")</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A11,Brasil!$K$6:$K$144,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A11,Brasil!$K$6:$K$145,"EUA")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A11,Brasil!$K$6:$K$144,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A11,Brasil!$K$6:$K$145,"v2")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A11,Brasil!$K$6:$K$144,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A11,Brasil!$K$6:$K$145,"v3")</f>
         <v/>
       </c>
       <c r="F11" s="6">
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$144,H11)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$145,H11)</f>
         <v/>
       </c>
     </row>
@@ -1173,19 +1173,19 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A12,Brasil!$K$6:$K$144,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A12,Brasil!$K$6:$K$145,"MVP")</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A12,Brasil!$K$6:$K$144,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A12,Brasil!$K$6:$K$145,"EUA")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A12,Brasil!$K$6:$K$144,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A12,Brasil!$K$6:$K$145,"v2")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A12,Brasil!$K$6:$K$144,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A12,Brasil!$K$6:$K$145,"v3")</f>
         <v/>
       </c>
       <c r="F12" s="6">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$144,H12)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$145,H12)</f>
         <v/>
       </c>
     </row>
@@ -1209,19 +1209,19 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A13,Brasil!$K$6:$K$144,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A13,Brasil!$K$6:$K$145,"MVP")</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A13,Brasil!$K$6:$K$144,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A13,Brasil!$K$6:$K$145,"EUA")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A13,Brasil!$K$6:$K$144,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A13,Brasil!$K$6:$K$145,"v2")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A13,Brasil!$K$6:$K$144,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A13,Brasil!$K$6:$K$145,"v3")</f>
         <v/>
       </c>
       <c r="F13" s="6">
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$144,H13)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$145,H13)</f>
         <v/>
       </c>
     </row>
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A14,Brasil!$K$6:$K$144,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A14,Brasil!$K$6:$K$145,"MVP")</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A14,Brasil!$K$6:$K$144,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A14,Brasil!$K$6:$K$145,"EUA")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A14,Brasil!$K$6:$K$144,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A14,Brasil!$K$6:$K$145,"v2")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A14,Brasil!$K$6:$K$144,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A14,Brasil!$K$6:$K$145,"v3")</f>
         <v/>
       </c>
       <c r="F14" s="6">
@@ -1272,19 +1272,19 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A15,Brasil!$K$6:$K$144,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A15,Brasil!$K$6:$K$145,"MVP")</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A15,Brasil!$K$6:$K$144,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A15,Brasil!$K$6:$K$145,"EUA")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A15,Brasil!$K$6:$K$144,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A15,Brasil!$K$6:$K$145,"v2")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A15,Brasil!$K$6:$K$144,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A15,Brasil!$K$6:$K$145,"v3")</f>
         <v/>
       </c>
       <c r="F15" s="6">
@@ -1299,19 +1299,19 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A16,Brasil!$K$6:$K$144,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A16,Brasil!$K$6:$K$145,"MVP")</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A16,Brasil!$K$6:$K$144,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A16,Brasil!$K$6:$K$145,"EUA")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A16,Brasil!$K$6:$K$144,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A16,Brasil!$K$6:$K$145,"v2")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A16,Brasil!$K$6:$K$144,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A16,Brasil!$K$6:$K$145,"v3")</f>
         <v/>
       </c>
       <c r="F16" s="6">
@@ -1326,19 +1326,19 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A17,Brasil!$K$6:$K$144,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A17,Brasil!$K$6:$K$145,"MVP")</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A17,Brasil!$K$6:$K$144,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A17,Brasil!$K$6:$K$145,"EUA")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A17,Brasil!$K$6:$K$144,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A17,Brasil!$K$6:$K$145,"v2")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$144,$A17,Brasil!$K$6:$K$144,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A17,Brasil!$K$6:$K$145,"v3")</f>
         <v/>
       </c>
       <c r="F17" s="6">
@@ -1347,121 +1347,112 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="B18" s="16">
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A18,Brasil!$K$6:$K$145,"MVP")</f>
+        <v/>
+      </c>
+      <c r="C18" s="16">
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A18,Brasil!$K$6:$K$145,"EUA")</f>
+        <v/>
+      </c>
+      <c r="D18" s="16">
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A18,Brasil!$K$6:$K$145,"v2")</f>
+        <v/>
+      </c>
+      <c r="E18" s="16">
+        <f>COUNTIFS(Brasil!$B$6:$B$145,$A18,Brasil!$K$6:$K$145,"v3")</f>
+        <v/>
+      </c>
+      <c r="F18" s="6">
+        <f>SUM(B18:E18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B18" s="6">
-        <f>SUM(B7:B17)</f>
+      <c r="B19" s="6">
+        <f>SUM(B7:B18)</f>
         <v/>
       </c>
-      <c r="C18" s="6">
-        <f>SUM(C7:C17)</f>
+      <c r="C19" s="6">
+        <f>SUM(C7:C18)</f>
         <v/>
       </c>
-      <c r="D18" s="6">
-        <f>SUM(D7:D17)</f>
+      <c r="D19" s="6">
+        <f>SUM(D7:D18)</f>
         <v/>
       </c>
-      <c r="E18" s="6">
-        <f>SUM(E7:E17)</f>
+      <c r="E19" s="6">
+        <f>SUM(E7:E18)</f>
         <v/>
       </c>
-      <c r="F18" s="6">
-        <f>SUM(F7:F17)</f>
+      <c r="F19" s="6">
+        <f>SUM(F7:F18)</f>
         <v/>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>EUA</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="15" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
         <is>
           <t>Aba</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
+      <c r="B22" s="15" t="inlineStr">
         <is>
           <t>MVP</t>
         </is>
       </c>
-      <c r="C21" s="15" t="inlineStr">
+      <c r="C22" s="15" t="inlineStr">
         <is>
           <t>EUA</t>
         </is>
       </c>
-      <c r="D21" s="15" t="inlineStr">
+      <c r="D22" s="15" t="inlineStr">
         <is>
           <t>v2</t>
         </is>
       </c>
-      <c r="E21" s="15" t="inlineStr">
+      <c r="E22" s="15" t="inlineStr">
         <is>
           <t>v3</t>
         </is>
       </c>
-      <c r="F21" s="15" t="inlineStr">
+      <c r="F22" s="15" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="H21" s="15" t="inlineStr">
+      <c r="H22" s="15" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="I21" s="15" t="inlineStr">
+      <c r="I22" s="15" t="inlineStr">
         <is>
           <t>Qtd</t>
         </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="16" t="inlineStr">
-        <is>
-          <t>Mercado de Trabalho</t>
-        </is>
-      </c>
-      <c r="B22" s="16">
-        <f>COUNTIFS(EUA!$B$6:$B$101,$A22,EUA!$K$6:$K$101,"MVP")</f>
-        <v/>
-      </c>
-      <c r="C22" s="16">
-        <f>COUNTIFS(EUA!$B$6:$B$101,$A22,EUA!$K$6:$K$101,"EUA")</f>
-        <v/>
-      </c>
-      <c r="D22" s="16">
-        <f>COUNTIFS(EUA!$B$6:$B$101,$A22,EUA!$K$6:$K$101,"v2")</f>
-        <v/>
-      </c>
-      <c r="E22" s="16">
-        <f>COUNTIFS(EUA!$B$6:$B$101,$A22,EUA!$K$6:$K$101,"v3")</f>
-        <v/>
-      </c>
-      <c r="F22" s="6">
-        <f>SUM(B22:E22)</f>
-        <v/>
-      </c>
-      <c r="H22" s="17" t="inlineStr">
-        <is>
-          <t>Verificado</t>
-        </is>
-      </c>
-      <c r="I22" s="16">
-        <f>COUNTIF(EUA!$L$6:$L$101,H22)</f>
-        <v/>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
         <is>
-          <t>Inflação</t>
+          <t>Mercado de Trabalho</t>
         </is>
       </c>
       <c r="B23" s="16">
@@ -1484,9 +1475,9 @@
         <f>SUM(B23:E23)</f>
         <v/>
       </c>
-      <c r="H23" s="18" t="inlineStr">
-        <is>
-          <t>Confirmar</t>
+      <c r="H23" s="17" t="inlineStr">
+        <is>
+          <t>Verificado</t>
         </is>
       </c>
       <c r="I23" s="16">
@@ -1497,7 +1488,7 @@
     <row r="24">
       <c r="A24" s="16" t="inlineStr">
         <is>
-          <t>Atividade</t>
+          <t>Inflação</t>
         </is>
       </c>
       <c r="B24" s="16">
@@ -1520,9 +1511,9 @@
         <f>SUM(B24:E24)</f>
         <v/>
       </c>
-      <c r="H24" s="19" t="inlineStr">
-        <is>
-          <t>A mapear</t>
+      <c r="H24" s="18" t="inlineStr">
+        <is>
+          <t>Confirmar</t>
         </is>
       </c>
       <c r="I24" s="16">
@@ -1533,7 +1524,7 @@
     <row r="25">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>Fed &amp; Juros</t>
+          <t>Atividade</t>
         </is>
       </c>
       <c r="B25" s="16">
@@ -1556,9 +1547,9 @@
         <f>SUM(B25:E25)</f>
         <v/>
       </c>
-      <c r="H25" s="20" t="inlineStr">
-        <is>
-          <t>Sem API</t>
+      <c r="H25" s="19" t="inlineStr">
+        <is>
+          <t>A mapear</t>
         </is>
       </c>
       <c r="I25" s="16">
@@ -1569,7 +1560,7 @@
     <row r="26">
       <c r="A26" s="16" t="inlineStr">
         <is>
-          <t>Imobiliário</t>
+          <t>Fed &amp; Juros</t>
         </is>
       </c>
       <c r="B26" s="16">
@@ -1592,9 +1583,9 @@
         <f>SUM(B26:E26)</f>
         <v/>
       </c>
-      <c r="H26" s="21" t="inlineStr">
-        <is>
-          <t>Pago</t>
+      <c r="H26" s="20" t="inlineStr">
+        <is>
+          <t>Sem API</t>
         </is>
       </c>
       <c r="I26" s="16">
@@ -1605,7 +1596,7 @@
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>Consumidor</t>
+          <t>Imobiliário</t>
         </is>
       </c>
       <c r="B27" s="16">
@@ -1628,9 +1619,9 @@
         <f>SUM(B27:E27)</f>
         <v/>
       </c>
-      <c r="H27" s="22" t="inlineStr">
-        <is>
-          <t>Derivado</t>
+      <c r="H27" s="21" t="inlineStr">
+        <is>
+          <t>Pago</t>
         </is>
       </c>
       <c r="I27" s="16">
@@ -1641,7 +1632,7 @@
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>Corporativo</t>
+          <t>Consumidor</t>
         </is>
       </c>
       <c r="B28" s="16">
@@ -1664,9 +1655,9 @@
         <f>SUM(B28:E28)</f>
         <v/>
       </c>
-      <c r="H28" s="23" t="inlineStr">
-        <is>
-          <t>Curado</t>
+      <c r="H28" s="22" t="inlineStr">
+        <is>
+          <t>Derivado</t>
         </is>
       </c>
       <c r="I28" s="16">
@@ -1677,7 +1668,7 @@
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>Setor Externo &amp; Fiscal</t>
+          <t>Corporativo</t>
         </is>
       </c>
       <c r="B29" s="16">
@@ -1700,11 +1691,20 @@
         <f>SUM(B29:E29)</f>
         <v/>
       </c>
+      <c r="H29" s="23" t="inlineStr">
+        <is>
+          <t>Curado</t>
+        </is>
+      </c>
+      <c r="I29" s="16">
+        <f>COUNTIF(EUA!$L$6:$L$101,H29)</f>
+        <v/>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>Risco &amp; Mercado</t>
+          <t>Setor Externo &amp; Fiscal</t>
         </is>
       </c>
       <c r="B30" s="16">
@@ -1729,29 +1729,56 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="6" t="inlineStr">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Risco &amp; Mercado</t>
+        </is>
+      </c>
+      <c r="B31" s="16">
+        <f>COUNTIFS(EUA!$B$6:$B$101,$A31,EUA!$K$6:$K$101,"MVP")</f>
+        <v/>
+      </c>
+      <c r="C31" s="16">
+        <f>COUNTIFS(EUA!$B$6:$B$101,$A31,EUA!$K$6:$K$101,"EUA")</f>
+        <v/>
+      </c>
+      <c r="D31" s="16">
+        <f>COUNTIFS(EUA!$B$6:$B$101,$A31,EUA!$K$6:$K$101,"v2")</f>
+        <v/>
+      </c>
+      <c r="E31" s="16">
+        <f>COUNTIFS(EUA!$B$6:$B$101,$A31,EUA!$K$6:$K$101,"v3")</f>
+        <v/>
+      </c>
+      <c r="F31" s="6">
+        <f>SUM(B31:E31)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B31" s="6">
-        <f>SUM(B22:B30)</f>
+      <c r="B32" s="6">
+        <f>SUM(B23:B31)</f>
         <v/>
       </c>
-      <c r="C31" s="6">
-        <f>SUM(C22:C30)</f>
+      <c r="C32" s="6">
+        <f>SUM(C23:C31)</f>
         <v/>
       </c>
-      <c r="D31" s="6">
-        <f>SUM(D22:D30)</f>
+      <c r="D32" s="6">
+        <f>SUM(D23:D31)</f>
         <v/>
       </c>
-      <c r="E31" s="6">
-        <f>SUM(E22:E30)</f>
+      <c r="E32" s="6">
+        <f>SUM(E23:E31)</f>
         <v/>
       </c>
-      <c r="F31" s="6">
-        <f>SUM(F22:F30)</f>
+      <c r="F32" s="6">
+        <f>SUM(F23:F31)</f>
         <v/>
       </c>
     </row>
@@ -1766,7 +1793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M144"/>
+  <dimension ref="A1:M145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -10977,9 +11004,76 @@
         </is>
       </c>
     </row>
+    <row r="145">
+      <c r="A145" s="25" t="inlineStr">
+        <is>
+          <t>BR-140</t>
+        </is>
+      </c>
+      <c r="B145" s="26" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="C145" s="26" t="inlineStr">
+        <is>
+          <t>Notícias</t>
+        </is>
+      </c>
+      <c r="D145" s="27" t="inlineStr">
+        <is>
+          <t>Notícias oficiais: BCB (notas e notícias), IBGE e Fed</t>
+        </is>
+      </c>
+      <c r="E145" s="26" t="inlineStr">
+        <is>
+          <t>RSS oficial</t>
+        </is>
+      </c>
+      <c r="F145" s="26" t="inlineStr">
+        <is>
+          <t>bcb_notas ; bcb_noticias ; ibge ; fed</t>
+        </is>
+      </c>
+      <c r="G145" s="26" t="inlineStr">
+        <is>
+          <t>Contínua</t>
+        </is>
+      </c>
+      <c r="H145" s="26" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="I145" s="26" t="inlineStr">
+        <is>
+          <t>Texto</t>
+        </is>
+      </c>
+      <c r="J145" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K145" s="26" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="L145" s="26" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="M145" s="26" t="inlineStr">
+        <is>
+          <t>Feeds RSS/Atom oficiais (BCB sitefeeds, Agência IBGE, Federal Reserve press_monetary); título e resumo em texto puro na tabela events (tipo noticia); fixtures reais gravadas em 2026-10-19</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:M144"/>
-  <conditionalFormatting sqref="L6:L344">
+  <autoFilter ref="A5:M145"/>
+  <conditionalFormatting sqref="L6:L345">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$L6="Verificado"</formula>
     </cfRule>
@@ -11002,16 +11096,16 @@
       <formula>$L6="Curado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K344">
+  <conditionalFormatting sqref="K6:K345">
     <cfRule type="expression" priority="8" dxfId="7">
       <formula>$K6="MVP"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="K6:K344" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K345" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"MVP,EUA,v2,v3"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L344" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L345" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Verificado,Confirmar,A mapear,Sem API,Pago,Derivado,Curado"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
+++ b/docs/catalogo/Argus_Catalogo_de_Dados.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Fontes" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Brasil'!$A$5:$M$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Brasil'!$A$5:$M$146</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'EUA'!$A$5:$M$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Central'!$A$5:$F$17</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Fontes'!$A$5:$F$25</definedName>
@@ -993,19 +993,19 @@
         </is>
       </c>
       <c r="B7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A7,Brasil!$K$6:$K$145,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A7,Brasil!$K$6:$K$146,"MVP")</f>
         <v/>
       </c>
       <c r="C7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A7,Brasil!$K$6:$K$145,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A7,Brasil!$K$6:$K$146,"EUA")</f>
         <v/>
       </c>
       <c r="D7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A7,Brasil!$K$6:$K$145,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A7,Brasil!$K$6:$K$146,"v2")</f>
         <v/>
       </c>
       <c r="E7" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A7,Brasil!$K$6:$K$145,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A7,Brasil!$K$6:$K$146,"v3")</f>
         <v/>
       </c>
       <c r="F7" s="6">
@@ -1018,7 +1018,7 @@
         </is>
       </c>
       <c r="I7" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$145,H7)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$146,H7)</f>
         <v/>
       </c>
     </row>
@@ -1029,19 +1029,19 @@
         </is>
       </c>
       <c r="B8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A8,Brasil!$K$6:$K$145,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A8,Brasil!$K$6:$K$146,"MVP")</f>
         <v/>
       </c>
       <c r="C8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A8,Brasil!$K$6:$K$145,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A8,Brasil!$K$6:$K$146,"EUA")</f>
         <v/>
       </c>
       <c r="D8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A8,Brasil!$K$6:$K$145,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A8,Brasil!$K$6:$K$146,"v2")</f>
         <v/>
       </c>
       <c r="E8" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A8,Brasil!$K$6:$K$145,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A8,Brasil!$K$6:$K$146,"v3")</f>
         <v/>
       </c>
       <c r="F8" s="6">
@@ -1054,7 +1054,7 @@
         </is>
       </c>
       <c r="I8" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$145,H8)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$146,H8)</f>
         <v/>
       </c>
     </row>
@@ -1065,19 +1065,19 @@
         </is>
       </c>
       <c r="B9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A9,Brasil!$K$6:$K$145,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A9,Brasil!$K$6:$K$146,"MVP")</f>
         <v/>
       </c>
       <c r="C9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A9,Brasil!$K$6:$K$145,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A9,Brasil!$K$6:$K$146,"EUA")</f>
         <v/>
       </c>
       <c r="D9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A9,Brasil!$K$6:$K$145,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A9,Brasil!$K$6:$K$146,"v2")</f>
         <v/>
       </c>
       <c r="E9" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A9,Brasil!$K$6:$K$145,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A9,Brasil!$K$6:$K$146,"v3")</f>
         <v/>
       </c>
       <c r="F9" s="6">
@@ -1090,7 +1090,7 @@
         </is>
       </c>
       <c r="I9" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$145,H9)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$146,H9)</f>
         <v/>
       </c>
     </row>
@@ -1101,19 +1101,19 @@
         </is>
       </c>
       <c r="B10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A10,Brasil!$K$6:$K$145,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A10,Brasil!$K$6:$K$146,"MVP")</f>
         <v/>
       </c>
       <c r="C10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A10,Brasil!$K$6:$K$145,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A10,Brasil!$K$6:$K$146,"EUA")</f>
         <v/>
       </c>
       <c r="D10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A10,Brasil!$K$6:$K$145,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A10,Brasil!$K$6:$K$146,"v2")</f>
         <v/>
       </c>
       <c r="E10" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A10,Brasil!$K$6:$K$145,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A10,Brasil!$K$6:$K$146,"v3")</f>
         <v/>
       </c>
       <c r="F10" s="6">
@@ -1126,7 +1126,7 @@
         </is>
       </c>
       <c r="I10" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$145,H10)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$146,H10)</f>
         <v/>
       </c>
     </row>
@@ -1137,19 +1137,19 @@
         </is>
       </c>
       <c r="B11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A11,Brasil!$K$6:$K$145,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A11,Brasil!$K$6:$K$146,"MVP")</f>
         <v/>
       </c>
       <c r="C11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A11,Brasil!$K$6:$K$145,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A11,Brasil!$K$6:$K$146,"EUA")</f>
         <v/>
       </c>
       <c r="D11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A11,Brasil!$K$6:$K$145,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A11,Brasil!$K$6:$K$146,"v2")</f>
         <v/>
       </c>
       <c r="E11" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A11,Brasil!$K$6:$K$145,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A11,Brasil!$K$6:$K$146,"v3")</f>
         <v/>
       </c>
       <c r="F11" s="6">
@@ -1162,7 +1162,7 @@
         </is>
       </c>
       <c r="I11" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$145,H11)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$146,H11)</f>
         <v/>
       </c>
     </row>
@@ -1173,19 +1173,19 @@
         </is>
       </c>
       <c r="B12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A12,Brasil!$K$6:$K$145,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A12,Brasil!$K$6:$K$146,"MVP")</f>
         <v/>
       </c>
       <c r="C12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A12,Brasil!$K$6:$K$145,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A12,Brasil!$K$6:$K$146,"EUA")</f>
         <v/>
       </c>
       <c r="D12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A12,Brasil!$K$6:$K$145,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A12,Brasil!$K$6:$K$146,"v2")</f>
         <v/>
       </c>
       <c r="E12" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A12,Brasil!$K$6:$K$145,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A12,Brasil!$K$6:$K$146,"v3")</f>
         <v/>
       </c>
       <c r="F12" s="6">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="I12" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$145,H12)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$146,H12)</f>
         <v/>
       </c>
     </row>
@@ -1209,19 +1209,19 @@
         </is>
       </c>
       <c r="B13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A13,Brasil!$K$6:$K$145,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A13,Brasil!$K$6:$K$146,"MVP")</f>
         <v/>
       </c>
       <c r="C13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A13,Brasil!$K$6:$K$145,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A13,Brasil!$K$6:$K$146,"EUA")</f>
         <v/>
       </c>
       <c r="D13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A13,Brasil!$K$6:$K$145,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A13,Brasil!$K$6:$K$146,"v2")</f>
         <v/>
       </c>
       <c r="E13" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A13,Brasil!$K$6:$K$145,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A13,Brasil!$K$6:$K$146,"v3")</f>
         <v/>
       </c>
       <c r="F13" s="6">
@@ -1234,7 +1234,7 @@
         </is>
       </c>
       <c r="I13" s="16">
-        <f>COUNTIF(Brasil!$L$6:$L$145,H13)</f>
+        <f>COUNTIF(Brasil!$L$6:$L$146,H13)</f>
         <v/>
       </c>
     </row>
@@ -1245,19 +1245,19 @@
         </is>
       </c>
       <c r="B14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A14,Brasil!$K$6:$K$145,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A14,Brasil!$K$6:$K$146,"MVP")</f>
         <v/>
       </c>
       <c r="C14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A14,Brasil!$K$6:$K$145,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A14,Brasil!$K$6:$K$146,"EUA")</f>
         <v/>
       </c>
       <c r="D14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A14,Brasil!$K$6:$K$145,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A14,Brasil!$K$6:$K$146,"v2")</f>
         <v/>
       </c>
       <c r="E14" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A14,Brasil!$K$6:$K$145,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A14,Brasil!$K$6:$K$146,"v3")</f>
         <v/>
       </c>
       <c r="F14" s="6">
@@ -1272,19 +1272,19 @@
         </is>
       </c>
       <c r="B15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A15,Brasil!$K$6:$K$145,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A15,Brasil!$K$6:$K$146,"MVP")</f>
         <v/>
       </c>
       <c r="C15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A15,Brasil!$K$6:$K$145,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A15,Brasil!$K$6:$K$146,"EUA")</f>
         <v/>
       </c>
       <c r="D15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A15,Brasil!$K$6:$K$145,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A15,Brasil!$K$6:$K$146,"v2")</f>
         <v/>
       </c>
       <c r="E15" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A15,Brasil!$K$6:$K$145,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A15,Brasil!$K$6:$K$146,"v3")</f>
         <v/>
       </c>
       <c r="F15" s="6">
@@ -1299,19 +1299,19 @@
         </is>
       </c>
       <c r="B16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A16,Brasil!$K$6:$K$145,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A16,Brasil!$K$6:$K$146,"MVP")</f>
         <v/>
       </c>
       <c r="C16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A16,Brasil!$K$6:$K$145,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A16,Brasil!$K$6:$K$146,"EUA")</f>
         <v/>
       </c>
       <c r="D16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A16,Brasil!$K$6:$K$145,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A16,Brasil!$K$6:$K$146,"v2")</f>
         <v/>
       </c>
       <c r="E16" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A16,Brasil!$K$6:$K$145,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A16,Brasil!$K$6:$K$146,"v3")</f>
         <v/>
       </c>
       <c r="F16" s="6">
@@ -1326,19 +1326,19 @@
         </is>
       </c>
       <c r="B17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A17,Brasil!$K$6:$K$145,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A17,Brasil!$K$6:$K$146,"MVP")</f>
         <v/>
       </c>
       <c r="C17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A17,Brasil!$K$6:$K$145,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A17,Brasil!$K$6:$K$146,"EUA")</f>
         <v/>
       </c>
       <c r="D17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A17,Brasil!$K$6:$K$145,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A17,Brasil!$K$6:$K$146,"v2")</f>
         <v/>
       </c>
       <c r="E17" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A17,Brasil!$K$6:$K$145,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A17,Brasil!$K$6:$K$146,"v3")</f>
         <v/>
       </c>
       <c r="F17" s="6">
@@ -1353,19 +1353,19 @@
         </is>
       </c>
       <c r="B18" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A18,Brasil!$K$6:$K$145,"MVP")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A18,Brasil!$K$6:$K$146,"MVP")</f>
         <v/>
       </c>
       <c r="C18" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A18,Brasil!$K$6:$K$145,"EUA")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A18,Brasil!$K$6:$K$146,"EUA")</f>
         <v/>
       </c>
       <c r="D18" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A18,Brasil!$K$6:$K$145,"v2")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A18,Brasil!$K$6:$K$146,"v2")</f>
         <v/>
       </c>
       <c r="E18" s="16">
-        <f>COUNTIFS(Brasil!$B$6:$B$145,$A18,Brasil!$K$6:$K$145,"v3")</f>
+        <f>COUNTIFS(Brasil!$B$6:$B$146,$A18,Brasil!$K$6:$K$146,"v3")</f>
         <v/>
       </c>
       <c r="F18" s="6">
@@ -1793,7 +1793,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M145"/>
+  <dimension ref="A1:M146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -11071,9 +11071,76 @@
         </is>
       </c>
     </row>
+    <row r="146">
+      <c r="A146" s="25" t="inlineStr">
+        <is>
+          <t>BR-141</t>
+        </is>
+      </c>
+      <c r="B146" s="26" t="inlineStr">
+        <is>
+          <t>Central</t>
+        </is>
+      </c>
+      <c r="C146" s="26" t="inlineStr">
+        <is>
+          <t>Agenda</t>
+        </is>
+      </c>
+      <c r="D146" s="27" t="inlineStr">
+        <is>
+          <t>Agenda de divulgações do IBGE (IPCA, IPCA-15, PNAD, PIM, PMC, PMS, PIB, LSPA)</t>
+        </is>
+      </c>
+      <c r="E146" s="26" t="inlineStr">
+        <is>
+          <t>IBGE calendário (servicodados v3)</t>
+        </is>
+      </c>
+      <c r="F146" s="26" t="inlineStr">
+        <is>
+          <t>calendario</t>
+        </is>
+      </c>
+      <c r="G146" s="26" t="inlineStr">
+        <is>
+          <t>Contínua</t>
+        </is>
+      </c>
+      <c r="H146" s="26" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="I146" s="26" t="inlineStr">
+        <is>
+          <t>Evento</t>
+        </is>
+      </c>
+      <c r="J146" s="26" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K146" s="26" t="inlineStr">
+        <is>
+          <t>MVP</t>
+        </is>
+      </c>
+      <c r="L146" s="26" t="inlineStr">
+        <is>
+          <t>Verificado</t>
+        </is>
+      </c>
+      <c r="M146" s="26" t="inlineStr">
+        <is>
+          <t>API oficial de calendário do IBGE (servicodados/api/v3/calendario), janela de 120 dias; resposta real gravada em 2026-10-19; vai para a tabela events (tipo agenda)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A5:M145"/>
-  <conditionalFormatting sqref="L6:L345">
+  <autoFilter ref="A5:M146"/>
+  <conditionalFormatting sqref="L6:L346">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$L6="Verificado"</formula>
     </cfRule>
@@ -11096,16 +11163,16 @@
       <formula>$L6="Curado"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K6:K345">
+  <conditionalFormatting sqref="K6:K346">
     <cfRule type="expression" priority="8" dxfId="7">
       <formula>$K6="MVP"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation sqref="K6:K345" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K6:K346" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"MVP,EUA,v2,v3"</formula1>
     </dataValidation>
-    <dataValidation sqref="L6:L345" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="L6:L346" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Verificado,Confirmar,A mapear,Sem API,Pago,Derivado,Curado"</formula1>
     </dataValidation>
   </dataValidations>
